--- a/Basic_Design.xlsx
+++ b/Basic_Design.xlsx
@@ -9,11 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23925" windowHeight="8055"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14460" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng quan" sheetId="1" r:id="rId1"/>
-    <sheet name="Trang_chủ_UI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -334,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,13 +349,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF7F0055"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,12 +371,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,7 +587,31 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>- </a:t>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="vi-VN" sz="1100">
@@ -611,13 +626,6 @@
             <a:t>Mức độ đánh giá</a:t>
           </a:r>
           <a:endParaRPr lang="vi-VN" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1100"/>
-            <a:t>- Tình trạng : còn hàng , hết hàng , ...</a:t>
-          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5256,8 +5264,8 @@
     <xdr:to>
       <xdr:col>53</xdr:col>
       <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>67235</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5267,7 +5275,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="30255881" y="4224618"/>
-          <a:ext cx="1961031" cy="1176617"/>
+          <a:ext cx="1961031" cy="1299882"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5354,11 +5362,88 @@
             </a:rPr>
             <a:t>- Đơn giá</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Tình trạng : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>`</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>còn hàng , hết hàng , ...</a:t>
+          </a:r>
           <a:endParaRPr lang="en-US">
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr lang="vi-VN" sz="1100"/>
         </a:p>
@@ -5375,7 +5460,7 @@
       <xdr:col>46</xdr:col>
       <xdr:colOff>593912</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>50427</xdr:rowOff>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
@@ -5392,8 +5477,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="28429324" y="4812927"/>
-          <a:ext cx="1826557" cy="868456"/>
+          <a:off x="28429324" y="4874559"/>
+          <a:ext cx="1826557" cy="806824"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -5695,302 +5780,295 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>56030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89651</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2049" name="AutoShape 1" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
+        <xdr:cNvPr id="73" name="Rectangle 72"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="1143000"/>
-          <a:ext cx="304800" cy="304800"/>
+          <a:off x="33281471" y="3485030"/>
+          <a:ext cx="1905000" cy="1176621"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>picture</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Ma anh (PK)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Ma </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>nuoc hoa</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> (FK)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Ma</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> huong (FK)</a:t>
+          </a:r>
+          <a:endParaRPr lang="vi-VN">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>ten anh</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>img </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>145677</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>44825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Elbow Connector 7"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="68" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="32216912" y="4045325"/>
+          <a:ext cx="1187823" cy="829234"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>470647</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2050" name="AutoShape 2" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
+        <xdr:cNvPr id="82" name="Flowchart: Process 81"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="1143000"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
+          <a:off x="32261736" y="4908176"/>
+          <a:ext cx="280146" cy="280148"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>324974</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134472</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2051" name="AutoShape 3" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
+        <xdr:cNvPr id="83" name="Flowchart: Process 82"/>
+        <xdr:cNvSpPr/>
       </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2438400" y="1333500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2052" name="AutoShape 4" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2438400" y="1333500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2053" name="AutoShape 5" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2438400" y="1333500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2054" name="AutoShape 6" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+WL97/PXqES74eI/bmE7yxejEjF/yVB8Zk0lh+4P9j7zzA67jKrf2eqlN11HuXJVmS5W7LJS5xjVOcRkIKIYEkhBa4wIX8ELi5Fy5cEnoLEAIJpBKMUx333m1ZlmzZktV7b0c6vcz8z4wc9xrLtuzMfh5HjjWzy9p79sysWd/6eGXZk6gm/5nHx4Tw93//ieiMhfTteZ6wBb/l1gmZGNTg76vhx399CkfyQ/zwztsIwcGKN77BensGTz36FPFGcLl6cXg/2pxPHqn0wBViCCfMaJBvqIGAh7bGvZQ1w7QpE2nd9xde3O/g8fu/QW6UCZe9jl27t9IpK+qku7AasbuEdXVHeOzhl5iSHHcyUXe0uYCzk5VvfY6X2qbyzMP/QUG8BbXbCR0HwWeEpNFgNEh39GF5QLjWKzkXUSf6nZRuXs3+TjOLb5lNfKielrJdbK7xccstswnTqehtOcTyVfUsfPAWUg0qfA47u99dxl5tNvctmU68VcWhlS/yZpGOWXPzMQt97F61A92UG7ltai4d+9ZQEnoDX5iXiRo/Rza+w/qaUBZMN/LG5m6+/tidWNU+Omv288qbe1n0la8yPkpaEGch6qQJkR/qBVwDDbyzbCe5CxZgqlrOMsdsvn3HkCLPXb+KP61UsWCylg9293Pfo7eTog3SVlXES28e4a7HbmegdCO9EeNZMmOUTNSV71xHiSeWT82bhJxn5QxEXem/fk6xcR53L55EqE6g4/BmPjggcvMNEfx7eTVLHr6dTJsOX28Tb732CpGLv8aS7OF9GTxJUReVyJvP3srehKf4f/feSbRJi5Rlt+nQe3zv7RV85r5fcFO2FHKkFAWBYUbgtPBXkf62In76h+8QcePP+M6CKWcMSQza63jnjRv50Pck/3nfo8S5ythRaWfc9LkkWMzy/cDVX8ULf3mEIvUSfvz4U6RaNSDde8Re2NUB2WkQZQa9TiHqhnlah7O6Myrqgk6q9rzLmkY3+VmjyUzNIzEiDLUo0N9Wwq7yUux+WWN/tCsqAp5O2vqrWbzoF4xJsB0NnxRlpYfD4ZTDKnXSPd/TS3N7I+aYfMSuvby6dgP5Mx5h7uikY9m56w+uZV+ryII5N2IzSN6nn8xyauirIHrIS5zBZ2f9kNiwFKS521W5ijd3PoPHH0Qth6hzUUTdR8jKhJ0/gNPto7qlh9bOfhwuN8GAFP5++fGXmpCy1a8tbaSt14ExNILQmBS0IZKH6xXowOUf4jlbCAb8+JwD9PZ04Pc5mZ8bS0ZM6HntC65yt481L/tvBwIMOpz09w+edc1oNWpiY6LZd6CcktpWNJKqaaQM4jL2w2S2YohIpKe3C7+UMd3RhTogb6KXUFTyB5Ggux9fTyP+7kpEUXNUbSuR9idW7kcVTGHerTcQpunknXe3MHrqLeSnBti2aTP1XU4kq2Y5evYEuyOpCkEYstGIHCGKOtHvxZ+cw6QEM3avnmnjc7GXF7N9WwkDxpDTBiHhIKsOAUNIyIhQ1En77ejRoykoKKCmpkYm6+Lj49mwYQPd3d2ySu5snmfSv8fExFxVRZ2Ep84Qx9TZM8iJ9rNs9WbSpywg39jHuvdfocWfjG7oE88pXrbHrZEkhebVUdQJBHwGCiaPR2jbQVnkDD49LpX2knc44EljfuEUPIf2sqn4MG69dmg9HbtRgvwAfNSjVyJ+h0dR10vHxEfoCVr4f7cvVYi6s+2Kwx76ioCjr4mKqnW88PbLxGYvJbLzj6xU38l3Fz9ASnQs0RFx6DwtvPWvR/Fmfp/s/lUUBQp46KZPoWv7kD+8u5U5d36TwvQoqnY8z8/f/5AHHv0b87NTZFKl/sDv+NYb67jvvt9z17j0M4eWnOM2IBlD+z2DVJa/z/KtNcxZ8iizspPkr9rSZiCIweNnq9QIDat55o0fcusDyylMOVlRJ9XldXSwe/Nv+G2xj28//DRTUyOPeewNLewhwk8pxxE4G1Hn9wxQsX0VO6tULLznJlIjLPKLUV/jIT7Y1cDcmxeSbFLTULqDDY0a7l86E5Wzhz3rNrLPlcDDd00jXGJ4EbF3NFHX2IlHmlNvP3tWbkM3dT5Lp4/BVb2F9+pi+OL907EEe1m/7C2aYxexKKGZP23q4Zufv52wEA3e3lpe/tMaCp/4IhMipVpFOo+8z18+DPLIF24j0awDMYDH65eNqbVqEbe9huVv72XColuI79nOzzZq+eaXFhClE6h4+znWG5eyOK6Tt7Z2cf9jd5Nm1ODvKef5v+1h/qeXomrYRpk7jrvmT0ETsLN11ToCSZOYPzl96PlmsJnXf/0y+kWP8ampcTKonXte4/XqaB5cOp9ok58Da17jkHYGS6eaePul1Yx4++kkAAAgAElEQVS64z4KUy301Bfzj7eOsPRL95IVOrwvgyd71E2gfdev+MK/3uXuW37EonGjwdHAsmX/w35fNs88+X+kWhQjb2VPuPwIBHyDbFn5NH/a5+PbT/yEKYkRJzUqEcie/npWfvhjfnswkp996SkmpUo+qdJDrnrog420z3sG2L7iGf64q4nPfPZn3D428+TOn/5sdvkHp7TwsRA4m0ed4O6lsu4ABw69R0XHIAkZd3LzrIXEWzQnPxcM3dRxdlewcecOCm54gPRI6V51ehGCHqpLV/L+oV7unz+LPUVrMGUuZUG+9DwzVISgndXv/QUhbSkLx2ahP0m2/7GGeM2edGoyCSn8VSI2bhr7OLdOfJSW3hr+vvX7NPZUolEdv4ddTOjrSAHH6fGx82A9f1lZjFNlwRqdjEY7vPflkTLWY+98okjA78M10INnsJdBr5vF+YncMSOH7NRYzIZrJ6u29L4Q8Ptpa2+job7+zOSqpJLU6cnNzeMff3+ZH//gO1jDbcfUoSNtfoajP9KtUC36SZ+6lPApD7Bx+1Y6o2JJK3kVjeTbrTlFZXyxjUq2FmotqHVICruzFm8/3oLbeWzuKJIjTbRX7iIkeQExZpHB5q38+Per5ERSbq8bQRTRiirURj16jR+nV0WIyUpMRBihoaFXNfRVsmVwdXtY8NX/YVGumdZeF1anE02kng/feIXS2hbcAw4CGhVydlc0smJQcDvwGUyEG02kpKdRdRVDX6V+SdfLt771LZncljz/pkyZIickkEi6P/7xj/I0SgkvPsriLXnrSedJf6Q5kEJfpXK1Ql8DoorESYu4a34BRq0a9aBHylWKEBePdsfL/OqVYhz6IN6AIAsTRCmJh8lEiODGIegJMRqIDQ8nLCzsioe+SvvU2Nu/yBeXjGbry39iIP9exsaLaD1Oulo1RGfrcHkCvPbiCzR2OFAHenH71QR1IlpBjcoQgtrrJcRkI0SrJSEhbhhCX48SdQEzP7r/foWoO9tGNtxEnSRH7uutYe+OlyjuN3L3/M/TuvFbvCIu5Se3zmXbe/9La+6PuDe6jFfe/ym9+vlMSo5h/LS7ibfo5BS9VaVraQrEkG3ezw9efZ7cWb/i6zctJNwwtCF7+2t4581v8Oe2Ufz+Kz8mL8Z4/m1eFPB53Qzam9jbUM5gQy0tQSeTJz/K9IwEWbouhbEO9jWyv6EMQTIolh67VSqE7gpWHdjL3ff+hklJUpZNAb/Pg6u/kS0NZQzUHqbBD/NmPk5hhuQZppTzIXBmok6gavO7vLiqhqmzpxIXbkAIihgjU8lLNlC6bRttQgiRoUa6W3uIyZnIDQVJlO14h/d3dTFmfAFRZumFCiKSMslJjDiebMTTy5p/vI1+wZ3MzYzE3VXPyg82oE3OxCK4qKsZZPo9d5IZ0sOGDzfSEIyiIM3MYF8n3foM7p0/Fl3ATUNdNeWHdrLjUJBp86YzIX80CQY7azfuwqWJlMU0fS11OKLyuWXmBCzBLj5YthIhJpVIo5fyA/VMuesB8q0uVr33Lm2GVLLiQvH1NNNvzeCmmROg7wgbdhzGGJaIQXTQ2R9gypxZpEdKis8uag6VsH7ldrT5NzB7cg6jUhPR+9tZv2ojXmsKNo2f1tp2xtx6G2Oi9dTvWcf6Vi3pMVbcXQ0MRkzk7tk5hAzzy+BpWV8DDjas/DGryirxY5K/MQXowj4IhbO+xwOzphFh0V/ax9XzLTTl959ABER5f/a47VTVb6SmvYFdJQcouPEp7p84hhCtWn7w8/t9ePqq2VFTTFvVYaoNmTww6z5y40OPCZ+lDzEeZw911WvYe6iYqk4X0+Z8lfljR8thTEq5NhE4s0edMBRWpNEi+B3Yuyt5/92VxN74eW7OTThtoMHAIGXbl1GrHsPCwolY9CevB3ntOLooP7yZPS0Cs2YtYXSYHofXg9FoQy8p7SQC2N3Fnu2vUmdPY+HiW4k7NVT22oT4Y/f6VKJOqigo+Ag1RrF04pep7drPzqoPUKE9LevrhSST+NgdG8YTJVKgu8/BX9cfZGdZMypzFNbw2OtWhSt/AA/68bgcuB39WAQn0eEm8lNjWDQpg4z4SDQayTtrGEG+AlXJikyvVza3lzynJP+vU8tH2Srz8/N5+eWXefbZZ7FYLGc89gp0+Yo1oRKDpI6fS9ike9i2cwftkTGkHVqOtrsONFeIjBaCYDARFhPPwoWziQj2o2kboLwnwLzFVr731MvM/9IzzEhPJMwm0OVU4W5tpzdoYlRKgJWvvk5llxtrqO3qEXWi9DzjxRo9gcf/8wsYVE587g5+/aXlPPA/DzK47TX2dKXzxDdvQ6Vxoun2oTL4qN+7BfIXIRzcwPtrdhM6KoPqq0jUSdfJtGnT+PSnP30s+6yUjODw4cMUFhby85//nE996lNMnDhRVtr19PQc8z+Tzv3ggw9kgk4Ku7xaRJ2kfo4dM40Fs/LQqEJIC0+gbPfbVKhn8HBaC7/83/cp/O43KEzRgVaHSxXE01xCg66AbFUTy//5Fu0ug+xTd6U96iQ1oCk6gfvvW0LPoTrMGYVUHFhN1vRPM0k7yMrd/6RNt5T8suf5yfYJ/PHVW7BZA6g6/aisIbiPlBNMTaZqzxr+saKI3FFpw0fUBc388NP3KUTdlSHqRAZai3lnxyYC+lAmTbqd/BgTlXv+wbLyDpJjwrB39zFl8TfR17xGQzASkz9Au78Xg+YjqaVEmKkIjcojQ6zgH83xfHHeQlLDjMdu4qLgp6N+Oy/uOsy9Cz9HdvT5iTrB7+JQ8XJKWprw21LJiswjNyubcJPpeCirRNT1NrCvvuwk6apKpcNsiiEzJZ9wowHBP8ihAys52FiDIzSLMTGZ5GTmEGEyXXAW2it2txyhDZ2NqOttqqOyqZugWlIZDHnESETduJw4cPdRU1VJp1NFRGwSmalx8leNnrYaapp65RCSoPTVRqUmMimT0UmRQwSsJIgJeGitb0UTk0BsqBQGLeLsaeRwVTNuTCRnZpEabZETM/hcdir3H6YHFcawGEZnphJq0CL4XNTV1dDS40anEQlqjKRlZpMYpqGtroa61j4CUn+tMeTnp2E+mtXU1d9B5ZFa7D6BhJxxZERL2YNF/K4+DpdX0+cMyA/p2TmpcuZA6UvMQFcLh6tbCKgMpKSPIinOKhPAkg9eZXU9bkEGCHNELKPSUzDp1Tj7OqiubsTu0ZCUOYrUeJvsxSX6XdTXVtPY5cIcEUduZhLmkOHPmHQqUSdNXsDnpKOtlqa+TtBFkxwTRVvFMn731stMvesVPj9rDMYr9Mw2Qi8FpVvDjoCP6kPr2XXkIK29faTkTGJc+mTS41IJ0UqfX0S8gx2UHFhDeVsr6vBUshIKyE3PJuwUNUcw4GD/vtWUNtSSmJFHTsZsUsIsx/aVYe+6UuEVQeDMHnUOKo+UyH4pkq+cz9HC9qIjTF7wIBMSj/t5Sh8je3uaKD+8iv29Ydwy+07So4ZCo4duNj66Olux93dSUlOEVx3H9Mk3khYVftJHvIDfQWvjYXYd2UPzQBT3LrmdRJvxE//h4kxEnaywQMASEoov6MUX8MoJJE4s14qiLhAMUlHfybNv76KhL0h0dCIGc+h1GeoqvRwG/V5cjj76ertJCdUyISOKafmpZCVFEWkzI4WFXqtFIerOPnMSUZc2fi4RU+5j686ttIZfDaIuQMASw0133EKwpYS19Vb+Iy+EQ+1e5sy28v3vv8rtTz2NrWMTlilfwtK4gt5AHurBbtnCovidt6n3ebFYrxZRJxHcQQK2eD53/+Okmrz4EpIxB5v4wWdf48FnPsPg5lc54B3HEw9OZv/hQ8TEmKgI6ploC9BYqSfgL2HDlv1EJmZQXXX1kklISrnbbruNjIwMmpqaWLp0KaWlpezfv58ZM2bw3HPP8cgjj8gLKi8vj7KyMjmRh9FopLe3l40bN8o/ryZRJ4kNCm6Yx5wJ8Rxo0zNrYjYV616nTHUD96c28evnNrDk6SfR/HMt1s8tob2znuSUGA4Ud5EWP8CaFR/i9BgJuwpEnfxoIgrc/fD9BBrasWZOo7x0JWnTPs1YrZMte1+n1bCUnNI/8tz22fz1pck019cQlRjJSzsHeezmFNqbu3Ed3MSKTVXEpCfRccnJJD4KfTXzkwcfVIi6K0XUSS/mdrcPkzkMg0bWpMm+cA7XIAFRRKM1YTObZUNPjc6ERvTQ4xg85SFFJR9nNRrxC2oM0svVSZ/aJAJHwOMHg+7CMtjIBpCuXtxBFVazlKFNIiqkek9A5pi30ZkchI8eKJsXBHG5+/AERULNEWjlr2in1HWtPnlcoX6fmag7l3nz0Av2yTMjx6Sds8fH1s0JvlUf/dupXgjH19jp/ZD9Hs7qLH16P05crxfbztCGespIpXV3mvfW8aGfqX/nG89wT/VpRN3QQE6bITHo5kjxe7QbJjM9dxSfYDum4Z4CpT4ZAQGPawCHz4NGa8FmGvJ7OvF6kNQdLlc/HlGNzRJx1Aj89D1cDjlxDyKoDHJIlpQ59lpTfSiL4nQEzpr1taOMjfveo82rRm9MYkrBzYxOjEKrEhnsqmbnvp30+Jz09HUTnjCVRTfMIdJgOGq+7KW2fBsHaypp7u9E1MUzdcoi8hITMOt1J6w/AUfnIdZsWUuLJ0ju2AVMGT1OTpKkrC04E1En30rk5A6S6/BQ0oWhp8vj5Vog6iSSbsfBOn73zi4GCSU8LhW1Vookuc6KSo3PNYijt532ni4khvrp2ycyZXQKcVGh6LSa64KYVIi6cxN1CWNn40m6gUM11ThiE0kru7KKuqC9jbC7vskP751NV+UBKo80kjh2DhmRfg6vepufvrqKh5/+HpbmlzAW/hRz9Ru4Qhdj7uklLDeLqqK/sW5XHXpj+NVR1ElKVEl8kJDLI3ctJNYWT0pSOL2uQYyeIC5XB6/86Q84Im/iybvHUrSrnPBRevaKYTyQaaSpz0CCtps3f/snnPGjqb2KRJ0U7pqZmcnjjz8uh7FKZJ30U6fTyWSdpDT9wQ9+gNPpZPz48ezdu5dRo0bJ6jrJm27NmjUyWWcyma6aok4Q1UyYdRf33pJNj8qKqc+O1mTDFKZj31vP8tv31Xzn6UdwfX8NkT9eRGNbM3kT0jlypIuc/DgO/f2nbG9RExYRfcUVddKVqtJouP/xzyIUb6Wj4EGW5IbSX3+Iki4b86Yn4Wir5Xe/+xnbi+/m5b+Oob6slrCcMJ7e6eSvn5qAajCAtr+cH/3X84SPy6VzOIi6SY/QI4Zy/4SxClF3ZYi66+xhQxnOZUNAIuo2V79KUPAzP/tzaDXXji/JZQPlmq5YpM/VyT+L/48F2Q8zKmbCuUcjSv5fqvNmF7qmIVE6ryCgIDAiEZCIuk3Vr+IP+Lkp73E0x3yOhhQMsrOsSoVG9dGHQMl7tJmD5buw66PISp5IUqT16Ee6j4YYoLWhiKoOO6mjCkmyWdBotGcgYQQ8/bWU1veQOWoikeaTQzhHJGBXsFPbKz7gpS1Py56AEjF+oUXKfDgma4o8n1kxk09T3F1oPZfjOInQ6R90s2x7Ocu3VqCxxmCLjEd1hlDJy9H+5a9ziESVfJC8rkH8g91oBA9J0VYWjk9n0ZQsjCF61Mdkp5e/R1eiBYWoOwdRJwSIzJtJkScKj6hCn5JBypUm6gI+wuLSyc5IxaDx09veTp8QQXK0SNWRCrr6vSSkJKFxt6CJGI3G0UIgJI4IiwWLRaS+uhS333J1Q1+ljxTBAIO93ZCcy+goA25BS1ZaEq7WBior6hDCkkiPt9DX7yDEpKE7qGZUpBmdIQx/bwu1De3Ep6dfVY86aaVIWXSzsrJkpVx9fb0cAiolVpDCX/v6+khLS5OPkQg8u90uZ4OVjpFCyqXkE1KR/n61Ql+lBCMabQRZuZnEhAlUHahAl5pLUoiLw/u30hNIJi01Dn9VF7qsaDweN6HhoYQYQ7HgpvbAYQJW61XxqJOwE1ETnxSPaqCBBnM2M5KjsDfupMkfT25mJoHmWsobmnAJceTkhOJyuNCZddT0BRifmoDVoGagu4mDtV2kJSUMT+irlPVVZYPeToWoU4i6K3HbVtq4UASCQoCytq2UtqxlRsY9xFrSrr+vyhcKxnVwnDfopqR5HS0DFSzJ/TLRlqTrYFTKEBQEFASuRwSk+8/h9u0UNX3ItJQ7SQzLuq7N3a+ZOVSp2Fu9jrd2P4sgXBhRJxvXq1WEWkPJT53OwtGfJ86ahmqEJPCSVHQ1zd28vLaE9ZW9JMUlY7SGXxeKMmldCQE/fq+LgYF+gr5BmUjIT4miMDeJrJRYrKaQa2b5XWxHFaLuXESdn6gxcygiGbdKhynUROLBt9EMtA0lgrhCJeD14Bh0EJCsbMwW1KJHThRhs5rljNw+n1/uj+h3gzYEBC/egA+/F4wWK3ExkYRarVdHUXcKRqKUJTkQkC16BpxuNCYLocYQVIIPt0+QxyMKomx54/IGCPo9iHojEbZQ0tNSqbyKHnUyUSSKsmLO4/HIZJzf75eTSUiejZKyTvKikyIfJPWd9P/ST7fbfSyZRFzcUPK8q0XUybpuwY9jwIkvKGAJteJ3u/AGtNjCLGhVAh6vD3WIDvw+VCoNfq8fAh48aDFZLMRGXq2sr0P4S+tdpdGiDXoZGHSjM1nkqKZB+yAqgwmr2YhaFcDj8cl+vVI+TMl+1+F04PWLGMwWwqzmYcn6qvIN0jPmLrqsaYguh0LUKUTdFborKM1cEALShjHo7WVX/bvU9hZhUEseQBf+9fyCGlEOukIIiARFn6yAmJ52F7lxM05QqFyhLijNKAgoCCgIXCAC0v3H5Rtge90y6nr2o9eYUaEkB7lA+C7fYSoVA+5OugYbhuwfLiQWWETO3BhlSWDOqM+QE1uITsoqeSHnXr6RyDVLnrk7DtTz0poSWp1qbDEp6PQhFzauy9y3S6pesgIJBnAP9NLX1yXb1yzOjWPBpAzGpMUREWqUFXTXe1GIunMQdQEPUTPuotSYieh2ENZUhKntoPQyfs2sf0ndJam/rCOEqPs415MUOqvX60lNvfpE3cfp/0fnSNealPVV+nn1iLpLGQEy4fiRivBKJ5O4tJ6ffLbkExgbG3vJijopgafXlkR/2nR8pnCFqFOIuuFcpkpdw4WAL+CmpruEHler7DuolGsTAYPWTEp4HjHWlBGjZLg2kVR6rSCgIHClEJCSEtT3HqTL0Sh/aFDK1UdA8muTwlgvWGIvqmRiLsE2msSwUVd/AEeVI/5AkBW7Knj+/X3obLGERydd06GuQ7a5IsFgAFdfBwO97agJMi07gUdumkh6fCQ67SfrY6tC1J2DqPO7iJp9P03tHZiqtyGZnQxle712HBkVom5EbKdyJxSibuTMxfARdaKc+V4lvfurNApRpxB1I2eRKz1REFAQUBBQEFAQUBBQEFAQuL4QCAQFGtt7+eemgyzb10xKQgomW9SIUPh9HKSlD6jBQGAoOYSjH6PgYlSsmcKsBCbmppCeEPmJzYKtEHXnI+ruo7G9A2PtrmtGRXfiiBSi7uPsGJfnHIWouzy4fpxah42oO9b4UPJElXj2lI0fp5/XzTn7ynbyzO++TLe9GY16yEtCkmfWDnbz4bNbmDRm2nUzVmUgCgIKAgoCCgIKAgoCCgIKAgoClwOBoopGXllbSnl3AFtkAnqj5dok6VQqmZxzO/pp6u0lzaxmVn4CU7LiyUmOJlLyZNJ8shR0p64XhahTiLrLsYcMZ51K6OtwonlpdSmhr+fGTyHqzoKPQtRd2oWnnK0goCCgIKAgoCCgIKAgoCDwyUVACnXdsPcIf1ixn2BIOKHRibIZ90jwyruYWZFCXP1eJ/0dTTgcA8SHhnD7DaNZPGkU4VYjWo1Gtg681sZ1MRhc6LEKUacQdRe6Vq7WcQpRd7WQP71dhahTiLqPtRplou63X6Z7QFHUfSwAlZMUBBQEFAQUBBQEFAQUBBQEPnEICKJIR+8gr60t4S/bqhidnI41cig74bVSpBdIIeDD43bh7m9HL3qYkBLJ7PEZFI5Ju64zt17KHClEnULUXcr6uRLnKkTdlUD5wtpQiDqFqLuwlXLKUcVlu2SirmugSQl9/VgIKiddKgKSibfkgzIUpa6UaxEBFSrUkhnoCMi0dy3ip/RZQUBBQEFAQeDaQkAi6Srq2nl940H21A8MhbqabdfMfVAIBvC5HdgH+vB7HGREhFCYE09hdgJpiVGEWYzX1oRc4d4qRJ1C1F3hJXfRzSlE3UVDdtlOUIi68xB1Dk+/wgOcgpFapWb/4T385Pn/pHugBY16KJ264lF32a5TpeKTEBCxu7spa9tKt7MJQcn6es2uD6PWQnrkODKjx6M9uo9cs4NROq4goCCgIKAgoCBwDgSCgsDKnRW8trGMQcGIOSoRrS7kmiDpJILOae/B3t+NNuhlYmY0c8anMy49hmibBZ1Wg1p97WTnvFoLVSHqFKLuaq29C21XIeouFKnLf5xC1J2HqPuPZYkKUXcqUafRM9ipo3zbAEG/+tgDhkLUXf4L9pPegvSA0+/qZHXFn7F7eoizjEat1nzSYbk2xy+KuHz9NNr3cUP6/RSmL5XVdUpREFAQUBBQEFAQuJ4QkJ5dXF4/f/mgiL9vKiMlKQNLZPzIJ+hEkaDfKxN0ne1NJNl0zM1LYu7UXMZkXFuhuiNlPSlEnULUjZS1eLZ+KETdyJkhhag7D1F3oHGHQtSdStSp1ZRXHeTFV3+N3dGNWq2Vj1CIupFzYV+vPQkKAfY3r6OiYwfzsj9LnDUNlfqTnUHsWp5rj99BSfNGDnds4Za8J4kLTbuWh6P0XUFAQUBBQEFAQeA0BGpaevjnhlK2HunCFJmE0RoGjEz1mUQkBQP+o+GtvZgEN5G2EG6ZkMbU3BSS48JRK3YVH3uVK0SdQtR97MVzhU5UiLorBPQFNKMQdech6gRRUIi6M2AkedT99+++Qpd9eDzqJK8xybfjozL0+KKS/cek/8o/VWr5sUa6yUn/6rU3cKihivi0GcSFGpD8riSvq2H3uxL89DTtZX9XgPF5s4iU7TeG+ir1SSlXDgF/0MemqlcRxADzcz6HVq0balwM0t9Zy56SWjwBAVV4CrPH52AzaRG8Axw+eIDq9kHQGUnLGkNBmonSjTto8QSOPStLayuAnsy8CYxJNtNYVc6hmla8umimTysgNjRkhD5WXzn8L0dL/e5O/rnvJ8zPfphRMROONSFd50PXOjIZeyGvNEPHS38kpe/QdXpsW5H2hosZgCjg7K6g2WUkPSkd/RnFfiKCIJ7Uv4/6PLQ/XESL0suRKCJZC1zMaRczpDMeK+F8dKe9qP6eoTKvq5uajkGS4pMINRy9Ns/TwY/mWX1RhLuIdGsWVZLH4RDGJ+IuAXjByMvjP7nIK+hckxD00ly7h163iC5yNLmJMafVII/ro3vSCb+VlTX9XQz4BKKjY5CWlb2zGafORHxEpPICfMkLWqlAQWDkIOALBNl5sJ6/ryul3anGHJFAiMk8Ikk6aW8KeN0M2nvwOgeIMEJ+Ziw35ieTnxpNqMWIXquo3i91dSlE3dkRVPldRM2+j8b2Doy1u6SHqEuF+4qfHwwGiYiIwGq1Ul9fj1Y7JGa5lopC1I2c2VKIunPPhUo86el/5Ezc1e6JnPX1d1+m2z48WV8dbSX8Y+vbeANBmZgz6ayEmeOpalxOk8tDcvwcFs39Opaa53i1uBSDUUVFfSW20Jmkxsdi0Pro6NvPmEk/565JuXgHOnEF5Tflk6BSq/VYrDbM+gt7iZRP9jso2/B9frwPvv/or0jwbGJn+REE4hg//RY5FEAuPie4BbBaJZ5AKZcBAYmo21D5kkzQzc36LBpZzSnQVrKKlz6sZfzcGcSboLG8nFp3Ko/cM5rSFW9TEZLBpIxYgs5u9m5vZdLdC0j299DrE+g7vImXD2t4cMkMosw6YhKSUXUfYMPeZjJGjybYW8vhygC3PryUROuQH6NShg8Bp8/OK3ueYV7WQ2THTpIJF0dXJVs2vcirZavRhN7KI/MfYUZeBsYQ7TkJGJ+nlaLt75Iy+RESQ40IQQ+VpTtwhaYycVSGvLd4XXYGfSoiwsPOfZkKQdoO/IYNnZksnXs7p0+9iL+/gr8v287i+z9Psnnoog/6eynas5/IjPFkxkdeOGFkr+QPq16nIP8+8lJSibQaTib6ZJWDh/7BfnwB4djeJn+80IQQHhqOQatG9Lvos/fhFVQnCzaOfuAwWWOxGY+/bImCh4O730OdNJPcpEQ0J26ZAbdcl0feS0+fc5MlilCj/tiv6kre4I09xSxZ8FXirEP7ol5vxma1oj0jEeen4cBytrTGcOfiG7EIXgYH+3H4pQZPLtJHEbM5HIshBEQ35fve5UCfjekF44mOjMLbX8uBg0dQhUWRmjSG5NjQC9qGg72VFDX0MSp/Co7yHTh0Zo4Malk4vgBriARuAIe9lwGff+hDkLTjeOzs2vAzNLHT2FPjYMmiB5ieGYvmqD+Tx97IOxtfp40sHlhyO7EhHz2oB3H2d3OkbC/NToGJU+cQbzVRt28TraYYZowZi/YafDEZvt1AqUlB4PpAQNpunW4vyzYf5J/bjqC1RGOJiEOtOfc97GqMXggG8Xud9Ha14XcPMiUljKn5qUwbk0pMmBmDXntxH52uxiCuoTYVou7sk6UQdSNjIStE3ciYB6kXClF37rlQiLqz4DPcRJ3XXs/movX0ywJGkRBTLGmR0RRv+g1rWp0snPMkd82cQ9mKZ9jvzSbHfJin//kud93+JBmRelSCSGvNYbTJn+Zz88ZyeNtv2dXjBo3m2EvkYH8RWw8b+MZXfseCrMQLf4H2Oynb+B1+VqLimw/9lHTTAIerG9CqtEQn5ZASEYKqtQ46D0GlESaNgYRYht7ylDKcCJJD7wcAACAASURBVAwRdS+jVWtPIOoG+PCPf6ElaxEPzS/AoIKAy0Fbay96fS/vbKhi3u23kxWuByFIX1sH7hATCVFS6Al07VrGf+/R891HbiMpVCUTHdtWvUV71CzunJaJRrDz4ZtvYZp0B7Nzok8mMoZzcJ/Quk4m6ibi76/iDy9+kRJnBBOzpiMMlrOvpoJ5N/+cB26YSoj2dBZcUuQG/B4cjja2r3mFrLlfJclmQAh4OLRrE86IDArzRmPQauht2MSK0ioSknLITBtLSlQ0OkmxdyoRJQRpP/gCG7viWTRjMTaDkZObFvF27uWHv32fh7/932TbhsivgK+DdWs2EJ93I2Mz4i5gnxGRTLq9Pi+DAy0cOLSJusFwZk2YTWZKHMc+KYginv46Vu5aTqO9H81R4ss7WMXunnH86LFvkBMRQtBew+btL7LfriXkBNZNFIMIKhMzp/8Hk5MlRcdQCQzU8N66nYyZeRtZsbaT++tsZuPWFyjuF9Grj6vUZAU0WgoLv86U1HD5mhA83bz99rPs7NeQFjm09zntzbiYwBfue5RE6xkyAQYH2L7qH+xVF/LlJVPQ9JSx/J372Ku7h1RD8JjSTRB8tLeVM2bK09w/cwpCwIvb46Cz9SCb9+4lJn0K49KTcfRU4xFDCI1KJykuDf15Ppj4BlooLXmP9ZV9TJ60iL6yVfRozFTbg8zJzyUmMpWctERaS95lbWMVaq1uSNXt99BQtwlr0mJiDAZCY+dz27RJmDQ++tsPsnXXXkKSC4kJNlHtFplYMJ+0SDM6TYDKXW+yvraS9q46vLH38czSOTQf3E2HJZpxGVnodUZCtNKL8Sd0Q1CGrSBwjSMgRYfYHR5e/GAPq0qbsUUnYwqLlmS/I2ZkElkkBP24BvtwD/Rid/azKC+JRZMyGJ+TgtWkPL9erslSiDqFqLtca2u46lWIuuFC8tLrUYg6haj7WKtouIm6wZZN/N8LvyR8zGxidA4au0UyoyzUVjeSkxXC9toE/t8TT6LvKWXP/tXsOriRzX1w87gZNNduwGGcwT2zbyc3PYfE6AjEgIeARPqd8LLTWfs+P/jLSh544n9ZnJ10cljcmVCQ1RMqVAEnhzb/kO+uL+HGiXczJi2LxIRsMmPi0GpUaMQAlK6C3/4e2mxw80PwmYUcjZH9WPgqJ50ZgTMTdR72LFvGbm8UU8ckk5KSQozNLGcfc3bVsWJtEeGpo0iMDiM1LQ2z7ijhcPRNuG37W/xwj5bvfu4OUsLUBNy9rFv2BiGT72POaEkRJbJrzTKajOO5Y+Yo9CdJjpSZulQETiLqYnIpeusr/KJSzZP3/TcTUqMQPXa2rfk1r1Q6+M5jz1EQYzqtScE7SOXh9exprKCmYhfRWQuIMGoRhQAtdRX4jGGkJBYyr3AhCaEa3I4WDh7YQHswgjF5c8mMDkOlOh4mK4eAikHaD/yRl3YeJiJ1DjmJOWTEpZAYFX5UOSXi7Srmp39cwYNff5pRx4i6Tjas20x87mzGpMfKL2fnEmZLbbl6a9mxcydiWhrpEYlYxABOVRhpCdGofYP09HVjikzDpBbwBbxyuO2QtMvNkf0bKXUncdfsQqw6FaIQxOf3EBTPzPRodUZ0mo9CiYN0HF7NlkY18+YuJDxEfVLo5VBd7rPUJaLVGuVMfwQclG57k+1tepYsvo14s6Q8VdFdv4n1R3zcOv8WWa16chHxDzTxznuvYpz2FW4dZcPfUcy6ne+SPPe7jDIeJ+oQPBzY8jJthhu4ffZUOmo2UdTSRXh0NukJaajsDejCRxFh1uN19WIPhBAVakOtOvuLsYS739nOnt1/ZPWhNgoybyMEJ7pQJ9uq+inMTiM6Ipsx6bkY/Z3sa6hApZbUMAIaMZSeyn8TM/Xr5ERbUam0+B0tlJbvoLa1Dl1YAemJkehUPnrby2hqU5OQWcDozHEkhYbgdvZQcegA3YKA6Kilqrkel95CSnQcqZk3MXlUBoZrL1rmUrcC5XwFgWseAa8/QFltO6+sLqa0w0dkTCIGU+iICOGTw/GFIB63E4+jHzwD2Gwh5KdEcc+0LJJiwjAa9Er4/WVehQpRpxB1l3mJXXL1ClF3yRAOWwUKUXceoq7H3i1KXjUiWiwmK7qPXtJFQZaKi1oTGtGP0+1ECtpUa/SYDSa0mus79nHYibrmDfz0b7/BZwqn19FKQuJMClMi2bV7HTGpesrax/E/T36HQPW7rC4tJjm7kJJ/P0GJdiK9bhvfffLHTIyLx2oynkXBItBa+W+efuFD7vvCj5ifZqP8wDKKWusQjibDOL4URPwYyci8m3k5GWiDLso2fpdn97l44p7vYO7fS3H1bnRRN3LjhMUkhqpRF6+Afy2HzgiYtgjumAMJocN2oSoVDSFwZqJOxD3Qwb6dJXQ4XPgcHjwaDXkzb2R8chjddRXsO9SIX3Dj6vNjSMlk3g2TiDQOvQmfRtS5ulnzzzewznyImdlhqESRonVvU6PN487ZOSeplJR5uXQEjhN1nyXbFsbzP16KfcLv+erS2VglCZso0Nm4lf/3t79x853P8qnxp2eakwg5x2AnXX0tFG9fTmqhlGhEjxD0Ub1/Dx5bAmOyxhATEYtRN7Q3y+c4B9DorRj1OsSAi4q6SgxRo0gPt6CSiLqDL7C6xcD08bNort1HV28vwbDJ3DZlLBajHl9nEf/7+/d56FvPHFfU+TvZuHYzcbmzGJMeh6PjIJtL3qHVJ6A5QSYligEElZobC58i3SbQ11XHloqdBLxq4tLncENOJhpVkLbqraw81MXSW+8l6kTyRhToadnCpv3VjJvxAJmRJlQBNy21W3i/fCs6jeSpKCL5pUheblq1hmBwkLCoucybePPQdwS/nZ0rX8KZcRczklTsquqiIG8M0RLRFvTQXruVD8q3oFJL4a0iQSGIKKrQaDQIgpuwiOnMGTuT5sPr2d7iY/Gc28iMDJUVdqLgYsf6N2g3jOGWGVMxnEpwi0E66nayvKiOu29/kJgQNf7OYjbs+oC0ef9FjuX42hKCTvZt/Ast+hncPmsKXlcnVdVFVLa14vbFMPOGBaSFm1CpApRs+AX15ptZNCaB0m3PUeo1ozsaknp04hFVBvJG38+U9ASa9r/Bn9buJ2v8jSSpKqh1dFLW2EduZiYRJitTxt5Ppt7OO0Vr6eloQjCGkxo3HY2rnsjRtzAxKUwm77qbS6l1+IjWujjSUodHcp8TRZkAjomdiinYj9qawZhEG/t3vs5hVzQLp81EdHbRdOQAvaYIclPTsVjiCTOZuc4fIS5941BqUBAYYQg43T7e31XB8m0VDIhmwqIT0eiOWwNcre5KCmgpOYTHacfe20msEXISwynMT2VMWjRxkaFDH28UGe8VmSKFqFOIuiuy0C6hEYWouwTwhvlUhag7D1H38388KbZ3VuCMvpOfPPAFwo4aqQZc7ax771l0BV9nUmQvH6z+EUV9DvSmOXzhzq+TKX1lH+bJGknVDTtR17KRXz7/M5ox41f1YY3LJ8tqprWunKhEDUf6JvO/X/06/RXv8EHRHho7dlPW6mfO+JnUVG0iYAmnIPczLJ6ygNzkRAy6U+UIElG3jKdfWCkTdQsyo+lur6LDMSgbfp9aBDSEhmeSHhWOWibqvs1zxRqe+txvyY0OMtBVwd7iFezxTebJRbMIdXVD7xHoDIeMZLBawKKEDgz3mj0zUSc7yctx/FIoR09bK40NlWzY0cLSJx5mdJhaViD5PG5aa49QVLSHroR5PL44B2mGzqSoW/uv1zFNfYBZOREyQbF77XLq9GO4a1a2QtQN86QOEXX/PeRRFxHNX390K035z/GNOxdh0x9VttWs5xuvvsa9d/+COwuiztoDr7OG1e/8ldE3fY+sSAtBv5O9m1fjic5h7ti8c76ItNdsYmNJM9Pn3UVqmOkoUfcnNnSmsnTOLRg1fgZ6Gzl0oIQWYx53zsiFvnJe+fd2Ft73eVIsR0Nfve2sWbOJxDE3MjY9Fq+jg8a2OlySrdwJPR9KYaAmKXEikRYppHIo055jsIuBoJHEyHA8/bW8t/J1wgruZ/GYUSeFQ3p7q/jXyn9B+hLumzYerURGCX7sPQ3U9HSikZPvuCjeuY4m03TumBBDMBhAZ4wiLSEHSeDm7izjtXc/ZM7dXyXD4GDLxtep0Ezj4fmFmDRBBnvrqenuktUgKrVAS9G7HNAWsnhcIiohiN4QgU3lobiyhfHT5pFkOe6r527fy0vvvsWkm3/A1KTQ00I5A54+dmz8J86oGdw0uUCem4+IutR5/8XocxB10rGidL0LLtpa2zFGpRBpEGkv+zd/2NrIZ+75KlnhKprrS+kJSirBE5eMhLya8MjRxJslEn45RfZ+IrTx5I5LoKviLf60oZ7Fi7/K3PwEoqIyiTSbCPpd1B/ajjcih5zkBA4Vr8djymNybopMTEprrbWtDrvXj0YrWS4IBIPCUDokUURviCIlJpKWQyv4x64itG6BwoVPsDA/ndriTbSZYpier3jUDfP2olSnIHBFEBh0e3ll9T7+sa2G+LhkzLboq6+ik/ZUjxNXfw9tXW2Ehaj5zOwcZhSkkRIXgV6nVdRzV2R1nNyIQtQpRN1VWHYX1aRC1F0UXJf1YIWoOw9R9+Jb3xX3VRwgKWUxmbEa1Fo9TsFAXloBh9ffz3LfQ/zywS8TGxKk5fBb/HX1Gh76/F8pSApXiLoLXroi9rp1/OClHzEoWjDqdMSkTmFqrI3N21diS9BSY5/Bs197kuo9f+S1TX+gTbeIRblJQ2++opf9q5/DnvppFk1/gDumzcNmONX0X6Ct6m2efmGFTNQtyk668PmRPeq+zbP7NTz1yO8YEzs0sKDPicMHFrN5yLcs4IGgCkIUgu6Cp/4iDzwjUecbpKnbjtYSRYwlBDUinp5a3vzrO4z+1AMkhmqJDovEoFMjBN3sX/seG7sy+PJnpyI5dbVuGwp9/d7nh0JfRZ+TrSvfoid2LrdNTUMTdLJ6+b/Q5C9hXn6c4lF3kXN2vsNP9qgbS9XK7/Dk1k6+cte3mJqZiOjtY93732dddwzf//IvGWUznLXKgK+Xqop9RI+aQ6RJj7v3CO9sWkNKwd3MHBV/ElE3FI4q4HL00lK5lq3VVYyb+gQT0o7OsexR9yc2dKVw25zbOJobAcHvwekHi8kgE2Nut48Qo6SAksKKBHpqNrO6uIZpCySV23EvuPPhIP/+aAZSifTpbithU/FmVOGFLJk251gWVSHgorP1AFu3r2TQlIDa7SZ17BKmjhqF+aTUtCIBVxPv/fsXePKf4YGJEae8LQSo2fx7Vvpn87kbx2PWqHB1HeS1f71F9uKvcUNmzElrXfD1se1fT9E++r+4Z9JH+6dELvqQcj+E6PVDL6ZBL/2dZaxd9w7etE9xz/SxGLTHmTIRAb/LTlXxGxR1apk37zMk2SQ1HPg6i9m4W1LU/YDsEyKcJXVe8ca/0HxUUXdc+TEUVuweaOFQ+TbW76vgxlu/yeRUm5xN9dxFpKumlIrmZnqDasaPm0uIczd79+9kT18Ukwkn/oaZjE+LlcN7Je/KIyXrcEfkMz4jg87K3VT0w4Sx6TRWDZCcFMKe4tep7O2gs6mSPl0k2VJyDlEnUXaER81iScEYOXFFhNiDs1tFbEoSGVkpNO3bLCeTmJ5foCSTON+0Kb9XEBhBCASCQY40dvPGuv1srOwhPjGdELPtqqnTPvKe80rhrQPdBH0uwkL13Dklk7lj04mwWdDrzr87jiCIr7uuKESdQtSN9EWtEHUjZ4YUou48RN2G7f8QN5TsJEZjYXNVO0sXzeKD3etZuOh/uCeph827NzF65tfJjtZyaMsv+eWabTz2hb8xLTX2lK/4I2fSh6Mnw6qoE4O0FL/GC8VtxKm7Ka0rIixtDnOT4ti8+R1C4q30iDfw9KNfJlzVx7tvP85mzyzun5xDUJBCi7xs/stjRNy9nkfmTsIgDlJbvo0Wvw9UHyWTELG3b+OV1U08/uWfsfCiiDoHBzd8h58Wq/nu537PmNMj74YDUqWOC0DgjESdt5ctW7ZQVBWgIC8Ro9ZHV3sL7epc7phiZOO2EjTGGBLjzPhdfVQ1OBg7dxFT04eyQrZuf4sfSR51ElFnk0ItgzQf2cOW/W3EJiWiHuikZUDNnJsXkGSTwgmVMpwInJb11dXG8neeYXtdPy61FxU2BG8zfR4Ddy39CbdMLMBiOJ4k5sS+SCE+fsmfLeChs7OcPbvXoooqZO70+UTK2UmlUFAfPkm51ldDVeMROnr6cfr1TCi8hZyY6OMJI+Ssr39gQ2caS+cuPUPW16GWpSQNPq8bx2AbFQ07qKpqJ23sp5g+Op2QC41flJJhBHy4Xf00Ne2ktqONtuYuEsfdwg15Y7FKJJgQwDXYwuGKHdR0OknKXMDUrEScbXtYX7Qfb0QqC6csJNpkQBS8dHfVUly6iUPdXu66/WukW47bMUhhv97BBt5bsZrsOfeTE6XH099AdXs1NeUbqPAn8vgdXyfBqkcMeOnpqqHkwEZK2we4445vMcp2evZjCXN7TxOHq3dTVd+AKWMxSyaNJ1Q/pG6WvJHcrh4amvdwuKoRt9/MzNl3knI0VFY6xt9VyofrfshA+qOkhpzgUSf6qDu8CVPKZ7ln1mQ5HNrnc9LfU8vhtkpaG+tx6xMonHwrBXFDSWLOX0Sc/f347ZVsr2kjIy6K6uZyQuPzOdjsY2l+HEVlFSTnTGZsciQBn5vq/W9R4Q4SF5NNclQq9ZUNRCeEsG3PIHffdiPhJhF7WxGb9tSRUXgzedFQsfcNSoMpLJl6C9FmHRJRWVu2nR5HOAXj05HWbFPpdjrNUUzKzkWj1qPX6mSPTaUoCCgIjFwE3F4/q/fX8trGQwx4NITFJKELOUPSnCswBEEIEpDvQ/1Inq1JFhXZyZFMykpkYnYiYSeona9Ad5QmzoGAQtSdHRwl6+vIuHQUom5kzIPUC4WoO/dcqH7/+tfE0sYGFhd8mhW713LvvHvYUb6NaeNvRuhbT1swl/lTbyLFbOftV7/GG5UBHrrn/1g6Ne+o4fjImezh7MmwEnWCm9INz3M4mI3VeYRWVQRJ4UbajuyEuDmMTTVSsr+EmPGfZUm2nvdX/BfbB/K4tSD1GFG3+9//TczNr/Dg7MnohV7KS7bS6guiOuFlR1JTeQNhjB87i5SIiwhNDjg5vOW7/KZUy388+EtyY4YTSaWui0HgjESdKOByDlBTcpAOT1CKJsQcHc/oUZnYdALdbY2UH2nCr9Gg0epJysgiLT6So1ZlOFqr2NcBE/IyCQ0ZIjMEv5uGmmrqW3vxB0PIGp9PSpTlJI+xi+m3cuzZETiNqBNFfM5uamtLKe9sQB2SRm5yEk0HXuXXq1by4ENvcOeUrDOa7Qd8/ezc+meKO1yEh+UQF5bMhLFTiTSHyB9OxKCXtupNrDiwBnVICrG2DBJTcsiITcV2apY7QUq08He2diVw0w03YTk1F8LRIfmdzaxb+zMqPTZSY/NIy5jL6MQYOTvtBVMtQQdHSj5gRfl+bLbRJMenMi5zPOGh4ceSl7jt1ewpWoXXnEdeziTiw2xDijcxiMfZzvrt7+IOm8Otk3JxN67n39u2EZo8jcljp5EeebLC29VXzbr1/8e7tQOMzchHhx+TLprYyGQ0uGhsqiBj0hPMyUqhu2YNq4t2YYgZz8SJ88gIs8gE98lFCjt9kRXlUoKHPNIzJpKXkHRShl6/s4l161+gnWSSkguZmj2aUPPJxLfo7qbiyGqqnWZC1CckghBFgqJAavoscuNjcNvr2bjlFepd0SQnRhMZnU9eahphhuOhtxd6zfk7D7DpUB0xcZmERiURoenmzaJW7rlhBipXOz3uIJrunXxQtR+NJo6EyFhMBhtZmTMwOKpZufXPdEZ9jsdmjKZy38usOfgifZoF5CRESulhGfBEkhymIcwygdnTZ2DRq6iv2E17lwe3dzel/U48XbU4dBYSwqMID1/E4ukziDBdfW+rC8VQOU5B4JOGwIDTw/JNB3llRxUh1hhs4TFoNFc6A4xqKGO4y85Afw8Dg/3MHhXFtLxkmZyLibBiPi265JM2UyNvvApRpxB1I29VntwjhagbOTOkEHXnIeoaa3eLr69fTsbET2HY9AQfDOZhDc/iy/d9Bdq28ed//YoFD75JgbCN5976K4XjptPpMnHP3V8j1qA/zZdn5Ez9pfVkWIk6UcDtsiNojBDwogmxYtAE6e/rQWuNxaIN4hjoxaWyEG3V43DaCWpthB1NBiCNxNnbRiAkTE4mMexCBFHA67Yz4BUItUYScqWfxS5tqq6rs4eIupfQqnXMzfosmtMSgVxXw/1EDOZUou5sgw567Wx991uU257goblTzmgBKQh++ns7cAVUWG2x2E7YI6R65Yx3Tjt9Lid6k40I65Cq8oxFFAn4HLiDasxG81n3FSkJRXdPF0GdlUhbmGzKfdFF8DM40MOATyQsLOaUENah2oI+BwNuH2bLcfLuxHb8fhdOj4hV8lNzd2P3agizhR9PgHTCwQFJjTZgxy9lHZWz0oLeGCrjoVGJeNz9+FRmrIYQfO5eHD4VNqvtnEmS3AOtDAYNhIdFoDsDQykE3PT19xNijcAccmnK1IDfTV9fD4SEE227yPDiUyZHUgy6fAFCjCakCF0h4GfQG8BsNA75/knh0fZu+twe9KZwwi3WE1SXfvoGehC1ofJaG+jvxh0UhhwZ5DBmEXThxFq1OF1eTJZQuc6Az4PfL4VND+AWRNknSm5JFNBoLESE2dAf9cO96LWknKAgoCBw2RAQRJHWLjsvvr+bNQebiU8djdESdgX96KRdZSi7t8vew2BPOy0uJ1MyY/jPJRPISIrCKtkyKGXEIqAQdWefGkVRNzKWrULUjYx5kHqhEHXnngvVe2v+IG4s2c20hf/FAs2HPPCbn5C04Hmeu/021N17eP7Vn5M36xF6DqxAzP0qD0yJZO3Kv1OmyuSxm+4g1nJ6iNDImf6P35NhJeo+fjeUMz9hCEhE3aaqV+Rwsfk5j6BRn0Xm9AnD5Voert3dxZv7fsy87IfJiplw7qGIQQRRrYQFXssTrvRdQUBBQEHgGkTA5w+w90gLf/6wmJYBgaj4VHQhJ5hpXsYxycS/EMDnceFy2NH7B+QP1+PTopk9PoPc1Bi0Crl/GWdg+KpWiDqFqBu+1XR5alKIusuD68epVSHqzkPUHSxbKy7buJz0vDswVf+IPX2jCMRM5eFFt2JoWMGv/v0C6RPvpiDjJmaOz8GgVuHuq+P9XavJm/Qok5Mv1C/n40zf1TtHIequHvaf5JaDQoD9zWs50rmbG7MeIsaSjEolKZhOCJP7JAN0TY1dhSfg4mDLFg51bOSWvK8SF5p+TY1A6ayCgIKAgoCCwPWPQO+Ai01Flby6vQq3ykpYVJxspXElit/rwuMcoLW3hwyLinGpEUzKSiA3LZakmDDlw9WVmIRhbEMh6hSibhiX02WpSiHqLgusH6tShag7D1Hn7qsXX1j2v9Q1BsgtvJklU2dStvdlNtUWYVBNZ3p+Oo21RXSLQVSqj8gCSZbuIz7/izxUmHs8TOZjTdHIPEkh6kbmvFzvvZIecPpc7ayvfIkBTx8x5lH/n73zAK+jOhP2OzO366r3XizZluVubNwxBkwzPRAghIQkJAskJNlsdrObn2xCkt0kpGxCKhAwLfQOxmBwo7h3uUiyJcvqvUu3zcz/zJVxKAZsI8mS/E2e5ImlmVPe8829o3fOOR+qqomnG4EDby3g6Qt2UNu5m5nZl3Fm9qWylHkEjqM0WQgIASEwmgnUtXSGl7q+sbuG2NRcIqLiUdST2OLghCApWIKuu62RptYm7HaFL84t4Jzp+aQlROFy2MKC7p8ZsE+ocDn5FBIQUSei7hSG33FVLaLuuDANyUki6j5F1BmGbgaDfkIGOJ2u8Gbyhh7E5+8FmwePXcPv78EfCr1vj4r+PX9s9gg8ztG5IbSIuiG5P6WSjyHQ6WtmR80qmroqw/s6yTEyCbjtkRQknkF+4nSRdCNzCKXVQkAICIFRSSAY0jlQ3cwfXthISX0fiRljBm+pq2m9bzQw9P4s4r1tDaiBLlKjnJx7RgHnnzmW2MihWWY7KgdzGHVKRJ2IumEUjsdsioi64TNCIuo+RdSZ1ieqHB8hIKJOguLUE7CEuIl53Kk1T32LpQXvI2DSnxU1vJG+DKLEhhAQAkJACAwPAlZW1ze3lvHUOyU0+p0kJGdgszsHpXGWnAsF+ujqbCPk6yIzUmFSThJnjs9gQl4qMV5JDjEo4E9RoSLqRNSdotA77mpF1B03qkE/UUSdiLqTCjIRdSeFTS4SAkJACAgBISAEhIAQGIYErFfzLR09PPbmDpZvqcAWk0ZkdAKqzTbgrbUyt/Z1tdPV0UJzVydn5sRx3tRspuenkRTnxe10yP5zA0791Bcook5E3amPwk9ugYi64TNCIupE1J1UNIqoOylscpEQEAJCQAgIASEgBITAMCRQ3djBLx9fy86qDtLzJqLanQM+39sSdD0dLTTVH8atBJmem8QXzp/BpLyUo3vOyd5zwzA4BqhJIupE1A1QKA1aMSLqBg3tCRcsok5E3QkHjXXBlt3v8OO7v0lzZw2a2p/5ygqm8q5mlv9yHTMmzj6pcuUiISAEhIAQEAJCQAgIASEwFAQscdLnD7KttIa7nt1IZ8hBcloONsfALDkNb9GhB/H7+ujuasMR7CQp0s788enMm5JHQWaiJIUYioEeJnWIqBNRN0xC8WObIaJu+IyQiDoRdSccjdaXzKvrnuPX9/+AvkAnqtK/JEBE3QmjlAuEgBAQAkJACAgBISAETgGBcCb5rj5eemcPz284SNAZT2RsIqrNYW2f+pmPUMBHb3c7rW0teO0GZ+QlclZRBhNzkoiN32n76QAAIABJREFUisDltH/mOqSAkUVARJ2IuuEesSLqhs8IiagTUXdC0Wh9wdTWH+anf/o3tpetRFMjjr4JFFF3Qijl5M9AwB/s5WDzdlp7a49kfR2AJ+rP0B65VAgIASEgBISAEBg5BFQVCMXwxAofZQ29eBOzcEZEf+bZbdZzcijop62xmmBvB6kRNs6eWcD8STlkJkTidtjRNKtyOU5HAiLqRNQN97gXUTd8RkhE3aeIur1luyXr6/sYVdVV8NAzf2bbgVVEe+NRw086/YeIuuFzY4/WllgPOD3+dtYfeo79Te/g0mJRkAfe0Tre0i8hIASEgBAQAgNNIKTDgaog727JIcKTQVxqDnan+6SrsZ5NrOytvt5OfB3NNLc3snh8OmdNzmHh9AK87v4tYuQQAiLqRNQN97tARN3wGSERdZ8i6s69fpKIuiOMrC+Xbl8bfcE23BHRaO+TdCLqhs9NPZpbohs6e+reYnv1Cubmfo6UqDwGZH3KaIYmfRMCQkAICAEhIATCBHr6Ary6fj8rNtfQo8YSGZ+KZj85kWYYOkFfL73dnTR1tZEXbWNyZjxLZ44hIyWOGK9bMrdK3H2AgIg6EXXD/ZYQUTd8RkhE3aeIuhlXxoqoex8jTbWhavZjPngMyow608TfdYhdlRV4kudQlHR8bzxN08A0TBRV6/c41ma+1n9My+soJ760wdRpathPSauN6fkFeBzHmMVl9lJxsJiQO5uc1CTs6icsxzR0dJSPyM7h89EwPFsS0gOsPfAoQcPPueO+gu1IIpPh2VpplRAQAkJACAgBITBcCNS3dnHfy1vYdLAFW1QirsgPrgw5nnaGk0MYOr6eDjrbmvAQIDvRy4zJOczPTyEtIQq3yzHg2WKPp21yzvAnIKJORN1wj1IRdcNnhETUfYqom3tduoi644zXkxd1JiF/F52+PkyUow831v+3Ju3VH9jI2i1bcGWcx3VLZqH7u/GFgv3S7WjbVDSbE4/Tg92mEew4wLvbt5A49hwKUuKxmUHqD71LVXM3jrgCCseMx3kCKybN3jqevudqbq65gg23X0tytBNUBafD2m/kyANZsJy7fvl5mnN/wg8/t4QoZ3+SjY8cwR5Ktj7Fu305nDtpAlEuS35GEOF2yiLOT4m1oB5gVekD2FQ7iwpuxBLHcggBISAEhIAQEAJC4OMIGIbJvkP1/PTRNTT2KiSkjcHu8pzQS1vrjwE96KOvs42G+mpiXQrnT87i7DPGkp+ZEN57Tv2kF7QyPEIgPG/AxO/3U1dXR2Vl5Qe2EHoPkHWOw+GgqKiIZcuW8ctf/hKv13vMc0cTVCXYS8LCazlc34C7fMOIXDGj6zpxcXFERkZy6NAhbLaR93eKiLrhc1eJqBNRN2DReNKiztRpKHueF3Zuxmfa/imrFGhr6UCxpZMS7SQp70rmprfx7MuP0O5y4LFMm/XkpCgYvk5aOlK58oqvMSktlmBvK2W7VrK2soaMzKlMKzwDpWU/e0sr6COZeeeeReLHibQPETHNEE0HXuZ/77+TxqTJzEhNx2aGqK+qYuz8O7j2zEJcmrUpcSV3/+6bdGZ9k1suWUyc54PZvKwv3kBPA3u2PssDax+kyeViUuwEWjsczJr3dS6dNQG3JkkRPikg+0XdMmyqTUTdgN25UpAQEAJCQAgIgdFJoNcX5O1dFdz72g66dCcxSZnYHK7j6qz1iGnoIQK+HjraW1ECXSR4bVw8LYczi7LITI7D5Rh5f4gfV+flpEEhIKLu47GKqBuUkDvhQkXUnTCyQbtARJ2IugELrpMWdZhYKex9waBl3Y62R1GaeeDvd7BPW8x/Xncl8d4oOqte53/vf5GLbvgec7OSjoq6jtIH+I8/r+TmH/yVuWkaG9Y9hT9lPmPjHZSVraO5J57Zcy4h1R2gtbMFd0wWXtVPa1s9PboenpllvQgNGSFM00Z0VArRHheqouDrqOCxl35FlWs2/3LB1XjUEE1lL3DTb37GpV99ltsWFPXPzgtV8vvffJ1toQksnX8J08fkkpyYSYTThmKGaKjdydsbnue1za+TN/83fGGyk5df/j82+PL5rxu/T0GCV2bUfUo0iqgbsNtVChICQkAICAEhMGoJWEKksbWLx9fuYc3uaoLOWKJik1C1Txdr1rV6wEdPVzvBvk5i7TqJKdEsGp/O3MIM4qMjwqs35BACJ0pARN0ni7r4hddRac2oO/DOiJ1RFx8fH55RV1FRMSJn1L03ozM7O5vS0tIRO5PT6kdiYmJ4FmtjYyOaNvI+sy23Ys3QjI6ODs/QtLbvGomH3W4nOTmZ+vp6QqHQgHVBkaWvx8/y5EXdx9TRuJX/ve9rMOkP3H7+PDx2hcaKldz14HKW3vQDFuWkHL2wZe9f+f4f3+Cmf7ubOakRlJe8zlv7D+DTUjln7vkkOUM4IxNpP7CcO1/bxLdu+G/GOJvZtnMdVT1+ag+vpaxZ4YxJc4l0RDJu3CImZCWjBFtYu+p+3qqN5rpLrmNcchRmqIetK77P5S81sez7d3NOfkq/XgzPqLuV+qRruXpGNmXF62mPKWDB5AXkJzjZsfVFqowEvO3beWrdUzRjIzV9KTde+hWmZSSiqXbZs05E3fHfcHKmEBACQkAICAEh8BECumFQUtnAXc9vprqpl6jELFze6E/9I8fK3Br099DZ3kx3ZxtnZEQxpSCN2ROs2XMx4eytI/UPJQmT4UFARN3Hj4MZ8pMzdykd3V3YGg8MjwE7wVZY4xsREYHT6aSlpWVESi6rD9aSXUs4NjQ0jOjPPGvJuNWfrq6uETsWHo8H679WPI3Uw5Kklrzu7OzE8kUDdYioOwGSAynqTGs57O7H+MXff8MFt73EuQUZaJhHRN0rLL3pPz8g6pr3/pV/PyLq5uWm9s+O83exf/srvFDWw1VLryFTP8zjj/6J0Ixb+er8ibz3TtWqa/vqX/PKbvjGzd8myfPekoggxavv5KF9mXz9c9eRnxQZvtl7W/fy8z98jcPx1/Orm24lLfKIoT+y9LUr53a+delivFoPG9/6B5sqmll8yTcpSohGD3ZxYOfz/O7B77DS72LxxC9yZnoypq6TW3gx84sKZfnrJ8SczKg7gRtSThUCQkAICAEhcJoRsCTd5n2H+cUzG+kOOkhMy/3UrK5W9lZ/TwddrQ20dLYzIyeeLy+exLjcFOKjIk4zgtLdwSQgou4TRJ1pMn5sAT09PegjfId4a5xHutSXPgzmJ8GJlT0axuLEenx8Z4uoOz5O4bMGStSZepCOmk3c84//YKPnC/zxKzeT6rX1T12teJ27HnyVS276AWe9b0Zd696/8W9/XBmeUfeeqLPaZOoBOrq6CQaa2bLmt+wxJvGFpd8Il/feYYm6rW/exfJik6/f/F1SIt4TdQbd7Y0E7dFER7hRMfH3tvDmiju5d3s9N3/+Li6YmP3P5apHRd23wqIu0qmhh/x0dXdh90TSXbuFN959ntVbVpAy7SfcetE8VDNEsKuJ5fdNZ/+0FfzksiVE2UfmtNYTCJWTPlVE3UmjkwuFgBAQAkJACIxaAtYzYmtnLy9uLOWV9aX0atHEJKShHmMz93DmVtMg6Pfh625H723F7VRIS47li/PGMT47iUiPc8T/oT1qB3sEd0xE3ScPXlZWFlVVVQO6PG4Eh4s0XQgIgU8gIKLuBMLjs4s6na6ORioPrGLVhjeo0GbwjStuDC83tdSV9eXWUL6Cn9/7OPOvuIU5mUnhn6GotJc9yE8e3sS3//M+5uelYeVkMEJ+2lpqqa18m9X7DhOfkM3C+ZeRERVpGTx6uhpp6+7FwGTnu3ezqsTghmtvJdHtQHNEEh8Tj8umoSgmerCPhtq9rFxzL1vbHMyc+UU+N2sGbvv71rtbou63t9GZ8y1uv+wcIj+QrCJITfkG9jc1UPL2k9TEXclXzp8VntVn9Law8uFZVEx9jf9cep6Iuk+IORF1J3BDyqlCQAgIASEgBE4DAtYsuoraVu56ZSt7DraQkJRBRFQcimptIPzBIxT04+/poqW9mSSHTnJ0L7EJHVwz51KKcrLRJHPraRAxp66LIuo+mb21L1p1dXVY1I30GWmnLsqkZiFwehAQUXcC43zyos6kq6GUraVb2bpjLVpiIUUFs5lROI0YtzO8jNU6rC+37tZy3tmyhjbDPLKfmyXqrHWuAYJGInNnn0d2rJvmio2sLyumrLaJ1NR0xhQsZGJWNhFOe1j6GSEfNQffYkvlIYKmih4KENIJp0O3DnfseGYXnUFihJNgVzUbNz3J62XdFGZNYNr0+eQmJoYl3geOUAW/+t+raM79Kf/v6vOJ+lBWWevtrRFs4oX7buLRpjyunDMDh5VIo6+dd1/5Hsp5y/np5RcQLTPqPjbqRNSdwA0ppwoBISAEhIAQOA0IbCup5s8vbaKiUyEhOQu7ldX1Q5tuBwN9+LvaaW5pwKXpXH5GLnOKcsFVTmnzOi6e+A2iXAmnAS3p4qkkIKJORN2pjD+pWwiMJgIi6k5gND+LqOttqWDH4RJUdy5FOTl4ndaGvR99E9q/XCGEbnxo8wLFeibTUK3/mkFaqndQ3NJBStoUchNicXw4y5dpYpg61lvY8KEoR2ft9f9bC4tAK+trsLue0uoD2OMnkJ8QG/7ZMQ+zj0Pl+zE86WQmJ2A/xptc0/DTUFtOt5pMdrIXTAV0H801O+jxjCU7KRn7R7t9AqMwuk/tF3UPYFPtLCq4MZytVw4hIASEgBAQAkLg9CIQ3jPYF+TVzaU8+voO+uzRxCVnodrshJ8Q31veGvDT196Ir6eNykCI2+YVcO3CIuJjIrFpCvsbNrCj+k0uLvoGUe7E0wui9HbICYioE1E35EEnFQqBUUpAmfb59BG+neXAjYzlp6w5ZJYaOZarOnlRN3BtlJJGNwFL1K0ueygsVReP/bKIutE93NI7ISAEhIAQEAIfIWAYJtWN7Ty2ejePbT5Edkom3pgEFFXDNAyCQR89XR2YfZ3EOUKMzYjlzPGZzJqQRWyk+2h5ljTZV/8uu2pWc1HRvxDllhl1Em6DS0BEnYi6wY0wKV0InD4ElH+5KUlEnfViEtBUk+aQSoVfQ0UJ7wP3/kNE3elzY5yqnoaMIJsrX6aqbR/nF95MtLz9PlVDIfUKASEgBISAEDglBLbur+Lx1bvYVecjOjEDhysynBwi0NtFX1cbfT1dTEyPYt6EdKbkp5IS7yXS40L90P5zQd3PugNP0OVv4bzxXyHCEX1K+iOVnj4ERNSJqDt9ol16KgQGl4DSeaciou4IY2u1aa1f44kWL8s7PWgo/8x4OoBZXwd3SKX0kUzAesCp6yznlT2/I8qZTl7CVFT1Q3sFjuQOStuFgBAQAkJACAiBjxAIvxtWTEoPmvz95XpwR5OQlodmd+LraqWjqZaezm5SYk2WzNPIz4wkPsobftEcTjx2jKO1u469jatZlP8lilIXYJPtNCTyBpmAiDoRdYMcYlK8EDhtCCjtd/ZvdSFHPwFr2WufoXBPQzQvt3usp6bwMkTrkBl1EiVDQcDaW7Ch6xCbK5fT2F0Rfot+NAiHogFShxAQAkJACIxiAgr4gqDr4WccOU49AWu7laY+2FkaQ1XNGOLiMnBGxtLb14XaUEmEzU9Ohkp6Zj1Rsc1YL5ZNw9qL+Mg+xB/ThUhXHNMyl5AbOxGH2p9MbFAOr3dQipVCRx4BEXWfPGaS9XXkxbS0WAicKgIi6o5B3g6s6XTz29pYegzlaFZWEXWnKkxPv3pNTHzBHqxlK/0Ls+WPqdMvCqTHQkAICIFBIvDIw/DGq/LdMkh4T7TYypjx3Js5gdIeL6rDi19TiWipY1xTFWcVr2Oc2yQ21Y7DpfUn6TrOQ1PtuJ1xqNZMuo+ZdXecRX38aZZl/PvfP3MxUsDoICCiTkTd6Ihk6YUQOPUERNQdYwwcCuzscXBnVQKt+j/3qhNRd+oDVlogBISAEBACQkAIfEYCP/x/8D8//4yFyOWflUAI2DDlbP40+XwOx8TRh0plezf/9dornB0qJjcYwNvdgn04r30pKIDS0s+KQq4fJQRE1ImoGyWhLN0QAqecgIg6EXWnPAilAUJACAgBISAEhMAQErjjDvjb3+D112Hq1CGsWKqyCFgyo9sX5B/v7Oevb+zAGQgxJTWas6bkcvnCiXhcg7hMdaCGoLUVbr0V9u2DnTsHqlQpZ4QTEFEnom6Eh7A0XwgMGwIi6kTUDZtglIYIASEgBISAEBACQ0DgPVG3YgVMnz4EFUoV7xHQDYOqhnaWrS5m04E6ZmUncO7kLMbmpJIYE4FiLSUdCUdLC9xyC5SUiKgbCeM1RG0UUSeibohCTaoRAqOegIg6EXWjPsilg0JACAgBISAEhMD7CIioOyXhENIN3tldycY9VSQkRjFnbBppCZFEed0jbydaEXWnJIaGe6Ui6kTUDfcYlfYJgZFCQESdiLqREqunaTuH88Y0p+mQnGS3g8EQtfUNdLR3DkhuELfbTW52JjablataDiEgBITACRD4BFGnGyHaexvpCXSEl2jKMTAELJTFh1rCOR0Ks2Kx27SwnLOSRw3GYSWQiHHFE+mOH4ziQUTd4HAd4aWKqBNRN8JDWJovBIYNARF1IuqGTTBKQ/oJGIZOa28dh1r20BfsxDD18M9HyGIYGcaPEFBRFBWjLY6+dhVvhIfPurLJ+rOurb2DhPg4pk+ZhNM5AvYzksgQAkJg+BA4hqiz/sAO6H3sqlnN7rq19IYaMI98/wyfho/glpgKqmJHVQ1ChvW9PjiC7j1CmuokypHBvLzPkRU7HisD7IAeIuoGFOdoKUxEnYi60RLL0g8hcKoJiKgTUXeqY1Dqfx8B6wGnsesw6yuexW90E+HwooiiG9ExEjKClDbuJKpjBpfO/QKpKUkD0h+f38/Tz7/CBecuCgs7OYSAEBACx03gGKLOekl0sHk7b5U/wYTkBeTFTx14uXPcDZQTPysBf6iXrdWv0hvoYPHYL5EQkT6w+9+JqPusQzQqrxdRJ6JuVAa2dEoInAICIupOsagL9LbR5Q/icEXhdbs+qGRMk1DIT9DQcDlsJ/2AZX1p6sE+egMBXO4oHJp6CkJNqjweAroRZMvhV6lq38vighuJcMaiIuN1POyG6zm+UDfL1v8IV0cBn1t0E7Ex0QPW1Icff4Yli88iOSlhwMqUgk4PAtb3QtDXSZevD5szlmiP80MdNwkFAgQM8Lg+/LsTYBT+/uml2+fHHRHz8d8/eoDu3g5MezRel0NeT5wA4pM69RiiLqj7WXvgMXoDPVxQ+FUcNtdJFS0XDQ8C1pLabl8bT+/4X2bnfI5xyWegKtrANU5E3cCxHEUliagTUTeKwlm6IgROKQERdUMk6vRgN1XlxTQGTBRruYMCimmnbv9T/P3tF1l06V+5bfFZ6L3ttPcGiYuNR8PHttV/580aBzd9/qskue39+5noARoObeZwD6iKimnomKqCav3WFsWYrAJiPI7w3jLhvU9Mk7rdj/D7VWu49vr/Y2pSZLjX1nI89AC1VcXUd/kwwuf3H9bSPEWLJjd7LPFep/zRNES3aVAPsKbskfCSGOsNuKbK/mNDhH7QqrH2ebr/3f/C1T5Iou6cs0hOFFE3aAM4CgrWA73UVRZT5wv1f4cc+Z+6spd4eNU9jL/wGe68aCGBvnZaOoMkJSagmn3sXPd3XjygcuMXvkaOx9W/ZFv30Vi9j8MdveEvivDSfFND1cDAQ3Z2IUleR/h7x7C+UYwQdcUP8V8vPcU3/+UZZsR7+r9jrFcQav+Cfmt5ZePe5fz4LzdQPfF33POFG0jxHvm+C//ewN95iMo2jaz0VDpr9lLZ1YemmBgGxCYVkZcSgyb7Axx/tB5D1AVCPt4oWRaWORdMuPloWeFnCdMI761mjbmq9M/ztv7Z/zvrmab/5+8dR39uzQlXlf4Xjda5RjgqwhHwgZ+/V471c6t86xnE2gri6M/7n1n6M6L219m/f977zv+sewocP70Rc6a13+DDm/8fZ2QuZULqHBF1I2bkRm5DRdSJqBu50SstFwLDi4CIuiESdUawm7Itj/J/z/4cs/CbJFY/zIGIr3HboiRWvLGShZf8mPPGp3N4z0s8uWYlkeOvYdGYSOpKXuP+FX8kddrPuf6smcR7U0iJ8dJ0aA1rNj/PioPNLFl4PVHNq7n7tb+y33klD97+GxZkRbB5w/OUd5hER3vprC9m/eFqJhUuIt1rp7WtmajMRVxclMZjf7uS9bY5XDpzLk7r4VgxaTz4GN9Za+Ppf/8tc3MTRdQN0X1ribpVpQ9gU+0sKrhRRN0QcR/MakTUDSZdKft4CBjBPqqLn+B3T/8a8q4hueVlHmq5kPuumsArb25i4RXfZsnYNOoOvMnDK14grvBzzBkTT8fBFfzxxWXEFX2LLy2eT0pMKumxkTRXb2bdpsd5fl8zFyz6AtGdG/jby79gT3Aev/7OP7hsfBQ7NjzNrg6F5CgvXY2befngBhZMuZUMt7W/YjXe9CVcMWsyoUAvpVsf55m31xIz7hy02ucIJl/HFQuXkhXnpru5lBXrn6e49B0OBXKYlTudnBSVyopVbCzZyZRZt7B49tVMTIsTUXc8wfDeOR8j6t4sWYbyflFnmnTVlvHWlt0EbR50E6LSipg7MZ1gYylv7TqIYdowdIXEjHxmTMzB9NWx/t1ddAUV0EN4U/KYMXUczkAdq5/fTCDOjWoEcaUVMHvyWOzdDWzdupmmgBPN1LHHZDFr6jjiHT7Wr3mDWr8bu6KDM505cyYQ5+xi1YqNdOrgUE1UbxIzZ08h0SMvFT8cAiLqTuSmkHMHgoCIOhF1AxFHUoYQEAIgom6IRF1f8z6eePdR9u3dRnv8PCb0baNMmcqEqEZKayvJLbqIyxZ/mYiGbeyvrcJvi6a9t5ZQZxWr3r0PJecbLC7MJS3lDGYW5OO0QX3Jqzy04m80OmNwdpbTrE3kgoVfZfGkKbiNVp587m7a9QQSY7tpDhgo4bfPZniZbXdtDaHkC7n9/Jk8de+N1OZ+m1svXITbevONSc3OBzjrga088t2fhkWdHENDoF/ULcOm2kTUDQ3yQa/leESdGeqj5vAedpT3Mn36ZCKUDrbs2ktC1gTGZWXj+pjVSuGlrzKjbtDHcGRXYNLbVsGKjQ+wvvgAZtQ4cowq1jfFMy/HT2ldI5m58Vy6+LfE9JVSemg3PmLpCLVgdpbxytr7CaVfw3lFk8hKm8nswvE4NIP6std4ePlj1LldRHZVUG3kccGCL3HO5DPw0s5Lz9zFXjOLyfGtVPtADc/YVnA4PfTWlBBI+Tz/ek4Rr6x9gNc3vEGHawxzJ2UQaK1kR2kD3qRULjrnm8xKjeCVl+7kzxu2cvasS3AbcUyM8/NiRT1jY3QO1yfwjVvvYFpCxMgepqFu/SeKOhsXTPhaf4tMk57Gag42teHyePE3V/Hy66Wc++XrKHS1cKCxlwini+6Ww6zb3MAFV11IdlQfpQdbcbkc4G9jy4ZNpM27illZsG9zPVGZXgKd9axau5XCS25kfmKQw9XVGM5o8HWwYfM+cqcv4KzCaEpL9hFwJuGil52vvQZnXM7F06LZvruemCgnNr2HravWYM5cypUz88IvG+X4JwERdRINQ01ARJ2IuqGOOalPCIxWAiLqhkjUNe9+mCWPvsjNCy4j1eMjaFhCzEBR7Sg9dfxj/Rvc9o0n6Xnn55So07j24iuJd6j4mkr4299vIveqlVxW4EWxlkL2NnO4tTW8rLVu3zJ+8+wfaIoYz+1X383MrBRUxSQqNotQdzXtzdUcau3C7NzKSzv3s+Scr5OfFE+E3YvmTiDVY/L4fV+iNOZKrp4/C1f4IVehqfRZrn25iie++zPm5MqyuqH6ABBRN1Skh66eTxN1hhGiZs9qVu7eh8e00RXoAZtGIAhaTwNjFtzKoilZ2I+xrEtE3dCN44ityVpWevANvv6HK1l43p/J8wbD3z/W9wSKhtPfwuMv/4zLb95L5IE/sCOYx02X3Ei0Hcy27fzPH79N9tK/ct20Cdis9a3+TmqaGwnqIVoqVvHnZ75PqZrNt669h1nZ6djQiY5NJ9jTSmdbNTXNNfS07eOxTeu54so7KIzxEmH3oNi9+A4tZ3V9FDPG5+Dpq+a5l35Ae8GP+OIZhfiadrGztI6Zcy6m5O37eafxEJqZwLgJVzDPsYXvvFPGBWOi2VEc4Fv//jvmJPdv6SDHcRI4XlGHia+7g6o9m3lp80EI9rCrNMiXv3cLs1MNSnduYcVbJaiOAIdqXdx0+3VMTdIo3bODDVv20R7Qaamr5syrvsmSCV6q9u7g7c3bae5VqK1pYd6N3+aSsS5qynbz8rvbCfhC1Df7mHfxFVx+ZiaH9m7jrU17aekJ0FFVQ+6SL3DNvEyaqirYtG4dh3pMWg9VkH7hTXx5cRGeAdyC7ThJDuvTRNQN6+EZlY0TUSeiblQGtnRKCJwCAiLqhkjUddfvZlXxLppq97G5ejfjx88ihh627t1Ir5FNUeEClp57LTHtG3l0zTZmL7gIW+0mDrXV88Y7fyZh6o+ZmxlJVvZcss0DPL7pJXpMDS3QyYYdLxFKvIp56QG2bH+OUvdC7v3WMiYl6RS/dQ93vZvBjy72ce8rjzJusrX3jwO7O4tphVOJ1Xp5/N5rWdkdw+T8Mdj6d52hs2EDy0ryePh7d4moG8IbU0TdEMIeoqo+TdSFgu289swdPLS9ilnZaaza8hilWgYXjl2AceBxDoz7I49++1rij5EERkTdEA3iiK7GpKu5lDXb36W1fj9vHy6jcPw0om06e3a/QYc5nol5Ezh/yS2kBHZy77OvMvOir5PYtp5DdaU8v/Yeogv/hXljxjAm+0zGuNtYvvFJ6vwGWqiPPbtepCxiCVeOjWTXtodY1+Plwf/cxhnpkVQxDXC8AAAgAElEQVS+83t+sSGeWxe6ue/V+5g096tkOkxwpDN74hm4jQZ27N9Bi68Pra+FNe/8id7Mr7FkfDrBoI2c7JlkuxpZt+l1tu9byevNJrdf+xemtD/B7W+Vc2G+NbPKxze//xtmJ0eN6FEa8sYfp6gzQ93sXPkSz+8wufqL55JitPDi06vIXHoNcRVrWFNjcNmF5+AKNfHyK/uYs3QxMbVreHJLJwvPOZf8BNi2bgV61vkU+Nby4zdNbr9+EZlunQ0vPUNg7heZru/n+ZVlLLj8HHJjNLas34wzczKzEpu454G1zLjyaopSvJRveJH9rnlcmNLAb57fxpwLL2d2lpeylc+yN34eN5w7UUTdhwJJRN2Q31mnfYUi6kTUnfY3gQAQAgNEQETdEIk6ayNm3TDpqV7LI8ufIHXKlygIbud3rzxL1vzv8o2zzyU50kmop4E3V/6VlvilTPXsp6KlgddX3U3irB8zJyuWrPQ5jEmM69/AGwh0HODXf7sWZfrfWaC/yCN7W7n8oh9wQWEWdr2Vta/cwW3b5/DMlTr3r3iI8Wd8icwoFw53HpPyJhGt9vD4fTdRm3MbX19yFm4rwagC9bseYtGD23j0Oz8VUTdAN9vxFCOi7ngojaxzPl3UtfLOpjW09fiwuzRMxYEZCOJ0hdAVN/56BwsuvYB420enioioG1mxcKpaa33/GIZJe+1qHnvlGeKLbuSMyFJ+9uhfyJz7A24/dwkJXg/4m3jj1d9QEXUFc5MaqGvcxzMr/kLs1G+xsCCX3IzZjE1JxtBD4WWsZnc1jz/0Be6J+wm/Tt3H45veZcYF/8Pnp4zBqfSwYfkP+cH2cdx1XizLVt7DtAU3k+1RUR1ZzBg7nWh7gLdX/4JX9jUwZ+J0Nr/9W7oyb2ZWZBWPFkdz123/QbZ5kGee/j6P12YyP8tDdyiBSZ42njzczvzcSHYVh7j1e3eJqDvR4DpOUaf3NrHyiWfpm3oRF05Ixt9Sxl/vWcmMa6/BKNmEmVTEohnZdDaW89jT2zn7qgsxdzzOHsdsLlowAbvRzptPPYI26SpiDy5nb8q5fH52DkpHFc8/8hTOJTeR17aFfS0xXHr+DNRAB6++uorIghlM1rfzVFka1185i0i1l7f+8SA1WUs40yzm1aYErrt8PrF6N2/94wHKspdw43kTiZAk6R+IBBF1J3pjyPmflYCIOhF1nzWG5HohIAT6CYioGyJRF67GDNLVVsmKl3/GU/v24gn5icq/nX+9+koyY2LCS5EaDr7GHx5/iGmX/IKrp2TR07CXP95zAzlXvsXni7wfaW2grYRf/OVifOMe5OoxfZix45iUmYFdMeio2879D/+Wdb02Li7K50B9DV+6/jcUJvyzHL2vlcfv+zIVKV/khkVzcB3JqNa07ykuebqUx0TUDelnhYi6IcU9JJUdj6jbuGMnUVoCrkg7fkzU3hARXpUgdupLKpmwZDFxIuqGZLxGbyU6Xa0VrHrtpzy6Zy/xRhOOnDu49bIryE+MRVUMWg9v4Fd/+m8mXn8/10/NQmvewo9+/3Wyli7jxjMn4/gQHKPzMI8++Hn+7LmDe2Z5CHnzmJyThYZBd+Ne7nvgB6wLjePC3Eg2Vezjm996gCnR/Vlf+78TDSr3PsWD68q5/qKr2PDSTdSN/y0Le+7hgYbF/M9N1xHpq2PlM9/lvpp0Zif7MSJncWlukJ889BiF+WNoNvP4/s3fJdvrGr1DNxg9O05RZ+p+ava8zcsbq7FFeIl0Q/HOes6/8TrSukpYvbEM1WPH5XRTVdnLRdddTJqvjBXrdtOneoiNj6CtspTsBdcyyV7Fy2s3o0ckEBcBNRX15F14I2d663hj7Sa6DAfOqGg6GlopPHMhi/J0nn1yLR2ah8j4WIzKElzTLuTcPINXl6+hXY0kNiqC3ppS1KmXcM3C8XhE1ImoG4z7Rco8bgIi6kTUHXewyIlCQAh8IgERdUMk6kK+Vkp2vcmr7/ye/b40zj/r2+SZh3l9wz8IxhexYMb1zJwwjncfv5lX65L5+tKr6db9BFrLefSZn5F+zl+4MN+Nw5VCfkY2LptGX2ctew+8zR8f+3dyL1jOD84uxK5am8wpBHobeemp2yjWFvDFs62EETewIVjIDRd/i7y4CHTTRkz8WPIiYdndZ/NEo5+ivMLw0lcr62tHw24erziDV/77j8wbkyRZX4fog0RE3RCBHsJqjkfUrd+8EdXvRot0EFBA6wvgcWv4cdBZ1cIZS88XUTeEYzbaqgoGOqjcu4qX1v6e7V0ZXDL/a0xOauGZF/5IIHUe8yZdzswJEyhe8UPuKfFwx7VX09Pbid5Ryp8e/REpC37K0onjifIkkZuZR4Sm0tfdwIGyDTz7zPVsmvomz3/uTGwoWO96/D3NvP7sLbzSOZNvXzCfN174D56vaOUrN/yFCZEqIVMlKr6QMZ4edu56kftff4up05dQs+1HNGf8O+mNj1GV9FW+tuQ8xsZ5ePvpr/Pfe03mpujYIhZypreYd0Oz+MK0saxa+y4zLvwSC/JzsIukOf7QPU5RZ22FYRpBGuvr6ejV8URG4dbA4Y3GY9NpbmikszeAyxuNy24jIjoSl2rS0dxIS1df+LxIl4bN4SHCpdHZWE1Tt44rIpIIh4bqjiLapdDe2kRLezeKI5IYrwu7y02U20FnWwONLT2ozigSY2yEcBHtdeJra6CutQfV5SEqwomiuYiOipDMvx+KAJlRd/y3hJw5MARE1ImoG5hIklKEgBBQ2n8c3pRMjiMELBhW1rCdPTburEmkVVePPvgZhkF5VzPLf7mOGRNnnxAzX8cBXln5S2x53+bswgIinPbwrIO+3g52736a7S3RXHbeVQQqttOmJhLb9waP7CnGoznRVCem2UvIUElMOpuL55xDnMtOa/Umntv8HAHbFC486zKyoyOOCjVfdw2b9m4mbcxixsRF0ttZzebtL7CzvhzrL6mA4mFc4Q1cND6DXRueoid2JlPH5KApVpIL6G4s5umdhzh/7sXkxUs2vRMa7M9wsoi6zwBvmF56PKLunfXr6OlU0SLshBcV+nQ8boUAdnxNQeZfcaGIumE6vsO/WVYygGrWvHE3bUnnc+H0+UQ67OEZ3L6eDsr2LWflgS6uufSrmDX7aLMlk9H7BI8V7yegRGLTnGD0hZNHJCYt5KL5S0lw2Git3cwLG5+mPZjHRed+iXHxR2bKmVZ9tbyzbwdZY+aQHxeLv7uRzZufYlNTBTYMgqadsRO+wnmJXby48UHqgpEoRghFdYRnnltJLlSjBTXp81wz40yaS5dzwLGImfFt7Ni3jcZQNlecNwuPqtJ56A1W18WzZNYMImzDfzSGTQs/RtS9UbIMVdG4YMLNw6ap0pCTJyCi7uTZyZUnR0BEnYi6k4scuUoICIEPE1B6nvySiLr3UbFg2C1R19TGjzcU0xLoQ1P6X9N/FlEnoScEjodAv6h7AJtqZ1HBjWhWll85RjSBTxd1nezYsZH2dh+KWw2LOnwGbpdCULFBt5eZ584jSpJJjOg4kMYLgWFF4ONm1JUuAzQuFFE3rIbrZBtjibqHNv2QmVmXMiF1dljCDtjR0gK33AIlJbBz54AVKwWNbAIi6kTUjewIltYLgeFDQOnuqhVR96HxUBWV7fu38T9/+yHNnTVoql1E3fCJ2VHdEkvUrS17BBODxWO/LKJuFIx2WNS98584O8ZyzaKbiImJ/kCvTEOno/kw1Y1N+K1PYwUUs/9j2UQlNj6P7NS48GzXDx/hZBKLF5KclDgKSEkXhIAQGDICxxB1Qd3P+ornaOyq4eKJX8dtjxyy5khFg0OgsbuSF3f/nrPG3MCYxKlYz7cDdoioGzCUo6kgEXUi6kZTPEtfhMCpJKD8YvlNIuo+NAKaTaWxtplNq7YTCARRZEbdqYzR06rukBFkU+XL1HaUcuGEb+CyfTSByGkFZBR01h/q5f53f4i9NY9LZl9PUlL8gPQqFArx1AvLufDcRSTExw1ImVKIEBACpwmBY4g6KztwdXsJL+/5HTmxMylKm4NDs5J0yGPiyIsKhR5/O2+VP0OEI5rzxn+VaHeCtYvkwHVFRN3AsRxFJYmoE1E3isJZuiIETikBZdPB1+QJ7ENDoKoqpeX7WPboX+jsaUU9svxQlr6e0lg9LSq3HnAaug7xdvkT4QfqaFdC/xvwY8ymOi2AjIJOWrMkSxo3Mt5zCY6+ZBxO+2ceTutDu6Oji6zMdMbl52GzyRLpURAq0gUhMHQEjiHqrMqtpZIVzTvZUfsGbX2V6Ia1Z+CRZsnT4tCNzwDU5NA8pEQWMiv7EuIj0lAG+jlCRN0AjNLoK0JEnYi60RfV0iMhcGoIKKb1iSrHRwhsK97Af999K00dVeFkDtYhok4CZSgIWH8oNXVXUdGyk95gO4YRGopqpY7BIqCo2FUn4xPn4zCi6fP7BqQmu00jLjYOm20A9xwakJZJIUJACAx7Ah8j6vplnU5voINAyG/lfO1fjx8+3v+4KPZuuI+x9ZLPZY/A4xikJcwi6oZ7CJyS9omoE1F3SgJPKhUCo5CAiLqPGdStxevDoq65o1pE3SgM/OHeJetBxzD1I38kDffWSvuOh4C1ifeA7g90PJXKOUJACAiBYxE4pqgzwTAxdcPaKDMs6IyOQ/hXbUUZexbOoiTCE7xVlWDpVvRgPI5xWag21XqTialbL5Xet7TSyiJvJS/Qjme5pQlBHVOzhev46KFjBo0jP1bApvXXdHSWmNnvEa1/6zqm1R5fH6HaBpTUNGxuh9VwFCspj3XO0XfU1qag76vN0EHVwDT+Wd77Z6JZ1xkGqP8sJ9zvcHkKimYHxWqnVe6Rgo/6TYuRfsR3qij2916yWG3/UDtMaxyscgH1vfYqoGn9M+Pea/+xZslZv3vvusGMfhF1g0l3xJYtok5E3YgNXmm4EBhmBETUiagbZiEpzRECQkAICAEhIAQGlcAxRZ2B0VpO34urMUwP+DpR08Zjm56L5o6H7moCh7uw56RBdxPB/SWQPAZbZiaaLUBg13aMzgDYbJjdrRjtJs6Lr8aeEERv7UJRdUJVpeik4EiPBcWOmp6KqveiV5fg330INTEP+5TxaB4nRlMVwfLDmEYEtiidwK496B0+tIxCnNMLCR4+gG3SVGwOFaOlDH9ZCOecsRjluwnsOAyE0Fs7UGLiUB0aanohzinjUT02jJ5agnsbsRcWokY6MfUAekUp/spO7GPyMTvrIToaGutQUsZhT4/pL696J771h9DyJuGcmIeiBAlse5dQVSM4EnHOm4vZfoCQmowrLz7ch8CuA5ixaWh0EyrehdGjoIyZgPOsM7E7TYxD2+mrzsCzIAWCoTA/vWYXfSs3o0Q4MarbUZLjUIIGtqln45yYRHBvMYYrEkduLoq/C8OvosZGgWoS2rEGI3IKmrMXM+BHic9Ei7KHx0Rv6gbTT/DAfpT4KdiTFHB6UUwfRl8QVDAbKgh1ebDlJqNGeFET48OC8yO6VUTdoN6iI7VwEXUi6kZq7Eq7hcBwIyCiTkTdcItJaY8QEAJCQAgIASEwmAQ+JpmE2dNGYNNmdCUGxWxHccaj9DVhRo9Bi7JmtWkoLhU629BralHiMlBj47HlZqCY3QTLqsDtxezpAE8Cjvx0QpXFBA82oBhm/0w0a7qXoWAaKmphJlQfRm8JYCvMh9YqQl02bBnZmN3lmFYq7LZ2zIR0aO/CDPpQU/Ow5bgJlfVgS3FgtrVjdNQSrDWwz56JI9lFqPwwRm8As6sbJTIKxeFEzczBlhgdnpFmdNcS2HoANTkNxeNE9bgxqksJ1JmoUYTPVxKSUB296LUB7AVZGK1VBOt82PJyMFtqwOdAG5uF0tfcL+pcUajxsRgHiwmpCTizo9DrGzFauzD9QUyHG0XtxfSZqKkTcE3JRtEMjPpiercqOAs9YdGp5o9B6SzDv7USLc1DcGsN2vgc6GlDTZuKPbEH/8ZdmK44bIVF2KJMQiUHIS0fR1Yy/ndeJhRKQXM5UN1d6O1uHDMmonRVEdheGp7spzfWgTcTW6QKaWPQIgzMnj6M9haM+joMZyr27ASUqDhsmSko781gfH9MiqgbzDt0xJYtok5E3YgNXmm4EBhmBJSSjfeYdRHzmFkwDo9D9jp6b3xk6eswi1RpjhAQAkJACAgBITAwBI4l6kIBgiXbCFb7scVH/HN5ZSiA3tAMOZkoSjSuwhwIdhIsO4iaWYQW40CvKA7LKqOtjVDlYZS0/H4p5onFVjAGJdiKXl2H3lSDocZjy8jAlhaL2VqHrrugvan/uowx2KyZbLqOYm8isLupX/idEUPglWJwa5gxaTgLXOjtidjHxqPoAYzWQ/jLgzhnFUJrJcHiSszw0ltrHpiJaaqoGWNxjM9FdWoYvbUE1u8ERzSKy4GWnouithAobQrLO+PAdvS+AIrPjjp3FmrHYYz2ToyADc1txwwGwsuE8XpQnDbMhmZMbwJafCz6wT0YaiT2nHTMjjb0hiqIGYstHkLlZf2z5ryT8Jw3CfROgtvfwl8TjSPXixKfji09AaNuN33ritHi3YRKmtCyU8DXhzZuHo7xTgLb96PE5mHPioPeZvROHdNmx5aZTmD1s+jOAlzTJ6A6Dfwb1qHmnonN00fowEHMkEmo5hBE5WOLsWYa5mBLscqpw7/9IGZ3O2bceNxn5Idn2FlLeI+ZiEJE3cDci6OsFBF1IupGWUhLd4TAKSOgPHJnjPlk2l+57/NXkOB1HJ3abgR62PjiN7h/fxWmWU9DdzkJST/h9suX0FxeS/bkheQlRRNoLefJh6+gPP8vfCG7hefWPUyzrtDd/i7ZRf/HzRddQrzbOZAJ4YcEloi6IcEslQgBISAEhIAQEAJDTeBjRF3o4E4Ch9pQ6uogwgtmENOWiOJVsE2bhS3CT6h0N4EN+zEDPtDsqAXzcExJRentASVEsLQEYtNRfTUEezPxnDUZo60RM8IBDXvwrT6AGh2JOmU+zjQd/5q3MbpCGK1NEJ+CZu3DNnk2NqOa4N5yzOR8HJNjCL3Thi3TTbDTjz3Sh64U4BifAL4u9KZygrVOnHNzCG3dhm5PwB7lDMvGsKQz+tDb/GiFk9CiHJjW0teSFuxjx6FG2jF7m/CtfI1QaTNkTcYxMwO91Jp9FomSnIE9Ix5VCaDX1If9HNjQ0tLDIsxobw9LPNz9MwuNyr0E7Sm4MiII7N4R7oOSNwtHbDeh7hCa3U+oLhLX/Hz0kh3oZhwOa0nu+96VG93NBHftJtjQjWNCLnr5fgw1FeesqahaJ/49FdgKJqNp3QT3b8OImoNrQkx4b0H/2pcg4yycedZyXYPQga2YrvHY073g78Hss2Y+lsCY2TjiHf176ykmoYqtBFvi0Gw1BJo13GediWZX/7mdX9jZvW8BrIi6ob5rR0R9IupE1I2IQJVGCoERQEB57jcx5hsJd/PdC5aSd2RJgNVu3dfAiocv4dmOadjbSrCnXsq86MM8sX4Z5b1+UrJv4Wc33kbzrifZ2hjAqD/E2EVX4Q1U020aVO/4M3Vx3+P7119PskdE3QiIBWmiEBACQkAICAEhcDoQONYedZbUCgUwOxrxb90JUUnh/cxMTwrOsekoBAmWV6IkpKOZ3YQOHUZNyUeNj0aL8hyhFsC/ZSNmbBZqMICak4tm1wlu30ooMg5boJlQKBlnVjxKRCSKFkKvq8YMKYRK9qBMPRPN14sSG49euha93gG2AEpSPEZ1H1qMHV3x4Eg10LtS0GJ6CVbUoPh70Hu18NJXe2Is6D0ED5ajRsURbLPhmpSM2dqMEpmI6rJj9NYT3NeAfdx41EgHZshPaO9uAnWNqImFqGoHhtOBZrMDLrQYP/71+1BiYlGthBSmH72hDW3K2ah9+wnVWrPtFBwLzoOGnYS0VFw5Hvzr12P4bJg9PeDxgEtFNQMYoSzcM5IJ7CtDmzgFe6T7A1GnH95OYEcFoU4fttQEjOYGDNOLfdIkNEcnoVYTRe/A7A1iNtdhegtwzJmILS4Ss64Cw5uD5jUxuzoI7ClGyz8DTW3Et6UYBQd6Ux0kFeHIS0ZLT0F12yHU0b8PYFUjZlQGroUz0DQTo62B0OFmFGvmXULUP/N3iKg7HT4pTriPIupE1J1w0MgFQkAIHJOA8tyvI80HfZ/joqIzKcjMI3vMXLJjIiDYwpvP/oh7d1aQlppBdvI4Epy97C0v5nBzB8k5F/Pls6exesXfqehtwus8kxmT8+jtqcOwO6nd8WcO2K/lOzd8i8LEWNRjZaYaxoMiM+qG8eBI04SAEBACQkAICIGTJ3BMUWdgdDQTqm/GbK8n1NAOdjdaRgaaKwJT60FvU9BibdDdjV5Th5KUjeZyoeZmo9pD6JWHCJSUo02Zgz0lJry3mdFUSWDnPgzVhllXg5JWiD01EsXas83tRj+0m1CnitnZiJozBqWtHa1gEpr3EH3Lq1AirOWZqeiNzahON7jjcOQ7CRwMosYGMXpAU3sJdSioKXFo0RHo+0ogzlpGGoF/WxWOjEj0ji605DQwdQi0E6pqx5aegWItp1XAaGpFDwbQYtPDS3KNsFRzYpo27Bk2/DurseVk9me5NX3hvipZ89BCBwh1m+j1TTgWX4HStJ2gmoq7IJnA1rcJ1XdgdvhQc1Mwe7rDy3qJzME5OYPQ7p3h/ljLaY8ecenoO18gVKehREagRroxe7swWtsgIRMtLgEtOwH9YDmKNwrFamtEMmp8PLb8HFSCGE0N4fEJtTShJBbhLMrCrC2mr7Qee3xi+PdKZg5q0A+xKdgyk/sT5h7aR+jgYcidhjMvGfQg1ixL384DqAUzcE8tCCehDR8i6k7+/hvFV4qoE1E3isNbuiYEhpSA8txv4sw1Kffwr/My2brnbcoOl1A46xtMd+7iV08/iqGlM65oHB5NCWd7V0ydprpDHCgtZcrFv+KasXZef+FeIhZ/n0KK2bJvE5veeQJ70Y1kam6mTruEBZPHoomoG9KBlcqEgBAQAkJACAgBIXBMAscSdYaO3lRF6GANuOKx5aVDsDX8b1PxoKZFozgiMOvLMbr0cFKC8KHb0KZMwuYMECjej2l6sRUWoHn7V1PoTbWYuiu8xNQSQXp7MJxPAnckanQUZlM1pnGksP4t5VDiMrFnawS2VYDT2pZFQ80pQvMG0eubUaOiMfv8KJEOQgfKMIM2tHFF2Lyg11aid0ZgH5sCei+hshKM7hBKfAoKvRjNHVi2yXqqDa9iNU2UiARsWSkYPd2oCSkoPU0Ey8sx7SnYx2WgGJ2EyioweoPhpaLWklJwYpswEaX7MEErmYQnCfv4sdDbiEEEtlgPRm0FoaqGcIZbXG60rBxUR5BQZRNqXi5qT3N4lqIZ0I8Ok5JaiOovx3SkYEuysuNarTQwrP39Ql5sGckoDiW8kiVU0QhW2yfmhbeTszLGYgTQD5cRqulDmzAOW2QE2DRrqQyh0j3oLT6UxCzsBekoRojwRnTW7628tgf2YTpisGWkhGcOmqYeTpwRLK1HzR+PLVFm1MknyicTEFEnok7uESEgBAaGgPLcr2PNVan38aPLLiE+QqO2dBUv7thDdsECMjjMskd+gqPoCopSIjBMlUDXAR7d0MRtV93ClPRkSouX8eQ7z2NLWcDSqVcQqXdTsum7HEq9kyJnMynjL+C8qVOxHX0FNzANH+xSZEbdYBOW8oWAEBACQkAICIFTQuBYou6UNEQqHbEEZEbdiB26wWy4iDoRdYMZX1K2EDidCIRF3erUv3PHZUuJj7CDodPX1wMOD5qvgddf/S0vHGxjyoS5ZLg62LrjLbpjF3PbFTeR7fGzdfNK3t6ymej8fGblT6K8bB1vbPo/tra6OOvM/+KbV9xAZoz32BmjhjFpEXXDeHCkaUJACAgBISAEhMDJExBRd/Ls5Mp+AiLqJBKOQUBEnYg6uTGEgBAYGALKM3fFmm+m3MdPrrBm1NmPrmQwDZ1AKEBHwya+849nuXjx91iaUsKfHnmAokvv5PyCdMxAD1s2rGTdlnvRsy5lcmwE0VERvPva9+kd86/E6kEmTbmMc6eNR5MZdQMzYlLKaUPAsJacmNbyGjlGLgEFVdFG3IuKkctbWi4EhMBxEbBE3a9+BfPnQ4yVHVQOIXCCBAIB2L4d4uNh584TvFhOH60ERNSJqButsS39EgJDTUB57rex5qqU+/jRpR8Udf6Ocl5a9wQVzft5d89yklIvY0xUK+v37KJg4mVkRkYwacKldJY8zsb6ENMnn8vk/Ol0l/yDO555iVtveZKZcW00BiIZn5kmom6oR1bqG9EEegIdHGjcRmtPc1jWvbcV0Iju1GnYeIfdTWZMPumxY9FU22lIQLosBITAsCTw7W/DH/4wLJsmjRphBFS1P0GGHEIgvOWjid/vp66ujsrKSlQrPj50WOc4HA6KiopYtmwZv/zlL/F6vcc8d7RBzc7Oprq6mlAoJC9xR9vgSn+EwAATULpaa0y/Fkm01/uBfeSMYA9Nba0EDfo/OMMze5RwVijTsDbgNXG5o9F9HZiOSBJjY8PZobq72ugOmMTEJOJxfPTDeYDbP2jFydLXQUMrBX8CAevhpcPXxPry56jp2oPb7u2/74TaiCNgbf8dMoL4A0FmZl/EpLRF2NT3ZfYbcT2SBgsBITBqCDQ2gs9H+KHuyGF9ZnX7W9lctoyQr5WY/8/eecBnVWT/+7lvT++VJCQhhQQIJYBIkaoCKiB2Vuy91921r/qzrbrq2guCImLHitJ7kU6o6b338iZvvff/v2/ABQQNEkISZnb5YMjcmTPPzG3fe+YczzA0tCYZEOUUEpAk6psqKa3NUfNe/C+Jxx+ZpKjP7loMRj2JUeeT2GMcBq2p/Z8lVIPUNRQZeQoBia47EwEh1P3xbAihrjOtVmGLINC5CUiKekUV5dV61hcAACAASURBVHcETo5Qp6Aoqtip/t36tOUSPn/7b9cPrVnIXI9T6gPQQdNaf3fwmOOesoPtSn8k+qh9d5QopDJoHYXUxTICHzf74zjAKTvYWbyMvWVrGB33N0K9e7m2TorSFQkotNib2FG0lMzKTUxOvo0Q7+iuOBBhczchcPB2/8fXXAVZfcl3XZdb70d//a5w6D3lYFsHbmXi2t/pVpV6/0krXUlayUpG9bqMHj7xaMXHhVM+T+r5ty79J+asfQI1JIbUmt/1T4uk0eDv7Udyz6Gck3gd4d6xaKS2HfunjYsKgsAxCAih7o+XhhDqxKkjCAgCbSUghLpjkGp/oU6huSGPzGI7sT38KCzNwyMoiUhPhcL83Vg9o4kLDcXRXE1uYTmBEaHUF2Si+ATQZNESH2YkN6eK0JhE/D1Mv73ptAp9MrIqxLk+bKoxsTSHiV/qTbOxOpeCmhaieibibTwo/LSqgLLsQHFaKS3cS4USTFJUBEasFBcVog+IItTbra3rqc31HNY69udk4O7bi+gQf6RDYhiezt5jdqeNlZlzURQn4xOvE9sl27yiOm9F1UNy/pZnGJ9wNfHBAw8xVBUuVE9lbft7OXReHMKyU0JAvT84qSxJp9rqQUxUBC6Hd0k6IMRpDghzTurKssioM9AvPoqW2jzyax0kxiTi/tvObQVZVtftAeHNdROSfr9lydZEfsEeyls0eLp5E+KtJ7PCTEyPMBoqSvDrEUegp/spoSE6PToBm8PCisy5OGWZick3ClGnEy2Udft/YPbqR5FdoTDa/pSk1uyXMIRzk28iIXiw+PDXiea0u5oihDoh1HXXtS3GJQh0NAEh1HWQUKfINvK3f8zjsz/nyhufZN/Pj2NJfpwrUup4Y+6/6T/+dS4/cwAtVXuY9fm7GGKGodn4BNb+17ChxJ074oqZu9ufu66+k97BHlQVrGFVRgvDEvzYuHkpJVYNGkX1hFDQhp/LjaNTaa5KY+H2Is4dO4nKLf/lo3XZXHvTCwQ1b2F9RgtDBo8l0NDE2uXz2FNRzq7dH7GT0UxPSSHYqGfN5tcZcuHPXDMsEY2zGYvdfojH3QE/C40Ovc6IXnt8AfNbqrdz51v3E536LP8YG83m7Vuod3oTG9ubhPCg09bLThXqlmfMRqfRMSb+aiHUdfQV8ST0p8YbnLvpCcbFzyQhJNXlQWtpLGHntuVsK8wFUyTDBk2gb3QP9BrVy7btL2EnwVzRZLcjoNDSkMeK5V+ycMs8ciyBnD1yBrHWevJtzUiSBrsjlitnXkaArZJfvr2SpfoHefy8IWSseoQPc3z4x4xHCDUp6HQmFEsxq1YsIL2uCUmrxWl3EhB8FlPOGYE1bw0rs2TGj0qlYONcXvv+Ob43NzDcfwhTBwzng5+/Y8SQqfQOj2DEkEtIjgrodrS78oBUoW5Z+hwkScfE5Bu68lC6ne2qUDdnzWPIstN1zrpk8mPshzn0HuJ0Oumf2CrUJYYMFUJdt1sZnW9AQqgTQl3nW5XCIkGgaxIQQl0HCXVNJWt5+f1nqPbuQah/EJK1EYvijrebQlVZNuVyXx688yE8sr/mi/U/snVfGnr/ASREBlCct4nKFm96JaQybPBVjA2zsGr9LD7bXs3lwwfz3bKPOOuSWYyPcGPVL3fyeOPt7L51GnV5i7j3w5fpe967XKxfzBebs5g54x/s+uwcFjmv5IG/3U44OWzN2k9dcw2/rvs3e/TnMzYMluzaTZ/kyUwYdC6De/eiOn0Bv6RnI6N66x2ApjjIzthO9OA7uXb8GDz1bQ+W31KbxqPvPklY33u4efwgSjPWU1Sr4BsRz4Be0Qe8O7rmSXUiVrcKdXMOCHVXCaHuRGB2kmOPFOpstZm8/8mDpNWacfdxR7G30NAUxLjxt3LJ8OEYtWJrUieZum5jhtPRQm1tKSsWvcHm6kiuv/RyPKuX899P5tF36Gjmf13Ea3NexLzqDWZtKeOC1EAKqvwxV69it92NgWFh5BTsJ2XU7Vw+9AwyNr7FB6vWcc7QyXw+50dmPPYCoeZ9bNn2KVsbx/LQ9Vehq97J+vwcvIwGSrI2k1m+k82FbkwbPw335nVYA67m5rNHdRvG3WEgQqjrvLN4uFCnPoSpf+T/7SN3mS6Ba2vrQQVPwik76X/Ao04IdZ13fruTZUKoE0Jdd1rPYiyCwKkkIIS6DhLqzOWb+WrhYpqMGiwGPRE+vq4oI831hdQ16mjUhHDJxVcR3JTNpv2/kpm+iRZTGFqpCMluwqyJpU9sBIlxo4iQclm09mN+2NfC9KEDWLrqS/pPeo6zwtxYv/IB3rHexYobp2Kv28eP3z3MEzv8eWRUOGn5xQxPiGbe4k+ZdvknTDtjEKam3axNW0d2WSbfrZjHXrsbfxt3O4n+fmi0eoKDBnFG/354aOzYHEdk9VJamPXfS6iJuZf7pp2Hl+F4hLpdPPTWAzR5DeOcvqMY2CuO0KAw3E16l0h3unoVCaHuVF4OT07fhwl1wUls+/J2Xkz34I5LH2BgdAiKpYbVi19jXlYL/7zh3/QNav+t5idnZKLVrkLAbqklfddyflo7j6zmaG6YcRcxzi28/kM6EwdH8/q8XTz/xtNoMn7g82Xz2FcvMa7fVHYV7GHcOTcwKgTmfP4U9riLuWXMFKr2zWHWypVcMOJyPn7nJ6b//WrMWen4BAWzO7OMsWPPw5E+j0dX/Mr4pGgKsjNISk5lwcKlpAwaQEtjHmMmPsPkPgldBeFpYacQ6jrvNB8q1KlCiJ9nCPEhgzHqjIcJc3XNVewv/RX1WUINgyKEus47p93VMiHUCaGuu65tMS5BoKMJCKGug4Q62WnDWpXF598+iaXfP7k8JQrQULDjMxbstXLFhTOJCfCjsWIXyzctptqh0FK9my1ZW4hOvISePnrQRTH6zAuIC/KmOP0LXpw3n0EDhrFtyywM8dfQL8DA3t0fss73WRZdfx41+SvYmJNJg03BqNO6ttypD2411btJz63lqqtfxLNsDQs3fMfeykyCYqeQGOyLUW/A2rSPRTuMPHDLQwyO8D+qcKbI9bzzn4upib6Lu6dOwlywnk2ZWbRIWqRDt2S4YpI7MXklMXLgYPzc9agedY+9+xSBybdwabKJJesWo3gmcfZZk4kN9BZCnWvrq/Co6+gL4sno739C3VUk+Pjx1jNTaBj0OrefPxovvdQaO6xwDY98OJuJ057nogFhJ8MM0eZpTECRndisTaz58XFmr9/L1Ivvxy9nIZu8z2ZaZC03f5DHN68/RmBzMV/Nv4W10gVMivEHzxiG9e+Pt7Oc2fOfwBo/nav69GLhopf5Yd8+BsYMZcOGDYy74iUuHxrB6m8eYXaBB8/d/DTS/k95dOUOLjyjL7m7txERncjcpRu48LzrSQ0yIJsSOHNAksgp2onWpRDqOtFkHGHKoUKdGqcuxDeSq0c9SXRQ8m8JyZyynVV7v+O7ra+64gxqNEKo67wz2n0tE0KdEOq67+oWIxMEOpaAVNlYKLK+HspcTcig0bB7/zZefPdRqhpK0GoMrhpqAO2cxioWvrCa1L7Djm+m1PhxzeUs+PY5lpab8dTbMRr90VvqcAuZyDXnTyXI3UBdxX525eyg3iFjrtjJ2j2riEu5jtgAd3TaEJLih+DI+pyPVs1lty2Za4Yk88uaJVxwzduMi/Ri5Q/X8c/yq9hw8zQ0jjqqm2pdGfx+yyUrSdQV7+DL7+Zw7sy3iZJKKK0o4Oc184kbcwdjeka54tw1123jtbdXc8Xd/2JkTNBRQxcrch3vvKx61LUKdc7qfewvycHC0TzrnBjdE+gbE4+nUdsq1L33NFEDH+TW8YORbbVs3jifdZlaZlx7M5H603P7n/CoO77TqivUPkyo8wvgg2enUZz8AndPG4+PQesSsctylvHQJ/OZNv15pvUL6QrDEjZ2GQIyDRV7+WLFPHKLa0noO4pgey5frVvN1HE3kJn+HvUh/+CRqcPZveFD5iycRbUpBA8piZH9IqkzRTNzxDAWfPU4ltjpXJuawuqVr/D1zjTO7D2K5Ut+ZeKMe5HLVlCp7cuUUefQ09eNvC2f81VNBFNCcvlu3Qr6p17M+kWPQ+wkDOa9eETdzAMXTjuOsPhdBniXNVQIdZ136g4V6tQtrrJi48z4KVx+5j/wdg9Azdi7t/BX5qx+jJqmUrTa1udW4VHXeee0u1omhDoh1HXXtS3GJQh0NAHpreX3CKHuCOoarYbS4jJWLlqPzWp1Be49UaFOzapakr6Ypfk5yM1lLNyxmuCQkaTGhGDUehIdM54z4nqSv/cHthfsJStjCYsLG3CX6zFo/YmIn0hqdCQRPUYwOMKH/bs+5dOtdm4+J5G538wmqP8FxPsayN7zDYuMt/L1386hoWQDK/avx+JU1ceDg5Rors0kbX8tV137JsNjQ2ksXMkr8x6jOWwYSUEBroQR1qa9LFxv5B/3PMvwYwp1Zt5/ZTqVPe/grqmT8DreGHWqUDfgAW6bMAS9VoPsaKGuoQl330BMh2SB7eiT4lT2J4S6U0n/5PR9eIy6vqT/8i/+tT6fGVP+ztDYMBRLHcsXvsDCMncevf1FevuJra8nZyZO11YVzLW5LN78PY2KB/5GB7u2fMlPlfHcM/EMZHsTOjdPhqRciVy+jo3rP+OrTBNTRo8kMUDPe4tXM2PSleTu+AziJzNz2HD2rnyVb3JK+duI83nrla+4+JG7CGyyIenKmf/jN0y95Gl6aAvZmF+Mp7WOqvpyKuxRTBvVn/raQrKrraQkn0VMgNfpOimdctxCqOuU0+Iy6shkEqow52ZwZ1rq3YztcykVDYXMX/8MuwvXodOafhuIEOo675x2V8uEUCeEuu66tsW4BIGOJiBllu0QQt2RQp1Gw76MXbwx53lqG8vRavQnLtRZG9jwxTg+ctzBjcOTMaranwSKvZFVq96iKWgm906biqOpiE0bPuHTdTvwD+yBLKcRYOhDRnE5o8bfyLmpQwjz8aJk/3xe+yGNq6+8GzdrAQ02NROY6jenRe8VR+9ALypLdpFdWYHTFQ2vtaix3xoq9rFywzKmXf0eI1ShLn8Fr37+b7z6XMbg0DBkCSyN+/nk2yxuvvsJhkd5U168h7za2kOyvqrbWR1889ldkPIMj108Fe/jilGXxqPvPUXUgAd/E+o6evF3xv6EUNcZZ+XEbDoymYSjqYRvv3mMn9N3Y9FqULclauxO6h3h3DDjFSYNiEN1tBNFEGgfAgq2ljryyvOoLd/BglWfUWz1pqfSTIU+hAmjLiQ+2IceISns3fApe/ZvYUdDJGcNSmZAyii8pRoMWg0/LfwEt5TLuDDOyNzZM6iKeZ6r+jh59vmvuf7Fl/AtXsrHi+eg7zmF6yZcQu2Oj5mXWYdvyzaM8TeQGtCDcPdc5v/0LGmWSC6Z/iKX9I9vnyGKVtqFgBDq2gXjSWnkd1lf1V0aip0Q72hmjHiE9LINLE6bjSxrf/u4rBoihLqTMh2i0T8gIIQ6IdSJE0QQEATah4CIUXcMjtv2bOSJ/95KZX0RWo0arPfEtr4q1gbWzxvHvVm9uKxfb9x0rS5uit3M5rSlhA54nH9dPJEfPr+XpaUGLp/+MAP1u3n363c5a/r79Kr5gNcXLcMZcjE3j4jjix8fIk2ZwiXJBvIb6tC6vP4kZNkOWjdGj7gNbdF3rMzah02NGXfIOJtqM9md0citt81iVFw4DblL+L85D9AQcAbJIUGumi0NGXz7qzv/fvglRkS5sW/r5yzLyUTRHNqWhMkURnLvCQyNTziubJXN1du5841/ED34Sf458QyXR50ouAJAi6yv3WslHCnUqRvRnbZmcvdvYEvBdnAfwBkJiWSsfYw7l1Tx3C2vc8HAWI5D9+5ewMRo2pmAgqWpiDWrZvPzth34Rk3isnMup1dAEwu/eZb1xY34hF7ADRdNoCZvCyX71/Hqdk9ee/A+oj0t7Nv6LYu2fEdxYxOXXzqHKPM6Xv92BZde/wyBNUt4+KkFjLo8ln3p6Yyc8CjnDeyNtS6f92c/hVv/K4kt+z/m5MUyrHdPCrc/g6nfVwySF7BPmcDfr7jikM9I7Txs0dxxExBC3XEj67ADjhTqXM+P6v8UJ77uQVjtLbTYm11xiA8tQqjrsCkSHR0gIIQ6IdSJk0EQEATah4AQ6o7BcevuDTzx+m1UtZNQh+ygrjKT7OoKbPbDs6fqDG4EBsTTM9CboqJMDL7RBHt54GyppqSmCt/AaLyNRqwNZRTXmwlwk8gqy8c/KA5tczHFDeb/JV9QFBSNjtiYEYR6HT0Lq8PWTElJET7BUXi7mXBaqimuLME3uBc+JvdWAdHRQH5BKd6hMfi7t8Y6ac/itJvJK8nD6BlBuL+3K9OrKAeFutnoNHqRTKKbLAhVqPtk0xOMjZ9JQkjqMUdlN5ex5PuHKQm+kytGDcDDIM6JbrIETvEwFOyWOnJydtKoC6F3dBKeBy/pspXK0r1kVWlJ6ZeChwas9YVk1yjERkVi0jooK9xDTkUlAWGJxIRGINkaqWuQCAz0wt5SSX5pDVqDDY17CBEBIehQsNsaKawswycwGs+WbPaXlGJ24MokHhXVFz/ZTIPdncAgf5FM4hSvjkO7V4W6pelz0EhaJibf2IksE6YcTag7SMXptLueATWa3z/zqUJdSsIQJibfRGLIUNfciiIInEwCQqgTQt3JXF+ibUHgdCIghLqOEupOp1UlxvqXCagedSsyP0JCYlzCNWiP8uD9lxsXB54SAk2WGuZteYpxCVcRHzzoD22wNddixYSHmxunaZjGUzJHolNBQBAAl0ddxkegSEzqc5NA0okIrNv/I3PWPIosq2FO2rYDQRVM1D8piUM4N0kV6oYIoa4TzWl3NUUIdUKo665rW4xLEOhoApKsqDlB1U2Tf817w/Ug4Ipcprrht7ajOkep//LXWuxoBEfvr9096jrHsIQVnZyAU7azpfAXsiq3cG7SzQR6hHdyi4V5f0TA7rSyq3g1W4p+5PzkOwn3jRPABAFBQBDolAQcTjvbihaRXr6Jc3pfR7B3zy7+JNcpMf8lo1SPug9XPeLK7iq1ccO46mXn6+1P7+iBTEy6mQjfxN9tjf1LxoiDBIE/ICCEOiHUiRNEEBAE2oeAtGv1a0qh1xhGJfXBw3h4LLM/68Jpa2TvrsXsKi3CLsvojIH0TzgTpWYbe22hDI9PwM/DG43TjNnuQKMxoZesWJy4vEVkRUbSGPF098WkP9C37KDRXIdTMuDp7olO07Yvh39m6/H+Xgh1x0tM1G8PAuoDTo25hKUZs7E6Wojy7ftbMpP2aF+00YEEFIUGaw1ZNRtJ7XEew6KnoNO2/zbyDhyR6EoQEAS6OYG6lgp+3vsmLXYL0X4p6LWtMXpFOXUENEjkV+9nT/EaFOTWTGRtKGoIDR8fX87oOZ3Bkedi0nu04ShRRRA4MQJCqPtjfj179qSoqAiHw/G/sEUnhlwcLQgIAt2UgPTZc37KDz0+4NXpFxDgoW/j7b+Vht1cytdfPc3eqmbSC9YRl3ovYyID2bLtU9IDkpgUNYjkiAQKt8xlr+wPTl8G9PKlqqqQ3JICekQmkF5o5rxJt3BmjD/Ym6nIWc07iz6hzhTLpROuZUh0DLpToNUJoa6brvguMCx1a0u1uYS95WupbSlqFbS7gN3CxN8TMOq8iPDpQ3zQINwMXgKRICAICAKdmoCiyFSbS9lfvpHq5jxkxdGp7T1djNNq9Ohcic3a+jSgoNUYCPaMJTF4KO4Gz+M49nShKsZ5MggIoU4IdSdjXYk2BYHTkYC04CUf5Re/l7hn0jQSQgOOK6i/vbmM7797mTwllNgwT/Iyt7C1uJZeyTO4buxAJMWIv97MvLfvpDJiFE21Ti6dcgVNW1/h8xxfrhgeyyvL9vHANY+Q4tfEtnUf8vHqVQQlTyKQInYWlzF62ANMH5aCl9FERyYGFULd6Xg6dJ4xqw86DtmGrKgbyl2700XpggTUAABqnEERa7ALTp4wWRA4TQm03n/sro9E4v7TmRZBW0W6VpvV2mqCCZ2IdduZJrHb2yKEOiHUdftFLgYoCHQQAWnBS57K+3VTGBOTQkrf4ST0SiHSzwdJbiA3K41Ki711n+qhxRWXzo2ePSLZsOjf7CitJaP0ByKTH+OC1MFYizaxu74FD88EzhmYwur5l7GoJR43bRDjUqJJ32fhzFEDqCjKxi18BCOjJF55fxI/5jQSEjmTBy+/Gh9LPt/++CQ/FpYTnHAdL1/xMKkxIWg7KMK6EOo6aAWKbgQBQUAQEAQEAUFAEBAEBAFBoMsTEEKdEOq6/CIWAxAEOgkBacFLfsrK8A95aEwf9mVtYn9+GT3ihjOkdyw1+Tspa7apn+SOEOpkZMWDhLhEdi5/hU2lLdQ1ZBHT72ISAnzBaaWxoQiP0DGMSQzks7fupSZ6OI0lpXg68yj2HsmEpCiw1VMlB5MaHo5ddmDU67HZzVgcNhQ0aHXueBg9kW11eAYmEhsWjE4IdZ1k6QgzBAFBQBAQBAQBQUAQEAQEAUFAEGglIIQ6IdSJc0EQEATah4BLqFsR9iGPTT0Pf5NCVWkam7PyiIwfT79wH9cF9+hFcglyO5c9xCPLdnL2GdMJclOQZQVJoyF903OYo57lnxeO5Kf3ZrDDZyy9g6MIbVrPO5kOJvVPRVe3kW+KevLSzLvRNu6muKkRp9OGotGi1+qwO2xIGgO+XomkJCbj42Zsc3SOE8UjPOpOlKA4XhAQBAQBQUAQEAQEAUFAEBAEThcCQqgTQt3pstbFOAWBk03ggFA3i8emnu9KJoEiuzLRoNGh/5OgcLLDyt4Vj3L/kt1cPGYGoR6ghr3XShI7VtxPZfjzPDLjIvKWPsyX6T70inbDqAvEXPo9e7TjGehYwjbnWB6eeQOOmn3kFm3ns3lPEzThZc6Jlvn+x39T0eNm7ho3mT49o3A3Hl+yixOBJ4S6E6EnjhUEBAFBQBAQBAQBQUAQEAQEgdOJgBDqhFB3Oq13MVZB4GQSkL55yU9ZHvoBT6hCnafhuDzWFNlOVcFGvl82iy82fE5032vwa95EnpLIuYPOxktyJzQyGvOG21jInYwy7STdnsx5fZx8ubSY884KYs6qXK6d+ThDw/TsW/M2/1xr5cGpE6F8A1/99Cof2BL59JZ3mNw3EoNWDc3eMUUIdR3DWfTyewLqQ47daaW0IQeztf6AV2tHrXwxI+1HQEGvNRDo1QM/txAk6RSkr26/wYiWBAFB4DQhoN6DFOQ/2FFxmoDoRsN0OJzk5xdRU1cH0gk+TygKRqORhF6xuLu7IZ1oe92IsxiK2Pr6Z2ugZ8+eFBUVuZxixLnzZ7TE7wWB05uA9Musc5RVgffz4ISx+Lofn8eauS6HdRu/YXdhKYaQVKacMZ7Gfe/y1JZcxiX2w1qTT4PDhLMojXEz3iGy4Ue+zdQzdVgqi5d/RNKwmyj4+UnsZz5EspzG0vXfk6aJYmRgAKFRvQgJCKB6/yv8XDeDxy+/lB4+JiHUnd7rtduPXn1BMtvq2Fa4iOzq7chKi+uFqTV/myhdh0BryAANBoxabwZHTSIuKFVkf+06EygsFQROSwJO2UF5Yx6ZlZtpstbhlJ2nJYfuNGhJkdA0hKO3BRDg79sueeQbG81oNRpSB/TDw8O9O+ESYzlBAsKj7o8BCqHuBBeYOFwQOI0ISOb6AsWq8cPb3eO4M6o67Gaqa0qwKh4EBYXippGw2xqpbqzBrn4p0Oox6d1wOrX4+PijczbQYJXxdvekqbkBg8kTpaUWm9YTyVaL2elEI6lfcb0J9A/EoAXZVk91ox1vHz8MOm2HyRXCo+40Ogs60VDVl6Q9pWvZXryIM3pOJdQ7Fo3wxOpEM9R2U9TwnlaHme1FS6hoymFS0u0EevZoewOipiAgCAgCHUhAUWTKGnJYkTkXN4MPPqZANJKuAy0QXbU/AYWt+YvQVCQyY8LNhAQHtksXqofe0pVrGJjSh5DgoHZpUzTSPQgIoU4Idd1jJYtRCAKnnoCkHDtbxKm37hRa0J2EOnWKW5oqqG6yERgUjptOexSyCvVVOdTgT89APzSKg/raWiQPf7yNR6t/YpMjO5opKi/G4BFKsI8nGrF1wgXU4bSxMmseTqeV8YnXodMaTgy0OPqUElDPvbqWcr7Y9hzjE64hLnjgKbVHdC4InHwCCg6HhdLKEtAHEhnoc2JdynYaawsoaYGeYb0wtf/t6MTs60ZHq/efTfk/UlyfxblJN+Bu8Oqwj6PdCGOnGoqsOHl/7QPYisOYOfF2l0ddexRZUVi+ah19kxIIDQlujyZFG92EQIcIder2fMXpiquObEdx2kCxdnKCrTstYuIHUJi3F7vNKkKidPIZOz3Nk0BjciXzRKNF0uhAOIycsqUghLpjoG9/oU6msWo3G9Oq6D90BEEeBuSGLDbt3kGPPpOJ8HF3PRDL9ib2pK+n3jSAMyI0/LpjEcWNFleCDlmWCAhO5cw+ydhqdrG9yELfSB/S9q6g0m5CpybilW3IQWO5pH8i1vps1mZUMWLQUEq2vcFnm7OZMfN5Qh1Z7C5sJKn3ELy0LaRt+5nsuir275zPXkYyKSWOIKMbW7euJG7cQ0wfGINia6DJZgXlkC2YkhrqRIfR4IGbwXBcsRZaanfz1AfPEzXgbm44qxcZ2ek0yR6EhfYkMsD7uNo6ZWfPSejY7rSxPGM2Oo2eMfFXia2SJ4FxRzdpttUzd9O/GBd/JQkhqa64TzZzFdnZW9hZkg2mKFITzyQ62B+9VnvC4YM6enyivy5CQHHS0tJAs93WKr5o9Hi5+6GYS9i4ayXFTc2u+8zBoiDh5Z3MyP6peJl02KxmbLIWD5P6AKc5poCjru/6onU8/dHLhAx+iBuGR7u27ms0ejzcfZBs9ezdv4b0ygIcihG9DdxiCwAAIABJREFURgLFRovTAXIkY0acSw8vHZbmRqyyE8XZRPrq13khrZ7nbnueUL2CIulwM/lidNSzY+9S0qtq0Wk0qF6srhFIargAX1IHnkN0oC8iOmTb1qjNYWF55scujpOSb2rbQaJWpyageum/s+Yu7MU92leokxWWr15L36REIdR16hXQ8ca1u1CnXpAOFvUeJclo9Xr0ftFo3f3Qegah8/BDa/Ts+MH+hR7VRI12p3qPEkUQ6IQEFAWHuQZncy3OlnrsdYU4msqRHa6Hq1ZxXP1bONh0yOQJoa6DhDrZaSE//TP+75VN3PKPuzDZC6kr+pUvf/mI5In/R9+wHvSKHoI1ZwEf/7KUoRPvwr9+NZ+smo8pfDJnDxyEUdHg7ZNAT88qVm+czeebq7ls1BC+/flD+pzzKEOCTWxb+yKvyfex9/Zp1OYu5P7ZbzL20g8Z6/iOTzdmcc1Vj5Lz7YUsqB3HPTPvJ5xsVm1bQlFjPfvTPiJTfw6pvvXsyiwgMGYI5w6/jnH9k6jN/pkVWVk4pYMvaGpiD5nC/N1EpNzM5SOG4X5UT72jA26pSePR954kPOV+bh7Xl8xtiymo0xEW24/Biep2z9MzJlurUDcHnUYnhLoOuQSe/E5ahbonGBc/0yXUORqL+fqbR1mdV021JCEpFjxNSUyacANTBia7BAdRBIH2JCA7LFTkruGXbWtp1ntgkuxYW6yMHPcESd51pOfvpLLFerhQp4CbRzR9YuJw0zrI3L2ELVm7CY7tT3zUUEJ9/DCq13xFxiZLrmRPalGTTG1a+ghvr1lLRNzZxPl5UledS3azhltmvERvTycFRWlsXHk7c/YlcvWkqdhyZ/PC8u2EBozgiTtfZ5Cfma8/eZTCgD6EmGQa60ooMluJDo/HJFkpKMjljHNeZXJYA69/eBX5/ldy0aDY38TDxtLtfP79l1x455ec36cXYvNm21aTKtQtS5/j+gA3MfmGth0kanVqAq1C3d3Yi8P/UKiTnXasdhmD0YAGGbvN7gpfoz/Gc50shLpOPe+n0rj2FeoUFNmBxuSNwbcHer8eGP3CcQvsic7kgaTRotHp0bg8f4S79amcd9F39yEgOx2ofxTZidNhx26uxVKZj622GFttEY4GVbiztXqEnqbv6x0120Ko6xChTqG++Fc+XvICSzfXMeW8e0gM1mCt2M6Pa+eSOPJJegUFEh+fSuayp6jwPouR8WFs2vIdG7KziEq4kgtGDsJDo0Wn80TXuItf1n3Cwv12pg3tw7K1Cxk5/TlGhHuwYcldvFR/G6tunorckM6P3z7ESxmpPDZSy6+ZBYwfNJTPvn6VkZfOZvrQgejqdvBrdhpFldl8t+gDspzRTB89hVA3HSaPEHr492dQSh9MziYaWiyHnZDqC9m892ZQH/cgD0w7Dy9D21+HWmp38dCbt1Fm6M2UYdcxMj4CH88AjAbVQ09/mnvUCaGuoy6AHdHP4UJdP9IXPsLDGyu5btp9DIkJRbHWs+znF1ha68fD1z5NnJ+pI8wSfZw2BBSaazP46LULSAt/kH9MPx93yUlzVTZSyAjCTc3UqHFlD3FaUNGosTG1ehM+Hv4YNWBpriY3dzWZZRVkVdYzbOi1DI8PwVaVydoSheHJibjpJFrKt/L8nAfoPeo5xib2BKeVjctf4INtJTz36Gf083YDxUFZ+pd8unwV+RYLkrUMnx6XcuHoCcSHheKo2cOb7z2DR59z8JfyqbN7opfAJjfh5eVH8eZlREx+n7/FWXln7kw0/d7j9nF9f5vRmtxVvPzmfQy77ksmJ8ciXt/attiFUNc2Tl2pVluEOsVuoSx3C2v2NzBoyFACdfVs2rELt+A4BiUn46H//ccjIdR1pVXQsba2m1Dn8tyRMYYmYQpLwi04Bnf/MAxu3ujdPNDqDEiqR7ak7kSQTtv3ho6dXdHb6UBAkVszvyPLyIqMw2bB3tyE1VxDc1UxlvJMmgt3ugQ7SYRoOqlLQgh1HSTUOW1msjMW8vrb7zHiiqcY3Msbe8Fq3v/sDVIvfY8RsQlEBPvTXFfA1vVf8MXO9fRwi6DZqsGpH0hi5Kes220gNHY6d110Jc7yn3jly0VMOHMAC396hFxTEqHuMhUV+6mN/5Cfr5lIzrYneWfNt1Q01aM1BCGp8RzkJqwON/y8L+X2GXcQJuezeMXnbMnfQ6m1FK3Oia9vIp4aA832Adx65a30DTv6VlRFruOd/1xCTfRd3D11Ekp9LnmVxdjU16IjHeIUGYNbFL169MRdr0EV6h579ykCk29lcmghr/68nEkTbmX8oIH4mYynrUAvPOpO6vXulDR+mFDnF8j7/3cB5f3+w53TxuOt7lfHSUXuSu6bO5fpF/6bi1JEvJ9TMlHdtlOFxqqdvPrkUJaG3M8Ll16Ov5ueiB5JuOGkMnsFs358iAyb0SWGtRYNkt0NmxTD1Zc+zphe4a07HlQxT7FTW1eDzuSLl0lm5+KX+efihbz26Bp66bL56N0ryev5PPdPGYOPUYvDXMb8OTfxfWUKHzz8BHpLOdnlBThRaMhdw3+/fwhb6AzumHIH0X7uaLRGgnwikGQ7zfVFNLbYKdzyFk/usfH2va/RwyihVe9lBh9Mzfm8O3cmJQE3MH1wossTSLWzrmgrX/04l8k3fskkIdS1eWULoa7NqLpMxT8T6tQPrkW7l7Fw224ig/pSWLQKi+SHj0cItsqv8RvyIheckYDJda/6XxFCXZdZAh1uaHsIdWr8OUnS4t13Im6h8Ri9A/EJjUavetFJkiuEiPq3KIKAIHDyCaiPfurZpjidWJpqqS/Lw9pQSWPmeiyFm5F0auZvcT6ejJmQnLLziO/oJ6ObrtWmutS27dnIv16/g8r6QrQao2sAsiyT01jFwhdWk9p3WNsHpcjUFm9k0YZP+HLlPiacfSMtWW/zY00SM4clsn3LxxQaLueD+x/Ekv8D73+9lMSUaH5dvxlToDc11cFcf9MdFCy7hYY+zzIpoIxf1n3ET5nVTOx3Jlt3reOCq9/j7ChPln9/NQ+VX8O6my9E62yg1tyAGvT3YFFvbDXFm/lswRwmznwD76r1ZFc3sTVtIUnj7mFcbLT6qoO5egsvv7mMGff8i1GxwUc9/VxC3cuXUBNzF3dNnYQ5fyWr92yjSdL/vr7iwM1nKOcMHY6/u56W2jQee+9pogb+nVvHq9sBc/lp6TwqlCQunX4xgQe2UbUdcveoKYS67jGPh47if0LdVST4+PH2c1OoSXmNO6eMwVuvxtVyUpG/msc++oiJ055nev/Q7gdBjOiUEnBam8je+TXvL3ufRbmq91wNwwbew30X3kHfMM+jXK9ldq56jTdXrufGW95iSOjvszrKzhYKdn/N6589R9jZX3DbUG+WLXyb7dI47r1wAl4uB2snOdtm8a95rxB3zrv8c8Io6kq2sWr3ehptMhpnLRu2LMcjcgwJpgp+XjsfY++beO66J4j1N/D9J/eznXOZ7LeWvy9bxzWT7yTAYMfoPZAJA5Nx1uTw3tyZbHUOZ1ScmlG59XGypTaddds2MeOWL5mYJDzq2rr4hFDXVlJdp96fCXVOWx1LvnuKj3flMSCiNzszF5DhCGZsz77YqtdT63sTL9x8HSGexsOuE0Ko6zproKMtPSGhThXhJNB5BuDdewyeEX3xDAjDzSdQJF7o6IkU/QkCxyDgtNtoqimlpa6C+v1rMOdtQfXMPm29bE7iSpF2FW4QQt0RgDUaDfsyd/H+3Feob6pCo2Y8OSGhTqG5rpCdafN557ta/vnwY/hVLOO/vyxm/MipbFr7FqaEW7l9wpn8/M0/+XLjfqJigtCYziLAtJPa4gYShz+Ikv0slj6PMb2XBzu2zuXL/QbuGBfBfz95lh7D/86wEDe2bHyBLwyPsf6mqTRX7WNXQQ72Q2OWShL1ldtYvTmNy699m+GxITQWrOSVT59BG3sRZ0SGuV51zLVpfLqkjHvufpLhMUHHEOqaeO8/06mKvtMl1Hnpj2frqxqj7mmiBjzAbROGoNdKOCyNlFbW4tcjCk/Vnf00LEKo636TfphHXXAS27++hxf3Ornt0scYFBOCYqlhzaLX+CyrhQdu+jd9A926HwQxolNKQI0z4lAkGmoLqW6soyrzJx6e9QxX3raFq0cnoT/COntjLnM+vIo0t4t49IpbCPE6fDu2LNsoyPiOud+/jyHhQW6cNA5vyUxpVQN+QRF4uhp0Ule2k3feuJ6cwGncP+MeEoIO9852NmXy2qwX8Ui8jNCqL9li7sn0STeSEhGIVqlm1qz7yfS8iAu81vLE2v08fPUzhBpldMZg4iJCcdZku7a+0vdt7hjf/7f7VHXuMl566+8MV7e+CqGuzWtPCHVtRtVlKv6ZUOew1bB+82YMOi/0egd2owG50Y6bOygGb2ozSkgZO5pAr9aEZweLEOq6zBLocENPSKhDRh8QjXfv0XhFJOMVFIHBrWskiehw0KJDQeAUElCfK1saa2isKKAhewtNWeuRLQ0iQ2w7z4n01MJzhFB3BFStVkt1aTObl2fhsP3Pvfove9S1ynxU5C7g6VdWc9Mjz5DsXs33Xz7Aq1vTiIm9jAeuvIfkQA/Sd/zA3B8Xkzx2KgMDfVi7+ROsTQoNgRcR3TCL5qSHuOrMfpTv+4TXf07n2hm3om3Kw6r1waSRsNrqsbjHMzgiEJulnkaL5XB3VI1EVeEyPvl6HpNmzmJEbCgNect57atXiR75EJOTYlzbmxoq1vHSu6uYcefjjIz2x2ZpdGULPNS1VVHMfPj6JTTEP8KD08//i0Ldg9w2YTBqFiRRQAh13W8VHB6jbhD2+hzeeO8aNtf7khQ1ALk5h/X7f8TicS7P3v4OI2L9ux8EMaJTSECmrnQP328pYfSZKXhrHWRs/Jj7vnqeJ+4vYEKy329ZUWXZjtVcwPfz7+SzAm/u+NsLnJUQ5fqQ0locWBrLSd/9E5+v+5Lo/g9y8Ygx+LkbDn+JtzeTn72WD774Oxu15/N/l9/JkOhgdEd4Sjubsnj1gxcw9Z7J2XFumPyT6OHrgVYjU5X+M4+/eS/mqMkMM1byc50nbzzwHlGH6Nj2A0KdOfYprh89AB3q/VqhMncF73z0b8bcIIS641l4Qqg7Hlpdo27bhLqteGt90BoVbAYtSoMNL3cNNqMH1RnFJI89iyAh1HWNCe8EVv5loc7DDZ2HP/5DLsYrLA7vkGhXnFSxw7UTTKowQRA4CgH1XLe1NFJXlEFdxnoa9yxC0ok42+25WCSnfGQI6fZsvmu2JaFh6+71PPnGXVTWF6HVGFqltr+69RWwmytY/+u7fLRE4c7rzmP7L8+yxRJN/x5hVDc2Eh03gmEpw/G37ea1j79j3N/uY6Apg9k/vUXq2Ffo2bKTLxY+RPDoT5ge58aade/wQ4YXMydOxst0MBOruvNHcWlpAf7R5G/9kJ/2pGGTDvV0k2huyqWwxpN7b36T4bFhNOYt57m595CvSSDW11991cHavIOf8pKY9feXOSPcwLbV7/Dt3v0oamal36ZVgyT5MCD1YiYPTj3OrK87eeC9R4ka+Cj3uTzqhFCnYhVCXde8ZvyR1UdmfVXPUau5jM1rv2VZxjY0HgMYM6A/2b/+H/NzY3j0pqcY3isIcUp0v7VwakakYK7NYMHXr7OruUWNPodWH8f0i25lULCPa7uo3FzN7oJM8nd/w4K9O+kRcj5/u+haEgO9WuOSyHYqK/NI37ecZet+xhGcxPnj/86wWL/fDclak8nCVR+wZGcZA0bcxLVnj/idx5764aqproiMnA18s3gefca9yKVDEnHpeIpCfeku3n5jMvoxczg/0sFX3z7FhkYf7rj8WXq4OZDRERicTLCzmHfn3shP5V4MCA9Go/qDSxKWxkz25Du4886PODc5VmR9bePCE0JdG0F1oWptEerWbd6Ot94XnUnGqtciN9jx9tBgN3hQlV5AnzFCqOtCU37KTf1LQt3zz+Pl60vA0EvxDO+Nf0QiWkNr2CFRBAFBoPMSUL29LA011JflULNzEc25G5BU3UQo7O0yaSKZxDEwbtu9gSdev719YtSpi7g2n/XpaXj4JRPh1kJRrY2ExL74GfVYmivZlZGG7N2fAaESWbkFBEQnEaA1k11UTGBYPA1Zi8h3hNMnsR8+zbmsyc4iICgBk7WIvLpGpAPymaJmSdJoSe4zmUhvjStby+FFwmIuJTuvnLDoZNdXUntTGRkFWXiF9aOHjxoQEqwtlaRnlhDeqy+h3iZk2XmUttTzUOvKDni8QV0dllp2Z+3Fwy+BXmGBaE7Tra5HLj8h1LXLda1TNfI7oe4365QD55R6Dik0VaXzxfx/0NL7Ca4ZPQiP1u8DoggC7UJAkR04D9wPJEmHVnPw44iCsz6Pxbu2gsaLqIi+JEWGoznkIUt2WsjJ2UpWZTNxMQOJCfVDKx09l2pz0QZ+LXMQ32sg4b4eh7Xzv4E4qSlOY31OHt5eIfSJH0zAwQWvyDTW5pNWXEWfxFR8DQrNDSXs2ptGndPmCiLuRE9s3DgS/Jxk5e7C4RlPfKif6zxSi6WhhPTcIkJi+xPu6/Wbx2C7gOzGjQihrvtNbluEurUbf8WgeKAxyNgMGpRGO55uGmwGD+rzKhk0YazwqOt+S+OkjegvCXUvPEvogEn49xmDX2SS2O560mZHNCwItD8BRZZpqi2jvjiTmk1fYKstQjoQNqz9ezu9WhRC3THme6tLqLuNKpdH3Qkmk3A5CSioIpoktb4ctYa8VtOJt/6kxvtQf1B/e7S9yC4BzpV+XIOkqOmS1S0+am31vw9kYzlkLBpXuvJjDE615cCvDmZPOljzUMFNtdnV50k4J1xtH2LDSeiiSzYphLouOW1/aPSxhbojD5Mx11dg0Xjh66Fu/+t+LMSIOikBVfxyiXiSS1g78sNL6/Vavdcc/feHjkq9V7luHZpDPL2PMmy1Xut9TG3z8MXuul+quWcPuYmp8VAO3jVc90/XRyL1vnrgbnpo3db0tK3Za0/GDayTTuOJmqUKdUvT56CRdExMvuFEmxPHdwICfybUOe2NbN+0iqLSKmxaJ3a9hGJ24m6UsOndMDnDGD1hJL5Hbm+XFZavXkvfpERCQ0Sm8k4w1Z3GhL8i1P3nrfeJGHUlQQlD8fAL6TRjEYYIAoJA2wjITgc1Bfuoy9hAw96lqD8frxNP23o6vWoJoe4Y893eQt3ptazEaP8qAYfTzq/531PakMXkPrfjrhdBdP8qy85wnIxMVsV2VmR9xKSkW4nyS/oTs1oFipMjj3cGIsIGQUAQ6KwEVKFuRdY8nLLM5OQbO6uZwq7jIHCoUHfVxNvx9/c97GhVMLeZayitqcahfvVVi2sLuvp/BW/fSAK91Q9HhyveqhizbJUQ6o5jKk6bqscv1M3mg6UZhKeMwS8iAa3uyPRGpw26Tj9QdW7VBIXqZz2jRv1gJr6EdfpJ60ADHdYWyvatp273EixlGWJ9tAN7ydpcpzg0JkwGwzG2qLRDL3/2aqo4sbSYscutX/TVYjS6ozhtyFp33PUdfyEQQt3Jn3fRw+8JqA/NJfU5LM/8ED+3cKL8+v3O20Rw6zoEmqy17CpdQZRfMqPjZmDSe3Qd44WlgoAgcFoRcMh2dhQtJbNyi+t65ecWIuLMdPEVICtO5v76KM6ySM4eeDHhoe3j/dZisbBlexpDUwcQ4P/7WJVdHJsw/wQIHK9QN/vjT/h0t50ecf1x8wkSL/cnwP5kHqo6qiuSwjnxPhi0Er+k17t2dIkiCBxKoLY4i+p9a6jftVAN7i/gnCABaeN3tyi7fa/ikqFD8DLpDtvmqNjNlJVlUN7UguMgbEmDTudFaFgvgj301FXlUVxTidUpI2mN+HgF467YcLr5orGZ8fQJxdvN+IcXXpuljBWL51Hs0NDYWE549BAGRiWwZ8uX7PMcw7m9fAkPjMLeWEJFixl3g6+a7oAmmwW9RsLhdKI3BhMTEYOn4UDcHKeF0sJ9NGgD6RnaA5P++PaRCaHuBFeWOPwvE1C96orrM9hVspwmW+2BrV1/uTlx4CkkoNcaCfOOo0/oaHzdg06hJaJrQUAQEAT+mID6gl3bXMaqrE8x2+swqdnbxItYl1426vSV1GfQ1/dCNI3BOJ3OdhmP7JTpGRVBbHRP9PpDE5a1S/OikS5M4HiFuhfe/Yy1VZ6ERSWiMx6S1vtPGLgCMhwSRudo1dUADCfq9HWwD9V77GS7jbjEsAMX3f+FR+oci8EpK8QFmrh+VBjL9texPL3uqDxcgSdaIyf95pmrjuDQUBbHGtHB8bcX6+Phqc7zgYAZJ7xm/mjGfnNclg66Jh1e+6DNB205+NsTXccdsYpaE0tUU5n+KzWbvsTZUi8+9p0geOnrF/2UFeEf8q+p5+HvoT/spHPWpvPuJ/eQ4Z7KWbGJrngwtsZcPlm6jxnXPM1FfQNZ/vUTrKk0kdqvH0X5adQ1+RBsz8MSPxmpYieDht/MiISwPxTqLE3ZfPjuP8iQjZjri4hOupRkDzMZ1RWERvYn0NObXoEhLPnhcardRmCSa4ntOxpLznw+LAliRqyJTTk67rrhUVJCvXDYmsja8inPz32JSp8BXD/9X5yf2hvDcQR9EkLdCa4scfgJEVCTgFjsZpyyXbwnnRDJU3uwGnvLoDOh1/zxx4pTa6XoXRAQBASBVgLqvafRWkNh7R7MthrUrZOidGUCEjqNgWj/AbhJ/lht9nYRG9RkNJ6enuh0R08q05WJCdtPjMDxCnUXPTUfvXc4vqHRaDRtW0+qIKDTQLCbjmPlolMFj6oWJ1anGgv1r48pxEPrcgyqbGmNk3oCTbXJCH+T1rUNvc4qH3NsbWqonSupQl2Qh46EQBP7Ki3UtDjQHgH2IB9Pg4Zme6v9gW5amuwKDX8yHnW+PAwavPSSa94cB+Kvn8gwVFHM16Rx2VlrOfZHCnVsPkYtPiYNVc1OLI4TWzN/ZHOQuxabU6HeKh91PakM/UwaDBqJUrPTxUP9txYVSCcv6rnvsFmoLdxPxYYvsJbtBZFU4oRmTVrwkq/ys/dz3Hr2BfSNDEWj0fymejtr9vHuxw/QkjiTaSmpaBSw1u3lzTlfMWzGY1zaN5CF818mz9iXqWPOYN+2n9i6vwhfuQJrwmQ05TsZPOpWRiSEHvPipiBha87jo1lPUBeaSkqUgSXfv8IOSwS3TH2EM+Kj0Op98dGUM2vOM/hGz8DetIPhE66m8vvL+c79Xv4WVcdn2yu59foHCXDks2rVG7y2Npsp599HSssavlr3PUlj/8X0QSMIDfBD24YvLEKoO6F1JQ4WBAQBQUAQEAQEAUFAEBAEBIHTiEBbhTqj0UBgWE8uevEnekXH4+7b9m3ZqrCSHObOw+dF/0b2oGB36HbM15YW8Gtek2v31fEWVThSdcObR4bRP8qLlxcVkF7eciDh0vG21rb6Br3EfeMjqTbbeW1FCe6647e7bT0dX62DyQVvODOEIb18yalo5r+rSmi2OA8TE1VmcUEmLhocxPx1pTTLEreNDkOr03Dv1zl4636frOqgJXZZ4bx+gVzQP4D/Ls5nX4UF3V+Yt0NH1uKQuXdcBF5uWl5dVoT9CLHroPeah1HLw5OiCfDSsSm7gU83l2O1qwkg24+/ui7VUF5PTetFToWZOevLaDmiD9WrL8LfxH3jI/D30rNhfw0hviZWZNazNrP+hATn45vxv15bTSLRUFFA5c7F1O34Do3e/a83Jo5EWvCSjzLHOonzeg/Bz8tIYMR4Bkb3xNvkhly7j3fn3MxOXSyDo3shSQrWplyWrCnnkhte5bL+kWRt/YKPfnyZUt8RDOrZk56+vahMW0hdr8noKnczeOileDQtIt3shXq9OXTJK6gZpqIYmhjJ8s+eI1frRVNdDuG9LmZ4QjTlZZspt1gIDhzLqPhA5n98D/mGGNxkExEBHlRqQzmzZyQV1XvxjxxPSrCez358lY05e6n3HMiMEaPxtpexadO37LNCQvjZXHL+DaT2jHbtr/+jIoQ6cXYIAoKAICAICAKCgCAgCAgCgoAg0DYCbRXqTCYjFp0P/5i7gcjYPhjdvdrWgcvzFzyNGvqFurkSnagiz5SBwa53uwXbKlCDHcmywr6KFirMDleCLtUfSdVpDJrWrZlqUQU8VYtRf7bIius91amAGhpdo5FcbShaiRuHh5JR1szqrAY0KK52VBvUqEo2Wc0v3ppgwakoLu8ttY+DWz1VUdGqbqtU1AQMkqt9VX9yvRMfIQTp9ZJLWKpqsvOf5SXotRLq6+qh7alijkMGu5o13eVZKLnsVdt12a7BlfBB7UO10aGo45Jc/36s7aet21VbE0Wo9dV6aptq36qNqoffwAgPzukTwMqMWpLCPDCbbXyVVuuqc7CoYx0a480VQ4N5/qc8ChvsJIW6c+GAQD7bXEFhrdXFTj3moG0Heam2T+wbwPn9/Hl9SSE7y1sOjF1yzfGx3tpV5ioPdbzq36qfmv7AeC1OhbvH9MDLTcdLywpptqljO8DzQIsaDYxP9CUlwovv9lRzboIv6zLr2VrU5Kqrzu/BdaHarnJRWf6RiKfOkXqcapurP3XbtCThppN4fEosOZVmZq8vo8Emu+bm4Pw6nAp9Ij0Y08uH4loLA6O8KWuw8vm2Kqoa7V0iiYcsy5irS6nev5bKNe+hMR6ewKjNJ7mo6CIgLXjZT1kZ+iEPj+9HXukmsrNyqNWHM/bMi4jXFvH2R39HP+R+ZgweguqQ3FK1jWf++z6pVzzCFYMSsdcWsGD2FH4xTCHF14GBcAzlW2mMPw9tRRqDz7yKCN0WCq0+roV+aFEUJw5dOImhASyc9yAra6GHnzsREX3wNOiQrbVk7V9P/OinmJroy4cfPECz/1nozLk025ooM4YwLK4HlrpMSq19mTF+Is3mPNxp7uBDAAAgAElEQVQMgZht1ciyDScadBojfm7B1DaXEhycQmRg0J+q9EKoE2eIICAICAKCgCAgCAgCgoAgIAgIAm0jcDxCXXmLnn9/v4sevfqhP474dKolqtCjCiGqANb8/7e3PnleT9z1Gh7+IQ81b6yqgalCnOoNp3pMqWKIn4+R7LJmfNy0LvFnbXqdaxuiTidxXkoApbVWAr0Nrjp71XpGLamx3sQHuaGKUHtLzazNbuDMnl54uOnYV9TEsEQ/qhtsmIxa/Dz1NFsdbM1poLzB5rIxys/IoFgfjHoNu/Ib6OFvoqrBxu5i8+9C26hC3T3jIqhvdrC1sImewe40NtvZnN1ATXNrGAIPg0RqjDfBviZXjL7Sagtrs+pdQlqgj5EtOQ2MSPSjptGGXicR4muk3uxgS049dS2O34l1LpEO8HfTMiDaG38vAza7zJ6CBrKqLKhx/lTOvYNNjE7wo8GlCMrsK2wirazFJXcd1BtNJh03jAilX7gHv+Y0sCKrDodDYXKyH++sK8NLr+HMeF+XCBXibcDPy0C92c6O3AZKGm1M7hfoEuo+31Tumis1vnxmcRO7SppbRYsjlqA6J+E+BpfdlQ1WIoPcXbZU1NnYnNtAvcXBPWN64OOhZ1VmLZGB7jRbnezIa6C4zuZqz8ukYWSsNzHB7pS2OPHRwPrsevaUteDvoePMOF9yK1sI8zEQ7GukpMbiYqzG5j+a8KnapB43ONbH1a/689bsegpqLLjpNC6hrqi2xbW+VNYtViebsuqpaLIT4WtgRIIvW3MbyKmy4m3UMCjKExnJJUB6e+hZvqem3b392nZmt62Wev4311VQk72dsl+eRuMW2rYDRa2jEpAWvOSnrAibxWNTzyfAXUdLYwl7stPxCBtIpJLNi2/eTHnoYPqGBrkWtOpRt/LXWi678T9cMSgBc9UeXn/5BXpf/R8iq79l2eYcvBzlh219HZkY/ofKs2JvYvE3d/LOrjLGp56Nj1Fq/dphrWTj8ueJmvwTNw6N4dNZd1ASej4jYyKoyf6ZnwqNjE3pRVPZRvbW9+WRK6+jMH02aTUKblp3ZGcTdpeq7g5KEyavRM4+4zLCvP888K0Q6sQZIwgIAoKAICAICAKCgCAgCAgCgkDbCLRVqHMzmciotPPeymx6xA9Eq/3zd7NjWaAKdY9NisJNr+GJH/NRW1IFG9Wb6ZIhwZwR4+3KQKmKV0vS611eX24GLa8tKXTF/jIaNbx0YSzrMuuICXJjc14ja7LrufqMEJcoVlbT4qrv7WHg260VLk+7+P/H3lnA11Glffi5Lrlxd2mbSuru7kALxReHIrvI4rq7wLI4H4v7QqFI0VIKbal7U3dN07jbvclNcv1+nJME2tLSQkMF5vx+7KbJzJkz/3PuzJ1n3vf9xwQwf0cVfxuViNmgwWZ34fb4iAkzkplTy7srSyRo+udZKQQaNNTYXQRb9BJ6CUD49dbKn7mmtoC6hFAjXq+PeodHwpwdBXZeX1mCWavmwt6RDGwbIsek16kJCdCzYEcVZXUueiYHysi1O8YkY9KrcLp8uNweooKNLN1n5fMN5TI67uBoMDFfgUYNl/WNpntyIGU1jViMOgQWvOvLA2ia01mvGxwrgae1zonFrMOvUvHByhK2Fjf8mP4qwNSdI+JICDdRUtXAF1urMOg0XD84lss/2EtSoI5bRyYQZNLidHlwurwSOO4ssvPfJcWM7hjGRb0iaHD5cDg8mI0aqfvz3+ezq6zxZ0E24ly6xJi5aWSCBK9VVgcGvUZq9tryYlbst3HniHgJa0Uqa31D0xwU1zh5aWkRbq+fi3tF0jctmJpah1wzoRYDdU4f9808ICHgbSMTJGwT9fNcbi8hFj1LdlXJKLfDTS8EunD9EEH5wNhE0iJNVNc6CTDrqHV4eGtZMVX1Hh6elEqIWYNd1E90eWRqa+aBWt5bU0pGjJlrBsfx1opidhc3gdwr+0dL887cyga6pgTz3wUF1DZ6WjUt9/g+2ce/VWNtJTUFeyn68mbUAW2Of0dly58pcCioO8hMwu9zsi/zTZ6Y+TlnT36W7glBkmU3Vm3jlelfM/SKh7m0RxsKts3gkYV5PHjtPdTvm8aidYXoG3NxdJyETtSoG3wTgzvEHwPU1TP3y7/z9k4r5/QbS4DOAxojGkcxS+c+QcJZn3PTiIHsmnUfnzV2o0+AFn2IheJFN1PR+RVS679ml24wD15yI25rLiW5a3nlk8exjH6Ha5JszPj0Qera3syt4yeSGJVIgOHYDrAKqFM+LadSAeE95Pf7mh1fT/8CoqdSqzPl2F6Pn/LKSurq7K1SjlhvMJCcEIdW+9u/3J4p2injVBRQFDi5Cvj8XuX+c3Il/x2P1pTCV1ZeRW1t7Qk/4IkX6Xq9noT4GAx6/Qn39zueuNL1KVDguEGdycjmnFo+2VBGQvueJzTSXwR1vaMY0T6EVxYVsjinjmiThltGxP8M1D17Xhrvb6ggPkBDgYgk06i5YkAMC7ZXMm1LNXEBWq7uF0XvlCDeWl5MYoierQV2bh2ThNPt5ekFhRTZXNw9Io7YUAPPLSxkTLtgRnQK441lRWTm27moSxhT+kQzd1sVs44C6kTqa1SgjtcWF7GzysnVfaPolRzI8/PyJIC6bkgcq/dV87/1lQjjiSv6RDKiUzhvLS0iyqxlebaNu8YnywjCN1aUsKW4gask3Avmv4uLKKxqPOQzK6L+MmIFIIphxZ4a3ttURfcYE1MHxvDl5kp2FNdz9YAY2kaZeGVxITsrnXSIMHLHqAQJoF5eVEitU9Sqa0qRFWO9rF80T36bQ36dhwkdQ7h64KGgzqBV8/icXIrsHu4dnUBquJGn5+WRkRDIlf2iJQj7YEMlnaJN3D46ge931fDxujIZkXZwawF1ApZuza/lqaXFJAXpuWdUPLlVDp5bUsyDoxPommDhg1UlLMyp5ZxOYUzqFs47y4ootXvkWticV8e7GyrQadVM7hzKlX2jefr7fKrrPdw1OlGmrD47v4CiOjfXD4ymd2owz87JIavKeYihhhxPfAB3jE7kk3VlzNxZTacwAzeNSODbbZVyvfzrnFSZPvvmihI2FTdw2+AY2sSYeGZBIcnB+kNAnYiQuqJvNNGBOu5bVMwTo+J4bVmxrLXXiuXzTuizd6SdG2ursBZnU/Dp9WgsbVu9/z9Th6rPnwn1z495myfOO4dwi/7HsFJn6SZeef02ClKu4/4LryDGosHZUM2B7Lm8MO1bRlzxOJNSvMz84iFqYi7j/L4ZZC5/mRL60iM2gCqvh+3bFjJ49MMMbv/Lrq9uewmbt37DV0u/pcyfSK+MdOryVlCuCic5wozZEEdSeCqZq9/D0uNu2tfOYac3idGBS3lhXx+m9ork47W7mHrZP2hjqmHVkud5f7uKqRNGUFeWy8Yd89lf42DwmMeZOmqQdFA5VlNA3bEUUv7+eyng83mpbighu3ojDTKF290qYOf3Gq/S7y8rICprqFV61LUJOG16gWBP3DZM1B3xeAgPC6V71wz5sKQ0RQFFAUWBE1VAuL7WNJSSW72ZOme5dB5X2pmsgKhxZURVG0NjjR5VS62nY38NPvpJi8w3r5ew0BC6du6EyWg4kwVSxt7KCvwaUCdSAj/dVE5Ch97gF1Xefls7FqjrGmfm9pk5mESdMJ2KG4bG/QzU/d+UNPaWNpBf7eT7XdWM6xBClwQLLywppt7hlXXwOsaauW98EtnljczdXkWZ1cm9E1PYW9bAOyuKaXD7mdg5lHEZYRKoXNYnCrvbxzPfF8i6ZqIe22OTUyUYOlpEnQB1Ih3ysfmFBOnUDE8P4fxekby6IF9G641sHyIhoIiqElmoyeFGHj83VdbQW7Czmp3F9fzjnFT2lzXw0doyHB4fgWYt/xifJKPANuXUyvp7LU2kz47tEMrwDiG8uKiI0jqXrJsmUmHr3T50Og13jYqXqbgzNlTIqD4RFXhxzwiGdgjj6Tm5FNpcEtQJiN8vNZCL+kTz/LxccqxuRrUPPgTU3TYqgfzKRgnRRM2+C3tFMqFzOE/PySE5KoALe0by2sICNpc0kBis565xiWSVO3hhcSEWIeJBrQXUXTcsni82lLH6QC16rZqpg2MRzrN3zsrlkbGJRAbpeeL7fLweHx1iA+TfZ64rZVWeXcLAwEA9gcYmR9s2kSaigvQ8PS+f0lqXNHZYl1PLjE0VMpW6e6yZuycm8+aSQlbl1B0C6kRNvL8OjqFTvIUn5+ZTUeeSUDTCrJEuuEKff01KpbjGwburSrA6fIxpH8JZ3cJ5cn4h8RbtoRF1KiQ07BBjZndJPdvLGtic99vMUX7bJ+u37SUi6qzFBxRQ99vkO2Qv1fp5//RnBU3i7B7dsRi1P4G6im3MW7mbzgPHkRoVjFrlo7JwKyt3ZlLWYGHkkPNJ1FewftceUhLSKcxfT3Z1FR27TqFbuI+V6+ZS5DQwpO8UEkObcsaP1uoK17M6ax+1jT5i2vaja0I8uTtnsrmknoigcOz2CrT+AKpcXsaMuQxj2TLWlcHANpEsWL2Nfr36snXnSuLbDMfYmMWmrA3UEkhcYCBxif2ICVZjzZ7LWlsCU0aeT2zgsSNQFFDXCqtL6eJXKyC+4FTYC1hxYAZurwuLPlgWwVXamamAmDu3z8W+8g0E1fbi3EFXEB0d2Son43A4+fzr7xg/ZjiR4WGt0qfSiaKAosCfVwFx/6lqKGbJvvcQRa0thhDUKvFgpER1n8mrYnfpGnTlGVw4YipxscfvrPlL5+x0uli8fBW9unchKjLiTJZHGXsrK/CrQd3mchLa/36g7qI+UaSGGbn/m1wJvozNoM74Q4rkS82pr3qDmuenpLFgr5X5O6slBLuiVxTJkUZeXFqEy+2X9eAiLDqemtKGRbuq+WRDBdEWDfdPTGVLoZ2PMktlGu34TqESPL2zqoTL+0bJKLvnFxVKwCWi1/4xMYm9JQ2/COqEmcQry4oxadQMawZ1ry3MJznSTL+UQB5fUIjP45NjErXx3vhLOot31zB9XZmEXyK9cmt+nYyIE9dycX4PjUtkyT6b3E6kiR4M6iZ3CadHsoXnFhZJKCmaeKkstgq16Ll/TAKfba6UwEqYV4i6fuPSg7igXwzPzMnjQE1TZNnxgLq/j0pga6Gd9zPL5D7n94yU9QGf/i6XpGgz53YN55WFBeypcBAfpOeusYnsr3Lw34VHAXWxZq4aHMfn68tYn2dHr1VJEBeo13D7rBweHZsozSReXFIo51HAVpHGO3NdGZtKG7hhUAxpESbsjW7yrS5pSDGgTbB0iRWgTkQOfre9ihVZNoTxRLtwA/edncqna8tYuMd6iOttg8fPQ+MSZO29R2bnSjAoQJ2YJ9FaatQJM4mPMsukmcTo9BDO7hbBE/MLJKi7ujn1dY9IfW2OqGsbaeKdzDLyKhubDFBa+TPb2t0poK71FFX5vMLfpcmN5PCcdXGx/en3IhWv6UIllsjhbicyTU9GjjQtH/FvETbStF2Tq87Rmti2aRH/tL+4RLQsbLFfy7Js6q+peKj4uWWMLdbR4g8yYkU20Z9autWKv7fsczx2y6ca1InUY4cHDHqDdBM6seaXUVlujxet1njIBfrE+lX2bm0FvD4PGwrmkVu9nXEdriXI2DpQp7XHqfR3/Ao4PfW8s/IBjLZ2XDD8akJDgo9/52NsOX3Gl4wdNZToSGWdtJqoSketooDP56HR5caob4V7jl/U2bHjV5vQa3Wn/ZfUVhHwFHTi8bnZlP892ZVbGd3hKsIDYpVo7lMwD615SBGh/9bKO3AVxXLF+JsJD2sdBz7x/XzxspV07tiemOjWgX+ted5KX6dOgdMR1AlDhwdn5xHcAuqGxEnjh+fm5lHn9hFk1vHUuanM2FDOsn1W+bx4Qbdw2scG8PKyYmlAIOqUdYo1c+/4JGZklvLtLiuJQTrun5giwdOHh4G611YUc2WfSGrdfp6Ym4+p2R71kXNS2F5g/0VQV2V38/KyErnPj6BORNSFmxjaNojnFhXR4PDK5+SUCJOMqJshUi23VhGkF4YFqewpqZf16pweP6EWLQ+JiLqNFaw7UPszUDehUxiD00VEXSHldW75HC0gkhhyQoiBe0YnsPpAUxSgcNYVEXUXdA1nVOdwnvouj3zbrwN12wrrmZZZelRQ9+rCAnb/COqS2F/VeNygzqBVSRB3LFD31bpSSuu93D4mkemrS5i/3ybdYke2C+b6IXH8d2GB1EJE1Ilad7O2VqHTQM94M3dNSOGNxSKo4tCIOgFq/z48jrYxZp6cm4eYR8EcbM1ahhs1PDwpjZyKej48CqibOiROQl6RJiu+7Fw3IEZ6CLywrAiv98QTck7GlUEBda2nssovCZfSDleg9UGdH3dDFTkFJcSmdOQH2E5t1X62HrDStWsvgow66Q9ut+VS1eBEVbKB/6zK5rJBozEZneg0OlweNxHRPUgNs2At3UiOrQ6HT4Rxm1H7XdQ5G2hUR9M7rTNhZh0ejwuPt6nOTHnW93y+bhNjJt5GephFfvnWag3oVF6K8teQb3dh0P0U+ej1NGDzhdOrbWdCTD+lRCsr5fdVQETRLdv/MT6/m5HpV6NVC+8qpZ3JCtS7bLy7+kGMVgHqrvkdQN0wopWIhjN5iZy0sYuHdrfHhV+lxSCAl3yB5sddW8S2ohyQL7Z+Go7XqyU6sj1JkcH4fQKWuVFp9DK15Jea39NI1tZPePTbjfztyifpEauRL9vUGi06rRZXXRFZpbnUO2tBG4RBrcbtrqPGrSIytCOdExPR4sHldiGToerzmP3R3ZR3vI1LBgwhQCuGqkWv1eNvKGV59lbMWjN6Wa+x6SuNw1WDMaAtHZPaYdIKz3qlHUsBl8fB0v0fye8NEzNuONbmyt/PAAXEy783Vvwdd1Fc64I6n5/FyxVQdwYsgZM+xNMd1ImIq2sGxpAWZeb5+flUNXiYmBHG2V0j+CCzlGVZNlR+PwNSg7igdxSfbixnS74dlUbFpG4RDGsbJNMaC6qdxB0N1HUJ5+kFBQxLC2Rgu1BeW1IkXT8Twow8MCGJeceoUXckUCdSX3UGLVcNjGHutkqW77eh0qg5p3OYdEt9ZHYOeVUOAnRNoM7p8fG/FcWU1rkZ0zGUoe2aatSVW50/q1HXJc4s6/F9t7WS1Tm10pH18r7RFFudvLeunBsHxRAXYuCxBYUYvD4JOW8YEivB0cuLCrA116hriai7pG80ryzIZ1+1S+p1zaCfatSJiLrTBdSVNXi5dWQ801aXsqu4HrNBy+TuEYzqEMK0VSVsLmrg3jGJNDo9PL24CI3Pz5SekQxIC5IRgHk21yGpr8Kcomeyhb8Oi2d6ZpmMQAwyabhhcKw0h1i0x8qDZ6ceEdQ9Ob+AEIMaoc+nmypYm21Da9DyyPgkKm1OXlhWjE/kOp8BTQF1rTdJCqg7ipatDeo8Diu7t83mnU+/4YJbXqWnpZJZs15i9s46Jl9wBxN7d5e183ase55FB2wMi4nn5oWrOC/CSK4+iIkZGSxe+iqB/V7m3pG9qc75ljmZs1iYU82ogedjqVrB24s/pDTwEt689WkGJpjIXDWdHLueqLBI7FVZbC8up22b3kSa1BRVFhGUOIZzM+L56PVzWE4fzu7dD4N8SvNRkTOH+1eq+PKB5xmY2uT4q7TfXwEB6hbve08CuuHtrkSjPnaa9u8/KuUIJ6LAcYM6GbHMj7VD/MKZ66D0hCONoSmiTgF1JzI/f6Z9raVrmb5gGlVB53Dn+HEEGQTA8uGo2MOC3ZtQqZqAWlPz4/HoSE0bRNekGFyNFWzYsAibNp5ObdKIDI3DLKpVH978fhy1uXz9xb1MzzVw4aBJRBgayc/fgTFpBOcNGIeubg+rts1nztxncLa7mZEJZtateJyXc/TcNP5Z/nnxRajK1/HV0lkEp/QnyGdj7/bvqIscSteERFTufDZWRXDN6CmElnxDt1ee5brhU+keF4ZKxParfaxd/jKF6v786+YnSLaY/kzT/JvPVYC6hXunoVZpGd9p6m/uR9nx9FHg14A6YTjRUrvqWPcfsa0C6k6feT6dRnKqQN3DE5Ol6+s/Z+ce4vp6cd9okkP13P9NHsF6tYyMG5xq4ZL+sVTWual3etBq1LSJMvHh2nLpjirujBajmindI6Tr677ieoLNWlm7bPb2aubtrJbRZrEWHQ+cncqWgjqmr2lKfZ2QEcrEzuGyjpy10cN9YxIwaDWU2pzEheox6jQs22s9qpnEnSMTqap38dLSpoi64e1DOL93JK/OzyfH6uKCHhH0bxtCVkm9dGGNDTGwaHcNn2+plBFhwvhAGBaI+3Op1SmBXVK4iaX7avhuezUeb1M6ZksTcM1i1HBRzwi6JQeyv6SBMIsOk14tz6HM5pLaXNU/GrNeQ1G1g8hgg4SZH68vlzXxWtxPRV+d48xMHRpHSY2DRXtt8sXedYNipOtrcpCOv49MYFtRvXQ5FamvokadrNE2O5fk6ADO7SZSX/PZXd6U+nrP+CT2Vzr4vwUFR6xR1zXWzNVD4vlsfSnrcu2IiDqR+iq+39z2dQ7/Htec+rq4EGdz6quImBM16raWN/L3EQkYtSpZNy7YrJPXwJRIk3TSnbfXxn2jE+TrP+H4Ktxoo4L1MvV5wR6rMBI+5OWmOH/hlnvnyHhZO7CgqpHwQD1ur49P1pVLuPvI5DQOVDTI9SKiFkWNunO6RUgzksIaBw+OTSA62Cjr+AUHaGVZsgqbkxeXFuNVQN3pdKk7KWNRQN1JAnWN1dl8s+RVvly2l3Om3E3wged5KSucSRnBLNmdw4Sxj3DdkG7s2fAqSw7UMTg6jLvWFHFn53C2u+O5Y9woPvnfECoypnHLsN4YNX5K98zjldkfY4rtg7nyGzY0GLl47BOM6NoJvbecdz96AqsvgZQYAw6VEZNOh9NZj1+rpjhrPY7Y83ho8gi+eOcqilNv5a8TRhIgwYCfoi3vMmzaJj684z8MTFXqj5yUTyPIunSL901Dq9YqoO5kif47H+e4QJ3PRUVJNrvzHGR07YCZOnbu2U9QfDvaxEbKL40KqPudJ+pP0P2upf/hX9OfoyLkLJ66+y0GxAY0MzkBiY9cyFslouwAr8tBWeku9mRvIbt0J+qoyZw3oD+hAXrqqgqwqSOIDzGj8vvI3vQm767eyPgxd5EeacZuPcB7796JNe1G/nnFjUTrwW0vZMnM//BtsYeOUU6WZxXQvvtNXD5sNKlRIRSu/x/3ffIto4ZMRKdxo9cHgrcBp9eDSWvj629zuPfB/9LOvoBR783mmev/jyFtI1DLr9R+Fn12DwuL4OYbnyBJAXXHtboFqFu0dxoqBdQdl15nwkbHB+q82Er2sTm7jo7duhCmrmP7niwM4Smkp8RzpLh+BdSdCbN/asZ4KkCdMHo4u2OITMv8eqdVlgwSLErcu/okBUhjhK93WTFq1DLLSMCY3okWusSYsDm8rMq3MyLVwoaCBvZWOH58XWXQqxmaFkibMIM0ZdhW0simwnqZASXuNIF6NWdnhJFvdZKZa5eGE52iTHSLNzN/n02aKUQF67ioUwhGrZqlOXauHhjDugM25uyoli9nD24iWH10u2DqnF6WZNfJemTpkUZ5DgIMldZ7JIwclBJIaqheprXuq3KyvsCOgOuiBJUEdZNSySproNLmIMaiY3+lkzV5dhrdTe6sB7emvDo/QSYtA5MDSQ7VUev0kZlfz/6KRgkkxSaxIXqGpQYR+oNrbmW9RxoxlFidsqsW8Cf6EoBwcGogqWEG1hfWY2v0MLxNEG+tLSfUqGF0ejD5NS4y8+rkfj0TAugRH8C3O6qJCNLTI9bMgn1Wyu0egowa6Rorfl64zybn9+AmrkOxQTqGtAlifb6d3GoXGg0MSQ2Uc/3FzhompgdJ45BFWTY8XogJ0sk53ZBnJ7vGSXqkiT6JARLWZVc72VXmYGSbQEpr3eyodCDMPQS8DVD7iQjQsbW0kY359h9Lbx3+KRPpyCFmLYNTAokP1tHg8rP0QC2FVmHSAZM7h1Fhd8n5EPMn5ldo8P1eGzUNHgmDR/2Q3mwxqOVYxDkGG9Qs2l/7s/Vyaj7hxz6qElF3bI2OdwsF1P0SqHvpb1TWFqJRNzla+Xw+DtRVMufp5fTq3P94NZbbiZpz2Wue54bpazh3xCSiYsIxVa9jxuIlTJlyNxW7lmLofg+DLHNYtLuaQdGh/H1NGf8Z3onPttt56Nz+fPHGFaRdNJMxbaNxuBpkDYHibe/wj3cfJS9kAE9d9xq9E8LwocakD6CmqoDGhjqq7FUU7p/HzM3bGDnqFrrERhFkDEMXEEWixc+Mt68iL+l6rh09BLO8Bvoo2fEREz/aJUHdAAXU/aq5PpGNFVB3IuqdnvseC9T5fV4qs9cxf9N6HHYvOosZjcZLWWU1JlR0GXE9A9Mjf/blSpytElF3es756Tgqf2MJ0z58kMzaNqR4ppMd9x5vXj4Qjb+BrNUf8dH2bag1P9V/E5F1fq+TsISRXDR6CpHNQWl+v4f6mkKyKmtJS+xAoL6BLz+4n10RU7hz7AjUzt28+OY/Ce37MNcM6o5B46cqdzn3vnwrbQe/wu3nDUHjbAJufncNsz65ize3ZHHx+c/zl0G90PpBr7egahSFk+vwuWuord7Lt1/cREX6w1zcfyix4XEY3B7CY9ugzpnJ6Pe+4tGrnmRgakv9LT8rZv2T5SVGbr7xPwqoO84FqYC64xTqDNrsWKDO7/dSnbuFRWsWYnVGYTC7MGmgpKoelTefLsPvY0j7GLRHeEBWIurOoIVwEod6KkCdOD2ntwmeGQ9aqwIcCXgmfm84bA2LNEWXyGIARHC4y4d0ZhVmCS1NRlJ5/bhFXfTm7YQjagvrEqDN6fPLl6k6TVM8unAidfuQphW3DY1Fq9fwz7kFqH1+ooK2JKkAACAASURBVC1anj2/LZ+sLZUOpYdnKwntxDjE78VYBMgSEYDid2L8YmhiTAKk3TgomvhgPW+vLsXW4Gk2LRCGBU2gbltBnYx4E06kItKuZXxHWwotWglNxPnoNcjvnS1jbDlXEdQlcn1a/n54fwf3o1eJPpq0FeOSa8OLBFZiPKKJ+RF6ifMTf2/5Wex3sL6HQ7qW4wqQ5fSDTkVT7T2/OF4TARXzKvoT/xI/H6yn+LcAtqLenvWHGnKPTUiSUHLamjIKa91o8JMYZuTWEQnM3VnJvF1W2b/Y7+A1cCQ9W+bR07y+Dp47sU7FmpOmEKqf1ovQU0QYCtAnNBKvTsWxhJ4Hj/8kfpR/86EUUPebpfvZjgqoO4qWm3Zk8vBLf6OitqBVQJ2rLpcZLw7kmaJghiaMxBJQKOvO7c+uIC01FCvDeOjKm6jN/h9Lsu0MjQ7hhlUVvHvxRWQu/IDGYAf7iyK46apbiG/YyLQ1n9HgM6L1Otmw5Us8URfTJ6KczB0LqQsfxDPXz6BrpJcdK1/n8cw0Hp/YyNtzPqZ7/5tICTGhMcSSntQOC3ZmvH0R39eayEhLkxdfceWwl2/m/aw2fHTXMwqoa73P2zF7UkDdMSU64zY4FqjzuK3M//pxZu2upE9qHMs2fE62Op6x7QfiPfA5+xIe5fWbLyZM8/M0QwXUnXHL4RQN2Ev1/u95+vU76TrlTWKLvuS+Zbl88J+v6BiqxmmvoKqx8ZB0GHdjJV+9/yB5UWfzr2tvJfQIWfg+t539a9/l6QULufTSl+kbbuWTL19E3+EWLhzQDYtBg8dpY/mcx/j3yt3c97ePGBPvJXP9DNYW7EWttWAr2sjWCg/9MwZgy/+OjVVuLj73Nf4yYDDumh1Mn/UxvftdQu6cKSwNv4ELe/VB4MS4uD6kRAVSv+sLxr1+P307jiIx1CS/1Yov3zl7VuMPHsc91z+ogLrjXHUKqDtOoc6gzY4F6rwuG4tn/5vPdlbSN607mdteZ7c7lQnpfXGUzaIw+Daevf5Koiz6Q85aiag7gxbBSR7qqQJ1J3qaAhiJJiDS8ZgOHut4AsiclRHK5B6RZJc1yJTRHqnB1NhdvLemjPI61xFfwB6rX/F3AQ8HtwmSUXCrs23UO0U6axPYMumaXF+3Fdj5YmMFAkj+kqHj8Rzvj76N0HN8Rqg8zbUHarE7vU1RhMGGZlBXxdK91h/h4h9djxM9PwXUnaiCP+2vyqvcc2ZUJmy9cz5mT6Iu1K4923jx3ceoqStF3VzQ/zdH1Pm9FG//gCc/nEaFqTtXDohjze6txCe0ZcuGbLp3VLGuuhcv3nwbxTvf4ssNe+gYFMCrOUbevO4Oqjc9xeXTZnLzNW9zzcgBBKjcNLqd8iLirt3P829fi7r7S/RzfMc3WQ1MnHgn4zJS0PusrJz7CLds7MfnF3h4Z+5HdO53PanBJrTGBDomdyBQVc+Mt68mP/EGpo4dgrk59bV4+4eM/Wg7H9+uRNQdc8G04gYKqGtFMU+Tro4N6mpYvW4ZtQ4wmjR4/Bp8Li8BZi8e9NQXwaBJ4wg/QkF8BdSdJpN8mg/D77Kyft4TPLtsPUMHTcJo38tXS6dz+dT1XDCgE4YjFCGtzF3CP955gk7DH+bm0YN/ln7t99azf/PnPPvpx/Sa8B+uGNILX10uO0rddGmbTkBz/bqSPTN5evrTmDrdzgMXXUigVoXb1YjL55X15HateZ1PdtdySb+BfD/7AXwZ93DNmAtIDDFRXTKf//vkXcaNupui789nedj1nN+jF1q1hsT4AaRFB1G/6zNGvzeLx656nIFtRI26prbsq4dYXqbnbzcoEXXHuzwVUHe8Sp052x0L1Hlc1azMXInLp0KtdePVmfE1ODEG+PGrLTTkN9B3zGgiA82HRP8ooO7MWQMne6RnIqhzePwMbRMopdpcWC/h1ok2oYN4nhyZHkznaLOM1KtocLNon40ikTLq/yky77ccS4BFAeZaIsVEHyL6SkSqXdIrgtwqB6tz6vAeVkfttxzrz7CPgHUHR66J+RMprGd3CmNDgZ1dpQ2HuOX+GTT5reeogLrfqtzP91Pd8UXHE78atd54ToueNBodteU+dq2swusWF9Kmr/4nAuqq8pezeX8eK1ft5NzLrsCWO4/PZz3OkioNGRkXcOGIG5jcJ53ZXzzC0lIXCZrdrHGM5ckpZzPr44fJMtjolP4g108cTpCIJW5uzqqdPP7mRfjbv8GUVDuqiC5kxMdLC+nGmizef/1int2fyOMXjmJn9lamXPA83aLEzajpvHyOGj555xoq2t7NjeMG/wjqyrZPZ9A7a5h++2NKRN1JXJUKqDuJYp+kQx0b1FWTuWkjJl8w+kAdLlFlpMFDgFmNS62jKruUrhNGE6aAupM0Y3+0w/ipq9jBs08Mwtn/S+4/qxfqhny+eONaFsXfwv9dfA2xlsNInbeUt1+/lsXWaB6+6b90iGhJKW3SxuduZN3Kl3l3yWr6jHqASwf0waJvSlsRNXKaauB4yc1ewr9fuIL85Ht55bJraR8TdFgRax/blj/HtK3VXDF4PFVeFb0zBhJi0srtdix7hjs+/JJRE24hde9jZHV9gVvHjCdQ5Meq1PI4dQLUvb+AF/76HP1TgiVMEONY+eUDzMlz8lelRt1xL2gF1B23VGfMhscD6lZt2EywLgSdzodTr8Vvd2Exq3HrzFTtK6Tj8CEKqDtjZvzUD/RMA3Ui1TDIpOOJc1Nl6aHZ26parRZYyz1RVk4VaaDNKbQimbE1ovYOn+2WB3rx/wff1RVDwF//uRBzJ+HnQRZbSmTi8emogLrj0+l4tlLlVu1QQN1hSqlVanbu3cZL/3ucmrqyE4+oa/6oWwuW8dJbMxl56RXk7Z1LrjWJsT1jyd61iZB2I+nTqTP1VQcwhKSizv6MsZ8t5PK4NoSnDeKSkd2Y/cV/sMZeyqWD+2HRa3A2VHGgYB3TPr2XwMGfc9+IjrKmgWjuxioWffsgq+0ZXDg4ja+m/4sDhm5cdvZUkoPNeNEQGJxCnNHDjLcuYHZVA2mJqQjPP5EZX1+9hy8KevDpXc8qoO54PkmttI0C6lpJyNOom+MBdWs2rEfnDkAbJEAdaBrdmAWow0h1bhm9zhqrgLrTaE7PpKH4vR5y1r/Dkws28pdLnmNEu2DwNrJnzZs8traEey+5my5xkTRY8ygsz2HrtnkszplFVMStXHb2JbSLDJO1WtxuO0Vl2RRnr2Hx5hdwBE5g8qh76JUSd0j6jt/vo7wgk2WZH/LV+kLGnnU3E/r0JTrAKOuytDS/x0FlZQ7rM99lcbmF2/9yHwkWY9Of/T4qsr7nlY8eIX34A2hLFvPN2q9IH/gQk/oMxKTygC6CxMgEfAe+Zvirt9M9uRdxIWa5u3B9LTywHmPkX7h/qpL6erzrVQF1x6vUmbPdcYG6dRuxaALR6P049Wp8dW4CTWo8xgCqsorpMmKYAurOnCk/5SM9HUCdYCwCqhh0auly6mmu+/YzsOX3I4LnzuscRkSonpeWlWARteZOkMgIDUS/smaeVi3H4vL4JPIRgRQCowknUPGySUTAyWiu5jG31gSKMYiaajqNGpfX9zOH0h/vxX6/3EZsKxxiD4d8R9JMo1GhU6txe3zyPH+US9S306jkfy730fsSYxPH1GpVOMR2vt8HXJ6olj9qqG0+11+ITmyZc1FbzixcQX6c89ZJpT7RczmZ+yugrvXUVmrUHUXLzTvX8q8X/9pqNerE5bqhOovMzVmYgpzUEk739n2IDtBSU7GP1fv3ktJ2IhkxosaOV9btmZ65gPioQQzq2Y9Ii4nqwm3sKK2jW0YfQoxabGU7WbJjETZ3PIP6jictPPDHByFnfRkbd68jLGkA7SPDqCrZxfb96ymsr5EXUA9GklMnMjglkh3rv6HGlEZarChY3ySIoyaPFQdsjOg/mpSwZmfA1lt3Sk9HUUABdX+8pXE8oG7Vukz8rgAMFh1u4b7pEKmvKtxosRZY6XOOkvr6x1sZJ+mM/H4cDdXUOj0EBUZibH6b43bWUlXfSJAlTDqCl+xfwKKsDdS7ExjaczCxYTEEm01N9wS/n0Z7EUs2z6aiMZY+7bsQHR5OiCVEFl8+uPl9bnZtmsZ+dzIZyZ1JjI7DcATbYp/Dys5tM9lQZiM1dQwDOnbE0FKH0eckZ88SdtQHMqJ7XzTOGgrzNrJ2/zYwGVD7nKgsPRnedShhjiy+3LSVju3EfVIU0mt6aqjI20a5O5h+vQYSYjiSb+VJ0v8MOowC6s6gyTrOoR4PqFu5dh06LGh1Plx6Nf56D2aTGp/WTE1OGT1GDycyMEBJfT1Ozf/sm50OoE6khAqH0b/0jWJLgZ3M3DoJoA65V0mQ5qdDtIlR6aGg8jN/j439FQ0HxVD9+tkUwM2kV5MSbpDPW93iAjBp1azKqWVnSSM9483Ehxj4amcNvWJMtIk0sWivFbvLe8KA8ODRClOLznFmxncM5avNleRUO4+YuimMF67qGyUL3M3cXk2jWwDFozfRb5e4AMZ0CJH95lmd0gRBNPG/g9KCyIgz89G6cml6cZA3h9ymCUj6mdQ5nPYxJrYUNTB3V7UMFDlBPvrrJ+sYe4hz7RRrZnKXML7YVMn+SscRNRRry6xTkxxuRK2BnvEW6VArDENEyuzhTrutPtDTrEMF1LXehCig7ihabtyxRppJtJbrq7w4+TzyzU7Tg4QWrUa8ZRHpQj7cHjcqtU6+YZC3Dp8Xp9sto/l0Wk3Tdj4vHp8PjUYrgZzP58Hl8YBKg16n+1lUg8frQaTxiguEOIbX48bjayqQKS6nao0evUaN1+MCtRaNpimermWs4u2PVqtTcvJb7/N2zJ6aQN17aNU6hre7Eo36CBXcj9mLssHppMCxQZ2VdetXYatxoQ7Q4haB9o1ezEZwa3R4agwMPGskIUrq6+k0rX+4sXg9Tlxe8aCgxaDTHfrAIFJa/T5cbhd+lbb5fnNkCcRDmsfjwK8S97Ome9eRmujP43YiXNF0Wj0atdi25Qbkx+N14UOLvnndi/unUxz/x87EfU+PGq8ct05r+OmBwO+X90dxu9VotX+6L8m/dXEqoO63Knf67ndsUGdj7dpVNDR48Gt9eHQa/PVuTCY1Xo0JTxX0HT2UMIvwIP+pKTXqTt85P9UjO5mgTjh2SvAjc4GamoBG0gjAouXuCcks21sj01nFvUa8MxJmQy0lEiID9Vw7KIZKmwub20eHaDPTVpdQWCPuNT9FubWUrBP7i3vaLwElkUqbEGrgxiGxxAQb0DdH1O0srueZ7wuICtRxXvcIDHqNdEJdttfK2rw6GVUmnxAlyGpy/2w6n+ZjNj09Ij57XnEezWBM/K5lm4PnXtSwG9gmmCsHRPP6okK2lTQBI6FZi7uoOERCmJHbR8UzY30ZG/Ps8txawNuR1pLod3DbYC7tG81riwvYVdr4Y78CTk3uGkG/NkE8MzePUrtH3pfF+FpglYgePKdLGEPbh7D+QC19UoPIPGBj5tZquZ1wuZX6+kUBjabzFONp0fzgaMWDIeDBDrWHj1toJPoV+h783lC6xDY3oYuMDmzWU/Qn5iDSoqNzjIltxQ1U1Xvk+jm8CTCcFGbghsGxRAfrf5zzHYX1PPl9fnOfTecgNBfHavlZzHXLC09x/JZ5F4dpen5vWodSv+b9xTbinIQ2Lev5VH/uDz6+AupabzYUUHcULSWoe/lvVNoKW8X1tfWmTOnpj6yAeDhdkjVdnuLI9KsUUPcHmGwJ6lY9gMGWzoXDryE0JPiQsxIA3lqym/X7dtEgfORFE18QxJ3fD206jqZrUsQRvxhOn/EFY0cOIzoq8g+glHIKigKKAqdSAQHqFmd9gN+vYnzHqa0a3XEqz+vPfOwmUHcb7uJ4rhx3M2Fhh9abFBkctaV7WbN7Bw0eP2rxAKhuepgUETbJ6cPpmhKLyOQ6uImHx8XLVpHRMZ2Y6Kg/s8TKuR+mwMkCdQK8JAbrMetU2Jw+EixaCTmyrW6sDi9xgTruGp/M0r017Cu2E2bUUFrvId/qbgqIaIZuMQFaogM0MjU0x+bG6vRKcBJu0hJh1lBs99AuVC9hS26tm6oG8ULr0BpwQoJmroZP5adzhAGvF9aUO7l5YDShZi0vLitG42tK+YwP1GLWNgHF6kYflQ0eCW9iLDqCDGpqHF5SgnWyz5bzacFDCUE64ixaqh1eapw+Ikwa9lY5m746HjQXLaDuiv7RvL64gK3FjYSZNHSONHCgxkWQUSPTTrOtLmpcfqJNGrpGGqSWOTbXUWGd6HdQM6h7fVEBO0ob5Rg6RRrYX+NmYNtg+rcN5pl5eSQFCo922F3plMdqcaYVM5AeoifcpJGaH6h1E6JTy+tM21C9vBaJSL/EQJ3cb2+1S6bvir5cfugWaSRAr5K/Dzc2obeCWncz5PtJBYk6m3OK2/yQ2izWQEm9R66TIH2Tbk3gT0VqqI7YAC1Oj599NS7qmtdBkEFDSoie7Gon9fIcDuq/Ob3Zr/LTJcIgU6xXlDq4e2gsZr1GznlKoJYQg5rsGnEOTa706aF6OX+RAVpqHV4K6sSLRT+xFh1JQVo55CK7h+I6D5EBGqmv2F88Ilj0alJDdDJKU4DQwjp3q6dNn+hFTQF1J6rgT/ur3K56v0+++W4q3nw6NPFmX7xJ14pIslM0IAXUnSLh/+SH9fjcbMifQ6F1L6PTr8JsEMXRT9Wn4E8+Ga10+k5PPe+veRi9tR3jel1AZGRYq/TsdLqYM38x40YNIzysyVZeaYoCigKKAr9VAfGiSNx/8mv2MLrDVVj0IahUhxGa39q5st8pUcDn9/Le6vtxlcRxTr/LiI2JakYUv3044huJ0+Vi9dqN9O7Zjcjw1rmn/fYRKXueTgqcLFBX7/Fx85A4+qQFUVHrktFpFpOOvSX1TF9bhk6FjKhrcHowaNXyP9E+yCxjU34dBp2Gy/pE0iXBIl+MikdgAVq+21LBwqxaxrYPYVLPSGwNbgINGrm93eHh8e8LqGtw/yxSW4CW8AAtl/WJIj0uALfbJ1++CvBT2+jh7VUlMmpORF0lRxibo6TA6fXz6bpyMvPquLRnJMM6hlLb4MGkU2PQqym1OnlzZQkVtW76pQRyUZ8o6SAroI/TLTKf1Dw484A8t6OBulcXFZBf6+aGgdFEBBr4JLOUoe1DpWPs80uK5EvhrnEB/H10Ap9uqGDuzqqfSlEctrgOBnWi32K76DeG0AA901YWk5FgYXiHUEqqHcSFGmS5jYIqB08tKMTr9REXYuCa/lHEhppwub3SGXdXoZ0vt1RKWHX76CSCzRoaHB4sBi0Wk5Z1B2p5Z3WJHMmlPSIY0iFUAryaejdGvYbiGifT1pRS7zw0fVisRQHGRqQHM7lHFB6PmBMvGrVaRtc9OitHpieP6xjCsA5h0jRSRK5ZGzzM2FDOjuIGBqQFccPQOMS5biqsl9q3NDnnFh1X9ImkXawFl8dLg9OLywc1DW5eXVbC5WI9xJh5eVEhpbUuAowaHhqfxNrcOnokWSiodPDh+nL6JVs4t2ck2uboQeE8/N22Kgkoh7cP5dWlxTKdVoDXxDABgv0ySvS7rZWszK79WWr3qbwmKKCu9dRXbVnwb/+BoLMZ3a0rFsNBYEykuTRWY220y0UiPv4arQ5Vc/qmeBcRHJwkHUgbGyuprm/Ar1KhFcnZqFHhlYUyzQFRWFSNVNbVotLq8HllYpfsS6T3mc3hmLR+6morsLsc4vbP7i1LqdKm06djinzzYDQEE2y24Gysps7lQK+1gN+F0+uR9F2kg+o0QYQGhTSnjgqBvNTbKnCoAwgOCPzZ28BjSaiAumMppPz991BApIMV27JZeeAzhKmJxRCuPCj9HkKfxD7Fw29WRSadAs7FbwvH4XK2Cnr1+X20TUuhQ7s26HRKDa6TOKXKoRQF/pAKiPtPWV0ei/e9L6O5Aw2RqOV3OqWdsQr4kfeftqZx+K0RMn39RF/+yVgkP6QmJ9KxfVv0ev0ZK48y8NZX4GSCur8OimVQu2Dm7qhi3YE6+qQEMjg9hPdXl1JmdXL/2SnUOzx8uakSa6Obq/rHUFbn5tXlxQxpE8T5PSOZuaWSrNJ69DoNF/eKlGv72QWFDG0TxGUDY9mcW8s32ytpF2nigt5RfL2lknk7qw8BWTI1UQ3ndw9naIcwZqwtI7/aQbdEC+f2iGRrgV0ec0LHUMZkhPPZhjL2lzeg02mYOiCGAqtT/v3ibhGc1SNSus+uyrKSGmXm/B6RfLGhnAVZNh47KwmHx883WyoIDdBxce8oCRfv/+rAz6L8Do6oe3NJIR0TLHSIMvO/VSUU21yM6RDKsPbB/Hd+AeX1HsZ3CuW8nlH8/bP9EqAdra7aj6CuTxRvLCmiS3Ig7SONvLe6lGKri0ldwzm7ewRrs20s2F1D57gAzusZyevLithSWM/UQTG0iTDxyboyKupcZMQFMLlnFAt3VrNkTw03DU8gNdLIjHWl7Ctv5Jwu4bSLCeCp7/NlXffbRycyf1c1mQdq6ZZgkX1nZtv4MLOM+sPq/Im1GBao5+8j4im2Opm3o5q0SCNTfjjPmkYP/5mdS/dEC5f0i2LZnho2F9gx6TRM6RUpa869uKhQpgYLUPf64kK2FP0E6sScazRwQXcBDsP4cLXQ1UnXBIvsf1NeLa8uL+HS3pGkR5t5bUmRBHVmo4YHxiaycJ+NAJWfAJOWzHw7fxsaR3Wdi6+3VsmIznEZYXSIDeCjzFJSwwx8urWaSZ3D6J8WxMzNFeRVOzm3W4QEf68tK5aA8HRpCqhrvZlQffVcjH9J7Bs8PHkiYQFNIaqyuevZPPsSnt5UR48OwzB4bezYNZvCgN6MbpMuXeD6D7yLHqG1fPbB9WzUDyFVk8vmgq34vTbs2t70b9uLbt3Poqt+HzMXzWRp8V7apI4l0eRkzeZPWFkVxd8veYmp/c288c4DWAN7E2sJwOOulWYHRnHzdxSyu7CKK86/nbWz7mS7pwPhOidt0gdRlf0in5ZHMykhit2Vcfzj5sfoGh2I3+ekJGsxL7z0VzaZBvHojc/Sv03sr6q1poC61ltkSk+/TgGvz0t1QxF7ytZhd9bINzw/D7L/dX0qW59aBcQXnq5xIwjSxeJ2i6D/E29qtZpAS4CsLak0RQFFAUWB1lBARGDVNJSyt2wttY01eP0e5f7TGsKewj5E/cdOMYMI0cXj8bTOw5y4/1gCzGi1Sh3dUzi1p+WhTzao65wQwEuLCzlQ6SQtwshfh8fz/bZKdpfUc+/EVNbl2PhiU4UEXFf0jaJjrJl/z82XEUgiWistQENokIH02AAJbUqsTh6fm8/g1EDO6yVgVCE7yhqJsui4ZUQ8VXUunl1UhKXZmElMgkiljAnUcfuYJA5UNPLOyhIZHdb4g5vrwxOTZeDKWytKcPggIkBDvFlLRIiBDvEWGcm2rdDOMwsKuKR7hIyoe2p+gQSNIQE67hyVwO7COuZm1fLwhCQZXbe7uF66xV7UI1JGsP3j65wjgjoRDXbVgBiyKxpl+u1Ly4spr2l6Wdw23MgtoxOYuaGctfl2bhgch9fv4/lFxRi1R8f5LaDuL32iyKl0EGLW8uqKYspqnOjUKs7uEs7IjmE8MyeXHKuT1HAj94xLljBtYZaV+8ckMmtrJYv3WBFl2UVE223D4jAbtUxfVcKVg+KkGcfTc/KocngZkBLIdYNjZURil1gzvVKDufGTLAyiFq0KnpicRnGNg+lHAHViXnqmBHJhj0gZ0VdjdxGo10hNYn+I9ntqTh4X9YokPtTAE/PyZZSauEJ2jw/gzrGJEq6JqLUbjwDqRN9xQTpuG5NIVmkj76xqivir9/h5/JwU6p0eXll2ZFD34NhEqZ1PpWLtfit6s47LekXw9PxCGR0qWttII/eOT5aAcWOOjY+3VvPmpW3ZVVTPJ+vKZUShiKYUVM93DAOQk32hUEBd6ymumvlciH9+2HPcMfFcUiNCZTiozIB129nw5UV85byUie3MlFlL2L3jK6oChzGwbRz60MFM6JFOzYF5vLA0h2umXElAVSafL1uAy5mPzTyB6yZfQEKwSUa51Rav4sVP3iWux+UMi7PyxvtPUhHan6mT7qN3XBWfzXyPdkNuJiPaQvauVdi0aXROS0Jt286ns7+h14gLWDPnRYJSL8RVt5NB426gduHtfOQ6m2s7ufh4RSE3TL2PJF0tO7bP4ZN5T+Bs8yj9vMvZVuFk2NjbGJrenqAA4WJ37PeJCqhrvUWm9KQooCigKKAooCigKKAooCigKKAo8MdW4KSCusGxtI028fKipmglUdD/5hHxfL+9WoK6u5rNJEQklUgVvbh3JF3iLTwyJ59gg5q/DY2VUWsC0JTXuWS6aa1Ib51bIEHdhG4RvL6kkNwqp0xxFKCuxu7mqYWFBB4G6pJDDNwzIYnle2v4dHOVLPQvUl/FMYJNWt5YUSzrwt0xMoGoIIOswSagoABoAto8vaBApnX2aRPM8wsLZXRVcICOO0YlsKfQztrCetnXi4uLKKh2yBpy4zuH0jctmIdn5R4R1Inoq78Oi8Pj9dPo8kmYtK3ALg0eAgwabhwai1qj5oM1pdw2IoF5WytYeqBOArejtZZIvRuGxCJ+bnR6eXdVKdsL7Wg1Ks5pNpN4dm4eFfUekkIN3DM+ifU5dSzJtvHgmASpf7lwi1WrmgBqz3AykoOYtqKYSwc09fvywgLqXD76JgcydWgs09eU0iMpUKbO3vrZfkIMGjmn941NxOH28sGan0fUCdfWUZ1CGd42WKYsu10+9FoVF4kot5gAnpmbz9UDomQa8otLSxBTKspDB+jUvHx5Ou+vKsHm9HLjkJ9H1AlQlxZm4I6xSTIS8IvNVTJ7T9Sxu21EvIzIe3lZ8Y8Rda8uKaKsOaLuoXGJuDx+ZpWfIwAAIABJREFUvthYzsaiBkZlhDM5I4S7ZuYg8mNkhOYPqdzPnZdKkdXFG8uLKbB7+OK6jszeUsG326ubnEUOmqbTqUiSAupa7xqvmvlckP9D91Wc17knIaHhpKT2p110OHpfAxu+vJivGs4huuwLsvQZ9OvcCbWrgexdb7Mx4FHev2YCexbfzadl8ZwTZWT5nr2UuW1oPWXYVe1oG92RUSMvomdyJG6XnX2bP+Kt776i2K2hfYfLuGHyuSSGBqHGzY5t37OlpJwgo5uVy16iSD+WSb17oHXZCU8aQc94De//705Kjb0w+utJTUyiuKaKzm364qzbiD+0L4PaJjBr7ous27uDfZp0rh91IdHe/cxf+ipF2qG0SUzkwom30C0uVr6J+KWmgLrWW2RKT4oCigKKAooCigKKAooCigKKAooCf2wFTj6oM/PK4kJKbEcGdQKczT0M1N3/bR439YukfZyF2ZsrqKxzYXX6mNg5jPgwA0/MKWBwWiATm0FdznGAOmFsIcwr1h+w8eH6Cgnq6txe7h6VIOu0/XdpsYRUQSathC0i7bO8wce1/aPwoJIRdQLU9W0Twv8tLDgE1O0ttLMsz869oxN4aUkR2eUNEtSd1SWM3qlB/OsooE5E1E0dHMvMjeXEhZukecN/Fxfh9vikw+m5XcIZ2zVCptYOTw/mrRXFFNvcP7qQHmmltkTUXT0ghq/Wl5EYZZYmDS8uLcLr8TOpW5Pr65FA3aL9Nh4Yk8DLS4vYUyzSSNUSyk3tH0VylJn3V5bIdGPPDymrLy04FNRNW11K94QAOsUFMvXjfVg0KpxeHw+flUJto/uooG5Y+xDOzgjj0Xn5NDY21Su8tG8UaVFmnp6bJ6MsTXqNjJIU8cHS1CNQx9MXtOWdFcWIWohHA3UpoQZuH5vImv02Pt5QIevX1bq8MmpQ/NwC6jrGBPDqkkKZciyiOB8Ym8D8vTYJ+ERw1IB2IUzpEsYD3+Ti8/gkqIsI1PHvSSks3GOVdQMbvH4+uroDS3ZXy3RtUVex2XPuiK6/p/Iqo4C61lNfNfO5UP+S6Le4Z0RXCkv3sG/vBojqz/jeA8ifdxkzG88lunwBRUFdGNStIxp3A/u3/ZfFmod5/aw4pv3vPPZGT+U8QynLiwIJTYokyLGLSk97gqmnY9/xaIuXku0zovXWsSXzPTY4u3Bu/wF4G7PZUhnErRc9RLJqL0u2rMWvdrJt82wqtV0Z1DEdLW4iU89iaKKWD97/F9rYyXiqllHpdFJliKJnSiLOur3YVN25cMhorLbdaDThNPqcmHWiboYPj9uGSRdFlaOc5Ph+JIZH/uLbAiGvAupab5EpPSkKKAooCigKKAooCigKKAooCigK/LEVOBNA3T3f5vHo6Hi8KhXPLyrC2uihTZiBm4bGYvqhXvuj3+TSNyWQs44T1IlzFnXeRYpkRKCeZ77Pp6jWRahRwxPnppFX5eD5ZcW8dlFbCdkEwLE5vHSKMnHzsDjpUvuP7/K4rHv4EUHdviI7722u4oUpqSzdY+Xr7VUIN9KbBsUQHWrkgWPUqBNGCHYP3DwsltX7rHyzo1rCoJhgPf86K4WKejdlNQ7eXl0mU3ZFE2YGovCOQa1qyrRrboeYSSwswOGHm4fGsXxvNXN2WWXdtCOBug05dXy5tZJ7xyRQanPx9soSmSaaFqLnttEJFNW4+Hx9GdcNi0dEwh0O6l5bXkx8kI6L+8Tw6Le57ClrJCFQy+NT2rAlv+6oNeoEALxlaCyfb6xgSZaNpBA9fxsWJ+sDPv5tLmM6hTI0PZSX5uez3+rCIOrO9YhkTEYYL8wvwNA8r4fXqBMRdcFGLTcMjSXMouepuXmU2t2EGrU8fX4b9pfV89qKEs7vFk6/tCBZ7253uYNhqYFcPSSOrzZXsmR3DT78ZMRbpMmIgMZzRUqwCsZ2COHS/jG8vLiQTfl2HD+YR/xjfKI0lHhjRQkltW4GpQTSMzVInpu9UZSpOD2aAupabx6aQF3s//jn5LMIN2tpsGazeus2QpP60LjkMhab72OIeSnf7sySwKvSqyU+rCs9+lzFOZ1i2Lr0VT63hjHCu5vVpSEEJ4YT1LiLSm9Hgv11dB5yOQPTwnD5Vag8dayYcTHfGO/m9n4xzJh5Lw3Rl3PLWedQVryL8jobBr2L1Uvfp9gwgIk9O6NReTEExNMhOpDP3r+V8piLGNwmjqp9s1hSl8aUfl2oLVjE0txoHrz272jr91PR6EOvEVbaXoQPhlqjwed1otEHk5LUQX6wjmVwq4C61ltkSk+KAooCigKKAooCigKKAooCigKKAn9sBc4EUPfgt3lc3DWMcV3C2ZJjo7beTcfkIKKDDNh+AB6PzMqRjpzHD+qQUWADki3cOCKBvMpGckvr6ZQURKhFz84iu4RzwnW1Z3IQW3Ks1Du8dP8hei7QqJUpsLfPPMCVR4mo21ds5621Fdw2NJaeyRY27rcSEqgnIyGQ8jr3MUHd64sL2FXq4PJ+UQxOD+Xxbw6QZ3PR4PHz9OQUUiJMzNpcwezt1T9mVPZNNJMYbGD2Hpt0l215bj4Y1L2+qICsCtFvNP1Eeuk3OTLCb0Db4J9F1G3MrePNVaVc2C2MC/tGs7vQTkl1Ix2TgiTcFCAsq7yRW0cnHhHUvbGsmIIaJ49NTsXh9LKjoJbOSUEyQnFT3tFBnVmv4aZhcaSEG9mQbSU+3ETbGLNMKf337BwSQw3y70adhk3ZVkIserokBZK538bbq0vplWRh6hFSXwXodPv9DE6xcMPIRHLK6skrayAjOVjWFtxRWCdhZHyQnn9MSkXA1tIaBx2SgmQa9Ufrylm6u0YkuhLwg3OtMKzonGghc0+1TAnukRpMWZ2Lh2fnSrdgAS8HpgVx7ZA4skvrKaly0LNtiISerywtkqnNp0tTQF3rzcRBoO5swoWZhN+P1+/F01jBZ6+PprrbdHr6ZjEnz0iGN49FBfuJTRrH5ef9lY6RRkp3z+LFzUX0d+xkTWkowUnhBDbspNLbiWB/LV2GXsOoLmlN7jEuKwvem8CXpvu4MKqYLJuNsWNvJdHYwLb9O7DXV5C5+n/MLiggRhVOl+4XM7prezTaAFJiktj9/aN85+vJgBALaB1sXXgfjo7/IrLuO4osE3noomupLsokO3czH817B1vG3dzS1sc3857F3+YG/jJkLJ1TexBqPnbxdQXUtd4iU3pSFFAUUBRQFFAUUBRQFFAUODUKeL0+auvqaGx0tIo3lVajITQkBJ1OMZM4NTN6+h71ZIG6Ro+Pi3tG/T97ZwEfx3H24ef4Tjoxs4yyzMx2DDHbAYfTMHPaQJOmSZN+TZukadBhaKB17DCZYmZmybZkFuMJ73R893XmJFumWG5Ux7Dz+ymxdLuz7/xnbuHZF0iJ1Mvk+hVWN4lheq7uH8fqPTWygMJNQxPZeLCOFXtqZYjlhC6RdIg18c7KEvRqlSwk0D42SEKobQX1VFndDGgXxofLi0mOMDK8Uzgz15dRVOsi3KTlmn6x1Ns9fLimTOYga94CfmgwIDWYMV2jZPXQ3FIbLi9oNUivJ51azfUDY2XfwpNq7Z5amauuZ2oIf51fyLgOoXRLMfPJ2jJqbW5CTFqu6x9LXoWdb7KqSQ7TMbVXDKlRAih6JZyJCdXx1PcHZd655kmdBNgRxTGm9Ijm83Wl5JQ7aB9l4MahibIi6ffbLdJr7uo+MYzqFCErh4q8fiKLu6hgK44ztksEj399AIvNdagKrOhX5IoTYcKfrytjd6WDjjFGbhgcLz3bqu1e+qSF8NGKYix2r5yTmwfHs6PYxpdbKjFq1YzPDJe59UQYaqXVxZJdNWwtthGsU3HdwHhZyfbfa0tlvrduiUHSlq+2VLK10EqPOBOX9osjxKCRx+uabKa42sm/15XS4BJA8bAKYk5EKKuomioqsUabdYE8cXo1Rr2Gv80+iPM/IaUdoo1M6B5NfKhOaiLy+M3OrpJVZEVl2cv6xDBTaFjmkCGtTU3AOiH6gFSzhL5iPLtKrPhQo8IvveZE/rxLekTRIzVU7rZmXy0dY02sz6tn3f56ufaEE2NciJYp3aNoE2OS3o6iKMms7RZZpViAO3EosWZHZoTRv02YDKcurHYwL6uKA1XOkzognc4zhgLqWk9t1VcvRPjnJ7zPs5deJBdw0/KrzZ3OY9O/YtiAyygtKaRHvwtxbHuf1a4u9I+uY3NRIrfdcDXavNm8tLmQIY4dfLengKjkDpg9lVg9wXicTsZf/AwTurcDnxeXrYwFH1/KD6FP8KfJFxAZZMRkMoHXQXHhKpZtWkZWfi0jRt1FgjOblduy0Ca1ZUTPKSQZK3nnwweob3snnW3ryNe1Y4hmDi+WjOT+TPhsWyn33/AHOoZ42LrsFaatrubGS6bSULSeNZvnsqdOx9QrX+fy/p0xHXluPa6aCqhrvUWm9KQooCigKKAooCigKHDmKyAesm2uWgprcrA6LY1VX898uxULT6yARqXDXx9JTZk78DB3spCSk4rpl9Vj4+NiyOzYAYNBpJlRmqJAQIHTBeoEzBBhgIKX2T2BfF2CoZi0Kgm/BOwJ0qkkeHH7Arn39WokaLG7A2GdOg2YNAEI0uAOoDaxj83tl+GHBo0q0Hdj3n7RtziOKIBwvK+RsEkAOFFoQtgiPNZELjkBvpyNNgqbjZqAPdbG44h+rS6/tEcUchDHFH2JY4jPxBg0OjVjMyPYUWSTnmWicIOAeMJj7B+LCtEeVShR7C+KGwgw1uDxSbvF11+MT3wmCjU4fX7uGZZAbKiet5cVSwgpQJeAW+2ijdx5QRJ/+uEgLrf3EAA73K9Kju/ofgXIE2MQn4kxikduATXFGAQUk2tEVNzVqaTGwhFMbCsfzVUQpA3Mh9BY/F9sY9KqsXt99EgykxRplAU7rC4vWo2aF6a2ZeXuGr7bVimLZjQHdcK2hAg9fVND2HSwjnKrh3CjRlaRtTo8vLm8BFXjnIl5GZsRLu1curcOl9cnoaWoTCuP35jX7+gM90fPuVg7Yo0Ju0W4qiwM0WxcItxXzKnQSazRJj3E90bM99C2oSSE6pmXUyNhbPOU+k19if1Fn06v+PHLef3Fp/VWPIEpoK71xFQtm3GzPzvyBq4ZNoRw02FQZ8n6mhl7VKQFQ0hMKsGOzczO3k2PvncyroOWRbM+Q9/tRvoE7efb3SV0dBewuUZPr+7dCNZq8Toq2JW7h8z+19K/XTLO2jxWrJ3Jhv2ldOx7J1P6ZmJsBGaO0s18seJHVGHd6ddtmCxmgc9BRXEW67YtI6/OT0ZcElv25zPhsgcJKZzLkkIV47pEMXPhFsYNHc7aTT/RtvPFGOybWLZ1OfV+IwlRibRL7SNj8Ctyf2KrLY3fXHQbqWEnfwOogLrWW2RKT4oCigKKAooCigKKAme6An7qHVUs3TedCmshRnUYatXJIxDO9FGdv/aJxzc/RTU70Vd2Ycqg60iIj2kVOVxuNytWr6Nf7x7EREe1Sp9KJ+eGAqcL1DVBwYBqgTxq0sOpqQWWf+BT8VkTETnm86admhBMIyFr1tfR+/8cFAnYcLQhjaTv0J+PNuzYuT88nsZtNWpemtpWerdtPVhHiFHHwA7hLMi2yJxzx6vUekiPRm+7JtNE3+kRerommZnUM5oZ68pYlFuDVmynCkAkEcZr9fjJKrJJj67mgOpE/TYfRZNGzeU48m+HNWqCaz+3rccPEztHcP2QBFbkVJNX0UD7BLP0QBSVebcWBrwBm8+NWIvJ0SZZ0OOgxS6r5yaEG+iVHsoX68pYur/ukIecgJNX9oiSRRpm7ayRGgTWWOOojvJYbD7Wn5tzuQyPWBOHlTx6HQk4OCYjnIwYI59tsVDv8B6h+2F7jjTqTKr4KmxUQF3rnctVzgaL36MOwqg3HHJrFd173S6cPhVqfGi0WlyOOvl7kClU0nmvqx6X34he48Pp9aIV+eD8BoxGkRtOLEofbpcdNAZ0Gi1+r4sGey0u9ASbhLvr4UH4PHbqHS5MRjN64R/crPm9dupsNjQaHai0BJuC8HqcklKb9Fqcdic6gxGPxwYqEz6PcDP2olb58an0hJjDZBUX3FZZicVkDD1pxVex+dkC6oTOXo8bv0qLCEU4k4h66y3T86cn6c1gs7F3717q6uqOGbjRaKRDhw6Eh4cf8dbo/FFIGamigKLAGa+A34/P55GhRlqt/mcryLVoLH4fHo8Tv1qPVq1c51qk2X+xkdfnIatkOdsKFzG83dXEhaZKUNf8kfO/6FbZ5VdSIPCg7+Oj1U/gKk7khnH3EBkZ3irWiHuVxctW0SWzI/Fxsa3Sp9LJuaHA6QR154ZiLRuFKF4wsE0IV/SNIzxIi8vjY9XuWn7YbqHOKZ57W9aP2EpsOrZLpKzQKkIsX1lUiFd6ox3uw+X1yz6bh3q2/AhHbimuIXJd+JE/wlFH3+gB2FKzpTeZGq7pG8OwjIhAhdX/5Pn7bmM5y/cFnpeOfgYWxxSQcXSnCC7qGS3DRa0Or6ycOmtHlcxjfwjP+v2SLYhm1Ajg11LL/ltVjr+fqGQrPECFZ6FMG3acJsYVaAEaLX5rsrclVh/ev7GXVh6rAupab02o/EfPVuv1fVb39L8CdfbaA5TWlxMb1weNo5yC0loS0jpg1mslcve46imx1BAVGYva58BSZyEoJAGju4x8m5a02MQAKPW68fh8eN0Wls95hb1h13DT8C7SBVyt0cm3Ig31xeRZCmV+hOjILiREhuCsPkBerY/U5HSCdNojSL3TWsrB4r1EJPYlJtioQL9fYQV7PB6ysrKor68nJCTkyFwLjRBPfGX79euHgHZKUxRQFFAUOKkC4oWO14PX72t8sytCcbToxIsxv4f6ij3sriqSL8MO3a+J65E6iJS47iSEGuVNtjg/qdQ6GXLzc83vtrNv62e8srmK+y57kHahPvwy/Ecrb66d1kL2lB3E41OjUombTBUqf8DFPjikPemxMbKQlLBZhtU4iln47R+p6HAPF/fqj0njR6XWyJdT9pp89pYfRNQ7O3yvKQiFlojwjqTERLfKg8ZJNT4HNnB5HSzbOwOXx8mkLnedAyNShiDg67srHsRVlMj14+8lqpVAnfA6Wbx8JV0zMxRQpyyzIxRQQN3/ZkE0hcKK0FVRiVUwJavbJ8MnxbWvJYCmuWXiedEswJVbhKT6TgiFWmM0MuxYq2JMp3B6JIfILt9dWUyFyL92CpBI3g+oIFwfCC0WIc61Lj/CxedE3QRCSlVyrGLMAoIJ3Zr0bI3xnc4+xHhEuHNGQpCsKyBy2IUH6bA7PeytdLboxajoQ+T4k2HgHh92d+vOvwLqWm9FKKDuBFr+b0Cdk43zX+H7naXcdetzePd/w+vvfcfNf/onXeJC5JvPsr0L+WjhWoYPHkFx7nSWHMwnvc0VDA3O553CJP56xXUkh2oo3f0Tiw7uwOOpZ9OKj8kLuZhLe6ehVmvI6HQ1fVOiKdyziIU5a7G5fGRmXMewbhkULf0bT6xw8ef7f0+nKPMRJ/bS7C945s3HGX/fKqZ0TmjRl731lqLSk1DA5XKxZcsW0tLSiIuLO+aNTnV1NZs2bWLAgAES5ClNUUBRQFHgZAp4HXXkbPqCtRUVaPUqPE4VwaEjmDysL2atl9Ldi1manysh3OGbfR9OdTi9Ok+ma3wYroYyVq1bjiaiExnpCUSGRh831Ebc/Qp49tmMO/hon5srh08mwuDBaVeT0mYCw7p3wlO+lSVZi1i36lO86VfTO07Lrs0z+PaggzGDn+Dxq65BW53Nog3zsJujCfLWsmP9HOoShtKnTRpqkQdX053x/YZTt/ktnlq8ldEDhxJlFO+7BPSzs3LLKoKTf8Mfpl4kq+op7eQKuDwOFu3+GBVaxne+7eQ7KFuc8QoIUPfOigdxK6DujJ+rc8XA0wnqhJeZyPl1dKCpAFkCyghAI4CMyG8mQiePbuJ613zbU5kD0Z0IjxR9CK8t8W/hRW7UBCBSUxPbeX1+HD5/47GORWpiGxH2KECU4aj9xd8ESBMgyqBWN45V+lAdkZtMaCHylXlFTrij+jjeuIQuja/JTtkxQ+wrxivGKby+BDATxz/a9ubHFZ/rNGrGZoTROSGYr7ZWsr/SIbU7lSarrTZqLXIItsTjLzBW0Y7V7ehjCzvtXr8s3HC8cOJTsfXQGmi02SUgWwvm5uhjCK2Ft1+QVi1fmvZMCqJ/m1DWFjXQLUpPYriBWTtq2FXSIOdUzIdY1yfSVvQ3KTOcNtFGGjzw1ZYKrNIr89Tm4kRaKKDuv1klx99HAXUn0PJ/Aer81nze/fge1sY+wJtTR1KxfTovvvkWdzy7kB4Jofi8Lpb9+DteW7yUbhM/4JbkSr5fO4v2/R6kc/WnPLqjDa9ee6Os+mOrzqOorh6Pu4oFX93IzsjnuX+M8KhTERrRhhiTjy0bZrCluBivykNCynBG9RpH7YpneWCJl3888gTtIgJhyk2tZNt0Hnv5Ji7/QwFTMuJP+cTdesvy/O1JgLqtW7eSmpp6XFBXU1PDxo0bFVB3/i4RZeSKAqesgLu+lO/fGcXLtgv4+5V3QME8np3+Jnf/biWTe6ah8nkO5WM5unORdkI40Hmd9eTnrWPx8vvY5R7E8AG/ZWSXLpiNOpz2ehpUZiKN4qHIx8FN7/HB8rWMuvBukkON2OsP8ulHf8bQ92keu+Yiwvw+bNW7mPFWL9aY/8zUDmq+W/QcJTGP8vTVN9AzLYGiDR/wyKdzmDRxCia9C0NQFGp3LXaPF72/ipkzD/L4M89jzHmTZ9Zp+L/7HqW9ufEhxlfNtE+eYb92GM9fe6UC6lq4YiSoy/0YlUoBdS2U7IzfrKWgzllbwt7iBlLbpRGkspNfUIw+PJGkyOO/EFQ86s74qf/VDDxdoE4ArBCThruGxB2Rm05AiNUHrKzYVyuhmU6r4sre0cSH6I7RRAC0Vfvr2JBnPaVQx0AoJ/RKDkYrqrfm2+iXZpa//7jdQrntcCiq2LZ9tIGJnSNZ3ngsUbjgEMRp/Mf4zDBCDFrm7KiWDhZNOerMBjWTukRKWPfd9iq59fFwihjnxV0jZSGCt1aX4RTFFk4RgrVk0TQVkxjUNpTiKgcHql2MzggnPkzH15stNLgDth/dRJGNsR3D6J8ewowtVeSU2tCrhVd9S456eBsx713iTPRNC2HuzioqrKIAxqn1caKtBaSLDtZxSY9IuSY2F9paDdYNSDcjfj5dV0lVg6fFocpijXaJNzG2cyRvrSiRIc9iTQXrNNw8OE5WKv58WxU+8Xe/n8z4IIa1D2FOVjWFta7jwjqxnd2vondKMA+MSOKd5cVsyqtvtbEqoK511qP8riuhr8cXs7VBnd/nZP+GD3nso9e44vZvubB9JCXZP/LOJ+9z7WNf0iE6CKMxAm/5Oj74YSmDBw1jX95CNuZsID3jYrp5D/L3HX6ev/VRuseZqLPXI+rR+N1VzPpkIptj3ufJKd3QqISLr4GQYDM1xVtYu28rdp+GxMgeuB272LXxC2bt9TFuxEX06DCCYZkdZNUc0Uq2f8aTL19PzKjn6Rkfil+TxJA+o0gND2q9Faf09LMKKKBOWSCKAooCra2AAHU/vDeZf7pH8Pcbf4e64Hue/PAv3HDXRiZ1CSYnaxFZFeWoRZ7TxoOLOncNVjfpHUYztGtnAo84IoTWS1neOpbsKWTUwIuJN3tZ8N3z7I6czC1D+uCuy+HVGc8S2/0hbh7cF4PGT9nuWTzyzmP0HzeTe8d1w2Gvw+524qvN419fPMrMXZsZO/YVbhl9KZEGFTp9EO6KbSzNKcTgK6Woej9ZG5dgi+tLj3btaJPUA12tky79L6Ru/cv8ea2bx265lzRzo/W+Gj74/B8UG0fz12sEqFMKIrRkTSmgriUqnV3bnAzUCbBeX7qbNWtms6VAT/tOcURpPWzeuR+DWcXgUXfRIyXymIc9BdSdXevgdFp7+kCdn6hQPa9c3o4yq1tWchX1QoVXV1Swlq83V/DDNgtmo5onJqYTZ9ZRanOjboa5BAQR+cqW7a45JW+iJqDzu7GprN9TzcytFqb2jGZcl0heX5DPnkqnzKcWeLpSEWRQc23/WDrFB/PI1/vBJ2BW4HrV5Oh3z4hEIoN1vLGokGq7SOaA9LCLDdZy3+gUGZ74wry8Rp+wgLdgIEOZ6M7PlK6RZCaZMRk0+L0+3lhaTHWDp1kWs8AqCPiUBfzxmhesaCxAKm1u2qapSEfz9SNAaJeEIO4Zlcy/VhSxsaiB24cm0i7WyN9mHaTKLirEirEfLuwg9umbYuaS3jGy2mxSmI6X5xeQX+08cR42aWyg4m5AxYDNoujDqI5hTOwRw1uLC9lncQQ8+xq3OlSwotFj8PB4D+dxa+xaep8d+lx6X/pJjTTyyNgUZm+3MCvbImGiQGPy+EdV1j1uP83yxQU+98t5vXNYArnldr7YVHEEEBOfS/DbNMajjiG8B0d0COOWoQncM2MPDc5ABd7Hxqag06rRa9Ws2VvL7GyLVKBHqpkxXSL5dkP5CT0WxTFDTVqm9o7BbNLyxuIi/L6A0k3j/CXnDAXU/RL1jtxXAXUn0FKCutfvobKuEI3aEDhh+nzsr69kzgvL6dN14CnMgp/60jW8+NolzLD04qHJ1xJlsmHJ28CiDesYMuYOokIiaZsxkajyb3h37jza9LuTHsEFLNm6iLbdbqBzw2oeWLCK68b+gSu6h7Ny5wYcXjcFeWtZvXM+DZqujOg9njax4Wi0KQwdOBpV6VoW7liLzaMmo8144kIc7F/zPu9s93DrZTeTmdyRjknxh27ASrZP54mXb6Tbld8wNCUCvzqU9umdiAoOjF9p/3sFFFD3v9dYOYKiwPmmgAB1P35wCW+XhnHZ4IvQVC9n8Q4nt985jcHJkVSW5FJkbe5RoMJRv4+3PnqTjFHQJgBDAAAgAElEQVRP89TVkwJFmY5qothTyc4f+cvMDxkz9RWGx9Uzc95MKttczgOD+hMRpMPrrGH57D/xj9UHePy+6QxO8JK9Yyk55aWoNDqKcn9geWEdIwdcjql+HzsrnYwYcQcTe3bHXbePOcvn0yVzKFnfXMyy2Nu5rGdftCo1yUkDaROjJ2fB3/ndnHVMvGA8cSaRcw/UXisLNszH3OZ2/u+qyxRQ18IFr4C6Fgp1Fm12MlDnc9ezcs4zfLgpl77tBrJ5618o8PVgQNuBOEr+iTP1PZ656Qqig470RlJA3Vm0CE6zqacb1D09IZXnFhWRXdwgCwlGGLXc0D+Ooe1DefL7A9TYPTw5KZ39xVb+tqIUUzP3KwF4gjQq9I1hsi2VSnQhYNXNQxLIyq/ju+xqBrQJZUxmBG8uKsQjwzxVlNS6sbm8Erh1iDFycdcIPlxfSW2D+xCgagJ1dw9PJNKs5c3FRVgaPCSF6jDq1ThcPm6/IEl6qr2/vJjYEB0er599FqfMzSbIikA9EzpHoPUjx9s21sTC3FoKa5wyXDI+TE+t3UOwXk2QQUOd3StzmwXS1Ksw6dQkhgdSX+TXuCTUrG3wUOc80jtObC+cO4a1D+Wq/vHM3lzG2nwrF/eMoV2siZd+yifMpJHehgernIJHSmgnQnJHdgylbbiBzSUNDEoLkd6FOaUNx81R1+SxGGpQy/GKeapq8GKxiVy7fkZ2CGNCj2jeXloUKHihgpI6N1anyLUWgGPCzqQwPQatCqfHR2FNILe7CO8UoFV8LiLUDFq1DPsU4xb7ClD38JgU5jSCOqFNu2gj9UIzq7sZxBQgVYT/qkgM0xGs1+Bw+yiqdQWKVKgC4cFmg4buCSa6xgexMs9KYbWTeqdXjluGC2vVcn+9Ri2rvIpxyGltfO94BKj7bA82p5dIs44re0RyoNIhYo8lsPsxu0quB5OYY5MWq9WDKAhytLehOKZw9BFeng0+pM3V9W6MWpUEqCV1Hvm3X+KlqIC6lp5JTr6dAupOoNGWHet4+vW7Ka8t+OWgzu/iwLoZPP39N7gaCrj21s8Zlh5BcfY3vPnx+1z/2LdkRAehM5jI2/JvPl6RyyVjJ5G78R1WFebTruOtDDPv5c190Tw6/mI6pcXhdruwHFjOvxZ8yu6yYnzGRHonDmPilKtICgvBHBREfXk22/JyafDqaJs+goykSA4seIaHl7p4/uEn6RQVfGTo6/bpPP7yTVz0SB6XdklssVvuyZeZskVLFWgJqBM56vr376/kqGupqMp2igLnuQJNHnUfuobz4o1Pkqgr4ad/PczXpot55ZpbSQ7XH6NQUfYX/Hb6u0ya+hY39cs4joJuSvYu5o337id48DTunTACf/Uessv89MzMJFgfKFZUvnc2z378KMZOj/Onq35DsMaP3W7F6RGZdPzkrH+XmTl1/Gb4WJZ++zjbYm/kycuvJyMmlJqyRbw680MuHPkIhXMvYXnkvVzRp7/M0xOf0Iu28UZ2zX+OZ9a4+cNtv6WNOfBOHV8178x4niLTaJ5TPOpavPoVUNdiqc6aDU8G6jyuKlasmkuleIg3GWnw1+Nq8BMWEozf76W+PJjREyYQE2I64n5RAXVnzRI47YaeblD3zMQ0pi0tIrekQXoaNXh8TOwayfUD43lx7kH2VTl5alI6eaUNvL26VOYea94CHkSnJpOAXfdfkEhmUjBOt4+1B+pkYYSRnSLIKbbSKSFYpowQOcM+XFWCze3n8p5RjMiI4P4v90kP9UOeX42HbgJ1ry8qQoS73n1BInkWB/N3VHHj0MAzmc3hJS3KKAHQd1sqWSg8Af2QEmHgNwNiSY4wSHAkYNDsLAvbi210iDRw09BEahrcxIboJTiqtHmYuamcncU2nF64d3g83ZMDecuzimxEm3Us2lXN+jzrkfn2/H6SIo3cc0EiKf8BWvV2Dz/tqJaAMfM/4DKv0k5GXJCEWev21/PRujKMahUu4KGRibSJNiHCfgWomrXdwrqDdXi9x6/WKmDUFb1jZL9iTAVVDr7ZXEFOuYPR0qMumgMVdhnqKbTJKbXz2rJidML7Ta3ikh5RDGsfLoGpAHVr9tXyQ1aVnC8BLCd1i2JQuzBpj6ge+/3WClk9tn2M6RCo+y7bwthO4VzaM5pvN5az+qD1EKhrCgEe1iFMVtA16zXS63HFnppAiLLQKlzPlX1iaBttkjYKYLuzpIFvt1RQWu+WdghPzN5pIRLY1Tq8fLOlgg0H6w+FLTcHdXd/tkeC24FtQ5jcLYpwk1auhexiG19uqqDS6mZg21Bp7yerSsitcBwR/iwgnah8O7VXNAPbhEpdBURdklNNdkkDNw+M5ZN15ewrt59y7sDm3yAF1J3a+eTntlYVV+89TnrN1jvA2diTSq0ma9dmXvng/6iqL0Wjbgz6+QUedT6fh4qDK3jz9Vvod/dqJnWMpWDLdF58603ueHYR3eICJ8ia4nW89d1SLr34FuLVJXzw/ctEdryJvu6f+NueVF687hZSwrRU7Z7Lu/P+SWKv+9Bvf5KdHd9mvGM2ayqNXHnl7STrYdPCvzN9WzZep5XMfs9ww/jBlCx6mkeXuvjbw0+RGW2WFWOaWmnWZ/zh5ZuY/HAeU7smHL4pO46r79k4r2eDzU3FJJKTk0lMTDzG5KZiEgMHDlRA3dkwoYqNigJngAIS1L07gQ/9k3j3rr+QrCng2/ev52XXJKbf9lvSIvSNb9YDxop8qm+/fxdLPCN4/c77SQwLOuJzfB7y9/3EW5/8Dl/X13hq6kRCGx2vDxeS91JftZnnXhzB+tBHeOmmh+mRENbsgcgvQy22r3iZT7ZWclmXzmys03HV2CuIN+vk8fK2fsAj//qciZMexLThdxzoPo37xown5JB7n4ud8//GXzYa+et9v6dtaADU+T0WXvvkafZphvDcNVcpHnUtXIMKqGuhUGfRZicHdRbWbNlFcmgy+iAPDr0OX42TMLMatyGEws1ZtBkyiJiQI1/sKqDuLFoEp9nUXwPUvbOsmN1lDXKk8aF6bh+eKL26/vjjAcz6QOhrfnkDH64pQ9ccykmvp0C+uVOCdX4/6VFG7h6ZxMZ9NfyQVc0FGRFc1S9WQp9PVxbTMd7EhO7RfLCimLm7arhlYBzju0Vx/cc56Jodr7lHXYRZyz+XF3PTsCSCdSr+Mb9APovdOyqZjPggVu+tZVlOFdcNSsBo0PD8nDyq7B7eurqD9Mb6Yn0pZbUu7hqdIsfz6qJCzFoVD45Nxe/z89HKYumNd9eoZDbnW3l/ZYkMI71uYDyztlawtcDKw+PTJNwSoGfV/vojCgs26dQv1Szh35dri9lU2MAV/eIYkRHOnnI7n68rlSHAvdJD+fOsg+wosfOHscl0TQ7mX6tKJBy8dnACHWNN0ntwV5nwhDySlIo1NLlHNFO6R8v+BAC8aVgiRRYHry4vYUyHMK4bnCCLdLy2IJ+MOBNTesXy4coSlu6pZWSncG4ZHM+8bRUs313LwHZhXNw7hplrSpibW8u4TmFcPziRpbnVLNlZxdUD4umUGCznJj3cIENfZ22rJLfSwWNjkvl2SyU/7apGJ56HmzJs+CEzzsR9o5MpqnEyY00pwzuGM7pLJA99sVeug7uGJ9A3PZRXfsonr9JBn/QQrhuSwBfry5iVXc3kzmFcPiCBOdsq2XSgjpuHJcpiIM/NzcMlvdpUsnBGU+jr3TP20CnWxO3DEsi3OJixroykcIPUoqjKwYsLi+idGsy1A+J5Z1EBO8rsh0CdrH6rVnFt3xjGdovmmw1lbDhQxyV9YqVd/1pTKkN0BUjcUWz7RfkNFVDXeidd1XPzBiug7ig91RojlmIfaxftw+0SSSoDN///feirfHSg6uASXnrxZnrdPofBSQbytn/Le9On85uHptMpLprYyBgqdn/PB/PWMKjvQBz2MvYVVxCf2IPkhmU8n9eWt66/FV3pMr5avJDuF95JvzQ9n785jKyOP/D8mBR2b/o33xcYuXTYFVSteYVsQwfa10xnpf5hHrr8QkoXPskDi1289OjTdI4JwVVXQqXNhk+lpmr3dzz7/u8Zc/sKxneIQyWcY7URxEdFtlqCydZbuudmTyL/04EDBygqKsJgMByT3NZutxMZGUlmZiY63bGJcc9NVZRRKQooCvwSBdzWChZ//hveqgzm2n7XoXccYPWWcqZeczu90jpgVPuorTpAZU0FOQd3U33gQ9b6r+beKVfSMS4KDX48HjuV1aWUFuZSWLqTnJJddOjxIGN7d8EkkvE0NpHzqqJwG1m7N7B4/RdEZd7H1KEjSY0KO/LNvNdFbU0J61ZOY3axkd9f/yTJZmMjKfRRU7SO92Y8hzZ1IkGuAgqzP4Sez/KboRcSrPWg0pqJDg9n/5LneGBuNldPuJKUYEHwVKjdNXyz7HPUKTfJYhKhSo66Fi0fBdS1SKazaqOTg7oqVq1bh94XhFrvw6VX46/3YDapcOuDqc2z0HP0CGJCghSPurNq5n89Y08nqIsM1fPaFe1pcHrwegOPswJu6HVq3lhWzOYDdTJ89I+T0kkO02N3eY9YxwJuvbeqVHoQnUrdBZmjzqzn4bEprMmtYua2KukZdWmvaN5ckM+awgY6Rhl4dHwam/LreWNZCXcMPjmoE9U7i2ucxIToZFhnUZ2bBLOWu0cmy1xij3y5V3qHjcuM4JoB8by2qICIYB33jEjiH/PyWdtYECA90sBDY1L4ekslFTUOHhiTysLcGr7aWC4r4D4wPJHEcD0vLS7mj+OSKahx8cHKEukRNjg9hJuGJPD5+jJWHgXqhL7Cg6trYhD3jUrho2WFbCpq4NahCfRJD+Wpr/eSX+emT0qwHPs/V5VQVO3k0XGpzN1eyQ+5tYRpVRLMPTAigb3lDpmzTQC3I9p/vPCeGJ/CwQoH768pxahR0S0xWHqoLcipYWjbUAkHRT6/7SU2CWd/OzqZ/Eo7760r54kLk6W33ytryojVqxGp2AWgSgg38vqCAi7vG0tsqJ4/fX9AgrC2UUYJGuftqMKgU/PI2FS25teTFmlgT4WDj9eWSRuOdrwUXnkXdAznxXl55Ne65EvGCzMj2FxgpazOxbAO4ai8PpbnW0kN00vvxsm9Y1m0s4o5WRbuvzAZj8fP64uLqHF4yIgx0iMlhBV7aqlucB8D6u6fuZeLu0WSkRjMPV/uI0KnllWPp3aP4jcD4nj5pzyMJi3XHQfUiTUrvgP3jkrhQKWdZxcUEm1QU+zw8u4V7WQobmW9izdXlMBxQmZP5YyigLpTUevnt1WV1hQooO4IjUQ8t4rsnM384/2nWsmjLgDqrJW7WLz4a8IzRuO3V1JbX0ReWTlJyd0INyfRq3sfKnd9w7YKFX0yekn32qDgaKLDw6jf/Q0fFUdy44AhGJwV1BNCbEQouCtZu/xdSmOu56JuqWi8dsotJWiD4qjd9wMby+rROvcQlHIbI3p0pDbne77e7eGSMZNJNBup3L+a7JIy3CoN7oYi9hTvJyahPzEyL50Prakt/UVlP72SjLv1vnYn7knc4Hg8HkR1V+Fdd3TTaDRERERIiKc0RQFFAUWBlijg97qprSqh1uWWL5xEWmS9IYrE2IhAAma/h/1Zs8ix1FBk1TCg22CSIhOICAmElAh3A7utjG25mym22EhL6UxCbBwx4dHojro0+Hxudm74loPuUNqlZJKakCLDO45uPmcte3JXs73wIIaYnlzYcwBBuqbQVRcHcxaxpsTB2EHj0Dkt7MldxPYyF/HRCWhVHlTGRHp07I47fyFf7apkcM9BRDZep1TeBjbtWoU3vB8X9+0jQz2UdnIFFFB3co3Oti1aAupWrluPkRA0Bj9OnSoA6oLUeAzBVO8tpeeFCqg72+b917T3dII6UUzi2cnpfL21QnoYiTO9yD0mKoJ2Sw7mwxUl7LE4ZOhrTZ2L73dYGgsjBRQSucRETjF7Y5XVluomoEdMiF6GSK7ZXSWrbl7SI5rxXSJ5Y0E+uRanzI/2yLhUcsvsvLiwgDsHx/+sR50oNtC/baj08NtdYuP5BQVo/BATrJWFG0S+sRfm5ktQJkIfbxuWyKuLi+gkvMm6RXH/53uxOUTxCBUqjYqnxqew5qCVg2U27r0wVYbC/rTDgtsHNwyIpVNckISUfxyfwuwd1Xy3tVKGBQsYdtcFiczLqmLl/rojPOqaQF23pGDp5fdxE6gbkkD7OBPPzc6jssFDZlwQj01MY/r6MqqsLu4bkUyNLXD/0dTCzXqyCqy8v0pUMj0SRah0Gl68OJ2vtlSyem+NHJPI+yc8+sQ9ichRN6lnDG8vKZQFE0SY7L0jk6i1unltVSkvTEol2KDF4QoU5RBNgE4RMTdtfj6X94ulsMrBB2vKDuWKEyHA4lYlTeSoG5sigZ1oM9eXsTS35phQUGGHCK8WuQSfX1AoPRXFs77TB3qZNxDaxpm4oW8soSJvn0ol88uJkOGfsqtYuquKpy5py/q9Nfx7Q4XcQawrtz9gR5OXYXOPuge/2MstA+JweHy8sbxEzpdYD+2jDDx9SVuph1elOi6oE7n9OkQbuX90CjPXlrLiQL0M+7V7fFzXN4ZhGRF8uaGcZXtrf5E3ndBMAXUtPZOcfDslR90JNNosiklMu4eK2tYoJhE4iN/nwS3y8og4dZ9XPiwdrvmjQafX4/c48aJBp9Ue4Qrs87pw+0TCyCP/LrwXPB43fpUWnajY14j7xYXS53Xj9orjiAuXHq1GVAIS/YBWJ5JzqvC5Hbi9gVLPsgJRYwmgpvAllUqLXh/YVmmKAooCigKKAuegAuLm0G1H3CuLc75BpzvSm1dcT/w+mRvVr9Kg1+pQn8D9QL5scDvwq3WN16TjXzvktcvtlMdsuj4dusyIPrwufI3XQlHJz+f14PJ4DofgCjt0elTiuurzSw/jputU4IWHuC6qf9aGc3Amf9GQFFD3i+Q7I3duCahbs3EbkYYotCYvDoMaf7Wb0GA1LmMIFTv302n4MKIVj7ozcn7PRKNON6h7WuSoW1IkCxM0XZZU/ykk8P51HVmYbeGb7ZbGHHU23lxdhuGo9zbi16YKrC3V80SgbmznSKYtyGdvlVN6LwlQl9NCUHfXcFE51cSq3dUM6xjB95vKWLCnnsSQAKgT3m4iFFaAmUFtQrl1WAKvLi6kc3wwk7pG8lsRbmn3yOugwFNPj09hQ4GN/aU27h2dyo9ZlSzYWXUEqPtgdSlPTEhlUU4NMzeWy9BOARjvuCCR+dmnAuoSaRtr5PnZeVjszUDdujLqHR5E/r2PVpZQbXUd0lp40YmcbCX1geIJzZtap+Efl6bz5aZKVglQ11h4QYDVJlAnctQJMHXA4iSqEdTVWN28vrqUly5KZ2NePVl59YfuVQSoEjCt1unl7guSKLDYeX91mQRwAgCK+wixFkRIs5i33SVWWZwiPdrIk7PzEJl8m9/NCA+0GwbFkRCq5/n5BYc8OkU/4l4mJVzPncMT5fE/W1sqYaSArY9NSmNFbg1LdlXzzCVtWLOnlukbyqUN4llczK/wABT9i3Y0qLttQBx2r59py4olqBM6Cm+9Zy9vx7tLi3AjQF3cMaGvYvwdY0zcPzqZf68qYU2eVYY4C1B344A4OicG8caSIplr8VS/D0fPnwLqWnomOfl2Cqg7gUay6uu0e6hsRVB38ulQtlAUUBRQFFAUUBRQFFAUOP0KCFC3ePen+P0qJnS5/fQboByx1RU4Gajz+9yU79/Ioq2bZQiVcJD1N3qDiByS7TtNYFC39rIiYPMmQMXiZSvpmplBfFxsq9utdHj2KvBrgzoBPPR6De9c24H5WRa+ybLwJ1lMQoC6UgzHKyZxFKyT/l3Cg6txGo52Vjga1M3YGgh9/SWgTsCs8GAtby8p4sp+sWQmBPPC3DxZ/EDkQTseqHt9cSGhRq0MfX15fj4b8kT1dmSV0vtHJUuPNEu1Q3rU/ZhdyYIdR4K65/9TofbJMckcrHbx0aoSnB4/PZOCuHV4El9tOHHoq/SoG5kcCH0tbuC2IQIyGqVHXXNQ99n6Mhlm+ejYVH7YWsm32y3yHKPVqOifFCSri+4qd3DYzy4guMil9sT4VLnvp+vKJCBrE2GgbaRBeoINahvKpB7RvLOkiP0WxxGg7pXlJTw1NhmL1S3z2ekJVGbtFmciPkTHluIGrh0QR3SIjr/OyZfeadHBWoakBrOtxI5PrTpk76ZiG0+MSWFzXh3TN1bI/IbNIdaU7lEMaR/GawsKyKtxyTQbg1KCKLV6cPrhwVHJfLiylNUH62QKKRHa+udL2jIvyyKLaYjQV7fbx1tLi6h2eIkN1tI7IYisMrusMCvsbg7qhNfkJd0iaR8fzJM/HEQjPfD8XNQtSq4ZUXVXVHw9UeirgLD3jExmf4WdN5YXY9CosHn9/P3iNtLj8aPVpdLrTwF1Z875VwF1Cqg7c1ajYomigKKAooCigKKAosCvooDb62Ltwe8pr89nfOZtBBvCfhU7lIO2ngIC1L238nc4CxO4csStJCbGHdO53+fF7fUEIivkfwKeHeI/Gq0ObbMclE07O5xOlixfRZ+e3YmNiW49g5WeznoFTjeoe3ZKOt9sqyS/yimBjl6jZnCbEFlJc9rCQnIq7dKjrs7q4tsdoiCAREEBIAQyv13Tvk3ii/Vv0KpI/k+ut7oGL2X1rkMeTmIbAeqEF5coOlBscfDF9ir6ppgZ3SmCaQvz2Ws5dY86UeVVJPOftqiQaLOWh8amygqiC3dWc8/IpOOCureWFLGn0sEzk9KwOT0szKmRXlvjMsMx6DS8u6IEkxruE6BOeNQdBer+8lMBw9uGMrV3tMzPJmDT5d2jiAnVM31t6THFJMTYhcdXl4QgfjsmhaU7q1i6v47JXaNpfxxQ9/mGMn4S9g9PoGuimXk7LLJAQ8/4IIZ0DJcFG5bk1shqqM2b+HVy9yhGdAxnTrZFhtNO6RIpAdIL8/IYlB7KxJ7HB3XPLyxkStdILu0Vw4b9tWwospEUopNVUoXXpYBRg9uGcu3AeBbvqmJ7SQMXtA+T6+Vvc/IkPPz9+FTmbLPwww4Ll/WMZnznSN5eWkh2yeHiDGINdE4I4o7hSbL67KI9tXSLN3FhlyhZtGNPhZ2HRidLD7Vvs6uIC9YyumO4rJor8t99sqZUFom4qHcsC3dVkVtuZ1xGOPEij97iQlnl9mhQd89ne8iINXH9oHhyim2sK7DK0OiJXaMornby7opiuiSZJYg8XjEJvVZUmY1iTNdovt5UxoFqF30SgxiaESG9/lbsrTv1wirHOWMpHnWtdxpXQJ0C6lpvNSk9KQooCigKKAooCigKnJUKiHDkwppcFu7+iOjgFKKCU9BI/welna0K+PGxuXA+CQxCb0tErREuIb9wNCJMzO0hNjaanl0zMRobi8D8wm6V3c8NBU43qHv1inayQmYT7BGhgMW1LhbtqmbN/jr0OhV/mJBGWoQBd2PBieZK7yqy8srSElTCFa+xiX8lh+u5fWg8m/JsfLml8givUjFGrVbN9QNiGd4hnK35VgqqnQxqH8abiwoOgbqHxqbIHHUvLSri9kGxjOsazU2f5qA9quqr+EreMSxB5loTHnWikusVPaPp1y6MrzeWM7ZLpAxRfFnkQhM56tJDuGVoAu8tK2Z9vpWOMUYu6RktK8OKUM69FXbmbLeQXdIg85fdMyqF2dmWQ6Gv1/ePlZVS/7GwkAa3j+v6xUrPMDGuDQetZCYG8f3myuPmqBOAKjJIK8M628cFSZ1NejXtYkz8fW6+9KgT+e9+Pz6FLzdW8GOWhfgQPZf1iqZnqhmDVk1Ng4cludWyIqvtOPkBhR0ChIox9UkLkSGp+yoc/LitQsIykaNOVNR9d9nh0Nd7RiQiQl9fWFQk4dWFncIZ3SmSIL0am8vLprx6qYmAfiEGDaMzIhiVGYFJp6bS5ubHbZWs3FdHeqSR341JZm6WhdnZVcSYdbIYRkWtU0K+OqdXAjRho16rYkCbUCZ1j5aa1Dk8ckxCa/GiY2i7MC7tE4NJq8Zic7N0dw2d44PQadW8u6wYEY46sWskQ9qHSw0F1Pt+a6UM25VVWkUYs8/P8Pah3DIskXtn7MHj9dEzOUQWLokN0UkvyPUH6pibbaG41s3Q9mFc9Z/CGSIMdmezqq8BwAxhRg3DOoYhCmFo1SqsTi8/brewZn8tDjkXv/QCoeSoa80zuaqy1uYP1rmpqa8TRT7kBOkMoUSYzTIh5/nalNDX83XmlXErCigKKAooCigKnI8KiGTdfgqqc9hSuJgqWxke77H5g85HZc7mMQcZzAxIn4zZl0hNXf0vfxDz+zHoDSQlxKHVaX95f2ezuIrtxyhwukCd4GoiZLLK0xii2sgXxJOrSQVGkZA/4BhKnRdcjd6izQ0WHqTC4yxYfWRIY1PfE7pEyqrn32VVyTDB5iBP/Nvp81PvDRxLJ/KJ+SFYE2Dh4nBWkRNc2KNGhkI2+CCisZ9DOcUbO3X4/PI5PEjYIjzXAJs38LuwXY5L7Ov34xV9e8Esc5mJY6lw+fzYfIHjivEYGtOOC43E38XvosiBtFvAdmmriv4JJkrtHjaVBwrYDUwwykIVImw1q+hw3r9DY2/kmXafX45HjE3mkUVFkFrkXhc5baHOF7C9qbCCyEcr7BDHFXoFqQK2i72PZkOBPOkqXH6/HKcIxxfbi/2kNn5wNGrVNMeibxGhb2zsU2RoF/oJ7cTfm7SSIEpo6A/Mj7BHjMGkVqEmsJbqhe2qwH5C2wZf4O9ynTQLk5b54IVXpg8cjRqLMTctFaGDOIawQegvPhPzKrVvNpYmXYQdTfPfBMzEMcT2op9wWXk2cEy7DxrE2EShDGFrs/7sjf0fnX+xyVNaAEIxP8IWUZrQrAmsLzERvxzTKaCuNS8LqifefMc/YUAaews2YnM7KVDsVRYAACAASURBVCnMxmoYxWO/uZ2EsPP3LZkC6lpzmSl9KQooCigKKAooCigKnC0KONwNeP1u+UCjtLNXgabZM2hNaNV6BaqdvVN51lh+ukDd/1IQMQaRb+zCThFsKbCyz+I8pvrp//L4p6NvcWoXwO+vF6XLnHD/XFNKfp2Lu/rHytDXd5YXU1LrUooJno7JOMeOoYS+tt6Eqj744Ea/J2w0ZnM9Xr+dgr0bKfP04fFb7iNRAXVKMYnWW2tKT4oCigKKAooCigKKAooCigKKAooC56gC5waoC3goibBIEZp5rr6uEIUKRCimqBIqQk3FixlLg4e5WVVsOFgnwy5bIxTyHF3qyrBOoIAC6lpvaaie+fwL//AEPwWWXTR4tVQWbWKHxcQtVz/PmMyU1jvSWdaT4lF3lk2YYq6igKKAooCigKKAooCigKKAooCiwK+mwLkA6oR4zZ2JWyFt1682Hz93YAEgRc45s0mHWqeWIag+lw+7wyP/rkC6M3LaznijFFDXelOkem3eJv+wmFJKPRY2fXwnNf3eoE+4FU3CeK4c2LH1jnSW9aSAurNswhRzFQUUBRQFFAUUBRQFFAUUBRQFFAV+NQXOJFDXBNtOBNqOiOxvSiwXSNV1XrfzAVKe1xP8Px68AupaT2DVfW8/7x+X0R59qIfcLx9lpXE4qaFtGT/mekZ369B6RzrLelJA3Vk2YeeYuaL6nt1tw+MTyV3PVaf7c2zSjjMclUqDURuETiPStSpNUUBRQFHgbFFAue6cLTPVEjt9Pj9WWwMOh0Mmaf9FGcNlxUstYaEhaDRKVeCW6H8+bXMmgTqR1F8k9D/e2awJRjUl/neLdS2qeZ5Pk3WcsYrxi8ICQhdRxEC085xbnucr4tSHr4C6U9fsRHuoXvpxpX9AUDG17lKW/vRnsj0ZpHeeykOX3UH7mJDWO9JZ1pMC6s6yCTuHzPX43BTV7GZr0TzqnBUIaNc6dXjOIZHOkqHoNEaSw7rQLXEUYabos8RqxUxFAUWB81kBp8eOxVqEw23D5xfpxpV2NisgXhh5bAbyD1Tg87XOfHq9Ptq1SaNtmzR0WlF3UGmKAgEFzgRQJ+BchFHNlJ4x7Cy2yYIQRwM4AepSIg2MzghHo1GzLb+OxHADG/KssojC+epVJ3RKCdczulMEu0obWLGvFoNG1gRVmqJAixRQQF2LZGrRRqpbXv2jf2zn/vTJbM/i1wdQ0fU90nXZuBLG8psRF6BvUTfn3kYKqDv35vRsGJGAciV1+1mY+wFGTQzJId1Qq8Qb6/P9Hd/ZMHvH2mh1VbPbsoS2MT0Z0eE66V2nNEUBRQFFgTNVAQHn1ufNYVfZUlxem3zoVtrZrIAKl9uDqaoHY/tcQXJSfKsMxm53sGb9Zgb27UVUVESr9Kl0cm4ocCaAOq8fEsxaHpmQxrLcauZmV0nPuqPbpb2jGZgWQr3DS1qMibxKO28uK6bK6jl/QZ0ftFoVU3tGMbRDBE99v5+aBo9S/fXc+HqellEooK71ZFbtLC/xpxgN7M75hufmvsedV3zDoLRQXD4VYWazdH89H9vpA3V+/D4vLo8HlcaAvskH+7SL7sfr9eDxId+Oqo/7KsmHx+PBr9KgVYukoyd3hhYXbK/Hhccv+tWjUZ98n9M+9DPogMKbbkPeLA5U7mRo6o0E68QNsPKgdAZN0SmYosLn93CgejNby75lQud7SYnIOIX9lU0VBU6nAuI80/z8fPTvLbdFnPd9Xjde1PJ6cuxZ/3jntBNcG0RfPg+iOp24hiiXkJbPw6lu6fV52V2+ntUHvqJ38iRSIzqjVeuUa9CpCnnGbC/C+HxMX/807uJkbhh/D5GR4a1infiOL1q2kq6ZGcTHxbZKn0on54YCpwvUiWIHep0an7go+MAvvL5EAQSvD7fHR4JZx8Pj01i+u5p5u2vxokLt8+F1++QLCJ1WTXqkAZvDQ1WDly4xRmo9PvJrhDedGq+49xbET6dGPhxp1PhUKjSyD68sNiGuZKIfn1YduM65fah0avweH16P75jnJHFc8eykEX02duDTalD5fLidXvSiL1HUQXTs9uL1+dFoNag1KnwuL16/H7VahVqnkfu7XQEPWZ1Wg08rQtpVqL1e3K5AJE7zxzRxbLmvXiPH5ReyqdWo/T78Lp8sHiGasE+MIcigYVC8kQ0lDmptbjlWobe3seBE00scrV4jx+5yeRWYd258hX/xKBRQ94slPNSByi+/aeJGuOkLGqj6cr631gZ1wlPq+G+m/dSW7WD9zl0YE4czrFMC4tbquNuKkyeNVXncNqrr6jGFRGMSJ2x8uBpqcLh9qPVBBJuCT+2BxtPAjk2f8FlpRx65cChhQSKUQZ7mD19ofFUsXvgBtqhJjOmRiVHULm/WfB471TWVOLxefCJcU6XB77axJ2cW2xyZXD70QpLDjXicVqprLDh8nmZVlVSoNUbCQ6MxG/UtgoDn4hp1e10s3fMpdqeHoSk34vE35pM5Fwd7HoxJeEPa3bXM2v13RmfcRMfY3ufBqJUhnqkKiOuKuBaJJvPQqDXgcVBRXUaDSzycHHnxV2vNxERGY9Rq5DUpgO5Odo/gx+2oYcPKr8k3duOyIf3QiNsMef1S4fe5qK0tp94l3tATCMVTadCIlz8YiYgIXNMOXTP9bsr2LeeN7TncPe5+Es3C/sZrod9NbX0V9XYbXl9gXIEnDTUajZ4wcT0xGJV7mhYuSLfXyfJ9n9PgrGdilzvRqJWQxhZKd8Zu5vV5eHfFg7iKErl+/L1EtRKoE88Mi5croO6Mnfhf0bDTBeoaPD7uHJJAz9QQKupdJIbp0WhUbDhQx9dbKjFpVNKjTnwWatQQbdZhsXn419oythdZGZcZwQUdw5m2tJjKehcGnZp7hidSVuMkOlQv2dyafbXcOiyR3LIGksL0RARrqbJ5+G5LBWsP1hMTrOOa/rF0SQrG7vSyu8JBl8QgvthYyeKc6mOcL4Q2ZoOG24YmCLaIGj8d4oKxurx8u9VClzgTPVLMEqgt3FHF7OwqxnSOYERGBNMW5HOgxiXDUh8em8qOEhtvLC2mXbSBa/rG0T7WJIFZUa2Tz9eXk1tuR9vszZaAfGnhBh4al0ql1SXDWWNCdAjW9/XmCpbvqcHj83Npz2gGtw0lzKSR1/wau5d5WRZW7Kvjuj7RtE0I5q3FRVTa3Gi0ah4Zk0yhxckn68rQKW/SfsVv3plzaAXUtd5cNIK61uvwXOmpVUGd30dNyTa25hfgEQ85h58m0Gr0WKuKKcjLJyhtIpcOTSNvXxaV9gb55uTwc4cOkyGGdm07EWMOwmMtZM2K2ZQZ0xnYYzDJEXryd85nS24eXnNnRo68gEjx1qRFzY+zKoe3Xrucp+oG8dGUyUQHG1BrtMTE96RjYgySyXkO8sqLN1Hb9gkevmQ0IYYj+3fZSli6eBrfZZXSv0cfCnZ/jz7xMoJKfmQjF/HnG68jLUJPxcGlvP7JX0ju9wDtwvTyQuBxVrJyZzaDht3F5O7tz2tQt2TPJzidXoak3ojHp4C6Fi3hM3QjAasdnnpm5T7P6I430jGuzxlqqWLW+aBAdelOdubtxyFfzhlo26YvqWF+tu3aQGm9FU0zUCcuP/qgRHp16UWkSU9NaQ77LfWktOlOdLDphN724kGkpmg9z75xG3vN47h/3CjUfjVqTRDJaQNID3GwZ88GNmf/mw3laQzv3gt/5QI+3LYeR20sTz34PkOTzOTt30yB1Y7KZycv+3OeXDefZ66cSbswLz6VkeSkXrQPd/HVrKdZZklnbGZH9GoBBNU4awtYu30Jg6b8HxO7dJMOEUo7uQIuj4NFuz9GhYbxnW8/+Q7KFme8AgLUvbPiQdwKqDvj5+pcMfB0gTqbx8fdQxIYlhHOkl3VzN1dw/gOYfRtE8YHK4ux1Dp5bHIbfF4fn2+upNLq5rbB8ey3OHh3RQljO4UzIiOcaUuKqKhzSQ+yuxtB3Xc7a5jaI5IteVbuGpGE1eFhxsZyHB6/hHn7yht4b0UxE7pGMaFbFF9uLKegxsllPaNpGxPEP1eXsuQkoC4jIZhvN5Wzu9rJ9f3iSA43sGpPNSsP1DOhcwRdksz8ffZBOiWZGZ0ZwevzA6AuNVzPI+PSyCq28e7KYu4akkDf9FD+uaqYMpuH2wYn4HB5eGlhES7h4df40Nkc1Ame9u/15ZRb3dw+KB6b28tri4tIizTw4KhkFuVUsXRfHTavn7v6x2LQaXh5USEZ0QauHhgvx5db0iCB5h/GpfDR2jJ2FloVj7pz5Uv8C8ehgLpfKGCz3RVQdwItWxvU1VfuY295ufSiDjQVGlU1X3/7CnnGC7h1wlhS4ntirl3CM2+/T4+xNzAgMabRzVlD1b5/8/LXu/n9kx8zrF0Cfq8Xr6OOnK0/Misrh/4X3CtDlm31Nnw+DeFx0ZhamvzTa2f3ujd5YVkOV0y8j3h9AzXlm3nn3adJv+on/jSpL9LBzpPHtFfuozb1bu6/eAxhRhESc7gd3DKdj+e8wtoSFb0z+1K0/yv0CVNRlcxlg7WQCePn8NC4UTgLfuDxaS9y8yMLGZEmcnapcNTv5+2P3yS5zy1cObjreQ7qPsXp9CigrvXOc79aTwqo+9WkVw58hAJeLAVreP9ff8GVPplxPXpj2b+MElc/rrz0Qswn9aL3UluUy9wlr7OoTM/Afjdx7aAeBOmP9bjy+zysXfB/TM8u47JRNxKq81G59yv++NM33HLjOu4eEA8+K2u+HMN9q6P46w3PUr/jae7+8UfuvmI6d42bTKS7jPf+3pfS3u8ztWsMaAwEaTXYXTY8zmoWffUAusE/8tDIOP752b3sD7uHpy8fg0mAOlRY89fxygc3kjrl31zbtx96BdS16PsgQN3C3I9Rq7SM73xbi/ZRNjqzFWgxqPN5sTu8GEwivNyPy+FArTOhPcH7XsWj7sye91/TutMN6rqnmHl1USEHLA7aRBq4Z2Qyc7ZXklti47FJbdhwoJYvNlVIyHb9gFgy4oJ4ek4+YzqGHQPq7hqWSIHFgcvnw+r2c6DSzsNjUlm3r4a3VpaiV6t4YGQSSRF6PlpRzLWDEqmsdfDGilIZmXZB2xBuHp7Ev9aVsXjXz3vUCTD40LcHCdWruHlIPH1TQnh21kFK6t2Mzwzn5mGJPD/rACnRQceAuocFqCuy8d22Sh4fl8LmvHr+uaYMk1ZFm3A9cWYt20sdOL0i1DawGppAnQgH3l1u59WFBTK0dmqPaEZ2CueVRYWofX5igzWsKrITE6JnRBszF2RE4PD6efGnfOqcPp6dnCpDiYXH36XdIunfTsDOQqqt7vP22e3X/L6dicdWQF3rzYoC6k4HqDvRfDkLefv9R8gLuZonrposPdTKD8znxU/ncenNjzMkLe7QnrU5H/DQ6/O46ZFpDIhzMevLV6lLGc+ATl0I95WwcctmOg2+iVRjDbsKc0lKGUy4xkZR8R6q3R487lrsHhXBRjNqlYG42I7EhZnRqLyU5q/jvR9m0qbPTVw/uA/4veRteocxb73Pk/d9zbW92iFSHwhQ99pLN7OsNoqRfS5lQPtkYpO6khAehl6jwe2oIv/Aar6c8zp5DbHoXftwaWNwEcnFF/2Oge3bEmnSUVm8ke/mzaRSa5IPUOLRyu/34vBGMWrIVQzKaPcr5uprvS/Xf9OTCH1dskcBdf+NdmfiPgqoOxNn5Tyzye+noWoPH71zGfP1l/LG3U+TYhahpR5cTjd4reSX7McqbugPSaNCpDKockO71L6kRwZLAOZ126iw7GP9qtmQdCFj+/eFqi3M/GYJw664m7ZhOiry5/L+jI/pM+UfXNi5DRqfg61LX+XPP83ngXtnMSJZi9Ptxm0rZuWC13ht+Wdow/pzw5QXmNirowyd8durWLHkO2qNemzWfRSXF7C1tJJeGcOJjkkhyVoC7a9iXHsdH824n5ygW3jikpEYZWIfaCjazLRP7qD9xf/i6j4KqGvpipcedbkfo1JAXUslO+O3OxmoEyHm9upCtm6cx4pcH737dSVWZ2Xlxu2YosMYOuwa2kWHHJNfWAF1Z/zU/2oGnlZQNzSB9nFBTFtcSGmti1QJ6pKYn1XFrhIbDzcWk5iXXYXL6+eqvjF0SzLzx1l5jO0YxgWNHnWVhzzqEmTlVxFyKn7+n733gO+quv//n5+9s/ciCQmQxd5TBbdo3VptHa2ztVqr1v7ab23ttLa1dbS1dbZ1FEWtqEUQGTKEADLCSIAsAiE7n+Sz1/3/z/0EARcEAiRwrg8fj4Tce+45z3PuPfe8znuMzLDxvVnZ/PeTFuZtblOfA2F1l5dsZs7H+7hqYjqrqzqYs7FNnbvyEs3ce042cze0smjrlwt1t0xLxx+G3y3Yra53vjk5jXHZdh6aV4vTG+Lc4ni+OSWd382rISv5y4W6BZUdPDgri6eX7mXjHjcGnUYV34RbrV6EmzhoE26/UCfcgdfUdPHiKiEuwgWl8ZxXkqAKdY1dQb4xLpnJhXFquIsOj4ibp8HtD/PowgY63EGuG5dCWqyJPy/dy49nZbKrM8BLHzchNH0ZOuukPXb96sZSqOu77pBC3UkU6ny1i/nNM3eTee4/+eakEQhP0uaahTz64rtcdNODnJGb/mntWrf+jQee/ICb7nuCKdkJODuqWb+9nNrGTlLzJzGptBiHJsCGJX/n3zU+vn/tj8g0OKnauZZGn5+dm1+hfLeG82deTrw5hrxB48hNjqNjz3LmLvwQe9Z0Zk+bRozFQMjbwryXbuVXlVn8/fu/ZFRGbHQBd5BF3U0zCtlRsZRaV5jklGImjxiDe+8Knn/nN1RHSrh69DlUrLkfw5CHsDW8xJw9Bm6a/SBn5lnYXrWST6pXoIsfS3psrPpyF4dwt9HpExk5+lxy7Efqttt3D0N/KEkKdf2hF/quDlKo6zuWsqSjJBAJ07L9v9z+u6spvugDfnLFDEz7i1IU/F0NVFSvpy2gfOrOKsZta80HPLumnBtveJmvD8895ObhoI+wRocm5GTNvJ/y1206HrztYWJaPmLOhwsYPPk2zh5RjM2gI+Cq5ZV/3sbC9mE8+v1Hsbh2sn7nFnwKBNormbvkH+gzL+Xi4aNp3LsMp20k35x5E2kxJnatm0OFM4lBugrufvMtHrzxbxTERzDoY8nMzMTsbeTZV+/mg/ahXDVuJEZdNH6dr20nC1b+k+lX/ZurxoyVFnVHOHSkUHeEoAbQaYcT6iJBN+UfPMbfy3cwYdB41m76Bzs1OUzLHolv74v4i/7MQ1dfRLzlUOtZKdQNoEFwgqt6MoS6Jz9soLFHqPvOmZm8f5BQt6wn6+sXCXVnCZfSDxtodkZdX++ckUFju4+/fdyMVaehON3K92Zm898NPUKdRqO6vuYmm3ll1T7VDbSirpsX1raoBg1Dki3cfXY2r69vYdFXWNTdMi1DjfH29+WNasiJ/ULdz96pVTOsfpFQ9+cF9dT2xKhTXV/3uJm/rZ0fnZ3NsysaWb/bpYqFIs6cP6Jg1moOEdgPJ9T9dmEDEwfZuWh4EvM2tVLb7mOfM6haHg7LsvOHhQ10eYIMy7Bx/bgU3vyklesmpvJqeTOrqrtkfLoT/Jz159tJoa7vekcKdSdLqAt2semDn/P//lfBzx+cw6h0IYYpBwl1P+KM3LQvFuryogknImE/Ha21bKprprBkLJq6f/L3+euYecmvmTo4SV10RQNyh1n34R+YvwVu+fbdpFhMaNSsrWFqNs1jh38Q40rKiLcY1HKbdrzDXc/9iaIJD3D/7LOx708a0SPUdefexV0Xn4VVF6Z5XwWVu1soHDKelsrX+du8l0gYdpEaY2jpsl9gK3mIEvMunnnvPabOfIgbZp1BpGk9f3/yGgqv+YALh2er91QPJUIorMERm4pVNeE7/Q4p1J1afS6FulOrPwdka4RQV/lfbv3d1ZRd+AE/Plio65kjRPKfQ5JLa2Ddh4/ylyVrues7f2NMevLnmx7ysH3lY9wwdwUP3vAXLiiKo2rzR3TEFjNhcJ6avU68xavXPM7Dr7zImPMf5/aZk1GC3XS4OtVM4FpPLc+99gyO4usYEVrMn+f9nWmXz+XbZ07HbtSx+PUfssIzkdn5jXzv5ce54twHybCFMJrLmDVtAhbXHv7xyt1sMV3B98+bglETUWPUefd+wnNzHmCotKjr1ZCVQl2vcA2Ikw8n1IUDHSxd/Brbm9owW4x0R7rxejQk28wEtRHCnjyuvPRrJDvMh2RvlkLdgOj+k1LJgSLUnTsklnNKEvjdBw00dfiwWQ08dMEgtjV08+zqZoQ0XfQlQp2wqPvb4j1cNTENJRjh9x824PJHOHdIDDfNyOTFVV/t+iqEujZ3kKcPI9Q9Mq+G1AQzs4cn8dj7dWxt9VOWZuUH52Sztq6b1z5p5cGzs6hr8/GbRXuw6zWMybYzvSCW9za1Udvh/1SsO5xQ96uFDdw4PoVku5GfvVtLlzeEN4xqNTcoxcKv/1evZn+NtRq4fUa6WLIRbzPw54X1qruuVprTnZTnrT/eVAp1fdcrmlBYfC7L42ACYnHxydY1/OzxO2npakCnjdofRCIRqrtbee+RZYwpnXhU0ESGu7C/m5pP5vB/z/8f478+n7tmjIq6gCoKTcL19YX/cclNP2RyzoHFkXP7s9z31AJuuu9JpuSlo9NEz1ciYUIhH/sqF/CfRf8hd/r9fG3UGHVnR4h0arptJcIni//A/7Yo3PKtu0m2mqI587Tankx86mqNcDiEq20zT7/4Yyo1ZfzklofIixMuTz3HZ4Q6h+nQHdagZx9v/OvHLOt0kxFvobJqIaaMc8k0NPFudR5P3vtLJmTZaNw5n4d/901cg88jJ6aHrRLAFUrlknPuYuaw3NM2zoEU6o7qseq3F0mhrt92zWlUMQV3exXP/GkaC2Ju54lv/T9yYvQQCREMRTCarep8IpQ6MacI0a67qZw/PnUzXUW/5aHLLjxgTdPz91DQza71j/GLeas4++LHuX7CEAyf7q2IciAcCuCq/i8PPXUP3tJf8dNrriEzJpqVbv8R7trOY8/9HnPuhRga/ot+5P1cN6kEs1YhHGrlX8/+gLWhSVw52MfPF6/gyR++TnHigesVVai7i10xd/LTy8/A1FO4t2E9jz3zTXIvlq6vvRnoUqjrDa2Bce7hhLpQoI1Vm6rJSc3FYQgTMBiJuP3YYnQoWgt1q9eSMXE8SQ6bFOoGRpef9Fr2Z6HumrHJlGba+dl79STa9PzswhzW13azdHsHF45MYuSgGBZXtPHsmsMJdRYeW1DPiBwH101IZf6mVtWi76JRyWq5z69s+sqsr7f2WNQdLNSNF66vn7Go+828GrQ6LbfPyFQTWKza6WRmSQJD06wsqezkqWV7uXlSKheUJTF3bRMN7X6um5ROlzeoxu3r8Ijs6tGJ8XBCnbCom5bvUJNjvP1JC9v2uJk9OpnhWQ46vSF+8V6dGodOxL0TlnSXDE9kXW0XTy9txHtQ0oqTPgBlBU46ASnU9V0XaD6qmiuFus/wFC/FXbt28u9Xn6PL3Y5WGxWkjl6oUwj5XXS6OtnbsJmqmnK2NbRSMOJmZo8frqbqVpdJikJL/TL+8sqrZA2fyKBEm7rgUbPYtZTz7opWbrztl4zPSSbg6aCjq43a2o3sbd1JZWuISeOuYlJxASadDsIBmvesZUtjg5ppds+OpVTuU5gwYQY2A5gchQzPLyHObEAJeeloq2H91lVs2LKKrqTRXDHtGsoyEhBa3gGhTmR9/TbOvPu499JZxHxGqPN3N/DSCw+yVRtPaUYSW7f8D3POBWRqq/jLSh2P3/sY0wfH0Lp7LW9tqGTM8MkkmxU87m46xUJy/lucef7DXDtmiBTqZDKJvnvLncSSpFB3EuHLWx+kiPnZvWslry18ElPGWQxOTyHk6sYeM5qJY0diUny0d7Th7Gpk276t1H78N/am3MIN51xGQXLU2tvvddLV3Ubt7k+obqymobmZURNuYeqwIZgOsoBWgh4a9mxj67YlrNm4CNuw73LFtKlkJTgO2nFXCHi7aGut4JlXniR13H1cMXYwdmscRp1CyNfBpsU/5+UNPvIHFeBr/pi36/384s5nGBqvqMZ/ZksiMZEW/v7v21nkHs4NU8ZgEJF51PlyO29/+CJTrv4XXx83Xrq+HuGzIIW6IwQ1gE47vFDXzso15VgUK1qTgt+oQ+kK4rBqCJrstFc3MeKsM0h2WKVQN4D6/WRW9UQJdd5QhGtHJ5ObaOKfa5pp6Q6SEWvk+vEpfLTDyc5mL9+ankF5TRdLdzoJhhUuLE1gaIqFpz5qJBRWuGREIhNyHei1GiqbvAgHoqZOP69talfD8hQkW/jmxBQWbutgyQ6nOoddOzZFjYX3/Ip9tPvCXDEqkbE5DoKRCHVtfkYNcvBSeTNLtnd+Lt62YGM16rhmTDLtnhD/Wd+CVqvhspFJlKZZeHzJXrp9Yabmx3Dp6CT+tmQvDc4A5xXHM7kglmA4wrp6N4XJZqpbffyzvJkUm4ErxyQxLMWqrtnq2v2qNV1li++Q+wvDjXSHAWHNJ+LZvbmhlYgCMwpimFYQywurm2h1h7h9arqa/VUcO5q9apKO8YMcPPtxE03OgMpRZKH95sRUXl/TxHvbOlQup6cf1Ml80vrvvaVQ13d9o3lhxU+lUPdZoU6rZc/uPbz/7iJ8fi9aTVStOhahzrl7NW+se4c2dwplQ4YwOKuM7OR0TPvdSnuEuoC3nbqG7XQEvMK+4aCaaTHqU8nNLiDerGX3lreYV1mB2TGMYVk55GeVkeSIUQOJqqJfOEhHyxZ2tTURVoQLkgGNRlg6hIkQwWTNpTAzH7tRj7+jikVr5rEnksHovFEMzsnBYbGqE9YhR3gfr7/6BzzpV3DFtLFYDYfGkQt6mlk4/wWc9iwKs7Mg0Ih/rQAAIABJREFUogGtgq+rkjmrW7jpsu8yMsuh1k1kXzIbTUT8bWxYNYePm+tRdMO48IxLyUt0SKFOCnV995Y7iSVJoe4kwpe3PoRAJBLC2VZNzb5aAhqFkGIhL2sMGfE2FHctb85/hnq3gjEhn7F5JeTljCDRblbj5wjL7d07FrJo4zpMsVlkZAxmUEoJ2cmx6DQijMJB+zkd2/nXojexxg6iMG8MQ7MHYzHq0R78Fa+E2bdrKf9Z+y5en56ZZ97PmJyknnMidLdsYd78Z0kc+z0mpOmp27WI/y37EH1WIQ59mEDEwsiym5ico+XdD56i3JvNBcW5aHqEurBzN6s2rqLsjHs4a2gRBpn19YieBinUHRGmAXXSkQh1K1YtJ+DWoTFF8Bu0KK4QNrOWkNGCZ5+XSefNJNkuhboB1fEnsbInSqgTwlOcRa+ue4TlmEiioNdpiLca1OQH/lCERJsBTyCMOyDCAIHDrFM3ltrcIdU4Qq/XkmjVqWsOkcTBrNeq2Vs7fRF1g0qEcIi36nH5wrgCYdUbKc6iw6DXqveYODiWkD/Ehmavet3INCvfmJLOk4v3sGG3SxUADz7EPcU/xVn1hCKo9xRHrEWv3rvVFVTFM5tRS6xVR5srhC8UUescazdyWUk8m/a62dHqIxRS6PCKdoDFGK2nuJsQ+jp94c/FjBPniWVbgs2ALxjB6Q2r60xxL2EwIhj6Q4qa2NBhia7vRLw8Edsv2a6n3RMmEFLUDLDnliTwteEJaubY2rYD7rUncdjJW/cjAlKo67vO0PiDIqSzPD5LYPP2dfz8ibtodtb3geuriCcXIhAKoGgMGPVi0SJep4dm5Im6HqkyW1Rs+0yl9u9XiCvD4QCBcAidzoRep1Mnj4MXS2IyiJZxoBRx3f7fPi1LXYQJF6ggaI0YdGJF89l69VREiRAMBUBjQK8Ti7PPTkARwqEQaHXqDtH+vwoX3GAojF5v/FzmMPG3UNBPSImgFffX69VyT9edmajr64v4/WGm5NxAKOJT+0MeA5OAEOr8oW7mVf6WmUNuYEjqmIHZEFnrU4JAdF44MCtE5w2NuoETCPgQSxOdTswDav62T+cU1SU2HCQYDqHVGXvmHBE54fPvJjGf+ENBtRy9Ggv1C95foryI2LARcW3Eosd00NwQDekg5gyd3hgV78QcEvQjlhXRQ4NeZ0avg1A4iIJeXaB9eoh5JSTqakCnFYuwU6L7jnsjpFB33BGf8BscXqhrZcUnVeSk5GI1hgka9ERcQawioZfOTn35GrKmTCLZYZcWdSe89wbmDU+UUKeucXrWOuqsoM5lB6+cDlr1iEngoPXVF59/gPf+eeuz5e+/pyhKiHD3nzeInHgTzy5pUN1Dvz4pnTi7gYf/W0On74Db6cE9+WVl7p/b1Kp+2o7oPCx+D2u1/ObiQWza7WLO+ha1PV9Uz/1t+6LRc/Aa88vaeCjDg6ZVwKTTkB5j5JoJqbQ4/fxl+T7Muuh3hDwkgf0EpFDXd2NBJpP4EpbrKlbx0ON30trHMer6rutkSacigVA4wLKdr+D0OJk26CY1zqA8Bi4BjUZLp28fC3c9wdnDbqYgeeTAbYysuSQgCZzSBFShrupFQMv5xbec0m09XRp3OKFOCfup3baclRWbcEciKGKTNRRRhfOQRkNOzlnMGFemuusdfAhrpsVLl1NSNJS01JTTBads5xEQOJFC3RFU57idImK+FadauW5SKolWg3qfNleQueuaWd/gQbV76MNDPHNdQUW1EBcZaU+0OCayyY7KtHLT1Aza3UGeWtqotvczRoN92GJZ1EAlIIW6vus5KdR9lVD3xJ20Ovs2mUTfdZ0s6VQkID6qt+xbztq69yhNPp90RyFC7DnUDfpUbPkp2CZFgy/URUXzIrqCu7mo+C4S7ZmnYENlkyQBSeBUIBAM+1le/TpObysXlNyGUWc+FZp1WrdBfFM8vfwefLvTuP6cO0hJPigbiyCjKIQCXrq9btXl7pBDAZMlFqu5x7L1oD+KUDDvf7iU0cNLSU35gqzQpzX107vxp4tQt9/oLdWhVxNICEtvkcm1sVtEBldz9Z1Sh2iv1aBR4/M5fWH2OgMy0+sp1cN91xgp1PUdSynUSaGu70aTLOmYCYgPHHegk3W757N93ypCyv5YhafYjH/MpAZAAQpoNXqsxngm5V5MQfJYdD2JaQZA7WUVJQFJ4DQjEFHC1LRtYvGOFxicOJ6M2EIMOhFUXM4/A3UoCKv8hZXPE+spI15bSEpywmfcA4+mZRqcXV3qJuL40SOw2axHU4i85hQlcLoIdarO3eN+u1/kFtZlp3L4nmhm+KgIqQZwOtXUyFP0mTzRzZJCXd8Rl0KdFOr6bjTJkvqMQCgSoKGjii5f+xdEK+yz28iCjjMBschNi8kl3pp2nO8ki5cEJAFJ4NgJiLln695VrG14jzZPDaGw99gLlSWcPAIaEfw+kzPybyTcEce+ffvQqL5qRy++qpkrrTZGlBVhs0qR7uR1bv+88+kk1PXPHpC1kgROLgEp1PUdfynUSaGu70aTLEkSkAQkAUlAEpAEBjQB4S7Z7etAuMLKbGMDuitV11Zh+WY3x2LW26QFzADvzoFQfSnUDYReknWUBI4fASnU9R1bKdRJoa7vRpMsSRKQBCQBSUASkAQkAUlAEpAETksCUqg7LbtdNloS+JSAFOr6bjBIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZKAFOqOwxiQQp0U6o7DsJJFSgKSgCQgCUgCkoAkIAlIApLA6URACnWnU2/LtkoCnycgLer6blRIoU4KdX03mmRJkoAkIAlIApKAJCAJSAKSgCRwWhKQQt1p2e2y0ZLApwSkUNd3g0EKdVKo67vRJEuSBCQBSUASkAQkAUlAEpAEJIHTkoAU6k7LbpeNlgSkUHccxoAU6qRQdxyGlSxSEpAEJAFJQBKQBCQBSUASkAROJwK9FurWN5M1bCwokdMJk2yrJHDKEjjYog7zICJo0eu0h2YdVxTCoSBhdBj0OjSao8ehRMIEQyF0egM6rbYXBSkEA0G06nXHUIFe3LG3p0qhTgp1vR0z8nxJQBKQBCQBSUASkAQkAUlAEpAEDiHQG6FuU72bf63eQ9bQMfTPZbLsXElAEugtAW9XG517dlL70u2kDjuTOG03u/a0RcU4jRa9QUfI4yKuYCTJ4Ra21zajFUKe+p+CeIco4lSNpkfcE/8WrYX4m/j3Az8rYEhk2NB0mrdX0RYOQSR68v7zUMvcX54oQ/wfRtHGMGxYNq11u2j3BA8VEnvb6ON0vhTqpFB3nIaWLFYSkAQkAUlAEpAEJAFJQBKQBE4XAkcq1JnNZmo7FJ5cWElW4UjVGkYekoAkMLAJiOff62ylo34rrsV/IjlvFLGaNtZtr0er0WBKzmNSWQZVK1ehDJ1EtrKPiuoWtGEfbq+fCDqsDgdGTRi3y0VIGNpqhMimQ28wYDIYCfm6COms2Cx6fM4OvPpMpk4ZQu1HK6iLaIi329ARUq8PKhrMVgcWgwav24U/GEajN2KzWdCEjRSPLKShYj17nH4p1A2kobeuYhUPPXEnrc4GdFqTWvVIJEJ1dyvvPbKMMaUTB1JzZF0lAUlAEpAEJAFJQBKQBCQBSUASOG4EjlyoM9ERsvDw3E/Izi/FYLYetzrJgiUBSeDEEFCUCK72JgLNlWS1f6w+1117drKmsh6t3khG8USml2awd+tGmnSJDEo00OXX49B0s758PR5LNqOLstBqI7RU72BnQxMhRcGSkMvw0lwMwQBNNVWYMgtIiLXib97F1p1+iiYUULt0A5HCIsqybUSCQVr3VrG11kPp+PEk2TQEWvayZlMVCYNLKUhLIBL0Y7Hr2VZeTmN3QAp1J2aI9M1dpFDXNxxlKZKAJCAJSAKSgCQgCUgCkoAkcOoTOGKhzmQiYk3gnmc/Iie/BJMt5tSHI1soCZziBIRRk6ttL5GaFVQvfYXSyWdhbq9m1fY6tCgYEvOYPjqbTYsWQ9lMRsd2sHxjCyOmjMVbU0nElgjtW6hoj2d8cQqV6zfS5vPhSCtlyvBUtpaXo80sJd3Yxqad7YwYPxLXzl1YstJpreuioDSbui2raAokMrwgjfptm3DrjLg18Zw9Mot1FTVk5WaqQmGHfTATi5LYvnoFu50BtL2Kb3diOlK6vn4JZynUnZgBKO8iCUgCkoAkIAlIApKAJCAJSAIDn8CRCnVGo5GcvMFc+us3SU/Px56U0S8tWgZ+j8gWSAInjkA4FMC5r4ZA+Rts37yUgtKJpOnaWV+1WxXqNPE5zBiTwyfv/g/9mPPIDtWw9OMWxp47mZhAJ+aETIwhJ96ADoPGQ+WGTezz+HGkFTE838aG5ZsZNO1cBjt8tHd6sdotNNVWYUnNxOUMkJGsY82y5bRpU5g8ppju9r0olmQS4uLIcfj5uKKJ9GQ9m9atxxlJY8qUYezZsoFGpy8K6ViyWhwHzFKo+xKoazev4KEnvktb1x50WqN6lnR9PQ4jUBYpCUgCkoAkIAlIApKAJCAJSAIDnkBvhLqSkhLuePRVWjRJJGUMVrMvykMSkAQGJgHx7Ae8LlyNO0ipn88n2yopHTcBU/MOlm+tRSeEurhsZkwoZNdHSwkNmUxWqI4lKxoZde5krO5WFEsSjlAzdS1u/B4n7Z0uQuEQ9vQSRhU62LB0HfGlkxmc6Gd3QxNer4u2LhOjxuWzr87J4KFZNFaupSkQy5BB8bSH7aRqO6jrMjAu386q9TvJGjyIfZUVdFkKGF8US/WOanTaCDs37yJoMfarxDZSqPuSZ+G9JW/w6PMP4Au40Wp0UqgbmO8MWWtJQBKQBCQBSUASkAQkAUlAEjgBBHor1P31+Vd5Z7eFjNxhGMy2E1BDeQtJQBI4HgRErlWvs4W2qrXkmppI0Pjxup00765hS+0+1WJW0VpU8S7D4KKh04fiaWZTRRuDx5VhbN9DcyiWiaMLMWgitDZs55Nt9QRDISyJ+QzJtrFz0xbcphTGjCkjNc5CsLuBtesbyBySReOmKpSsIsYWp6Hxu6jZspoadzKTJg/HqESw+JtYurYCR04ZxbmZKM5GnCKWXWeA1BiF9cs24reb0R4POEdZpiYUDvUkvD3KEk6lyxQIhYLsqqvkkb//kK31KzHqHdF0I9Ki7lTqadkWSUASkAQkAUlAEpAEJAFJQBLoQwK9FepeePGfvFjeQeaw8TiSMtH0wzhRfYhHFiUJnLIElIhIALGR9m3LaF3/JoGIAb3eoGZrNep1Udd2JYLf6yWoaDHotaDVY9RrCQcDRLR69IRxe3wIcUpvsmA26lXhLBIOEwxH1LK0RPD5vATVDK4mrGY9oVAYncGAJhzE4/Wp5ZrNFvSaMB63Vy0vojNis5iIBH34/H5xAwxaLTqdhnBEg8lk6FfWdGKgaJauXCSFup5HJqJEaNhXy/yP5rCldhUWswON5oCuKl1fT9l3i2yYJCAJSAKSgCQgCUgCkoAkIAkcA4FeC3UvPM9f5n5E5tgLSM4foS7O5SEJSAIDj4C7o4mWytU4N88n6Gw8REPpbWsU5fDh4sQ5qpgVtaf60uMLzzvSi3tb8T4+XzPi4jwp1PVA1WgUdBqh4gYwmk1oDxLpxClSqOvj0SeLkwQkAUlAEpAEJAFJQBKQBE4kgepqeOstMEZjUMvjCwh0dcGPfnT4VfBnLu29UPcCv3/sMbKmfYOkoROJScuD/Yto2TGSgCQwIAiE/F7a6rfSuXUJrp0r1EdYtaCTxzER0Ey+NlMKdUeIUAp1RwhKniYJSAKSgCQgCUgCkoAkIAn0RwIrVsDUqSDcLKWr5ed7KByOimWRyAkR6h75zS9JKhhF/MhLiM8ehjU+VS7y++NzI+skCXyBMB8JB+ncuwtXUy0ti59AozX3+r0hwX4xASnU9WJkSKGuF7DkqZKAJCAJSAKSgCQgCUgCkkB/I7ByJUyZAvffD7NnSwuug/vH54Nf/QqWLTtxQt0jj2C3GXEMPZPYodOIyyjE7IiXYl1/e25kfSSBzxCIRMK4WhpwNmyn45O3CbTvRqOT2Zv7aqBIoa4XJKVQ1wtY8lRJQBKQBCQBSUASkAQkAUmgvxHYL9T99a9w++39rXYntz7d3XDjjfDGGydYqLOhNVmIKZpFbP4oYlLzVLFOHpKAJNA/CShKBFfrXroad+Hc+iHe3Rt7LJSly2tf9ZgU6npB8tiFOgW/x4Pf60ZnMA6onSKtVotWp0On16PTC6W8bx5CkcXF7+kmHA6j1el70Rsn51QRe0OkjhE8NFoNOsHEYOy7uisK4XAIT7dTRawbQLsSGjRodWKc6NWsPNHMXX0zTkIBv/rsiNQ/Byd4OTmj4AjuqgYUUFQGYqzodHq0YpxIF5sjgCdPkQQkAUlAEpAEjiOBoxTqPB4Pb//3bV588UV27NxxHCt4YosePXoMd955BxMnTsQcCESFujffPLFCnd2uros0WgV74Qwc+eOIScvHnpAm3ehO7HCQd5MEDksgGPDRta8GT2sDzq3v498n3oc6+awellzvTpBCXS94HYtQFwr42L11HevmvcDerYsJ+9pAIwZ0LypwMk5VwGjLwJaYQ0xKDok5haQVlBGflkNcahZ6o0kVZ3rbEDXYrMfFjjWL2Dj/ZZqr3kajtZ+MFvbunmqAWwPmWMFkELGpuSTnFZGaX0x8aib2hBQMJstRp5f3dLZRsXQeFR+8TGfDmqgo9ZmkJr2r8Ak4W1HQ6myYYjJxJOcQl5FPSn4xKblFxCanYY9PPmphWuzWdDbvYcP7c6ha9m/cbTvRaE0noFHHeAsFdMYYLHE5OJKzic8cTOrgUhKzBxOXkonVEY9Wrx9QYv0xEpGXSwKSgCQgCUgC/YNAL4U68f1fV1fHo4/+nhdeeZqUIj3xqWa02v7+EX943OFIhKbtPtrqgjz0419wy/XXk3zvvWhOtEWd3a5uZor1gYYI1rwJOAZPwJacjS0hHYPZOjA2ag+PXJ4hCQxIAuLZVCIR/K4Oulv34G2to2vbEnxN29DqRbbmgf8+7G8dI4W6XvTIsQh1u7eUs+CvD9BWvwtUoWEgDWYhTkUnTohgdiQSk5RJ2pBR5I2aSsaQEdjiknolTglLuqrVC1jy3C/oamkEzUDzZxc8BJewysQal0FcWg5ZJePJHTGFlLxhWBxxvRhd4lSF1W88w+q5j+NzuUHT/y0MDzQwmpNGHSNKGK3egDUhg/iMQQwqm8KgEZNIyi7AaLb2iom7s42PXvojmxe+jKJoBhiTaJ+K8aEhjN5owZ6YSUJmHnljziSraAyJWfk9Fqq9wiJPlgQkAUlAEpAEJIGjJdALoU4sTvft28cjjzzC3PkvMvxiO7EZJgxm7Smx2aZunLvCNFZ1s3WBm7uuv5e7P1pG7ImOUdcj1KlfTkoEjVaHKaUQS2Yx1vRC9ZvSbI9Tv6Winj3ykAQkgRNBQF3tBvwEfS68XW14Wnfj2bMN754tBJ170WgH0nr1RBDru3tIoa4XLI9WqBOBFle+/CirXnsKjV6YdgsLtAF2CBV9f5WVCEokhEanw2w1kDa4hLJzbyZ/1HQMZqGoH/4I+r28/9SDbPnwDXQmx4D82FHdYHsORREZsqLuu1aHnqyi8Qw/71ayikar1mRHckTCIZ67YxTt+7rRGsTO4UASc6MtPMBEuAiHEVzEB5Uj3krO8LMYddEtvRKn6jav5q2HryUQ0ve4Fw9gJuIZEuOECAaTkdgkG8Omf4OSM6/AkZQ2MN8LRzKw5TmSgCQgCUgCkkB/ItALoU58+//7Xy/xs9/dT9FFRlIKLNE9uFPpUD+tFGrWuvAvNvGvDg8Frc0n3PX1kPAg4htb3Z81YYxNwl4wDWN8JnqzHZMtFqM1Rv2+1BlPjJeFWLsJ8XAgfpv3dqiKFZ8SFt/wwkBDHqcfAY1qORcO+VWBzufqJOjtIuR14WncjqfmY0JeN4SDPa6uA29tNlD6VAp1veipoxbqwiHef/xWNi9ehM44ANw7j5BJNF5bhHDAi8VhZ9TsOxhxzhXEJKYe1kc94PPw39/ewa41H2Cw9tby7AgreIJP2y9SiYktEnSRkDmYsZfdRfHU8zBZD9/v4UCAP8y2gSUXnf7IxL0T3MRe3+5TJuEQ4aCLjOKJTLj8TgaPmY7+CATMneWLef0nV2BwpPX63v31gigThUgoCBE3+eMvZvzlt5FZWIbOIHeJ+2u/yXpJApKAJCAJnCIEeiHUhUIh7r//fuZvfIFxlyehMwzAzfYj6TYN+H0Rap5u47ktXRQJj5FI5LDf858tWrXQ8/tpbGxU3YW/KDavOMdoNFJSUsILL7ygWivaD7KoO1Cm2OAUn0zCW8OP3pGOddA4jHHpaI1m1WBAa7SpAtrxEJWi65ywajEUl56PNTa5V95DR4K9352jKKrVlHBtDPo9/a56/aVCwmAlrGjRq+GfVEsFwpGw6kOj1+nQqL9HVF80nYhr3mPMoLp29xhiRFQhVMSxjv5dPSIK4t/FX0Sca434WYTTESJxj7WpKFeERRLXiWc0IoTVnnOEQUBY/VmL9igMPkS8cXHfcNCHEvKjBAOEfG78LdV469cQCfhFbB/Vh0qt81Hco7/04UCohxTqetFLxyLULXjiVjZ9eLyFumiiAzGnndAdH0VBWINptWGGTLuccbO/SUp+EVqt7kvpCqFu3u++w46PF2KwxvaiFw4+taex6ouix8vw05dGz+T+lSwO8Ipe9iU7Aj3WhOqfj5CveBFHwn6M1ljKZl3FqPOuJj5t0FdO8EKo++NsG4ol7wSZ9X/amIOg7mcqtjG/rFsOGmeHYP/qHRWVSchPbGoOIy/4BsNnXobZHvuVY3XXuqW89uPLMNiPh1B38Pg50t2go2v7l5IUE2zYR3JeGeO/9m2GTJylxmGRhyQgCUgCkoAkIAkcJwK9EOqCwSB33HEH65reYsRFCX36fa1u7CoBwp+xXNKgJ7oGj6DVGtFqorHbxLkR4b2hNaJRhFBwqMWTVmtCJ+JfH80hDNgM0PRMC79f1UGRKhqcbKHuMw0RnhrhIFqzA501CY3egPY4eOXsX0eZ04ZiSRlEbPpgrHHJp7TngxIJI9Zm7rZGPG0NePdV4e9oHFCBmo5m2Pf+GpH0z0dKznXkmCrYVLWVoDaCJbWYoUPLSDT6WL9+NV2RWEpKSomzm2mtW0mj20Zedh6KXoN/rwdNrBlHjANtoI2KTavp6hYWan4cg6dSkJ2G1WKke3cDbn0MaUlGqjevpq7NSW7JNPJSkyDcRdWG5YTiisnJyMSstFNXW449azpZsTaa6jdSVb2DSCQq8PXqUMSjH0QJeIkEPITdLSihAOgMp/Qz0CtGJ+hkKdT1AnT/EuqEECWCOgqXy2gjhKmyqm9rhJggfutR8FVVXhdV5g+WZIQLazisquF9Yc4tXHy1GoWskrFMve4+0gvKvjQb6rELdaL9wgVX3XNAoxG7aSG1daItYvdN3YXT6BCJNtVzwwc+aPZPwiLOnKKJmrIfEOoUIpFQtGx150MLWg1KOIBGYwRNGCUiOIv4JMIU/kvilIiPqkgInU5D4cSZTLzyHpJyCr/0I08V6i62oZiPQajrca9UIiLjqF7NTKtab/WMk/39rJq1R4RFl/gy06u7kmL3R4kE1HGjtltknBVc1MEVUctQdyzF31TGoWjQX63YWdnPJLoTo3L5AuFTHbPhAEazmRHnXc/oC7+JIzHtSwXM4ybUqWMnHH1GeoJBq79HPS0OHKIN4n/VjTfK4dC2m0ARzMREqIEet4jeCOXRsRnEkRjHhCvupWjaRZjtMb14M8lTJQFJQBKQBCQBSeCICRyFULe+WQh1iUd8i8OdKL6HhLVZcmwhsRYRAubA5mHQX88+l4Yku53W9kpcigGNEiYudjCpNgfOjno8piTSbPaeeMl6iHhpb6+hOeBFdzQhdhQQn3NN/2jh0f4q1PWsdtRN8/0ipRpSpI+PSBBr7hhii2YRmzUMe2J6H9+g/xQnOAa9bjydzXg7m3HXf4Jnz2aCXe0oQWlR9/meChPyt5Mz8lmKdW+wpHwRvkgaY279ITG711CbNJlRsW2sWr6M9BQ7Tv1kxgw10dzporR4MO8/+wTa5FuYcZ6WhXPmUnr+t3Bu+hMrPlyJ0r2HzBvncnZ+BytWu5l+8Wzql72EN6aUDE0Vcz+u5/xzxlC9ciGGYVeRHtlKh2YEIzO7mDvnRTLHTCLVqKFqXyJjxyaxZu5vqK7uxGg8GvF+/zpXrIp61kL9Z9ieNjXRjL0y81SLtHD0nSfW2Qf9/9mC+pNQp5pja7ToTWbVvFUV5qwO0ideRn6qnoZV/6Gm2qWKRGqI/4CbUOjAzlhUYNFisNgh5CcY8Ect8Xqvu3+KSRVhxMQZCZA9fDpn3PAAqfnDvlB9P1ahTggb1pwxFE2/kNDOxVTv6KRg5gWYutbz8Tv/w1Ewk5JpM4i0rmHLgvfxaIwYLFZVjNpvfhfye0nIv4zCURZqlv6RuhozWp0QmqyY4zIx281E9BYSSieRn5lE47rl6AaNIS2mmx3L59HSGkYJugj4/F9pKScELp02QtEZVzD12rtxCNfgLziOWajbb/lnMKsuBeFgN+Gg+JrRoDNZhIZEyOdTBUjRT8bUkQwdNYTm8r/R2BynJoCw50ymeMpEura8TtWGbUS0IlaeqKwJU0wyRrMBxewgbeQM0iwuasp3kTRuIlb3NraXr8PV3Y0S9BEMBNUWfqFg1WOBabCYGX3Rtxk7+xtq4o0vOvd4CHXCXD3k05A0/GsUj89nz0fPUL2rFbMjqSeD2/5XokYVf4WHqik2GYNeR8SeTM7IKSRoW6nfso/kkaMxtK9h27qt+NxewkE3oWC41zvuUWtDL9bYBKZc9yAlMy7sdeKNo3/cMMChAAAgAElEQVTxySslAUlAEpAEJIHTiMAJEOrUb2IiaL/Ewk11/zRZuGzyX5iQkYM/osdqiMZbC/u2sr0V0m1+Fqy5k2WNTjSmFC6f+jRnZOdRu+PfzG9soTBpEHrFjyXpDEY4DCxf9kNeb9qO+WiCuw8Yoe54jlMFJeTDkjOW+LJziEnPx5Zw6sYQDgX8qkDnbtuDr7Ue165VBNrq1Djk6iZ+9EP+eAIfgGULoa6b7BGPU6x/g8XlC/B2fpPrn/oGwV2LaNCPpDTVz4cvvUx8SQkO8whysnQ0draQYnPz2x/ex4TZLzB51Ape+vNTlNw+h4JgOYvmzSHUtYvM6+YwXLuaOYtrufG+37LlX9+nKXYSF44tZU2lhvy4eSz8z8vo8q9h5sVXqOsN05rneXFOC5f84lEydOupbTcwpGgoH8/5NZs2foL5CMIvDcCOOC2qrLnkjmQp1PVINzqdgtuvpbNbr4obYkPq4NdT/xLqApjsZ3Hmd+4mLUO4yikoOgOWhBRsRgO+9npcnkj0/arR0LTiRVa89Dxd+miSgrC/k/jis7jgu79A2b6CFf/+E7u7XVGBIfpmPuoHQDXlD7gZOv0KzrjhPmKS0z8nXByLUCe0tkigHXvpdVx2/yNY2+ey9M23GXrln8i17uDN+28n5rI/M+vCqex+6wHmPv0aqWc8xPk3nI0W4cuvQasJ42rdiFMzgqJchU0v3cGmKht6bQR/p4H40rMoLEkmYjATVzyZQUmxtFSUo80pIyHGy+7VC9Emj0JpWcNLDz+AwZb0leKMcA3W6XWM/drtTLzs2xgtn3dvPFahTrWGi81i+Nd/wpjiPDY9fSarVzcSCE5g1gN/Ii/Pz9LnfsmendUoIQO5Z93Pud+6BM/mV3n/6e+zpzWN/Iv/j3O//g1M3RWs/tdPWL1omSrWGaxjKDv3EjLz44gYHaSWTSHF4qVu/S4SR47H7NlC7Y49xGQMoWnDy3z471cIRw62Uvz8cBLWhtaYOKZd/wClZ34Nre7zOz59LdSpmcR0GmJzpzHxhp9SmOlk9TO/oaFrJJOvvQxHjBDn9ou5EGyrZMOc97EMH05igkUV6rJLJxCv66R+exOJJcPRd5RTV91FXGY21cv+wkdz3z/qGIPhoJ+41EzOuvVh8kdN/UImR/1gygslAUlAEpAEJAFJAI6zULffWk5spPtDfhGFKmqUctC3tdgINJqHcPmURxhtr6bcncHk9HzaOnehjx1OpinAzvrF+A0pdNS9xlbtZC4tHkNDyy4Sk3NoaliPV3iNEMKcMJ5hdi2LF32H/zRWYdEdRRbG01yoi8ajC2HJGklsyUxi0vKwJ2V+ZRifgfooCQ8Sr7OV7rZG/F0tuKrL8TVsIBIMRL1G5PEVBMKEfF1kj3iCoZq3mL90Li7tpdzwq9vo3vI+Le1ePC4nSYOvJCNmG9urbZSWZuP0tpFscfHrB+9n2iUvMm74SuY+8SSZN71EsbKeJe++Tsi5k8zrhVC3jjeX1/D1u37B1pcfUIW6i0YXsKIywoicct786xPYxt7NzDOn4gsqWDf8h//Mqebsn/4ce9sn1LU0EfY0s6d2K26X69SPq3gKj1fN228LW2t5CALCC9Dp1rFxp5UNu6x4/cIl8gCb/iXUhdEZciiadQnpgzJUd1fFaCWpeCIZ8XqaKxbT2BxU41qAj8Zlr7Jj8xb8WuFfriHs6yRp5IVc/X9PEKlYyvzH7qXa2a66AQqLMk3PeUc7MoTVllYbYNzXbmP8pXdgsjkOKepYhDohelkcIxl2xuWMuOh8EuwhGjasR5tVSka6lcaKFRhSJ5CUpqP2zWfZvHIhzYFCLvjRz4nTdODHhj1GT3fTXgzJ+djNETydTnS2BPSKh92r/sHcuVWMnj4ei9FI3PCzKMpLpXbJ/9APm05WXCdbPngN+9ALMHSu48Wf3ospJuOwVlSRUAC9UceZNz9E2czLP5cN9piFurAf+6DpnH33r8nPTWL3gmfY3dqJc5ubQRfdQl5hkPceu5varTvV7KPmpMFMvOkhho8tYs+ad2ms2wP2XPImnUdGsgVX4wa2rFhBwOumcdMi2i3DGTWqmLDORPrY88myOtm6pIL0M87D1r2a7RV7yCgZR9PGV/nwny+LfeSvtNCMusH6iEtL56If/IX0guGf27nre6EuiNaexOQ7n2XcyDR2rX4HUsZhat5Ku7WU0rIMWioW0eLNoHjSaJxb3ub9x3+DM2cWY0oGETLFkTvxXFI0e9i+toHMSTPQN71PZaWXnLIyapY+xbK5C9D17IofzfMTDoqyxjPr1l+ortLykAQkAUlAEpAEJIE+JHCchbpwJESMJYkJRbOoqPuYpvZaNWi8Gkql5xBCnc6UxxljfsbXhpTh87biD3SyvXED1oTx5Dti0BscmCItrN32HpaMc8g1B6ho3EViXAyfbH+HmjYnWsVHTMGNXDe0lA0rvsfLu9ejUcyqh1CvjtNcqBOhTczpw4gZdiaOjEJiU786rnSv2PaHk3u8WQJeF+72RtzNtXj3bsGzp5Kwp+Vz47M/VLl/1iGiWtSlDfk102ZoaNpTRyDQiuLIJ9FqorOjlc49CwmnX8IQh45GfQqDEjQ0NbaQbPPw1O8eZuysxxlZtJZ3nn2OjKv/QiGbWLlwHmFXPWmXPU2RdiPz19Rz6bceZMfcn9ESO55zRmcx9835TL/4ekwdtQQSC+ha9V98uTPI2vce773/Dhln3cPIsSU491YR6KphV8XHdHk0Pd5C/ZOmrNVXE9C8Pe+USzJ+TH0uhLlgSMPST2Ior7KhCMu6nsmuPwl1woIu5PWTVno9U79+MUa9BkVvwJqcSYxFg6upDpdbWNRpUTzbWPzgLTQ5stH2ZJZRhboRF3DlT59Ev7eKikVv0uqPWtT59tWxe9tm/CLO2TGYPEfCAWKTUzjnO4+SO2Jynwl1IhNNYvZ3+Nr/3Y7NsJOG6g414K6aRVME0jXoUUSW0YRcCgYlU/Pqgyyct5rxP3iRosIkNdNmQ/lyAgljGTQ0AX3YQ8vuvcQNHkFw1+t88Ldfsi//Xq6743r0rbWEzMkkJtlpWPsxxvwxpMZ0sXPlIjr9dvA1sHXew7Q4M9RYeIc7QkEfqTmZnP/9p0nJG3rIR9uxCXUivpxC3nkPMevar2Ho3Ea7x0JyXh5KRxNebTxG7V7e/cM91G2vVuPKxWaVkpqXQ0JGNj5TCpnpGWgxEJc5lKQUI611O3F2dKP429i56ClcQ2/l8ssuprN6I9qkAhzaNnZuqCd1zCQsnm1UbdhKQDHib97AtsVv0dkl4q8cQYKJQDuFU6/mnFt/gi0++RCEfS/UiVh7IbJm3Mp513+TkM+LESfr/3EPFR3juPgH38fWtY32cAr5g2P5+K838vHydWTf9h5Xziyjtb4GS1oepsAeane0kzZ8DPq2NVRtriWkNeGuX8a2ZQtweQ1HNB6+aLyInU6xoSkE7klX3vE5QfdwY0z+XRKQBCQBSUASkAS+gsBxF+qCOCzJXHvmPXR7Oyiv/ICafZt7IklHv4siEQ9paVdz6YQ7KIu3sqt+GY3eIDqtAZQgYcxkpIwm16FjV918Fmx/HfuQ73FNbhYfrL6LFsPlZMWkk5FcRJxZj9sXxOLfzhsrb2OTKxVzb5W601ioU8J+TGnDiCs5m5isYcSk5BzT+qe/PXvCmyTg6cLd0YSnbS/evdvw1K8n2NUE7I9n3Vtlt7+18sTUR3yjWx3xDBl5FemDMzBotUSC3bQ31WNPHYrZaMTbsY2OLoWEjELMShi3pw1vIIJJF6GlsQ5LzGCsZhedbU0Y4gsw48bl7ECJ+DDED8aCmy6Xn/jULHxt9QT1DmLtZlpqa7BmDSUpMQF8bTRW7kSbnost0E6ny4kSsZAwaCixdit+VxPrlsyhqXHvCUpQeGL4n253kULdF/S4EFyq6sy8vSoBf7CfCnU9WUUdqcPJGTUW3f4JWQSmV71d96tGWvDVUr3wVdyGdIR6IF7F+4W6K376JA69jpDPo6aCFqpk28pXmP/Mk7QFQ0eV2nk/0qjFlJ+yc65l1rd/jN5o+ZT2sVjUhUN+EjJv5uL7rsJT80def2weMRNuZ9r5U3FteoIPXviASFDBd+HP+e7tV7Dv/VeoiaQwYcY5JKWno1e6ad3dQEhRaN7yEXFls8nMEhl0fGx/7V4Wv/Ea2uIbGXf2JQwuHk5sgg3n1oVUVHWQO/VisuM62Pj2KxhKrqYgW2H1D0awqiUXg/7wk1w0LXeISVf/QI3NZjwow+exCHWCsyEmkbPuf43iQj0rH7+MOvdtzP7+tcTERNNo+9p3suD3N7Nt406MSVlM++6LDMvUsGvZy6x46884W7UEGpKY9Lu5zJiVyOInbmftu8vRW7Xo7SmkTLqGCTMuIL2wCLvRR93Kt6h2pTLirHOxd37M2pWVZE69jOSu9Sz8851UNZswHIEFvZoQhSDn3/M4wyafc8iE0tdCnYjlGAl3EzHlMvGep5k6bjBdu7exe+1vWb8xjpGXPkDZqNxoEuH2TSx8/Lts3baX5DO+y+SpZ5GSV4hN303lB/+m2TiC4dNmYGj8H+VrWhh85hXENL7H/x57gHp3LPojEG6/UKhT49X5SMwZxuz7/kTKoCGn27wk2ysJSAKSgCQgCRw/AidAqBMWdVedcQ82s51uTwdrq5ZSUbdcbZNwgRVZFRNiJjO64FzOGf41tM6VLNi2lZBIVqZEiIvLYnLxmbTsfYe31v+L5MxrGF0wi5I4A1UNK2l3Gwnrg5ByFiO1NazesZuRecm8tezbLGkKYdP30v31NBXqREw6Y0oh8WXn4cgcoop02qNxHT5+o/WYSg4F/bja9uJztuLeW4W7dh3BtmpVNI4m4zv82uWYKnCKXSzWLPa4FEonzcZgNKsx4qMPtXhu9zsp9sTOUhOe9PCN5vZT48urP0QX6wf9HH0zfJohUvyqxqM/+BxxbTSp36cJHg7+WS03Go8+FAywfd0C2vfVnlLj+RQbTodtjhTqvgCRXge1+4zMXZKEJ9A/hTpF8WC2X8P5991JWo6w/BPPbfSBVrN3HhzIXwOtS/7Oh88+SZshRhXfDraoo3I1y/79FA1un+r6Gna34XW2qcLdsb7AI+EgtsR0Lrzn9+SUjP20vGMR6tQ4Y4YEUopGE2Nsw9XdStr0HzP5zIn4Kp9g/kvvATFgisfqsNGybwexI69m0pkXkJKWgo4gEUWPxt+GL6xDh4d9W9YQsOSTlp1M86Z32NmQwZhzpxFri9DZ1IDX2UEgqGCwxmDAC5ZE4jOy8FW8w9yf3IpTWCse4WQnmKQVDufcO39FSu7QT0fg0Qp1akxAv4fBX3+G8684C5M2RHf9SvZ1DSIvV0f12g+xFl9HTrqGrpoVrHz+XmrqvKRM+A7TLr0Km+sT3n3xaQKBAPgzKLr6AYaPjmXD20+xY+06FCVIu99B2TnfYfzM8WhD3Tj3NeBxOglEdFjsDjQRL4b4XBKSHOx9/68s+NezdCn6I2YSDnjIn3Aes275CbHJB9yI+1qoE6zEZnXaqGuZdsP3STHsoa5RQ2a6CR9WzCJOZVMDvoiRuPQccFVTvvhDYjKmUjK5DHyddDbtxdvVSUhjxGyzoQn5MCQNJj7GQPVrv+LDt/6Lz2A+hiiP0WdZCbkZc9n3mHrV7RgttsO+zOUJkoAkIAlIApKAJHAEBE6oUGfD7eti/Y4lbNz1kQiBrQp1Yp4PhZ2kpp3H92b9EX33PJ4vf4pAOImIsofU5Eu5fNxt7Nr6M3694mXG5t9M2ZArmJlqZeXWf9IWzmdw1hgSHEUMi4/D72uhqvoFnl75JG5s6I7wm/RTWqeZUBeNR6xgTMghruxc7Gn5xGYUoDsFRDo1QVk4pIpzXc11+DubcNeuxde4HcIBOJpkI0fwWJ0up4gkgQFPC0rE39PkA0noov9w8O99HWFsv7D6ZeVGhT2NRo/BknLUMbNPl77s7+2UQt2AFepcmO03c8lD9xAbWsjGVVux54wi0L6VoD6PmFgr3vptOB0lTJl9Du4lT/Den39DizHpc0Kdsnkx8/90HzVdXWg0umh8Oq3+mEW66GaAsKrzMHL2nUy/5k5MNrtK/FiEOiJBQtYEyq7+NRPHDVVFSktMPBarkUB7K65ACPQmbHHxaFxbWPrUGaxfmkbp95/lrFnj0QZb8QZsKDsW0xmTR1K8ji1v/IHtu+3kjyqibc1TbF2Wz+x/PM2QzC42LV1Ed7dftVoUQo9wl0wbex5DhmRS+fRPePejpRj1hiMWZsRujMFsZto3fsio867+1Prx6IW6MBG/haJrf0ppSTwdrUFyx00lIcaIu34F7zz4MIO+8xxjJ6bgcfmwGANUL/gbi155lYxzH2Ly5DTqa31klhZj1OowOeKx2vR4nB34fUHcbeuY/+gP8QQv4MZ//x5d4wYqVizH64smK1HCYRSdkfzpV5IV52PlI3dQvnkLmOy9YBLBGudg1q2/oWDcjE93f/pcqAsH0adnMfmmP1AwKIOYRGFJ6cHvbKJ+7TbcoRbQmVSxO+zVo7CXrW8+RbfmG9z0z58QrClny5pygiGxFyncjSOgt1E48wqSwo0s/tnNVDR39Im7qrAcjU1K5ZIfPUNa/jCZeau/z6ayfpKAJCAJSAIDg8AJEeqSufqM7+H2d7GmcgHVezcBIvZ1z0JbiClKN0ZTAjlZt3DTlNtwBD9hXsW7pGVcyuTsImp2vMqbm5+ivKWSC89ZzHlJWcQoHTR6G2hu3Uk7WZTmn0WuMYA70M7yNT9mTtVKNFqbjFF3mJEovueNCdnEFs/CkTWM2LS8ge8iKL5dQwF8LiceNQ5dDd6GTXgbtxPxdanru54sgwPjOZW1lAROcwJSqPsyoa7RyNyl/dmizo/BMp1Rl5xPuP4Z6toncdbNl1H34e9pjb+KKaNy2fXsgyzfbWb8169Hs3MhWxa9h1tnOZBMoidGnVKxhAVP/ITaruOTGSYS9JOQNZhLHvwrSdn5xy7UCfFPq8FkM2EWubTMBUy///fkp2v45LmHWVe+jlDh2cz89g/JNday7G/fwJ/xf8y46iL0YQWNv5marbuJLyjE4bBhttoIebvweLwE2rfz/pN3U7+hkNlPPUVRPtRvq8DrDfSIThpEUoiY3FLSUx1UPvMz3lu6CL2uF0KdqH/Ez9ApF3PB3Y+gNwjXVLHJFeCPF9tQzL39WFDU5BBaowWjppuIbQbnPvg7CrIMVC98nLf/vJIzHn6aomFhVrz9Do6UdNzb3mLLmkpG3PI0U8/Ip+LFn7N21TL8zmxG3v4IYybFUf7KT9myfB0anZ/uVi+G2Cv5xnO/xtxZy+7KSvyB8AEhTqMladgkEs1drHr0O5Rv3IRiPHKhTrRfQ4QxF9/MpCvv/NSCrM+FOtU13E7u1GsomjyBvJJxaLz1eEMaup0a1c3ZGhuPXhPB29mOs249K5/8IY2Rq7jxn/+HtnkXDTt3EQqpjuLRQ2sgtWQiDu9uFv/yZjY3tvfJDpYQAZWwi1m3P8pIVdCV7gmn+Xwtmy8JSAKSgCTQFwSOs1AnYuHGWJOZWnqhmkxid/P2Q0U6dSM7iNFWwvCsCcQYsjhzxJXEUc+S7UtJTZvJiLQ0KmsWsL1lBx0dS2ixzeaCoecxLAaqGjfg9jrZ6fFSOOTrDIuUs6krliGWbl5e8n3Wdnh6n/n1NLKoE3GsdfY44kfMJmbQcGJTc/tkg7UvhubRliHiVPtcHXg6m/F2NOKu34x3z2ZCrmaZKOJoocrrJIGTTEAKdQNWqBOWTB3425rQ5XydC370CCWDPJQ/fx3O0r8yc0IO2353JwsaLJx1y40E1v6HtQvewdNjKRv2eUgadSnX/OIpVIu6x+6mutOJVuy2CPlFZ1GtmvpCHBBWdWF/HRf/6A01Bpko81gs6lRz9bCbkK8JXeqlnPGdBxkxehiuza/xxiM309xmwlx6JZf88I9kUsEHj92JbtrjjM/Y/v//NpXhDjcLfnAN7SMuZcoVd1A8JJbK/z1GqODbDMnw8d9fXcfO8nxm//UvFKY0seqtV+lo96I36FXf/4Crjawzb2LU2GJ2Pvtz3l28EH0vLOrEkBPur474JK595A1ik9OOUajbb7noRp80gsnf+iXjJpbRtfNdPnjiXio3Z3P+b55nWOH/x955wFlRnY37mZlbthdYdllYdukdFamCFRHsJhqjMYlG/aIxGtNNNCYxxhQ0MX5qNMXYE2MS9bMbFRsIIiC9w8L2wva7t9+Z+f/P3KVJcRe27zvKD92dO3PmOWfmzjzznvcN8co9X2PHJ8vAyCR1/Nlc/IMHyTG28PxdV7N1cyFm81hm/ugJTp3bn/cevolP3nwHw5OKjUHygK/y1Ufvwt61mOWvvkRzwERXCR2tGJZtMPaimxk1yOCje27k4zVrsD3JrY6oc5jEAgyZMJnzvv8wqf1yHCbtL+piWFYWs6//M5NPy8KK9scdrSEaqeTjRx+nxpXA1MtvItfdxIon/sKupmoaNn8MaV/ja4/9mODmhSx/800iTu5KDduMYruSmXTJt8jzNPD+XVeztry2XURdXN4GGXfyPOZ/6148iUld/HUhuxcCQkAICAEh0AsIdLCoU/ephmbgdnkIRnzozlTDA1+22ZaPtMFf5/pTb2ZMavoR7pei1BW/wk57MDkZObhMH6WVH7BoyzsMGfs95o+ZQfnW23l4+RvkZkyhpmE1NcFmDFWVqi1LXxB16kW5SoHiTabftC+SkjuKjMEj974wbwuu7rDunhRmaipmQ/kOR9QFyzfTuPFd7GAdaEZLTrTu0FppgxAQAm0lIKKup4o6K4ar/0ROuOhaJs6YQWpCjJ0fPMZ7Tz7AkKuf56w5E9i95GV2xAZz0pzZlL9xPx++vZaMcRNxGxqWaTr5GKacfSGUb2fDoreoDcdaclZGadr5X4o2l8VzubVDIE/EX81Jl/2Q2Zd/C3dC4jGJOvWmMnXEPGZe/BWGjx2Dx4hQteZFlj57O439/4dhBdmkDz2R42ZPx7fuaV6+68fUpQ5n9IyLGHP+Vxmk17L8+YVknTqXYcMGEazYxo7Faxh49hcYwDpeWvBtqnZPZs6PfsK4cYOJBptoLl5H6c5daKn5DB41mrT+A7D95Wx85n/54MO3sG1Pm6Sm4q/RzLnf/QvjTz33GEVdvPhA8rBzOevGWykYlEpT4WIWPXITO3Y1E/afyLl3PcKYkSFe/cN3KNqwFdwpnPDl+zll/gSK33uGbdvqcCUnYkYSGTrrQkaOSWHrkjco3VGKRpSaHR8SjJ7AOT/+Hv2T3UR8u6nZvILqWh/ezGEMHjWK1MxMInVbWP6XX7F2/RpMzdtGJhFS+w/golseJnf08R0j6swIRm4eZ9zwANmxHXhGzMEsep8qfwpa0QpKGnUmnvclst1+1v/fv6mIBqnbvpiY+ywuuPUm0j0W4cBuqlcvos4PCVkjGTxyOMnpaQSLV7HkoZ+xuaQMW1Pjoa2X44PXV1MYsvMHcMEtf6d/3rBj36BsQQgIASEgBIRAXyfQwaJO4VXZolVkvH4YYRbPJh1F132ghYDYfsnmVcJ45fYMsL3AALyuBGyrlrDZiGl6QRtAsteDbVURjnkwTZOoFcVlpOFqq6SLNxjdA1V/3c09S+sZp36m0nu08WZGScpwOExFRQVFRUXxF7qfWtQ6Ho+HCRMm8Pjjj7NgwQJSUlIOuW67DdWWnHSu1AGkT5xHSt54Z7qr27uv0F277asTNqTGViwSIuSro7FiB5G6UgJFnxCq2twyxbWNorYT2iy7EAJCoG0ERNT1WFEXwTNgJrO/fD1ZKX6KV7zB5iULqa9tIGPKjZx+6XySDHUboKPZEba88VdqPMcz5dTpeFq+NFVlWM0wnLd4Viy6N/UlRKj6+LcseW0dUUtNlW3boDrU2ioyaMzsecy74TdOPrljiahT0WgZoy/hlEsvwRsrZufK99i58m1qa6rIuuxx5k4e7OTYI1TFmn8tYNO6DVj5p3Hm179PbqKL+sKPKS5L4LiTJ1C19i3KmvszcepUPF6d+g3PsfjFd8icfjnjjx9HclIKVqia8o+eYfWHy9FzpjFp/qXk5w/GDNXRVLqe9W/cT3VdKrrRelDxaY1+ZnzhZk796g+OWdTZZojEgrnMuvxK9MqPWfvq01RW16K53MQC+cy8/mcU5IdZ8o97qdixCy0hmRHzbmb8yERWv7+WkXPPIytV3Qxq6Goar2aj3tA57bSC7Fq/lKCZScGoUXg9XiL1W9n637+xbUcNyUNP5vh5n2PggAwizdXUbFvCxg9eocFnt7qYhHOPqHL3eQzO/c69jJo5v2NEndpHSjIDCkaQnj+T2V+5nrKFC1iyLsbJ515CspuW4wcrGsWMNrF1xTL0zDyG5BXgchtE6jex/rl7Kd5tkDZqDifOu4D+GYmEGquo2vAmG5e8Q3NQFdI49vNGJQNO65/Bed97iLzxU459g7IFISAEhIAQEAJ9nUAniLrPRqyiu1SeOjNeDO5Ii7pfR6XuUGUoVES/+n+w7FhLYUiXI7mO6bajl4s6FUlneBNJn3gOacNOJH3gUNwJPbNQlxmNEGyqIVBfTaB6J/7iVUR278QMNTlytz1mQ332+JU1hIAQ6GgCIup6qqhzvtRNDFcMzdYxTc2Zfhi/ONsYroAjW5zFNjDNBNBVKH4wXtr5iDcELrBcmKYLu+Vm4FgHohIOg0fmcMGP/01q/5xjEnXqhkYjhq7K0lsuLFOl9Vfh3TYYFm49FJeOtotYVCVOVWWyNVxG0Jl5YJtuh4DLMDGjBpZm4nLF4qhMN6blxfAkoGthR6bZtsuJLLRUfjtHZJnoWgyMZHTdQyzcvB/71pFypgNHmhkz+zw+9+OHnQ8dfY66eAlvu2U8YLqImeqw1XhQ3a2hu7al9wYAACAASURBVKPOeDBNt1O5O14RSE1dVdGVBro7hGYrBoe4WdRc2HZyvMiIwySIbbmxLL2lQriGrqu3wur+QBUL0YlFQy0Vwlt/2+gUHonWMP/G33Pc/K86TNp76muck40VDZAydBbjZ5+Ob8dCtn6yCsOIgmYeiEBzO8eupoFjq+MOY1nqDbZCrqlDjR+7qrbsHDtOSXTb2lctunUj4tBrqRtLb6KHc759HyOnnXEsm5LPCgEhIASEgBAQAopAtxB13awrbNC8UP2XXhhRZ6ubYsiY/HnShk4mc/AoXJ6ENkcLdnWPqXvCUFMdzbUVhH01+LYvJVSxCSvkd+5t48+Arb/v7urjkf0LASHwGUrmpZcP9WTet7G5DNjVzYtJ7OuhT5eE3vOb/YXL/hft1paJbt8LvWVZZPZP4Qt3vUBGTt4xibojj85PH9+hjv1Qx3a40tpqb0da/3C//+xzKBpqYtDo47ny3leOXdR95u4ON04ONV4OtbG4AI4vhxsbhxtzn9m4vStEGquZe8NdTLv4eudn7S7q9muKknXBpnIMbxYJKelHaGTnHPuhGuDkuTFs5n/rd4w/5bzWg5Q1hYAQEAJCQAgIgUMTaKOou+WWW/jv6ieY+oX+GO6Dp3L2CswahEMWpX+p5c8bmhin5FaPn/oaj1o0PImkH38hqUPGkzFoRI+KpHOiLW2baDhAU3UxgZoyIrVFNK57xSlupxs9Tzj2ivNFDkIIdAIBiag7BOSeJeo6YZS0wy7UF01qShJf/O3zZObmd6Coa4fGdtImIsEmcoaN5poHFzp7PKaIuk5qc0fvJlRXzZk3/IKZl36zw0VdRx9Le2zfiR7VTM6+6R4mnH5he2xStiEEhIAQEAJCoG8TaIOoUy+an3ry79z5ux8z/kIX2SMSHH/Va8Ic1DtW5R41KF4VIPCGzlNNIUbWVPd4UWfbJrrbS9r4eaQNm0Ja7jC8SWk9ZmqoiqCLBP2EffX4a0rwV2whWL6JcPUWNGcmUS+Vxn376iRHLwT2EhBRJ6KuU04HJRxSkpO4bIGIuj3AI0EfOUNHcM0f3xVR1wIlqETd9b/gpMtE1Ckke0Td/JvuYaKIuk65VslOhIAQEAJCoJcTaIOoU9/DJcUl/OIXv+D1Rf9h2mWZZA724E5U+T56Pifbsgk3W1RuDbDm5SauPe9qfrTmEzI+/LBnizrbcvJwp449g7ThM8gcMhZ3YnKPkXRmLIq/rpJgQzWBqu34iz4hUleCFVEpjFR6lV4w+Hr+6SNHIAQ6lICIOhF1HTrA9mxcRN3BmEXUHcxERN2BTETUdcrlSXYiBISAEBACfYlAG0WdQlNYWMhvfv0bnvjHowwY7SI7PxHdaAlF68HszFiMsg0B6ktNfviDH/P9G75B1ne/h/b88z1Y1KnpoiZpk84jdehk+hWMx+1Vkq77d5Qq5BZsrKGpsohIcw3NW94jWLYezfC2FBNRnq4HHEj3Ry0tFALdnoCIOhF1nTJIRdQdTtSN5Jo/vuP8Uqa+gog6EXWdckGSnQgBISAEhEDfJdAGUbc/pMrKSt5auJAP3lvEjs1FxCLRHs/Qk+DmuKkTmXvWHGafNIt0VRnsa1+DHirq1HRRDZPUCaq66xTSB40gIa2fUwyuOy+q6F4k4HOi6PzVuwhVbydQsoZYYyWa4RE51507T9omBDqIgIg6EXUdNLQOFg4HTH0NBnjhzhvYuvgFXKneTmlDd9qJul2IBCIMHDmc6x5Z1SLqwiw4IxE7ORPDpfea9Cdt4R4q9zPvewuYfeW3nI9tX/4u/7z5Elz9VOXZ1hZCacseu/e6amqDZns59/v3M+nMz3fvxkrrhIAQEAJCQAj0BAJ7RN2118KcOU6y/tYuYSAUjWK14TOt3XZXrKfuRw1dJ9HtxqWOKRyGP/0Jli/vcRF1StLphoukYdNJH3MK6YNGkqgkXTfO5ebkoQs046+vIlRfgb90A8HyjUQbyrEtE003umJYyD6FgBDoBgRE1Imo65RhGI+oS+ayu58jc2A+sUiYla/+k6rCTRievpkM1YxapGX14/Qrb3H6wDJNXvvfn2AbGrrevd/8ddSgifpjTDj9HEbNPMPZRWXhRj5+4RkMj9lRu+wB23Vz3NzPMWTc5B7QVmmiEBACQkAICIFuTkDlXzv5ZEhKAo+nbY1V0w5749TDluqijrQMBCAa7XGiTgXNpQw/idQRM+g3bCIJyRnduq+i4SD+ugoCKhfd7p00b15ILNDkCDrJQ9e201LWFgK9kYCIuk4Wdbo7uTeOo1Yck01ySiIX//zvpGUNdMpl6S4Pugqx78OLEphmVL2fVYuGy7lh7JuSbs8wUOH/6o9DRDect6N9OmmuGiNmrOXGrQ+fLHLoQkAICAEhIASOlYCKriovg1UrQXcd69Z67+cjEbjgwhbRpXK+gSshCZfHe8R7MnVfGw6HqaiooKio6JD3+Wodj8fDhAkTePzxx1mwYAEpKSlH/UzgzLiwwiQNm03G+NPIGDyKpIyc7lma1wbTjBJqqsW3u4RQXSn+XasIFi9DM5KkkmvvPaPkyIRAmwmIqOtkUWd4laiLf+H1tcVw2WQOnYHLm+Acf/yFZN+WUs4w2G/6RJ8WUntOCNved3qoF9d9fIw4Q6SPXjP62jVSjlcICAEhIAQ6gYBhgCGS7jNJ732RDJHGOqZfej3jT5qDdoSX7J0t6uJFtzQSckaROflC0gYOdSSdrvq4my2WEnTNDQTqqghU7yRQtoFQ1TZizbWOoJNngG7WYdIcIdDFBLQXX+qLyujI1F0GFFV6eO79LAIRVQI7vr5lWRT6anhtwQdMmTiz1V2nooPe+P111DVGmTzvUueNUS9JbdFqBvEVbWwr1qZcIG3cgawuBISAEBACQkAICAEhIASEQDsRMGMRXr37fzjzu48z7eyLu4+oUw9ThkHi4ImkjT6FjCHjSMrMRu9med3Uc2A40OQUiojUl+MrWkWwbCNmoLEl6q+XTqdup/EnmxECfZWA9tzzIuo+3flK1BVXG7zwQX+CUXe7iLrXFlyHnT6U875xK5qE2vfV802OWwgIASEgBISAEBACQkAI9BgCsUiQ+y4dyGnfeJRp51x8xOIMnRlRZ5sxEvMmkTZuDplDxpCSNbh7MdW0eCXX+iqCKhdd9S5SfVuo2LmJWNSMR9D1xnyH3asXpDVCoMcS0CorF/XBSZiH7y8FQ1U/WrtlHb9//AHqm2vQW8TasUTUvXb3dVgp+Zx/w21ObjZZhIAQEAJCQAgIASEgBISAEBAC3ZlAJNTM/146gNNueKp7iDqn8IWFkZTAgFO+QerA4aRk5R11jrv2Zu/kn45FCTZU468pdQpF+EvWEy5bS8GwkZSWlRGLxWSqa3uDl+0JgV5GQFta+LyIuk91qirjvX3Hdp585m80NdeJqOtlg14ORwgIASEgBISAEBACQkAICIHPJhAN+bnPEXVPdr2oU5JO1/H0LyDj+HNIyx1Fav9B6C73Zx9IB6+hBJ2lBJ2vlkBtOf7qXQRLPiFUVYgVCTqRiAVDh1JaWiqiroP7QjYvBHoDAe3RRT8TUfepnjQMnbKSMt58bSHhcPzCqhaJqOsNQ16OQQgIASEgBISAEBACQkAICIHWEOhuos6bPYrUsaeRPmQsaTn5ewMqWnMsHbWOykMX9NU7UXSB3cX4i9cQKl+PGWoEzdUSPadRUFAgoq6jOkG2KwR6GQEtGG0WUfepTlU5A9ZsWMFdf/wu1Y0lGHp8qqqIul42+uVwhIAQEAJCQAgIASEgBISAEDgsgW4j6lSFV8NP1infIW3QaDIGDQdaKv51Wf9pRMN+mqpLCDXVEijbiH/HUmK+ajTdfVAOOhF1XdZRsmMh0OMIaLaK05XlIAKfrF/Kzx+4kd2OqPOKqJMxIgSEgBAQAkJACAgBISAEhECfItDlok49qmpgJKWSOeWLpOWNJS07H6MLp7valkU0EiTYsJvm6mJC1dvxF60iWlccl3OaccgxIqKuT506crBC4JgIiKg7DL6Vjqj7JjWNpSLqjmmIyYeFgBAQAkJACAgBISAEhIAQ6IkEulTUOfEkNu5++aSNPZ20IeNJGzgUlzseRNEVSywcINhUh7+2jEBVIcGy9YSqNmOrAhG6EnSHj/ITUdcVPSb7FAI9k4CIOhF1PXPkSquFgBAQAkJACAgBISAEhIAQ6FACXSnqbCuGKymF9OM+R1r+BNJzh+PyJHTo8R5u42oSmr++yomiC9aW0Fy4gnDlRqxYBCfoT0XSfcYiou6zCMnvhYAQ2EOg3USdbVuEg35wJ+B17Uma2XNBS0Rdz+07abkQEAJCQAgIASEgBISAEBACx06gS0RdS2Ym3eMl44QLSRt6AhmDR2IYnVvdVck59Sca9NGkprg2VBEsV3noPsYKN4HKQ9eGRURdG2DJqkKgjxPQfIHGfTnqWt4GqCqnhuHBbWiEwwHMPWuoKffqd7qBx5WAru97c2A2b+fPTz5AwYxrOHnsMFy6jm648Lg86Lre5ak+29rPIuraSkzWFwJCQAgIASEgBISAEBACQqA3EegSUWeZGClZpI07w5F06bnDcHmTOvV50rJMokE/gYZq/NVFBKt3EChaSaRuF7orqaVQxGdH0e0/FkTU9aYzQ45FCHQsAe3+f926V9RpmoGLZKIhm5Hjz+fUkZm8//7f2B4MoqE71Wt0y0Nqv4nMP+k8spNdLa0z2fHB77nqyXs54YSLGJOdhU4yntRxzJ0+j6H9kp28mj1pEVHXk3pL2ioEhIAQEAJCQAgIASEgBIRAexPobFFnK0mXmE7ahLNIyz+O9EHDcCemoHWWptM0oqGAI+hCTTX4itY6UXSqUIQVDbfkoTs6yiLqjo6bfEoI9EUCms/f4AQXK4+m22E+eOWn3LeoiO/c9Ffmjc51Iupiqhw2Gmaogj88+gt2Z57Lr6/8Eunuloo2u9dzxx9mknz6W1w9ayKJLlj/0rU8uiODb199L+NyUkTU3X0dVko+599wG7rL0xfHmhyzEBACQkAICAEhIASEgBAQAj2IQGeKOpVKSTNcZEw6l5Shk+mXNxp3QlKn0VL799dV4qsuIdxYhW/Tu0RqdzpPyvGnYfWfRx99IqKu07pSdiQEejwBrdYXtDOSveh2lKI1T3HXk7+n4JTfc9O5c8lI2Dfv3jbDbP7orzz81pucf/kfmTtmCBoW0eYK3n39bp7cnMqPvnYTwwakk+TReenPc3hfu4JbvnoNuSmJnfUOpN06RCLq2g2lbEgICAEhIASEgBAQAkKgCwmYVozdTaXsqFpFdVMJpml2YWs6Z9fKpyR4khiRM4X8rDEkulXgwKElS8yKUesrZ0fVaqobdxHrA3zizkmjX0oOw3MmMyhjGG7XwdVUO0vUqa7R3QmkjT2T9JHTyBg00omkU1VfO3qxYlFC/kb8NaX4d5cQqtiEv2g5diSM1o558UTUdXRPyvaFQO8hoH37bw/b1845i9TQDm555IsMnHA3373oCgoyU9ibgs6OUrn9LR545Gc0jf4GP//y1+if4CLqr2TRm/fwwpYwl5z1Zaq2v0ihns30QVm88Mr3GHfGy1x9+nSSPS2Rdz2Im4i6HtRZ0lQhIASEgBAQAkJACAiBQxIwrShbylfwn+W/pqx+G77wbiyrD8DSwGN4GJBSwMmjv8IZ4y8jPSnrIFmncpFtqVzBq6v+yPaq1fjCpcSsTpto2aUdoWk2yZ5McjNGctaE65k56lwnD/n+S6eIuuQkdE8iaePOJG3YZEfSeVMyOpyN6vtIoMmp5Kry0PnLNxOq2Ei0oQw0w8nN3p6LiLr2pCnbEgK9m4D2h7tn2Usb/QSCzeRN/C63XHgV+ZnJGPssHbW73ucvT32Lj3YbJPcbwle+cC/zxo8k5i/j/fdfJGnYWcwYMYSaus2s27KI5//xIHUTr+KuK77NqKz9hF8PYimirgd1ljRVCAgBISAEhIAQEAJC4JAESmu38dA7V1FcswtDVwn521c+dHfslh3E607k4qk/YO6Eqw6KGqv3V/HXd3/I2pK3Wvj0vACDY+sDC9MO43F7+fZZj3Jc/qmdK+p++1tS01JJn3Q2qUNP3CvpDhf9eGzHGv+0U8k1HKB5dynhQCP+XatoLvwYK+TDMiPxc+QYprgero0i6tqj92QbQqBvENDCzWX2Ky/9lFvfWc8vrn+GS04cikvTnWuTbcWoLl7Go8/cij7++1x98nSW/Pd2/rimlqs//xsunjoGr6EqutqoNxJNNVt5+flb+HfRCO686U5OyEvvsRRF1PXYrpOGCwEhIASEgBAQAkJACADhaJC31z/Dv5f/HI2OyPVlsyfZ9eFi0JQU2bPsky/23gmNB36uZXst0zLbqxNNK8Dw7PHcNPdvZKXlHbDZJVtf4vFFtzmsdH1Pobz22nPHHE97tW7/7YRjTcwZdyWXn/RjUhIy9/6qoyPq7r771+ROu4S0EdPolz8Wb5J6fuyY6a5q1FnRqFMooqm6mHBdKc3bFhOp3oLmVHLtWIktoq4jRq5sUwj0TgKabZl20F/O4jfv4NdvVvOjm/7IGeOGoAfK2LhuIQs3bmPA0FmcO/tM+ie4CTSV8MbrP+dHKyzuvfKXnDtxEIGmUpZ88G+21RXR7BrM/FOuZXJBdo8mJqKuR3efNF4ICAEhIASEgBAQAn2egD/s49mld/P+ln+ga+0toVRkkp+IaaHrXgw1VfAg4up1vknMCqJribh0lf9aveAPEbWi6HoCbn1fkTXbjjrrmnjx6t52C2pSOfqSEtzcdsF/yO8/8YBWvrT8zzy74se49QGHzWF3tAMpfjwhLNvGYxwq35oipv7sKe33aUG1h+ie36uW7D9veY9YUj/THNF0tKUOLDvKiOzj+Obch8hKHdRpou5Pr6xk4IRTyBwylsS0/h0m6cxohJCvHn9dOYHqXQTLNhIsX4cVDjoFLDpjEVHXGZRlH0KgdxDQbOc1l020uYzXXnuWodO+zJiCgVhVH7N4w1YGjDqV0QNzSfK64xd+2yLQWMo7G7Yzbsx0hme6KCtewZvLPmbKrIvI759DelIyegeEC3cmchF1nUlb9iUEhIAQEAJCQAgIASHQ3gT8oSaeXnIXH279D4YjydprsTGtEAne8UwbOYn63R+zvXY3lu2Je6eWxbYCGAlZjBt0PKG6dWysLcbWAqSmTWLykOk01CxlVeVGDD0Vl2agG1mMyZtJtmcXy3d+RHM0DY0Qph1t2aLhCD+9ZfZPa49GiTq3O8ZPL3qRoVknHPCxF5Y9xL9W3kaCK6e1m2vVerZtortcjMw7kwHabtYVbaDZdu/LAe48V5mYqKmWXrBD2JobQz2X2TFcmgfTaiSGG4+eCoSw0DFQAlNNz41hWn6HjUvPQCdG1GrA1pLifFrVyv36yo4xpP9wbp73GAP2izrsqIi6sWPHcdsDz7KhVicrbxSJGSp/YPtHtKlZXyFfHYH6aoI1RfgKlxOpLcYMNOBUmXWeWdtKq41wW1YXUXd03ORTQqAvEmgRdc43BWbMRNPVtFcdnDdAYBiug6WbbWPaOD933pNZMWddj7tF5vUCkiLqekEnyiEIASEgBISAEBACQqAPE4iLul/x4dZ/t6uoUxIqYoU5fvJD3Dx5Jqs3P004aRJ56Vl7aSv14av+iPd3rGDOqb8l0/c+jy5eQEA/gcmjv8B5E09hx+a7eWlrIdFoGaW+LRiuWVw55zdMSX2BX7zyI0oCo8hOHU2/hEw0J7QgRGNgPTWhSJuCArpC1FmWn4zM07nuzLtJ973D85tg/rRJuOw90341CG/h1fX/YPCQmxhorqHePYhBnnoW77SZPnQwmwpfZnvdWmaf+DP0mkdZ2zyWuRO+QJIWxorWsmTNz9mR8BW+MOE0MnUfa7f8i7e2PUej6cKlty1wwrZj5PcfwbfmPdrhos5wudi82+Lx97aQPWSUE0nX3pLOyUMX9OGrLiXYWEWwfDPN2xdhhgNAi8js5MASEXV9+GIshy4E2khgP1HXxk/28tVF1PXyDpbDEwJCQAgIASEgBIRALydwNKJuT045pZPUK/lPJ/VXv7cJkJw+l2/M+x15oY94ctnD9Bt0MXkpanrnnkUn1LiFRZseYcSJD3JBwWA2bH+QIeN+hdu3ne11pdiWQcHAmaSE3uWet66mjvlcM+dBpqY8x89fu4ficC6XnraAuUMmY1k2BvWsXP81/vpJLYmu1hd9aD9RF5+aGmeg+KgAh09HYymjaBK1w5wy7S9cOno473zwXZb7z2DexGFo9p6pqxparIjFm59i+HHPcEZuhCY9h3xtM5809Sff3UCD3p+s8PME064kuOuXLGqcyhUzriFcuxNvUgI7yreRnTcVd6iIRi2LoSmJ7Ch5h6WbnmVpxVpibYgU6yxRZ1o260ua+O/GOtz98knObO9IRhszEnLy0PlrywhUbCNQup5I1SZQUaUdELXX2suIiLrWkpL1hIAQEFF3mDEgok5ODiEgBISAEBACQkAICIGeTOBoRF3MDDEy90R8oRqqG8qc3Hb7yyg1XdDwJDNn2h84a3ACH6x6irW7CzFdrj1xSo7EUtMJdS1KXeMuImQxMDkNV4KHr5/9FLt3PsKzG97Fa5zARVO/RYH+Hne9+UNOm/53Tso/gQxXOVuqi2jwl+HqN42xiREWb6vmpHHj2Lj+Mh5YXk1SF4i6uKAzKcgeS3OonprGSnSVm+8A+WMRNYPk5H6T62ZdSnPV67y57TUaLRduXVXrU//GhZ9yfBHfDoz+n+f4gcMYl38mIxLreG/bYuqbKxg15mrGa/9HhfdSAjt/yeKmE/nSzK8Taywnau2iKuTCa7hxe7wYJEKggiYrzNbCf/J24VLMNlT47SxRt66kibc3N2Am55Daf1C75QVUfWNGwwSbavHXlhOs2u4IuvDunViRZjSnUEjnTHE93DVDRF1PvppK24VA5xIQUXcY3ivWLeGOB26kpqkMoyXJrWVZFPpqeG3BB0yZOLPVPWWZMV67+zqslHzOv+E2dNe+pLmt3oisKASEgBAQAkJACAgBISAE2kDgaERdKFrL/BOvZ0BGDks3vkHJ7k2gqVQ48fxhStS53SmMzTuTRM3LuPHXMDbZxjTjkWKa4cXr8kIsTCRWyabKZdQFLYhWE4psZc5JTxKtW8qaik0tUxCjBHzr+GDHh0wecytnjT+PLFZToQ2jv9FAWTSdgezkn8sLueTkeRRuvKJLRZ1pBzl10ufJzx7P0g2vU1S9ySkWsYePKvYQsyEr+2wmZaaRmTmNGQWTiMXMlum6Bl5vErqKurPCVK58kOLsczghN4+dVcvxRaKMGDQDr1WBzzOWodEnqUq4nMDOu1jcdAJXzLoBd7iJoqI/8OSanSQnDmT27O8y2Szh2bcfoMQI0RTYij8WbZME62hRpxhtLvfx/OpavBmDSO03sCXl0rHLM/WsFWyswV9XQbC2jOZt7xGuLcGOhrEPGfXYhpOoHVcVUdeOMGVTQqCXExBRd5gOfv39/+OeR39IMOzbW6pdRF0vPxvk8ISAEBACQkAICAEh0IsIHJ2oq2HeiddzwsjZ1DZW8tHG/7KjYnU8Rk7T4tM+bT8+M8qZJ/2d64+bzrJP7ufd4vWYpomRdwFfnnwJbH6Up9b+g7yxV3L2hCvI8TSwfccdJI94GL1pNVtqdjqiLj05nwytmofe/TalgVncdPY9DA/fy2r3hUzJSqM6lkYuRTy7YicXz57Lji4XdX5OnXgx08aeQ0PzbpZvXsjmko+xnCmteyq4Qji8i/Sca/jO/F+SGfiAR5b8h7AFlj2US866nRGuXby4/CFWFj7P6XP+yxmDc9lauoSmSJCRg88gydxBuT2EguhTVCVc1iLqTuRLM64lWrcDy93EusqduN1JFAyZy2C7kfW73qEmUsWq7f9iS11jm/K+daSoU2NmR7Wf/3xcjpGRR1p23jFVqN13itqE/I34aysJqGmuZRvxF36IFQ7t234n56E70uVDRF0vurjKoQiBDiagmZYqCyGL8wYQiEajFJUWcu9jt7Fy6zu4jBQnP4daRNTJOBECQkAICAEhIASEgBDoKQSOVtTNP/EbHD9ipjNFs7q+lNc+foJ6/25cujsu6nSD0aO/zTXTr6K/Vsnf3r6Rd4uW4rJ86KN+w+2nXI+94hbuXvUY4YQ8po74BVfNmEpF8V2kj3iAsi1/5pnV72LoLs6a+TPmDEngF8+dSbn3Gr5z5g9xb/o1O/t/gel5iVRFlKjbxbMrdnUrUTdlzFnYls3uhlJeX/E4Db66lpf7KrowTELKWK447QFOzsumcOOv+e2i+wlYXiLWbL5/+bNMdG/kobdv4OPyVVx14Tpm9dN47sO/UdrYwPxTfsjY5AaqyKMg8jSV3i/GRZ1vGldM/yK1pa+QkjmdDZsfpsIzlvHDL2KoVcVHW15nV8NyNpSvJ2CpKbmtj1brMFFnQ+FuP6+vq8VnpJOZO6xNAvFQ55qSolYkjK+mlEBtOaGqbfh2rsT0VbdUcm3/6rHtcc6LqGsPirINIdA3CGiLPnpHRF1LX6uLfnH5Dl58959sL1lOQmLqfmHsIur6xikhRykEhIAQEAJCQAgIgd5B4FhE3XEjZlJes5OV296iqHqr88Ja5WJTU19dngxmjb+Jk0adx4ikZh575zt8UPwJhlkJI37Dbad8HT75Kfeu/ic+l4vjh/+Sr8+aTUXxL0kZeh+NZS/w5vbFTn63aeNuZEq/GHc8fxpJgx7ghtln8e6H15Ew7C5OyzUoi6R3y4i6qWPmU1VXzCfb32NHxVpn6m9cjFnELJOBQ67mknEXMSk3l/Idv+eeJX8laHoJm1P5zmV/Z4J7M3999zt8XPoRV1ywhtNzsli3830aggHGjphPurWVj6sbyQy/TMaQ24gV/5JFTVO4YuZVhOtWmPKNcAAAIABJREFU4EkZTyQSxesJUBVNIlNrpsEcRGrg/3h80W/Z6lOVcVtfcKOjRF1pXZD/rKoh5MokPTsPw1C54o5uUZI4Fg4QUNNcVQRd+WaCJWuI1JVgt4xPJ/FfN11E1HXTjpFmCYFuSEAbNC9XRF1Lx7iwSXWFcLt0EhK96PqBb2Mkoq4bjmBpkhAQAkJACAgBISAEhMAhCRydqFM56r5BZmomi9e/RHVDKZpTMCEuQOJVYaNYWoD5p73EpUNzeWzht/igaCUJRiXJI//At2d+jdjKn/K7T/6IN/dyLp16GzOG5NJU8zYbanezu7mRmKU7c1bUZq3oLhbvWs7ZJz3OqZkNPPbBo8yYdSfjE1axKzqQ0am5FNX4GTIgkVVrLuPBFV1XTCKeo+5iBvcbxaL1L1NRV+hw2VdQIl4P1qaRAWlf59vzbyRcfh93f/gnQpqqinsSN33+McYoUfeOEnVLueKC1czMMPnTO7dQ6tvCFWe+wSh3Ib964yfAEL553kNQ/jM+aDiBL8/6Jt5oHbYrjQQD1q75HZW5X+a46E4W7Shn7swzWb3iF/xr4ztEu7iYRFVDmOc/qaTR6EdmzhAnT/fRaTQNMxZxBF1A5aHbvQt/0WrC5euc/IBqCnVboge76nIhoq6ryMt+hUDPI6DNvHyQiLr9+i3+5aFK0R/cmSLqet4AlxYLASEgBISAEBACQqCvEjgaURczw4zMnUJDoILaxnJ03XOQBLFtkxi7OW/OW3xuSC5Pv/NN3i/Zzpfn/oPZg0fgdcGGJT/gDx8/woyTX+Sycfl8UrqdUXlnkGXEiFiWU/1076LpWMFNWKmTiDVU4k7MIiMliZLiJ6lJGMVx2bMIhMKkJfhZvuZy/nd5FclG66PFTCuG2x3jpxe9yNCsEw4YDi8se4h/rbyNBFfOZw6TuKS0KMgeT11zNQ3NlbgMVSTu4AcHy2pmQPr1fGveN4hV389vF/2FvOG/5aoTzyMnPRN//Yf87b0fsrJiLV+9aBXTkkM8+MnzzDnxRk5KS6ei4nne2FHDRTOupr/bYv3am1kWPJkvT7uUlSvvZAcjGZk4jMHZJ5Cf3Y+Gsle45/UHOeWUm2kufY73ildgdaGoW75uK/+3sordUS/ZQ8ej6a3vrz0dEedtE/Y10rS7mHBjNf5dnxAsXYMZakYz3J/ZZ91pBRF13ak3pC1CoHsT0GZ9abCIulb2kYi6VoKS1YSAEBACQkAICAEhIAS6nMDRiDrVaMuOOfLpcFMn1fRXmzAFeecwOi2FDcWLKGtuYPTQ+QxNG4AdrWVr6QfsrCuhf/YsBrqa2Fy1mn45FzBpwDA8LpeKgdrr6tQLcn/DMnwMIOgPkz1gOIlaiJ2Vq9GShzHQG2JTlY/Rg4fSVPc6a6os3J+a+XIk2O0l6vbsw7Ja+BxBPtl2lATPWE4oGI/lX8eK8nUkJ5/McfljSXLpNDYsY0P5OpqiFqOHfY4cr82qqp0My51JnjvG7tp3KQ4kMC7vDLx2I0Wlb9Kg5TNu8HhKSl5ka305oeg4Zo0/k9wkm6qaVc4+dAJoWjqGdrBgPRKj9pz6+smmQh54eRX1ZjL9Bg1HP4rprqqSazTox19XTnP1LkKVWwmUrCHmqwbdfcx57rri5BRR1xXUZZ9CoGcSEFHXhn4TUdcGWLKqEBACQkAICAEhIASEQJcSOFpRF5+8+VmTFG1My0/MsnAbyU5e55jpI+ZEQYHLSMLAhW2HUfVQdc2DbTcTs9TWD150JV+IOXs1W9Zx6YlgRzHtGC7dwLRMND0Jl6ZETevRtreoi0d6xavgHn6xsewIUSuERhJuI84iZoWxbMXDjVtPdI4jZjZhKVqaB8sOEbVt578NHaJmxOHl0hPQtShR08bQkzGcfceIWQFUaUBDT3S47FnaOhW0vURdaWUN9z33EeuqY/QbWIDLk9D6jnLi52wiAR+BhhpCdRU0l20kWLqaaEO5U7zjaCLz2tSADlxZRF0HwpVNC4FeRkBEXRs6VERdG2DJqkJACAgBISAEhIAQEAJdSuBoRV1rG+0oN3ufsNojsOIWy0km44iX+KKpBHdH3vQe77XfRw5p9bTP1oj776i9RV2r+ex3vHFxZh+A4MC8fwdvVX1kf2T7/n9Pmp5Db6+17dt/vfYQdXVNAe587C3WlPnJGTYOQ+Wka7VR1VBTqptrygk0VBOs3olv+1IiNYUteRHVMbfBzh4NhA7+jIi6DgYsmxcCvYiAiLo2dKaIujbAklWFgBAQAkJACAgBISAEupSAEnXPLP0ti7b+04ng6quLaanqqDq3X/gCBVmTDsDw4vI/8eyKW/HoA3q8CDqW/rXsKMMGTODGuX9iQNrgvZuKhvzcd+kATrvhSaadc/Ehp5wqQVte28Rvn/2QdcUNDCwY2+pIOvVZy4wSbm6gsWIn4YYK/IXLCJauRdNd4Ewv7tmCbg9MEXXHMkLls0KgbxEQUdeG/hZR1wZYsqoQEAJCQAgIASEgBIRAlxIIRfy88slfeWXtfWh4u7QtXblz0wqTk5HH985+ktyM4Qc0ZeG6Z/j7R7diWq7D5uTryrZ31r5jZpCpQ8/hqlPvIiN5QJtEXXV9M399bQXvbaqhX+5Q3N6kVjXbNGNEmhucCLrmqkKC5ZsIVWwi1lwL+1UabtXGesBKIup6QCdJE4VANyEgoq4NHSGirg2wZFUhIASEgBAQAkJACAiBLiUQMyN8snMhTy+5nTp/DW6jbfnCurTx7bRzVfgCLcZJIz/H5TNvJz2p/wFb3lj6EU8s/iFl9Ttw6Sl9MqpOTQ3WtCYunX4Xcyd+lQT3PtH2WRF1wXCUP724lDfWVJA2cBiehORWMQwHfPh2lxHx1dBcso5g8UpizQ3O9FdnYnMPn+Z6qOEroq6dTmrZjBDoAwRE1LWhk0XUtQGWrCoEhIAQEAJCQAgIASHQ5QTqmiv577rHWbz1P/hDSoSoiq19Y1GuR9e8jBk4lXOPv5bxebNxGQdOAQ6EGx0+72/6Fw2BamzMz0yl15voaZpOojuNCXkz+dzUbzOk35gDDu9wok5NWfWHItz9zw94Y00ZQ0dMwJOYfFg0an2VYy4aCeOrKcP015JBM+vffIxYUxW6koOa3pvQHnQsIup6dffKwQmBdiUgoq4NOEXUtQGWrCoEhIAQEAJCQAgIASHQ5QRUtFRp7RZW7HqDsrpCmoL1mJaqw9q7F5XVzOP2kp02hPGDZjIhbxYpCZkHRXtZlklZ/TY+KVpIUc0mmgKKT6zX5EU7Ui8rkZmSkEZuxjAmDTmZ0QOn4XEdGHV5KFGnpFtDc4in31rFs0t3MjBvOAnJ6UeUdGY0jL+pHtNXxbAMgy+ccQLrl77Jgt/8iuTUdHS9d0s6BUdEXe++5sjRCYH2JCCirg00RdS1AZasKgSEgBAQAkJACAgBIdAtCJhmlN2+UqqaimgK1mDaZrdoV0c2Qk2fVNIpJ3UoOekFJHpT0Q8TsRUzo9T5K6hs2Emj4qNEXe+oX3BExDoayd5MctIKyE7PP0jSqQ8fStSFIjGeXbiafy3dQWL/fLxJaYed7qqknq+ukqbGWnITopw0LJWxgzOZPuU4nnziCRYsWEBKSoqIuo48GWTbQkAI9DgC2pTLB/eV6PfP7Bz1faze5Ti1hQ7x5Syi7jMRygpCQAgIASEgBISAEBAC3ZCAmvJqWiZWH5B0e/ArWWfoLqdSqZp2eaSlL/JRPJS81HVVSOPQEW2fFnUxy+ap11fwtw+2MTB3OAkp6Ydkq56bIv4mait20s9jMmNEOpPyUknyGHg8HiZMmMDjjz8uoq4bXiukSUJACHQ9Ae3aq7NF1LUEt5s2NFga1VGdmK2jqzym+/WRiLquH7DSAiEgBISAEBACQkAICAEhIAQ6h8D+ou74uRfxypKNfP/Z5UwZOZqEtP4HSTolPKOhIP76CuxAHcfnJjJtZH8GpHqc3Igqwk5EnSre0QdCNjtniMpehECvJKBV/FwXUae+NICYrVEX03mvMZEX65MJ2LoTXbdnEVHXK88BOSghIASEgBAQAkJACAgBISAEDkFAibr/vTSbGf/zKHX9xvPHN9aSkplHYnrWQbIpEgrQVF9NONDAxCyDKfmpDMlKwmPoewuYiKgrJRYTUScnmxAQAkcmoDXe2WcKP7VqLKh3G0FT47Hd6bxUn4QdLxDuLCLqWoVQVhICQkAICAEhIASEgBAQAkKgFxBQou6Br4ylbtxNbHQPh+QcEj8VSWfGIjTWVkGgjvGD05g8sj/9tQCJHuMQEXcSUSeirhecGHIIQqCDCWgNIuoOQqyi6BY1JvL7igz8VnwKrIi6Dh6JsnkhIASEgBAQAkJACAgBISAEuhWBaLCZ22+8mY8yZ5M5cDjJGdl75ZttWYSaG6gq38WQfh6+Pu94po/Pp6a6kl27ig5ZIEIi6iSirlsNcGmMEOimBETUHaJjPBqs9nu4sziLekvDEFHXTYevNEsICAEhIASEgBAQAkJACAiBjiAQjZks/mQrd/z9fTJyR5Lcb6Aj3yzbIuz30VhXSYIe5vNThnH2jDEMzEojGolQUVFBUZGIuk/3SUFBAaWlIuo6YqzKNoVAbyMgou4wom6NEnUlWdSZIup626CX4xECQkAICAEhIASEgBAQAkLg8ASUpFu4qpDH31xNQM8ktf9A0DTCAR9NdVX0c0c5btRALpoxitF5WbhdhlMoIhwOi6g7DFYRdXLGCQEh0FoCIupE1LV2rMh6QkAICAEhIASEgBAQAkJACPQBAss3l7DgX0sJudLJyB5CLBKisa6KkK+Gc44bzLzpYxiTn02Cx7VvKqyIuiOODBF1feDEkUMUAu1EQESdiLp2GkqyGSEgBISAEBACQkAICAEhIAR6MgHLstlWUsOPHnmTsDvDkXSh5noaasoZlOHhW+efyOQx+XjdKqv3gYtE1B2550XU9eQzQ9ouBDqXgIg6EXWdO+Jkb0JACAgBISAEhIAQEAJCQAh0OwJquuua7RU89OIyips1klIzIdhItHorZ00dzRUXziE7MxV9T6U9EXVt6kMRdW3CJSsLgT5NQESdiLo+fQLIwQsBISAEhIAQEAJCQAgIgb5OQEXSrSus4P4XPqJwdwDdnUBemsHp43PY9eTXOP+aXzP17IvRNP2wqCSi7sijSERdXz/L5PiFQOsJiKgTUdf60SJrCgEhIASEgBAQAkJACAgBIdDrCFTWN/Ozv73J2qJaKiImN58xjotPnUhuuocHL8/h1BueZNo5IuqOpeNF1B0LPfmsEOhbBETUiajrWyNejlYICAEhIASEgBAQAkJACAgBh4CKpCutaeTuZxezcmc1owf148ZzT+SEUYPxuA2iIT/3XTqA00TUHfOIEVF3zAhlA0KgzxAQUdeJos5MHsK519+KbnjA7poxZmGhtfzTNS3o2r0q7JYdAw0MXF3bmD6wdxvb4a2mSegcnHS4MxDYWJh2DENzOyNfFiHwaQLOdYEYtm3h0jwCSAjsJSDXj+4/GCxMLNuUa3w37iqz5fqqcfgpk924+b26abYNRVX1PPr6SjY3+Lnu1InMmjSU9OSEvZVcRdS13xAQUdd+LGVLQqC3ExBR10mi7vXfX0d9OJVxn7ucUCzQstfOlAY2Km9EqjeTUKyZmKlkVWfuvzucSnE7qntizt9W2A2a+llf49BZfdHCOyGKHdOxo66uQa1bTp9bYRfY8pDQWb3fo/Zj22jeGJpuYwU9XTNOexSw3t3YqAam+lqwQXdZGF6LWMjAtuS7ojv2vOE20T020YABtvRRt+sjdR55Y6R4U0jXB/XBe89u1yN7G6TOltqmEG9vKCVgl3LelHHMGDEFl3Hgi9VINMQ9lw7mrOv+3Oqpr+Xl5RQWFqLrB993qecRr9fLpEmTeOKJJ1iwYAEpKSmHXLf70ju6lomoOzpu8ikh0BcJiKjrJFH3xr3XUdOcRN1xXpZUPYhBYuferNg2YTPIRSPvZFXVq5Q1L8NlJPW5Ma/ZJlNGXkIsFmPZtr/j9aT3OQadd8AaLt3F7LFforh6C9urFmIYKZ23e/WcbUXplzKEKSMvZPHmpwmFAyJhOrUHesDOVDgBMaYM/xzpKTn8d9X9uI3kzr0+9wBMfaWJMQtuX+pj+DbT8fqaJxE9KR/LV4xtBfsKhh51nHriQDRvJmbjZnDOZ1m6FQEl6pIGYiQPRddzWt4Ri1Dt8j6ybULAIi2DqVWlpGU1oSek4k0ffnDTYjFqnniCLa/+m1lnf/4zi0kEAgGampqor6/fG5X36Y0ahkFeXh6PPPKIiLouHwzSACEgBLojARF1nSjqapuTaJycwrLqp3EpUdeJkVxqCmLE3M25w29n3e63KfOtx90HRZ3q7snD5zgRhcu3v0KCO607npe9pk2GDjPGXETJ7u3srF6FS+/caYVqOlRmcjaTR5zJ0i3/JhS2DnvT2Gugy4G0iYB6s6+mN04efibpyf1ZuOZxXHqKjJM2Uew9K0ctmzuer2bEO034ct1obg+GJ5VYqF4kULfsZhvdnYzuTiQWVH1kdctW9uVGqZQChjcFlycDQ+/cl3V9mXtrjl3NL3E7wcM2MbMJ3eXB68k48KORCOzYQSgQYOXr/2HW/NaJOtM0UTLucIv67k1ISOChhx4SUdeazpJ1hIAQ6HMERNR1iaj7e6eLOvU1HDar9xN1G/qwqDvDEXUrtr+KV0Rdh170DF1jxpgLHFG3q3o1RpeJujks3fIcobApAqZDe7znbVw9LKgMdUrgpzmi7gkRdT2vG9utxdH/Px6UqBu2solbb8ilIGsww/OmsbHwLcLqgVWWbkVAvYzJzzmO3AGjWb3lv0Rj/k59CdqtYHTDxqi4uYgZYvjgqYzLm8tA7wndsJV9t0nxuEZNZfKlyPch/TJyGZ97+j4gKkVOWRncdBOhdevaJOrUzBXtCCl21HdvUlISDz/8sIi6vjsE5ciFgBA4AgERdSLq+twJMnm4iLrO6nQRdZ1FWvZztARE1B0tud75uT2ibugaHxffOoQR2QUcV3AKH219kWAkLBKom3W7aUUZO3gawwdO4t21zxGONR9xWl43a36faE4kFmBiwWxmFFzI0MTpUtSp2/W65hT92uRbyMB+Q5hRcP6BLdy5Ey69lNDKlSLq2qHvJEddO0CUTQiBPkJARJ2IunjQ+35pXfa8AYs/wMaLLex9K+ZME2tZtEPX0Nz/c/HPdq+zqXeKunixkPh06u7DvL1EXfzY4m9+2zKe9k19lYi67nUWdp/W9CpRt//1ueVc2XfuqLR73exi3H2Gwd6W7C/qLrt1CEOzC5hUcArLlKgLh4VhN+szJepGK1GXM5H31j1PpDuIuv3OQ3XO7T0HD3PP1M2QtntzlKibkD+b6XtEXTe6Du3pm75+bVT3Spt8b5OTOYQZQy8QUdfuZ8G+DYqo60C4smkh0MsIiKgTUdci6qLYRNFIdN5GOzcvWhTbVqlm4/ma1D+2HcGyVUJ+DdvygqajYaCrv1tuSG07jK2F0bVksI1DPtjYtolpxauvHrBoGrrmRu/AG7ljEXWKi2UrVhpOHSvNQMPEVMmSNZejyZzfHzKhtZJMBoZ++JwdR3d9iUs6Gx+QgIbbeTsal3YGhqYyoh/dlo/1U4cWdRaWFcNGR9ddaLaFethCc6HriqdKBaWOKYZlW07+MF1XU85U1UVX/LhaOB5aFe9rdW8QdSq/j+pPNebi3ajOOTUObQzFDxtT/f5QY06dt4qrc57GF8XVtEw0XZ1n+35+rH3dUz/fm0Rd/FjCzlixbXUdN53/13QT7ERs53qsrj/mYa5R8V7UNA/q3O2LS7cWdbZJzDLRnT5U10bN+T6JXyNMbFwYqsKibcavGYeqq+B8l7dcE3pBF3c3URf/bouBZqLhdb7DNE3dWynmKker5uTRO+w1W13ndVf8e7uXLN1V1MXPD9t5+afOJefatz/zPcK1pQL0IW5Y2/TisDt3p4i6zusdEXWdx1r2JAR6OgERdYfoQY8Ga/we7izJos7UMFq+uS3LotBXw2sLPmDKxJmt7nvLjKGqvu4rJtG9ctSFY1UkZp/P58ecysZNj7OseitJhk72wM8zf8xJ7Nj5J5aWVKFjEtMNZhz/Q453+Vmy6j62uvrhNlWhinjuHtNsJjHxFC6ZdRHN5f/ljc3P0WC2SC0MXHq6U1BAlWt3u7y4jcSWG1IbywoSsSJYkShRRyDsVQuO/DItJSa8tP75cU+E2YFddTSiTt3QxcwGYrafpMRhJLk8hGJBrEgdMSOTRAOnkqx6LHa53Lh0L15Dicw9g8ckavqdh6xIzMSyfEQslUvnwEW1WNcS8BgZjkT57EVxixKzxnPR7MtJCb3G6xuXEbZT0e0Ith0lYiqxtf+2YsQsFRmyh/1n7+Vo1zhY1Lmdh0eX24VuW0RjMaLESPAkocXCxEwbW1MyTsfjSiNBnYyawfFjvkSuvpHF2z6mOeoFK0wg1ERsv2hPJaAU3/3HSI8WdXaUaKyWqOYiJWEwiZpBzAoRsYLYJOBx6USjUaUxcRsahisFj+HeT8hFiZoBYlETJR+cZw0rghoOiZ4kzHAtfjOAjRe33s/ZxoHPKEqmhzF0Je97wRP9YQZx7xF1St7WkjX8O8zJLOG9rcvwhU36p8/n9BGj2b7xUdaG1NRNC/QEPLqBaYUwLQuXDlH1t5GCKgBjRurxx+IiKC7OlQhSL2A8GM7Lid67dFdR54xTXSfBBZFYBN1IxiCIPwq6DV63Oo9tQtEIlqXj9SThdSs5GyTa8v2s6Sl4dHXd8BGMRfdpCfUd4mxeyftDfSsdpDC6zQDoTqJOfd9qegyST+DcCRcQrX6RN3ZuZ1z+5UwbkM6ij3/KJiuJRFemc/12uRJxG979rtkRomaQWER9Lzrx43s5O9duW4lZd4+TQ91R1MVfbuqkpGWQmqDj8zXQHIznVFMvv/bMUFD3qs5LQ1y4Djg51L3Xp0y4s822Rf13lxNJRF3n9YSIus5jLXsSAj2dgFZ/276ZjD39YNqr/R4d1gYN7qzIos5SbzbjW+59oi4RG4P8nDMYOfwSzhs1lY1bnuKjba+zoeptckcu4Punf5Wlyy/kH2vWEPUMY/aIBVw+aQK+SD0p/UaTFqti8Yff5unC99GNLGKGm7NmPsSXx59MyfYXWLxrPWFddx7+sGOU1K1gS+UHjB93Ozed9g3CvlIaAurts0ZyymCyEgO8+/RFPB324TE8ex8S3a6B5HgTqWzeQVR3xaPZnMUmGislbKnIv4MXr3sErk9FDR2NqDOtJkbkXkhe5mhmjz+bcM2HlCZOZEj5MpY0ncSXpqfwyls3sTicwbXnP8oYb4iqxkpizo2cjcuVRHZGDhWl/+C3b/+SjH7nMbZfPq5PPRSpgnXNwWI2Vy8nFIu0QpDEBWfIPJPbv/wQGb5f8av/vse5ZzzG5JQmSuoW8tSSvxFSdsZZYlhWFoPTB9PcvJ0mK7TfPlRkW5WT4+fgunkabiMHTxurYX5a1GlEiFjjufaCvzIu+hr3vfJ96gt+wJ3n3Ipe8RZ/fufHbAsHsK0UJo/4HnNGj8KlG+RkH0eaVktRTTFRy6Bx91u8/PH9lOv9nf5VN9KGuz9D0jKoqt9AwEpxHjh7rKhTETGeQYzOnk5OxnCmjDyF8M5VkDUTDwsps/KYU5DH/S/dwFbfiXxr3k+YmBaiuLGOmK4ktwVaJgMzMyhcdgcPbH4FU7OJ6inMnPo7/mfi6VRvfZ53Sjdjak2U1b7FjsbY3gcRJWZs0shNL6CscZ0Tw7cnylU9wJhWHWGz7pBfHm5XHl5dVbXuGUtvEnVRs5TBM17k5sFrWVKVzdQhF5HtCdMQjtA/rT8N9St4c9N/SEifw7j0DNLSC8hK0KmIucnzuqms24gvalBZ+F2e2VyJSQK6pq4x0C95PEZ0FzVR/345wNQDbZBwtEzFEB206Fo2ia70HiUWuqWocyK564kM+joPz/8Jm7f+hWImcFZBNn9+dTrlrju4+cyr8FX8mj9++BhJ2T/m+2d8DTtUjWYMJicj3dE+ZnAHRfVVbNx2H6/t2ICt6j3aEcLuwRRk6DTUFuK3kvfe86hzI2ZVEzGbDnGuu/C4BuLWVRR316nb7iPqYoSiCXz+tIc5efBo0r1uImYZQbs/WtSFy1XOyyteoNG3ibKmAXz1nDsY7vFRWl9G1Ikkt3C7csjNTGbtojt4aNureNyp8Xsd9dItYShZXh+1jfVO9Pm+Rd0D7SRsqdeEn14MEt0FjlzvyqXbiTonYl8nKT2NrH6ZYOvolo/q3bvxh+LzJTxeL8mpyaSlJhFprKFJSyYlIZEkrwsrFiHo99PU0EjIbKkkr0S6241LixGLHvyS+NCzLFp6Rb2P7MJzyHm+kamvnXaKiKjrNNSyIyHQ4wlo4XVvHWpyRI8/sGM5ADXlYNXOjdzx/MPUBOr2TlXsfaIuAROD40dcxdjMLNJSp3LS8JFsX/sy2yIh0rMmcmLBJIp3PsQTG9cwbPjX+eKYaQQqFrGuMcyYEXNJat5ASW0FQd96Xl32e7yjf8LVs6/E1fga75clM3fifPTGV1i4qxiIUlS9iNUl7zBh3M+58eTzWbziZ7y4sxBD78fxk+7gytHD+fAf5/JEpBmvrkSdhWmGGDLqdr4yIokXFn2HDf5M3IaBZptOtNGY8bcwL3sY2v4jWVORaZUs/vCXrAqpqV/xaalqabuoswhH6znzxN8zZ+z5DAqv44//90PcE77O6WPOIDPoJS3Tzytv3MCicAbXXfAUAwIv878f3kejymlkQ0bGSVx72k+g5iV+/dYvyBn4RU7IHupENzj34S1TLKYedwOe5o+4/60fUNnc1IqbNzXFTYm6OfzkigcZEHqcRz68D79rDgNT02gON1JcvoSocxOvWNbjyf4uN848i81rf86bRRsa47VyAAAgAElEQVSx1YOWbRHTkhmafznzhs0gQU0F2Y+nbTdRWPIPXtuxHJfubvXpdaCoWwXu/ozKv46vzLiCftFVPL/yJUaOuZ5JSaWU6/nUVC3kP8vuwDIu57wTTseINmC50hk7bBoJZgmFVcU0NIdITkpn146/srhsHVHN49xk5g++hq/POosX37+MpVWmI4tsTDKTs5k8omflqLOtMFbycZwx/kpmjj6TzOa3+NV7f2Bk7lXMn3A6mUlpZLlrWPD/2Dvv+CiOuw8/u9eLTr0iISF6771jwDR33BP3iuPE5U1sJ44dl9iJkziOexyX4B7HBZeYanoHAaI3gSQk1E/S9ba772f3BKbYphgLATf/oA83W+Y7s7Ozz/zK57eyy92feyb8gdbO9/nbqjeoMoFOtY4x/Iz7x16Hd/Nj/HXrl5jisuja7XdMbdONsq2fU2vLZXCHMeAp4M1Fd1NYE9Keq+ii3U984kiuG3IfJVuv5osiD4Jo1aCuLHu0PhyeNxRLU33tIO1jI8jG3e+woHSZZlV6+j7fj3uINllOnPlZXyXZS1rSeMYPeZCB8fV8tWoaJE1nbMomviyrY9LAG1iz5mHeLviA/h1uY1BWbxIT8mkdZ2Sz30j/RCvbSpfg9lbzfsEzeIKqxbOIolpx6jsxdcRjJNQ8z7ubliGrVpaa+3UI2TGWK7pdTobJeHisUxHc9bP5pPAVXFKGZrV3JpSWC+qcBNr8ijfGPoS/fh17GyW65PSirvwjypXudMvKZP6CaXywcwHDhr/K5BSF6Qv+jKX109w6dCCCJNJQ/BCPrpyPEA4gKiZtE0mWfWS0uYdpA4eyYP6dLKh2aZZ12nsJmW5trmdo62FHbSpJspuCXW+xtmJTkzv16endlgPqVAvoRPp3vZfze02gXVwCyG6KaqpIsCYSqFmDqdVQ6ouf5t9rqvnZpL+TE9rC8uINBHQqeJOwmrvSr20Hti/7PS/s/h9mQzwiMpGIl65dn2VSTpiPlvyBvQEdRi3UiOruLNG/02P0y2yNeHiwYYRwBTM3vsT2hnJMOtXt9vSUlgLqoiFdVMtRIzZ7EkmJFiS/G2ejRGJqAjrFS62zEZ9XJiElnaR4E5GQj6BkwKRTQayCUZ3nIgHcbjduj79pzlMXSzriUtKINwSoqWogKKsutdH4hGpID5sjHrPx23XogZ5QoZ/L7SYUVoHf6emfGKhrXt1joK559Y5dLabAmayAsKY4BuqO7ED15bprz07eevdFXJ46LY6W9iI761xfLURkH23ypzGulYXGYAdGd+7JuuVfUG0to17Xi0t7ns/GLb9hVqWZUZ1+zpBWbamsWoXX3JUeqYkUFi3B4mhLdngrL/73TQZe/A+G56RQVPRHZld3YmqvqYgN0/ls104U2UVZ5VL2Oovp2vkP3DXiBspL57Gz1o+gWk1ljaRvioX570/knZBXA3XqMQbTcK4a/TTDsxPYuvYhXt7wMUEhGXUPWnVFbZ17LXcM+wPZcerHY1ORAxSVTufFeQ9TF0nUXG1PHtRFCEWSGdTpFsZ0vogOploW7FxMXGZrGgM1ZFgn0M7h5PPZd2oWdbdMeYd8YS8rilYTiKiATMFsSaVv+xE07v+Ip+c+gYQeWQkctFJQLZgigotfXF5NW3kD/5h7H9Ue1XLl+4KjqJ/JWmCVg6Dut9e8SGu2s71yK9Wu9azft5yimu0gpGhwTf0gU8QMpgx/mws7tmH/rtf5+9K/0BgxEY1aJRGfOIkbRz1Mr7S0g1aL6sdAfe1KPlr+B5ZV7EXf9Dwcz8R3FKgTDdjSr+JXI/+PHH0526tKaAg66NIqm5C/HqfPi+RexuJt+2nfvi9WnZ3c7EHY5d1saYSemWksWTOdsKMz3vL3Wb5/G2FBh97ciikD/8Kk9v0o3vsYbyx6g4qw6rLJmQnqVABi6UDfNucztvv1ZCp7WFFaQl5CKqUuFzmZvegc54yCOk8/fjXhcdopm1hSshmf5v4qodN1YHCH3pQX/IF3ymHKoKvJs8aREmdn/aq/48m5kL4OO4tXP8VnZSsx6BOa3NBlZAIM7fcKV3ZXQfscXp45lU3eVpp1I4qH+KSLuWrk7xiQmnnQ+kYF8e66hUyf+xArGuoxqC5axzNITnOds8WiTnW7Mxjj6TrwJa5KL2F2pY7h6V2R/CGMlnjq/BEyjE5mLHiApG73cFn7fLZXFpNocTDbY+PKzAQ2V2+hXVIuz3w+jjJXPCa9TnOb7NL+GW4YehFm10Le/uaXrHRFsIh6zbU+orMxccCbXNatP+aDME4h5NvH/NWP8va2/2mu1ccfsuD0DoiWCuokxUmw/f1MH/1raqpWUxEU6daqO4218yn2tKJjZjZblt7J9DIn1417g3ydC3dER2JCHEZLEgZ0hOt3Uxuu4+M1j7O9eh+CIGM0duLy4X/hvLYd2Lr5Jaaveoka6UBM2gDpGVdy/ejf0jU+4bCOqa36hDfnPcYWt18DEaertBhQJwcImlI4v9f/0dqcSafsTgScc9kS7szQVu2pKX4NY/bVlKx/hqX1udxw3p04/DvZVLGTkOY9EMZoaEPnnLbU7Xmffy16iApdOigu9MZJ3DnpKXomGViw9Dbe2bwI0ZyibbCp7/Ws7Pu4ccyddLR9a8msyD5Kit7gpYUvsF9SNFf301VaEqgTjCaSk5IxEg1Dolet4ESBsOoyrui0sBxhj5OgbCUp1YEcUeO5QtAdwmgzEQwF0Ftt4GukqrYeSQ1QDBhMdtLTUzDpZOqrq6n3+lG04HcqHBSxOpJJTXZgOGQiVN89vsZqapweIqoR/Gl8YcYs6prv6YiBuubTOnalmAJnugLCqwsejFnUHdKL2u6XTqSifD8LZy8mGFRdA6NfH2cjqFOtJSxpF3L5gPvon5yE37uaJRVmhqa4Wb6nmsF9LmBtwWW8W7iJVMc4ho94iHEZudh0Bqpq9yAYkylzrifZbqVgxd2sDvbnimFP0lG/ka8LtjBk2C2INU/y7pYtWiIAp6uISlcRXbv8iTsHDWfWsl/xyc4iBF0S/fr9nWndurD8g0m8rYI6QUdYjjBwwD+5rsd5xBt0hLw7+GzJNObsLULWmbWg2apL36CBr3F911HY9dEg257GAt5dcC0LKkJYDokBo/bjiVvUqZYjEhZHR64c+RrDk0K8v+hO3NZbmNQmi31FJnr0svLlzDtYFk7itgvfJqnxY56a+0ecAY8GKxKThnP3hL9icv5PA3WK4Dhs7tDiq7GPO6ZWkC8X8uzsX5CWcz2Dsjpj0GjcEVONICAFi1m69U22OGsJy2M1i7pE94u8tvoNBN1vuLhPFxobZjJr02wqvA0aGMzrcDf3Db2XJJOBcLCMuatu48PN2xA0jWRkqR5T7kP8fsxdtLaYtYuGw5UsLriH/25cTkAxH4c77rf3eqTrq7pozc2/lbtG3U+qPoTTW0NVXYCcVh0R/ftwBsMEKr7izeWPs0/szc9H/Y2hORns2v4pxqzxJBg8NPoq+XTFM2yr24VJtCIrlbRr+xw3D72GLIuZcHA/c1f/js93LCQg6Umyn3kWdapOktyAZJ7Kgxf9kTz28Nn8X7KhzSPcnZtMQ8RMt8QIf5pxA0XeIdw78XEyy1/m0UUvUmUR0KnzmOE2/nDRnQS3/YnXiwtJcjTgC6QxbvBTjMnuRjBQy6qCf7O2eidexUO1exd+KQyRcszZt3L36EfoEpeEoPhZv+4h3i74gnqiySvCSogune/gjiH3kWxQLXMgEihl6dJfM33XIhTRcULj5HS+SM8OUKe6cgmYjXn0GPgIl7d2UNIo0zpOwOmGjMRMiuvqyY8XmDHnOkLZNzKl42gNzjuMJnZ7AmQZ9TQEXTiEep6eeS21PjsGPJjSL2DaeX+je3w8guxh9+6XeX3ps1RGHBqkVYGAMa4z149/m0EquNXelW527vkbry76N3URI/rT+QV6goOrZYO6XzN99L0UbPozqxtC/Lz/PZRtH83XFbdw9aDLKVlzOyscN3Fn//Px1pVhMtkQdBXUk4ldMBLYtwVjqyQ+WHQPhfuLQPDRp/MzXNv/SlLMZnzeImaseIC5e9YhCGo8UYkIIfr0+CM397+O+IMelzXMmnsLH+xaAVo81dNHGFoOqAsSNufRLWcMXVqNY3CGkY+WvkptOJXhXS6ld0YCoiHI9Dm/pTQwkPsm3Q/OeWxw1tO740R03pXM36swukt/qre9yj/X/gO3LgGf7OHiYZ9xaZfBWHQCrrplvP7N7ax1ejCKJi0xRRg3Q/o+yfW9b8Wu8TgZT8MGPl1wM7MqGw+LXXqCj8Mpqd6iQJ1ej9lsRoioMVwV4hKTSLDpqa+rwuMXMRj0KLKCJS4eu9mAqNcjhlxU10RISIvD6/dijEtA5z8A6mQEnY7E5HQSmjaLQwEP1dW1BMPSQas6dDqS0jJJskXXVWpRIj4q9u3Hp3ktn97YdjFQd0qG+nGdJAbqjkumWKWYAjEF1DeDP+SKgbojhoKaUW3dltU8+fJ91DaWoROjLgNnH6izatZeIamChK5P8tDAO7A2fMYXm95jWN+/E/YVEZ/Yh4KCn/G/Pe24vP/5xJvjibOEcVh6kKCvoVqyYjHEYZFcLF18Lx/ucnPZxH8yyDif52fO5vIrXkW/70YeWLxYjYONVW9BCacxqOfL3D4gn+17F1DcGNISBqRlDaZvmpUFTRZ1esWNPvUiHprwAh3s6r1GF6CVJW/zz0WPsstnRC+KyHKIlNSp3HTeQ3RNSEQK1bF6w1/514b3UdQstkf074mDOnUt3EBO2/u5Y+gdpJutlO55gZeWzKBzh99zWY+emPQR1ix9gs+qavn5lNdpo+xh5a4NBKRo3BiTJZm+HYbgqlAt6p7UQMahRZEPB3X/mHuPZgFjPDKI3SEHKbJARFKDTweaXF9fItHzNM/Nf5lytxtH+lWM6zweZ9kMvtm9DEtCO64d9TrnteqErslSz1W7gDe/nsAaX2sMTXFyQlItlw6fxeTOAzDpoLz4Q/6x4BEqgopW50TKoaBub9U6DIYUJvR7gYu6DyTUuI7KiAljpYyQlY3gLUHWZdFY/AQvb6qlX5dhZCRm0a/jBFJE8AYaKHIG6daqNWX73+CVhb+nymclGMnkxss+5bzMLDXikhavrrp6Dq8seJiihkaS7elnnuuramEpV9Gm23TuG3ghDqGRLVv+zTOLn2Xi2HcYldufTJOLz1c8zty9Cred90fayhtZUrKLgE6NOxVB1LVhcKdeVK5/hL9teYdA/AVc3PUKxnQYiuzaQrknTEDyY07uTPs4HW/Mvp01ZYUIgp/Lx6xnSqf2HHCW8ri38f7iu1hWVoQgmEH2oNh78rPRL3JeVj6C4mX3ntd4ZeED1EhtjnKTO5Ex09x1zw5QJxGRTOS3upKJg28gny/4vLYDk9Ic7HcGyE3LZ0PpXnpmpzNv+bNUmduRZZJplzueDokW1u2ay35vULOMEgUL3vp/saSsDpcic/7QF7ih28Xas6XNwKF9zFv8Kz7YvRJFiGYElxU3/Ts/zTUDribRZMDlXMf0RfezurpUs6w8k0qLBXWyk0CHX/Pm8F+yb99c9nj0DOs4jJqSD9jS0Jb+Hbuza8WdfO3pwjUjryNJ1mExmUFXSYMQBXXBkk0YspP5YNG9rC8vxBp3OTeNe4R+aZnRZ1YJsr/iPzw361EqwwbtPSHLjQRto7hj7F8YnpGNSJCSPf/i+YW/oTqcc5iF0Ono55YD6gKETO0Y1+sRLurUg/212yGuDcmhtayt20//dtdhqPyAv82/i3LpTh6+8DESpS3sdnnomDsEfIUUVCr0yWnNpsW/44U9szCLRuKzruOhiY/SynjgOQpSUvwir857mvJIopblV41TG5c6hFtGP0/PxFQkyUXBpvt4u+BrvLLjtFs2txRQp26AqfF3DY4kMhIdCJEAimjAZNDhD/gQ1fWp301NXSM6ezKpCTZkSY0dGMbrCWOyWQkE/RgsdtBAnVNLgGW2J5GWkoDpgH+/EsFdr1rK+ZCbAJz6nhEscWSnp2r11HVKY005tY1qNpjTHaEuFqOuOeeuGKhrTrVj14opcGYrICg/GOH0zG7cj7n7dZtX8ujz06hx7dOySJ6toE7NGCro4hk58Fkm5LXBIIrs3b6QRkMaSSlJZCfms3Ldz5i9twM/GzpFTQ2IoDfgsLaiY0Zrymt2k2DLYO/653ipcBn9et7MgNZdsYuNVNYLdGw7ADwrWLe/QtPQuX82Cyo8nDfmJSYm1LJo03vsC4W0pBa5+T9nTFYSC9+fxNvBesyGjkwZ+Xcuad9Ts9I4UMLBEhaseJT/bF+ALJi0GC0R0cLQ7k9wQ/8Lqa/+lLcXPszWRjUD6NFg6cRBnYQ/GOLaSZ8xqnUnpNp1bNizmmB8K0J+hdy0AbRLNbJs8e/4qtbHdVPeJCeyga82zsAbiSa5sNnaMq7XNfgqP+FPc59ERrUEUwP2R4vmQkYVd11R1eT6+n9UuhuOkelFDfCvh4Mx6l4i0f00zy96g2pvHApBDYDqBNXN1ki/Hn/i6j7jSTYdkmVOamTXlr/y2qp3qdYSp6iLfjcZqVdxy5iHaWPx8cm8m/myuBC9Mf6EF/xHgro4eyaT+/yB3vnDkCs/ZkNFkI4555OVmgWhetyeOrZs/Qv/LdpNbk5feuRezpBcHQ1SDsliGNVZuKqymIDew5KNf2JVVQUjevyLG/qfh+1gVyuEwzWs3vwHXlv6KQlJ+fTJP7Ni1MmyF71jCDeMeYZOKnz2bGJtRQW2iB+fXk9G5jB6xsNHix9gcZmDO8b+kTbBRXy6bTZuowFRiSDoRnNR3zHUrHuCD6sFhva9hG7JeWSY9CxcmsebO3WIxnZ0GfgP7u/aizdmXsGysh106P4kDwy+Ccch8cpVq6niond5ZemzVAQlzVUoIgXJyb6HW0bfTmqogI8W3MfcGqfmEnkmlbMD1GmTCJJSTu6Az7k1q5Av6jpxSc5AbFTjCwcxGpORFD/zFv2ebZKZdmk3c0W/rpTvX8zW2goy211J28gOFm2ZQZFzDlur60jLmsato39BO/uhGwthaiq+5M1vfscmT0Bzq1c3Gmz2gVw94kmGZuewtuAh3l73H9xYT6u11cmMw5YI6rTkLiLEZUxhSuvBCEoQqz2bPq37U1/5BVucKg6QKS//jIXFSxkz9O+MzhyK1WgEXQUNQivsgoFAyUaM2cm8v/BXrKoo4fIRnzC5Q29sh2wISaFqFq3+Bf/eshiBeERBJiJVkZn1BHeMu5W0wDo+mHsf3zirMR9hrX4yev/YY1oMqEMhIpXSpd3z3DBwAgWF00nrfifmspf5rF7g+v73k+D8Hy/Mu4dKw008OOl3BMum883+GiYOvQvqPuK5Qol7h11K7ea/8qfC10lIHMHUwX9iTF7nps21qFqRQDmzVj3KjB3ziSjqfCujCAb6dXua6wZcgOScyb9m/x+bvKEWAcpbDKjTMp/LCEYLaZmtEP21BBQTCXY9dXVOLI40RF8dlfVeTMnppMWZCQckLFY9HncAg9moJZLQma2E3U5q6hrAYCEtLR2b+fD4c5Ggj7raGlz+cHQO1BJYCNgTM0hNthBxN1BR7WzKXP9jn4Iff3zMou7Ha3i8Z4iBuuNVKlYvpkBMgRio+54xULB5hQbqal2qRd3ZCer0ohlJURjR+zeMazuQmeueokG2YQyUUu7S067dTVzVdyxLV1/F13tac93oezBLJeiN4Avp6ZV3Htu3PI7PejXtrdV8tugPbPI5Qa/TAuharBdz29hfIVY8yLNrVmmLFSWiJz//bn4+8GJKNz7BG+um48KC0dSBgb0f5ppOeSx+fxLvBOtJie/OoPzRWA8NWK/ZACo0uotYsWchEUkN7KFaO/oQDX258fw/UFf0ez7dvhFRy1h4tEvOiYO6EIFwDiO6XEj/tpPpKu7h75/eRmlSBlIwQt+2b/CzPnF8Put2lgQTuf3Cd8lVtjF/x0y84YDmKmi1tmVY54twV/6XP855jNRWl9ItscmKQRuDEqoDy8Bu96N3r+KVhb+jxuM+JLvi901Wh2d9TXQ/xT8Wvk61Tw1CrSoVzTqr0yfQt90U0q1x2v18WwSESCMrds2k0l+vZYdT3Z0EfRKDe/2afqbNvLHkNVxi3Em5rx0Zo06NFWjQD+TnE5+lQ2QRn2/eRs8ePydXWUKxvwfJSjFzN7/C8qpGurW+gsk9JxH0ziHouJg2wiLmV3jpkzGU/fsXsKzwLXYaMhjRbjxpR7EhEclXxrKNbyMndaDvGQfqAsTHd6Fb606Y837FGGUFf1n0HCpY1+nSGd7nYS5s6+Avn93MLs8A7p3wGO3lAr7e/Q1ugx5RkRB1IxjXbRBVBY/ywq7Z6I128rOncMPgX+Ise46VNYpmEZWRexkj0xJ49eurWV3hYnDnC8m2Hpm1VYBII6uLvqLM49IsKxU1WyQpjBrwJzpHPuPDdTPwEU04cSaVswXUqc+t+nx1HPgGP0sv0EDdpa37Y4yUsK1sMW5xCH2zk5g15zYW1NaTnDCJ68dcRSt7PC6fB4MlE9G3gi/XvMiy0l0gyrTPuZD2ya0OiUN4YGMhwrZ9c9hRoyYCMmrud7ISIb3dg9zeM4lPZv2azR4dOjWJzxk2HlosqDOk0LHVKPLscdomT2JCZ0Z0GE/dvtdYVukHRPzB/aza/TEjBvydMVlDMBnjsJi9uCPmaHbsxgZ09gBvLbidVfV2JnWZiEMIH/G4ioT8O1i1+zPqwolR92ZtI8nAsH7P0SX0Pu8UzicoqNlhT/+z3mJAXZO1VlLKWC4Z+ht6WI2oj8aaTbPQJbfH5y0hM3sg9Tuns7Sijl5t+mOQwxgt2dpGkuBdy7zdG7EZrUR825lROB1L8jj653QnTndkJhYBj7uQ1cUrcUcNspDVzPf20dw84l4CRU/y/vZlKGJciwDlLQnUqcBMDfWRmKZamfoJRgSsNhGnx4/dGoe/vpb6Bg8kpNAq2U4kEMFiMeFsdGM0m9H7vRAXT8jtxNngRjDZcFjUOfBw5yT1yQiHvHh8oWimpaakYaLBQlKiQwN9jf5wi5kfY6Cu+VYtMVDXfFrHrhRT4ExXIAbqfgjUvTCtyfX17AV1EeyM6PdbzN6lfLP1i6iVlyDSu/3VDM6fSKopxMzFj1Ek9eSyIdcg7ZtDqeIhJ3MY+Qmt+XjJ/eyXR3Ftzz6sWXY3K4LqmkTUXGjMlklcM+J2dJX38c8Ne0AwoNOlMKbP/QywBvl46aPsjEiEjKn073kfozI645D28eaceyiTdFq2s7DsQT5iAaR2mSiaMYpRmBDNrKU6NISx27MhuB93WN3d/O6YHycO6tSrhIkodsZ0f5JRCXW8Pvs2iq3ZRMJB+rR5lct6WJi/7FEKgvFcMeoZ0qWdLN61GF9Y/QhSsFnSGdhpIr7ab3hjxSvYE4eQY0s5+AGswjO1maFILd5gPVXuMsJSNL7JDxf1uBDByGBun/wgDu+bvFvwKXV+1ZLlwJFqHXW334OkRI4Od4cBo97WpFd051cWQGeyYRfc1PsEzb3mWHfyXfd5ZIw6FZxGFDWD5EN0dDRQE7ThdxXw9YbH8IgdGNDrd3TTb+WLLQoXdB9B3b7n+GLfYkYPfI8O+tm8ueJdLLZRXNlvGhVbn2PWvnV41MQLTVlzv70HNeOaGb3OTPKZmPVVDUsoBwgo++k+dC4TDRt5feWLeENhdIZEhnf/DWPz4nlj/qPs83XjmsF30SZcyNw9S3EbLAhKGL2uHyM796Fhx8u8s3c+QSVCXtZwrurzS+rKP2BtTRBFZyW19TiGpqfx6ZJfU1i1C52aTVmJHNWdgqDDINqjCSeaXKdlNZaPMQUjPtwhX/TZP5mBchrfpGcLqJMkD60yLmR8n5uwV85gQbgD5+cILN30HJv9bRnf+R46Orx8svwV7KlD6ZGZRqItD4fOxZLt/6bEJdK3/dXkJgRZsOBp1ntdRAgjycHvmDNE9DoV1BwAceocEyFsSCTN7KPRE0RSDGdMAolDh1/LBHUqBJBRM61G1P5QJDIyL+bG/tMo3zaWd3arbxDVVVV1RfYzotcjDEjti14Xh8u3jNnbZ2p9ZTBezYU94/l8zdNsrypCkv2aK+DRIVAtGHXRsBHRV5DavxJmfTIGvLjDIfUl3CIe9RYD6mQ/IUtXRne/jn6pWSzZs5Cs7HG010NR2Xt8uOk9unR8hkmp2ZRW7iAuI0l755qMSWQktEUfrmC3s1TbnBNxs2HZUxTKOiJyQLWXO2qGFEUrhqbM2gfXQIqeeFsykYATj+otIbSMPmopoE7L6yDoiU9MwGoyIorRdZcgCkiKjCiISJEwXlcDXtFMSpyJkF/CarVoa+OQ34u70QW2eOKtBryuevz+SDRz+Het1QTV6+HQF2LUqk6n06FIkrbOaimvyxioa75FSAzUNZ/WsSvFFDjTFWhWUKdIYdwBP0ajFbPhSBMYBVkK4/X50JvsWIyn131Ks6g7y0GdQafGfVMzPKpwJoyA4eBaw2RI0+KjBCOV+MMRdLoErAYRt78IWWxFgjmZiFSNJ+TVso8aRZlQBES9sSlbqGrLpdMW+4riIyJHLbvU9YxOZ0ZUfAQkpck1VcBsao1Z8eGPOPFJEQ0GnMwCRpLUeHdGjtqAPuRJPTlQp96/gCha0AtqW1UooWbAVIGQBYNOJCL5NGCk18eB7MQbcqMcyJ0q6DWgoVdDc0thLaZMRFZdfo8sekTBgF5n1BaNx1dUrUUMOjuCEtCyNP749GGqpZ5q5afT3BxPthwJ6nRavCoV/Fk1lzkVp/rCZYRkC6IQRhHtxBsSCETCGHRhfKE6FIwY9Wrg+hChiJ+w1IjB2AazECEQ8f5gW9XFZ+IZCOoO6q0lt7GgVzPUyerOfLSo41DNHheMeFEUnQZalXA5HhUA7vsAACAASURBVC0m4oFMwXqspnREJUREBbRNHykGnYFgaC8hWQ1qrbqyJxNnsBGOeLUPwhONlqNa+alwX43tefIj5WRH2I8/7mwBdWr0Jb2YgFVvIBB2EsKESQjiC/vQ6dOIUy11JCf+sITZkIbVYEeSXQTCqmusS5ujjYZkHKZ0IsFyAt/38flDkqtJceToh+iZOBbUprVEUHe05Opzqsegs2ihCiLKIWqrwEF9x6LGGxQIR2rxR6IbRmAgzpyqvau+Fy58b/+q7wR1o0fUYhm2lP5tMaBOmz1N2Izp6JQ66gIV6PXZOAx6vMFqJFlAEBWMuhSMoh2jUd1QUZcQ6kabC0Q7ZjVBllZCePzFBLXc9idS1NimES0RSEuwdjxw5y0F1B24HxVsHnhLHvy/Jm+NA+9PdRPqYNJWtb4Wr1HF2tESTTJ3MiG+o+vg6DlOrHdPZCScaN0YqDtRxU6+fgzUnbx2sSNjCpxrCgj+gPcIe+1o3Cu9Xo8gBSjbX4xoSyc9IRG9qODz1FLb6EE02ElJTsF8IHjqsZRTZBrLlvLnL+czbuTNDGmfor3i1I87vQp3BInGqkLe/NfztJ3yOBf0an3IAkVBDnspLtnIfm8DdnMWejFIQ6ARFedJioTBmEPHNp2IN0UBnxR0Ubq3kAZ9Bh1y2mA1HR4/4li3e+6AOnWhqC4+oguRaInunqs7iKiLfTULhObapGgLdPVv9Xdtwa5+nAtqVtTowuWwvUMtBpt6DrXeAeiknrsJBxysr2gxjqJ3IUbP8xMuYE4O1EV1ORBX7lAoEdVKadJCdUGRNMuiQ0Gb+lGkxtI7XItjjcIT+V2OLiI1TVX9TuTYn67u0aBOTU8QhYAHxhpNVjlRq8KmcaZaSWrQSB1farD6KIA60DbVzU7V8lgWA2cDqFPHTRSfHXguDuikzp/Rj4WjnzP1uf52zB3QSXv2oiYEB3f6tWdZA85Rrc+1craAOm2G0p4f1RJX/cCPWm9E+z76/+o4UucubUxp87uGzZvm3APHy5rVyenM5Hk6x+CZAeqifaX1oRAFcgeL9tw3PedaB3/7Loq+e9WtubPnWW85oE4VW30Pf/ucqVnpVcXVNfUBq7foXH1g3XWg147GRqJoOEFIdzqfmh++dksDdScUmvsArWuaLaPG5NGgIqc7U+up7PEYqDuVav7wuWKgrvm0jl0ppsCZroDw6mePau+b6DJPQJGMxCcO4PyBw4g3htmyfiZz91TQs9NoenXsCPXbWLF+Hf6giW5DL6BTuhrz6thFBW3r5j3Cb76ez6Be48hLsYOkwxbfgzEDzyfTrqOmdCG/f+Biek8r5Lbh+YeBumD9dv755iP4HIMwRqrI7TqCyK5/M72mPdfm61m0U+KuW35LzwwbQV8dW9b8hxc+/Ru+uN5cOuFBJg3oRdzBrFnHvt9zCdQdW42zq8bJg7qzS4fmaM13g7rmuHL0Gmc8qGs+qc7ZK51NoO6c7cRT2PAzBdSdwiaf0adqWaDujJbyJ7v5lgbqfrKGnsEnjoG65uu8GKhrPq1jV4opcKYrIKwp262kNrVCECUKlr7K14UefnvvX3EEy5HiWqG4K5i34HlWM5L7zp9IqlnNAiajt8RhMRydVfNwUdQdfQV39Qaee+9JMnvfwYSObZEkL3M+fpgZzo4886vH6JpspHbfEv74+AUkjn+b60eOpFWymno+enzQuYWXX38EXdYUlNA+xo6/hp0fXM7ihGlMyapmxlaJe2//PYmBHcz55mVeW1PK1CufpF/gE6bP+oTWgx7hyiHnkZOS+L2xyw697xioO9OH9vfffwzUNV/fxkBd82kdu9LJKRADdSen29l6VAzUnVk9GwN1Lb+/YqCu5fdRDNQ1Xx/FQF3zaR27UkyBM10BoURRlJyDFnURVs55nA9WV3HfHU/j2vgvZhWJdO0+iL7tcqgqKSCYOopeKRIrVs3AnH8JneM8rNq+Gk8ohNdXSQArSZY49AYbPbqcR3aig5C7lFlfv8ZWKZ+bL/w5GXFGwvW7+d1rd+F0XMZTN9xCmgUN1D391AW4Ok9jZG4X7HEJtO/Ul7ykdHT+Xbz86i/Yq2+PVRFIjzfitOYyvHU2+6sKScmfSK9UHW/P+DtryvcgJA/nqn4DschOCtd9wcZGD0mJg7nu0l/QPy8Xo5rK7AdKDNSd6UM7BupaQg/GQF1L6IXYPfyQAjFQFxsfhyoQA3Vn1niIgbqW318xUNfy+ygG6pqvj2Kgrvm0jl0ppsCZroCwV1GU3IOgLsSKWU/w4doq7rvzWVrZZfaVbGbLrkJcikCfAdfQPlFk26pXeXNZFddd9widHUGKK/cRjIRZPPv3FIiDuW3UJOLMZjIz22FXqvns05eoNvbi4rEXkpMSp8U4K9n4Dg++9w6Dz/8jd44eiFGUqN23mMcevpBetxVyZTcT23euprBkL0mJXRjQOZ0P336YYMpo9N6duAJeXI7ODO+YTahxJ3sbs7ls1ASIONHpLYTCfiJSGEkRMOgN2M12vAEviUm5ZCQmHTNA/tkP6rZqgajPxRKzqGu+Xm8RoM6eRu/8MazY8QmB4PFk0m0+fWJXOv0KxEDd6e+DlnQHh4O61uSltaZ77nBW7fwcfzB4TsZxbEn9c+S9xEBdS+6d6L0dCerUILrHEzKn5bfs7LlDNbbiVvc8MpJyGJh3weEN27sXLr+cQEEBBTM/Zsj5lzQl0/ju9qvvVJ/PRySiJjb5/p5W61mtVl555RX+/Oc/Y7fbozGxz/ISA3VneQfHmhdT4BQqIOxRFCXvMFD3OB+urdZAXW6yXYNqoZCHqsq9iI62iFVz+OfshQwe9xvGds7mgGGamgxg5vt3sUI3mvsvvowEi5rdEULeKrYVl5PRuhtpdjWrqIDsK+etN+9iibc1D930RzqkqnHumkDd7y+k+01ruXVER9QssT53GeU1XhLtMu+//QDhDrcyvI2Dvevf5sNdIsM65+GtXklxeCCP/uwmija/RWEdWEQ1G5qPiAAGwYYgeDDFteX8odeQnRC9tx8qPxWoc/Yys6LyNXSC41i3cGp/VyAkNXBB+0cprPyaMk8BBl28Fob+3ClqOH6FPm0nEJEirNr1AWp225PL3HXuqHayLVWX4jpdhKEdr6akZidFVavQiaaTPd1JHacGT0+yp9O33USWbnuXQFANvn5Sp4oddFYrINE3fyIJ9hRmr38RvZgUGydndX9/f+PCMvxxRgNtCr1c+EAq7dPb0CtvDMt2foA/qGZPjU0gLWloyHKIztlDaZvRi282fkgw7DoFWc9bUgvP9HsRCEUa6Zk7nmFtL6KNdeAJZxY/0xVo6fevzmhqUr4tjXNJSciLgbqfuMNioO4nFjh2+pgCZ5ECwp6gX8k62CCJ1fP/xH/XVHHfNBXU2TSGIUthQmEfpTsX8OWyL8npey+X9e+mQTpJtVqTZS1r59yP72e1bji/mnIxcSY9oqhHr4tmF1N3TmQ5jK9xD7O/eZkPl27m6uv+yUW92xNNHHs0qDssg2jEQ8Hnv+Ef5Qn0MlhJz2+Hb8mvqOv9OvnuD9kgDODXV92NVXZTU7SAv7z1f5jHfsy9nXy89sYDeLtO494pF5Fms2hx745VfgpQV+O2wqBcttYvRCccK7bfse7wxH5XEz1GZA+Dsq6mqH4ttf5idGI0A+e5VQTaZnXTxuyusvUY9KoGB1Q49rg4t7Q62daquSWjRc0w2Sm3LzUNlVQ61THXvLulajbeOEsibVt1ZVvpGkKhkJYR99tRH+vzk+3lM/+46Dg9MBbUecFqiWPDrsXomjIuHsjsd+a3NdaC41VAzWA+7cMtZBfs49dPjCEtOZ28jE7s2LeOQDhw2JiJQbvjVfXU11OzGqtFzcTeKqUdmcmt2Vi0krAU7aPoez02v5965Y/3jN+qH5bC5KZ1IinufJJ0PY7ql1gvHa+mp67e0St/iXL/Snq3sdMvb+LhGxIxi7pTJzwQA3WnVM7YyWIKnNUKCB8v+1zRbLs0U3SJfXuWU+JN5/Yr7yDJEKCipoySkh3UeyvYVWdk5KDz6ZWfj1EESYV3e9exp9aJIsCurV+xX8hjYPuumHQiiSkd6dImH4texFu/l3U71rFnxyI20YFLh1/KgLxsvs1FIVFbuoiHH7iInnes4Y6Rnb5dYikynsp1PPHPB2k94ina1/+HNb5MJqWW8PT6JH4xpC3TlxVw89UP08HWyOK5T/DmNivTJo4l2OCkcPvXzN9TxKSJL3DX+OHEqTd/jHLKQd3fbqPKZaD/VXdrrrgnlB7+WDd7vL8LEPAHSc1IwGAwaMvcc2mBpC1MZIWdtWvQiXo6pAxCIqipoOqg2tvFyo9TILr4U+001b8UIpEwW2uWkmlvR3pcHjJys4256PgWcAec7KpbS6eUQVhNcYeMe/XXc+kJ+HF9e3YdfcCWOPqvoCgU1W2gMVhN31aTkJEOZkI/kBH97Gp/rDXfp4ASkYh/6imMs+dSO3MmDQYPe5yFdEodjMVoi80fp3HoHADrB94v0VsRKWvcTlnDdvplT0Kv0x+EdNE3emyOPx1dFl0FRFcEOgxsr97Os/PaEFGysFoP/BJddWk9FOumZu0mdfNebtqoUqG32yNgoIJHL9lMn7zxMVD3E/ZGDNT9hOLGTh1T4CxTQCgu33XIxoqaYVXEYHSQkhCPt24XBbu2ElISaJ+XR2JCFok2CwcM0hQ5jKuxinp/AEEREHQ6zbVQkiXUl4DZmkRyfAJ6JKr2rmRVmZP8nG5kp2cRr57nMDFlPPW7mT3rMzL738Dgdunf7orKEZzlG/hq025GDr8Uc81y1tcK9M9NZvHarfTu2YfN21fRKm8YllAxG4vWUa/YyHE4yMjqS4ZDR/3eb1jrzmDS0Emk2Y5tzfZTgLrKRj2Df3YvJpMZ1SWvuYsGLTxu2nbIxmwxI59z1nQKSgTWFM9ErzcyMG8KYQKICIQjISpdxbgDDdoOfQzgnOjoVDTruURbGqn2Vog6PQoywWCIZXs+pV1yL9qkdUNCOtET/6j6IiJ17kqtzwfnT8FhSz54vnpfNbXuctTd/lg5txSwmxykO3Ix660ogoIiK6wvXUiVu5jJ3W/RQJ365SjLESpdpbh8ddq8ECtnswIKBp2JdHs2CU/8A91XM5EWL6FKX8f6fQsZ3OYC4mzxUQikKDi9VdR69muxcGPvi+YbF2ajlQxHa+zGBCRBRkTH9orVbKtcyeSut2EwqqFNombTVe4S6r01qPG3YqU5FIhuj9nMDjIcuZgMVg3WGTCzqnglL/yvFRf1zmRYpzCyoiMsB6n2lNLoqzvHwrA0R198/zXU77x4SxLp9jz0orppLzNno4GvN1bx0MUb6Zc7OQbqfsIuioG6n1Dc2KljCpxlCgiyrDp6HF009zBZQVKhhSAiqhZ3RwUFVTQg94NFPU51e1Vkra4aKPS7g4uq51LdY5Xo9Q5xT9Wsz7RzKE2BRtW/Vbc6tPrqOaPgK7rfqtaL/iV862qnyNFjvvf6h7fipwN19zSBumMJ99OMNI/HQ74G6kzn5MJIjsisKZ6tubwOzJtMhACBsJ8Ve75ge9Vy7aMrtrV78mPPYrDRP3cS3VuNVA0dCDWBurZNoC4KQJqvqB/QKqhbWzxbA3VxtiStf0vqNrNk98c0+KpQ5ANzR/PdV+xKp1cBg8FEx/RBDMm/BJPBrI2B9SULqfaUMLn7zUhNtgYrir5g0/5FhCKB03vDsas3iwLquiHJms3k19eRsnwv0uKlVOhrKdy3iMFtJmO3JWjrmKKa9SwvmoErUNss9xW7yLcKqGvR1oldGd3xGuLMSRqQ21axhu1VK5nU9RYMRpO25txSsYLlRZ8RiHhj8jWrAuqaXEe71P4My78Eq9mBHiOr967iha+zuWF4BmN7hPGHgxSUzmVTxQJtfo25KTdfJ6kWdEa9hZ7ZY+nfeoL2fTdjtYEPVlbHQF0zdEMM1DWDyLFLxBQ4SxQQlNPig9ny1Tt7QZ2X/A6tYqCuCdSFZT8byudrC8ZheVfSJqU7ejHqOhMrJ6KAQEgKUFi+iKLa1YzucDWtEtrjD/k1i7qWAuocthRc/lrmbHuLsFdHe/sIrLq4I2I1fhvh6EQUiNU9MxRQwzRUB/dQ5FtKz9yRDGg9AUmJHALqbtEsDHZUrmX+jrcZlDuVThkDMOii8Sxj5WxVQMAVqGPh9ncY9Ne3ab1ZOArUOWxJOL2VzN02nRRrHv3zJmE12M/BWK+nZwyoy9UqdymLiz4gM74dw9pdjEE0s61i9UFQZzSYKGvYxcyt/6Jr2gh6tRqjWXade/F4T08fqZvy+5w7WLr3P3TM6E+/1hMx6iwHQd31w1RQp7ClagVrimfRq9X5dErvr1nkx/qoOfpMICKH2FG9mnVlsxnadiodUnoyY42B91dW8duYRd1P3gkxUPeTSxy7QEyBs0aBGKj7nq6MgbqzZowf1pAjLeqCER8zt72EVZfJmI7Xxj7Gf2S3N/prmbntn7RP602vVufhC7lbFKiLt6ZS1riL+Vv/QwfzKJKMOQfj6X3bdEFLhCMoEaRjmgwfSzBBcwNGjmiWvrHSEhQQkJQw29zfIJvdTO35a2ThaFA3e+t03D4XF/S4E5sx6vIYK2e/AiXVGzH9ZhoZa2qOAnUJthT2ODeyYvfXjO90I+mOvLNfkBbWQjW0yuqSr9hWuZzLet+L3ZTA1opVGqibrFrU6U2s27eQ1aX/5Yb+zxFnTmxhLTj7b0eSI9p7v9q7g4md78JqtLOqyaJOBXXndRdZtOc9fAEfYzveiNlgO/tFaWEt9Ic8fL75L6TY2jKy3aV8vjYG6pqri2KgrrmUjl0npsCZr0AM1J1hoO6AAeR3uw8fe0B6PEdb1H2bROHb4L/RMx0Itn94NLtv6x/6/wfqHnmOpjMp6m6ppCUdOZC6QQ1lezi6+O7rHbtVx1/ju0Dd55v+Sqa9JyPaTz3+E8VqfqcCKpj7avNL5CZ3on/rSXhDjSzb89lJWdSpsYcERYeixr8UJGRBOmF37SNdX1VQV1q/jQXbPqG7fTI2XaJmPaWlEhENmju9IIeprVxLnakvXVJNRGR1TEtI0pFuu4JWX4V5h8fB1qFTs12r/ysHqCxeTDh5FK0TjNEkMkqEiOZuGyunTwGBne7FuPTFXNvn0e8EdV9ufBVkE1O636rFLouVc0OBmoZilPtvIm1l+XeAulR21RawZu9cLuz2CxyWlHNDlBbWyvX75rKy+Euu6vcQDnPiUaBudfFc1pV/xrShb2qJo2Kl+RVYUzKT3XXLuaDbvdiOAHVjuot8s/stBEnHmA7Xo49ZKzd7B6lxGz/d+CesxjTGdbw6BuqasQdioK4ZxY5dKqbAGa5ADNSdIaBOjcGnIKLX6xHkCJIKD7RMvSdWjgR1SjhAbW0jwYiMyeYgNVF1A5TU4H94nDXUBxQsNgdJifYolAh4qK5zIclgiUsiJd6i1fc3NlDj9iMKBhISE7FZ9d+m8vI7WTj/c+w9pzIg00qD04krGMJkSyQ53hpNThIJUed04gvLmOLSyHTokYRTb4H0/aCuByPaX36EmApyJERjYwN6ewpxJjUWohpHUSbsbUQy2rGaTdF4iGoMRFnC2+jG4EjArBe1ODka4olE8PkCWGw29HoV4Jy9RQV1/9v8Eq1/JKgTwhL7di3j03lvUVDbSKe2l3HJmEl0zEpEOJgm7tg6Hh+ok/A37GTe6ncoDyvoUHDWLKPeOIQOSTqCEQmjaRRXT5iE9QCsE0QaKzextV6hX4du6NWxKkQRdmPZEj4u/IggDvRqpmVPBNlkxGJUx0IjsjiBaydMJkH9fjz1Q/zYosRqaArsdC/BpS/h2j6PfCeo+2rTqyiSiSk9bsUgxkDduTJsjg/UzeOCbncRHwN1p2VYREHdV1zV78EYqDstPXDsix4fqNM3gTo1AUisNKcCqovypxufxmpIZ1zHq2KgrhnFj4G6ZhQ7dqmYAme4AjFQ90Og7vlp1LrK0DV9pKmAZo+7lq//vJi+3QYdd9fLUoRZf7uNaNbXE0smccCCzmyLw2w0Y7NZiNTXUu3xoqiJMY77LqIVDwV1arT/ysL/8dXOtcg6AcJZ9B06lb5ZDmqKVvDN+v/iMqZikHPpP3AiPbKS2bHqQ2aXbUfNGesPdmDC+EtpY/axcsGHrFUasQX0WBIHctHIYcSZ1LsT8Owv4L8zCzjvshvRVS1j0fqleE1hIrRldP9L6JJhYFPBPFaWbUMSG3F58rlo3BW0z7AftwWVppOsspIDmihIkoygPzwJyomAOjkSYN/2mXw4fzVDLvwdw/OsBDyVbNyygLWbdtFr5I30b5+LusT0u8oo3DaXVevqGXvlL+iSZERQJBqqtrFw8zdUVCRy4eTLyEqynXCfnWAXn9bqpwLUiZLM9hVv8uqcz4nL6k5eUhoVZTPZF+7B9Zc9wOC2qVqmzuMpxwfqZIj4KC1dQUHFLg0cN9Sso8HYm7aJOiQlnnZtxtA1M01LaqMVQYezdBUFtTC2z2ANyKnAWp0jJCmC27mTzSUraVBMGFTXV9WKLhLCbO9Ir9y+JNhNR2S9Pp7WxOqcSgVOBtRFQh4aPfUEJdAbEklx2BGUMB6vE3cwqFllOuKSsRiMyJKPhsY6grI6DyWSluBAlEO43bV4whEE0UJiXCJmo55wyEODu4GwLGMwJZMcZzuYXf1Utjl2rmMrcC6BupDPidPn1eYtW1waDrMZKeLH6XIiyTI6g42EuCSMOoWg10m9z4eMgThHKnFGnVa3wa0+DxIGg0WraxAF3O5q3MEQgqAnPj4Dq0EgEvJqdUOygl4fT1J8PHoieL1OXIEAiHriHalY9XoiYR+Nnoam8zpIiIvHoK5RmkoM1B09jhU5jNcTnYcQ1HkoBavJACEPNa56zYrbaI4n2RGPIoVpdDvxh0OIOhPxcSlYDCKRoIt6dyNhRcRsSSbRbkGRQrg9TnyhEIKoJ8GRislgQAq5cDY2EEHQ5qxUhxoH8NtyzoA6RYrO6aruop7E+AzMOvD7G2nwebTNXYs1iXirHZEwrsZqPGEJQbCSkpyCAZlgwEW9160tLyzWBBxWO0hB6l112jOgN9hJik9Cp9b11dOgPrMIWK2pxNvMCJEATncdgYiEzmAlJSEFUZEJ+hto9HmRFLVuMg6r5eB7JQbqjv0u+KlqxEDdT6Vs7LwxBc4+BQRZkY7vi/fsa/sPtEhgw5bVPPL8NGoaS1sEqDMYjRgsqmWbA6m2ikq350eDOtXay1tVQcTkwGo2U7R6Oqv9PZk6ojOFiz5Fyh3N4PxMSrfPYVODiQmDxxByVqDYk7SF99ovnqYm5zLO69URb60LR1oCsreCWV8vpMPEqXRLMqMoQXYumcE2y2AmdnawYOnnWHNGMahtNkWbZrLPn8OgDjJffvkVvSY/QMdkiV2r3mJzaDCTR/fGrDu+4Sn7XWxZuYg1RQ3oDQJKWMac24eLxnTHolNbGi0nAuqce+ezalMhJdUl5I9+nPFt4wgHGigpW8eShfPIH3ILg7u0RQ0xH/LXUVy2lDlfb2P4tffSI0XNPCfjdZVTuHs+GzfJTJoylZyUuBio+8G5RI9UWcCTL16HrttT3H7+OJJsBvzO3bz70eM4kybzy6uuIU5/pNv0d5/0eEGdWi8UrKfKXaM6wWrusKoFq/oXgoXkhFZYdIcYwAk66ktXsGDPLtrk5GsWdTpDOnnpedgtcQQrlzCr4L+EHN2wiCpBhrCvEr++BxcMuRiHGGjm/Lfn1AR+XI09GVC3f/tSFmyYi89oIuSxMnT0z+gS52bBko/YFdJhQiIz9zzG9OpDoHYlX8ychZRopbFOZNS4G2hv9rDgm7cpt9kQvBJ57cdzXu8e1BQt4qsNaxAMEqFwPGOGX0vHzMQYzD2unjy1lc4lUFe89BlmlEvYRB9hSx8uGDEeY/163luxnESrQjiip3fPK+iTl8KWRe+zwlmJIIno4ntzwbDRGGpWMWPdUmS9EUkS6d5rKv2yzMyb8y92BHTYBC9JrS5iQv/euIoWM3vTMiSTGclnot/gy+mRpLBy6Vus8YhYlQCmzAlMHdwPd+lK5q9bStAoEIkk0qfXZHrlZaHXzO8hBuqOHvMBdyUrFr3PzkgYnaQnPW0AIwcMwrRnBi+t34bdJOCPJDFuzHXkiOV8vHS2in2QwmHatL2A4d27ULtlNnO2rSaiJt8Qcxk7cgpZ8j5mLp9BlWRAjPjJaXcBI7t1pb7oa75YsgZ9qg2/L53JE6+hbaL54I2dK6BO8dexaN7zbArZMEW8JOZPZUK3XDZv+JIVJfuIN4UxmlszavBlZOobmf3Fq5Ta4qAxTFbvK5nYMZO9hV8yt7gYq15GtOQzcuBk0gJbeHfRPBSDTgvB0LvvNfTOtrNl6XuscdagE1Ur/TaMGjmFTM8m/r34a/x6E1JYoFv/GxiWY2fzyi8oqC4FUUFn7sD4oRPIio9uFsdA3al9b5zI2WKg7kTUitWNKXBuKyDM3PTW8ZGQc0gnURTZu3cP//3kA7w+l5ZqXoM8p8Gi7oDsqmulzhpPemoySl31KQN1GsESRMSQh2/+9w7uVpM5v6PIN4vW02nYaNonOnAWL2f2znomjBhPvFkN4qVH8O/n3bdeJXvkHYzokqn6riJgxFuxmncX7+TiC6eSYTUQcRXx75nrGD3uInKkUuatmkXb/rfROc1E+c6lrC8LMqRXJnM+eY+c0ffSLcOGa9/nzN2ayEUXjCPedDzDU0AIelg9459ccdMzNAqq4VNH/u+Nv/PbKwcgCpETA3UqYNu/gv+tLaRPn0nUrH8TX48HOC/P1mRRFWHJJ89Bl0sZ2ATq1F1TRark0zc/o/0lN9Ej1dzkEqvg9+xk3uxN9Bp5PjmpMVD3Q1OJiJG6NX/jjg/mMu3OtxnZLgkEl+s+RgAAIABJREFUSfvwKJz3KO9tk7jjxidpEy9pkeWOVY4X1IUDFaxb/xl7wl70ogEUGVSLVUUiHAGLeTDnDx2O5aDrq46G0mXM3r6BtNRcbadbb25FtzbdiDebCbn3sH7XPCpUQ5GDN6kQn9yXAW37YNYdz90fq3Wx33+MAicD6lw11fiCfgRLiOKtM1hX3ofrL+xFo6sWyWAjXF/E/MJiRoy6gtYWN9U1foxxevyFr/B63Wh+MaIviq8RvUOgvrqQeasauGLqFViC1VQFRazGICWFH1MYGMy144dji4XX+jFdfFLHnkugzl1eQIMxA6MoMfeDu7APe5qReSnUBiRtM6Rm53/Y3JjClDHXEigvR3HoUAIVzPviPVJGPcjIbAVnIIig01O2cxnbGyNMGT4Jd30dssmG0b+Djz+dzairHqONzoVP9qHodJRv/YqtjflcMqoPHlcNkiWOUF0pX3z5LEOue59Oehcejw/BKlK2fS17XGYmjh5LnCn6QMRA3dFDOxzw01BdhWITCbr3s6ZgOR0G30hnXQmlSio2o8Kmha+zzTqEq4f1p9HrwawTCFStYOmOckaNnobDV0tQDKGIfrYvf5c9SddwTb906t0NKAYTntq9rCxcztBxd5IcdtHoFTDHh9m+8A3WxV3NXeO6ahuXajlnQF3IRXV1GRFLAkF3KR99+hGTr3mQVF0IP2CWfWxe9V8i2ZcyrksOVaVVGFNMhCpX8+KHu5n2m7uJ89fgF0QUKcjq1fMwZPdjbNs0Sj0KVqOAZ8e7fFLSg9svGo/grCBiVpCUEBuXz0BoM5XzchVKfXpsZpF92xbz2aYK7r7xboTaOhQxgqRzs2jFMpLzxjC2Rz6iIMRA3Um9HU7NQTFQd2p0jJ0lpsC5oIDw8oK7j4eEnAtaHGyjqBOpLKtm4ewVBINBzZ3ydIM61ZZHtKigLukUgjoVFogooRA7Ns5jXpnMFeMvJim8l9mLNtB5+Hm0T7DjLF7BrJ31TNRAnY6wr541K75koSuTu6acT4JRBWF6Qo37WbxoNsGsPkzs0w1RUKjeNovV9Q7GDh6JzrmTuStn0m7ArXRONVG+axlrS/yMHjWext1z+GLd//DqjEQaFLKyJnPRxBHEGf6/vfMAj6rKG/c7fZKZ9F5JSKhCQm/Sq3QQseO6dtFV11V3Leuu6+4qrt+6n676rVtsu+oqCIjSawCBBAiQkEJJ771NyWTm3v//TggiKgRNIgnnPg/Po8mdc895z7mTmff+zu/XvuWpREE5q0/x2uP38cv3U5ly289586XH6ROgw3nO6m1PRJ2rsYQv1r7ICb+JTIzQknFoJbZe93PT1aPw9VA2ujpIWvkXVAOXnBV17vXhLOXTf31Kn8V3nhV1ys+tjVls2ZTuFnXRQtRd8L1Ekb2Nx99n+VuvseQnHzM/MQq1RkLd4iLps2fYVOrHAz/9FeGmDhR1Khe2xgIOHz5NaP9YbPVV6D28wd6IS+eDSWfnVEYVI2ZOw7utCIQSUVeYwpEazZmtr0qRCBdOqQW7JZ+k3auoMftj0rZputZ13GytpFw3hTvHjkCvbl9U4BX15tuFg71kUSdLNNSc4tDBtaRWF9JQU4+33y3cuXg45VkH2H1yBxXWchyuPtyw4DEidaV8efALMstzcNiKsHjfywMzE6jM2cWutI3USBrsTYO5/8678GrKJenIVjKqcnBWH0IX83vunz0Jk0jd1IUrovVSV46okyg/tZvdmV+S11hF3ekNDJvzIZN6eZF+bDM7i4+jsxTgHbqA22bdgqX8ELtTNlDgqKEgU2buzU8zPrSFI2nbSco/gmStxitkPLdOv4GqU/vYe/oAFZZiaqr8uPGG3xFnKid1339JqS7BYnESHLSQW2ePpSrnS7Zn7KG8qZS64oMsuOMgCZ7K+/FmDpZkYrE68QtdwO2zpuNtbL0hhKg777aQZZyOenJOHGD/sXWUuJS0v7Esmn07vfUVJB3eREZ1IY3Fawka9L8sHTuCkhO7WZu9C4OjAoc6ktsWPI+flMOXB9aTWZ9PZamTuBHLuWlEGCczd5F0ch+W5gZUmLh2wW8IlorZnbqRU2W51NY24t/3F9x3zRDcGU+uIFEntTSSnbaVvTkHqVG2h1fI3HDLbwlqLiDp6CbyGstoaWwgcdTTzB4cTHb6FvZl7KBecpKVFs+zzz2CZ1U6u45uJKu+AmdtPYPHLmduH3+SjyaTWpyKpe4gFq9f8OjiGdgqj3IgZSWnWuw0N5oZO/YuJsR6cPTIRvYVpWOpycKqHcvy2x6H6lS+3PsZp50NlFXpmTRpOQuGxKMRoq7L/66ce0Eh6n5U/OLigkC3IqCy2BvaZ0K61bB+WGeViqpHM1P4/eu/OJOjrvUZ4Y8dUaeIutDgAKSqcsobm5A0mkveGvX1YhIgWxvJzthHWjWMGD6R+AAzTmsZO7dvwjdxDiOiginJ2sTeYgfXTJyD3lpKaloy+a4Apo2aSJCHhEt20VSZzd6DB9D6DWP00MF4GVVIjnp2J21FFz2Gq/tF0tJQwvqkDYQNXMTomEBy0jeRXuHBlEkTMGkk7FYnTkcth5PepzpsIXNHxbUm6W/XoUIjy+Ts+zd3PLOSpU++wD1TB6I+b+tse0SdZK/j+LG1HGtoQtfSRE72F9QHPshDCxYQ5q1s7XCy99P/hQGLGDmgdeurcsiucndEXd/FdzAoUH92i6u18STbNiuibgaRgWax9fWC86mGhmLe++cyUqRJ3DxnGX0DPako2Mvf1/6bwMH38Pi1c9FrvoqSvFBz7Y2ocxcDkTVopUZS0ncREz+BpsIj2L0SGRTjj62pCbXRg9bYWiUIVUtNQTKHKl1MShzpzlGnUv6pVdgastmx/QDxI0dTWngA9zusJOHlO4QB+hr+cVLNz2dMxqRprTcrjh+HwCWLOmcju7f+k1xNIrNHDaL6xA6ST/sxfrCNL1KrmDdrASZHAbsPHidh/FJsh15gn2YCi4YPx1mwhrezo5gT08CWrEZumrsQbcNJtu7OY+biqZza/hdKfRYydVgstWmr2FUTxw2zpmEWoq7LF8cVI+pcpbz7ym8Jm/5zRvQO4uiqxTQmvIR/+TbyDaOYN3ok1afWcrjCyPSEBNZ89gG9J9/DkGAnO9Z8gsfwJQTU7CHbHsY1Y0dRfXoT6TUWRkT58PEXaUy/7n56Gcr5bPV/SJj1GA3ZqynzGMTMYQMpPbmXzBIDowcY+XTNZ4xb+hi91CVsW/so4Qs+geyPKNYO5Jphw6jISeFYuYqZEycKUfddd4MsUX56J+tT85kwfh6+6noOHEwmfujVFG/5M6WRNzJjRH8qDrzCAWk4wwNqOFgI86cuQq5JZVf6ScaMnEvGltew9VvG1P6BnEheR5ZmFOOCCtiTWc3kyfMx2k+wP3UjCaNu5ujGP1IX/yDzE2MpPbiSTfbRPDh7KMqmC+W4UiLq6vLX8+GWHCbNvo4gqtn46Z8ZMOcBcpI3EZR4HcPCzaSnfEKT/zQSjRn8Y28Jtyy+HR97Jn//xz6ufWAB6Umb8R84ncRwH9L3r8QeMZTIgpfZ3vJTFk0ch7NgJR9nRnLThHh27dtC74S5DAj14EjydghOILBmJ9tKgrh2zkyceZtZlZLBogU3sD1pDf0SryMh1MSX+5LQhY1gakKcEHVd/lfl6xcUou5HngBxeUGgGxEQxSS+Y7IOpe/jN68tp6r+xy0m0dY9vdETg6cJH28zcmMD9dYmbM3NOFvTX7X7OFfUKWUXsjYu4qVDccweO5EALy0aQ2+G9YmjMmsru04XEhUVTm1JJeGDZjAuPprtK3/Gx6UBzB8+Ak+dCx//IfTxdvDuOw9RFrqEqf3C3Ql1Q6JGE2soJykljYEj5xLtp0WSnGSnfkFybg0REWGUFucwIOE6hsdH0FCVSWZeNlUVNdSpIpg+ZQohnu4MYZdwqMFeQ3pqBv5XjSLCW/uN17dH1Lml25miAa6mcvZu+TO2hGe4Jt5Ms7WK7FPJbNv+Dpqo6UwcPY+EiAgclnKyTu9kzboNRI6Zx9VXjSc+JBhbTQ4HMjaz/9BJ+g+bw7hhVxPu1XMLSnREMQmVrKa+KIVV699l06lTlNktRPn3I1hdRqNxMHdf/zgjeinVXy++Otor6pS7SHbUk5X5KSedA5k9dBCnju7A4TuKwdFG0vemEj15Cn6SE0lWdsVqqSlsE3WjzghlFeozom7XrlRiE+LJyDqAMTAEbDU0qfswMVTDOydkHpw+CbMQdZdwb3f8qZcs6lxWDu1ZxaHaFnqHBVJ/YjeFqpksuVrPrgMH8YmOx2AtJL3Iydz596HNfo+tJc30iu6L5vQGdqtnc+NAA1uOptOvXy+kyjzS84wsu+16yg+9Q1qdL2FhflRkbKDEdyn3zZ0qRF3HT/tFW7xiRJ1Uxbp/v0B9UCLRAZ4c2voHome9RW/7UQ6XqYjtFUxFzi4aDP24Yfwstm9Yja1XJOEqBylb9nDV9U8Q25xCSn45YeHhNBYdpkoXwdzEq9i89XO848Zhkir58nAmS5Y+jatgB4cbLcQGBVN76ggN+kTmjAlj68b/4NFnDF6OCg7sf4spP92Jd/4G0mqaCA2JpDY/m1ptH264ZoYQdRcQdTVFR9mYvA9zRDiedhuncsqYMHspjtR3OGgLIi4qmOLDH1IfcyvTotSkHD9NWEwMlqoTnK5qZMk1D1Dy5SqyPHyI8fGk4OAeWgbezjXRVSQdSsEnqvX9Lau4iNmzllO+/13S5Cj6hgdRcmwH5RHLeHDOMNrqY18poq6pcg9rN+zCFNsfn+ZKdhw8xMIbH6Xy6DqqjVEE+xo5kZFM9OBljPOv4v0dh+mTEI+xJofVm5p45Ne3UXBgHZVaH4JNWnIyUwgYsoRE20a2FvgRERtHfd4W0h0zeXBWIin7v8Dq50+IXk9uxnGihi+mj3SYjemlxPaNx5a3jwPVntx3/e2k7l2N5B2Kj97IsYxMeg9fwryhfYSou+hfgc49QYi6zuUrWhcEehIBIeq6iagzmrxR0rO4/ZESuiO1YLNacThb/7e9x9ervjopyU2jsLqBFiV5viL9DCEk9O2Hl8ZBYW4qufUO/IJi6B/dG6PaSu6JNEoaLbiUdPuSjLdfb3oHmygqzKG22YbkkpFVaoLCE/Gs3kt2QyRTRiei1SmxQ0qRBws5p9MpqbfiE9KPAZGRGDRqaisyyMovosUQxriEwWhVzu8XbSQrm2AVwedC/hYu7RV1bTylFiuV5XlI3n0I81a2qlWQfTKbBllGLcv4BPVlYGQ4zZYyTuacotHlQpZcBIQNJC40GFv1adIKilCplS2QRqLjBhHp03Oj6jpC1CnsVbIGp7WG3ILTVNsdePlEEaKzsOa/d/FxzXRefvhxEkI8L1oVuH2izkVzYz4796/G5juKyYNHE+Sl4XTap2xKy8Tkr6WibiD3Lp1LccZGjpXm4VLrsDXkUGxzERukPKFWig5riY6cTGIY7NmZwsDx1+CoyaG+ucWdB9JhrSSveAOF5jt4eKLY+tre96zOOu+SRZ0s02Kv5mROFtV2CAoIw1PnRViYL7XFmZwoqcRg9iPA7EdgaBSe2Dl9MplSi5HYiFBaND5E+ntSWXycU5WN7gqX3gZfwqPD0TrrOHniONVOPWE+XhhNAYQGhaLkERdH1xK4YkQdMvamIo5nn8Cu9yHcU6nYHoWfp5rTJ9KocMj4eQUQ4B1ASHAoUl0OqXn5qPU++Hj44h8Yiq+Hk5ycDEobrfj7h+Br8iE0KJyG8jROFFeDKYRYk4QheCC+1HE8J5Nqi0RwUBheHv6EBfvSUHmCrIIydF6+BGllTBFD8KOO07kZlDa5CPKPwOTjR7i/P/ozqQTE1tfz7wklR66T6tIsMksq0Bv9CPYPIcA/CLPRRvrRQ9SrPAg2e2IyBRAY6E9FXgZ5tQ14eAURZDYTHByFh6uGYyczsLgMBPgGuc8NDTRSWpBJXkU1Hr6hBHl64B8chVmqJS0rjXqXNxEh/jg1gcSF+52NOr9SRJ0SjV9ZnM6pkgoMPuEE6px4h/ZDYy0hO/c0Vq03oT5e+PmHE+hjpiLvMNkVFvwDgjE4PYiIj0ZuKiEr5zR2tYEgL2+8/cIJ8TGSm32IYquEr7c/vp7eBIVG4qrLJT0/HyeehAaF4aPco74acrIPU9qknOuNt05HQHRfqMslI7+AFtmbAP9A/AKCCHJXFBc56rr2r8rXryZE3Y9JX1xbEOheBISo6yaizl2s4EyUl7vLKhXKFt1LcHTul31966uMCmX77FftKJvx2rJ/qc/87tyfqdCe/SCmtNd2tgbNOX1RemXh+OFdOAOGMjA6CNXZLaytIk255tfbbf2pkovP1Yn1ML9b1CUysc913evuvQx7q4i6z9Nfp1dAf0ZGz8HiqGdvzmriAoYQGzzIvV7af7Suk7a1Iksy9SXH+GjdSoYueIyREd4dJOokXE4bDRY7nkpFYy1uEe1yNFFvsbqFsUZrxs9sxGqpx9biQLlz2u4/yX1fug06er0Zs1GL3d6CwcOMTtOao065I1qaG6mzWtDpffDyaNsw3X4a4syOJXAxUbfu2P+5q+3NS7gbnbotTqRj+yBau/wIXDmi7vJj394etYq6ddw44km8jX5klB4gq3w/c6+6C53WQHLeZg4Xr2H51f9CoxYVWdrLtSPPu1JEXUcy68q2RNXXrqQtRN2PR1tcWRDo3gS6UNTJuFrsVNXXYzT54eNx/hcfJRmulZraOvRegfh6ftcXo9YvxMoX47b/ap2CS1VWF564y23ra0cts/NFXUe1+812ZCSXO5DILTQul+PbRN3nx/8Xf2M8U/reeLZwyOXS3+7WD6ujnnXpr9M7aBDDImehiLu9OZ9+T1H37aOXXcre0/atq2+LqCusy2ZH5icM9JiJly7ErYaV9w/3OpW/KvCgvLZt7bpFuVvPqS8YwXr2PHdbre9RXx0q95PstnO629z2pP4qc5DVuAO7voIbhz6FpHKSmr+TiqZ85g6+y/0QYX36P3E4nMwffB8GnWdPGr4YywUIlNWcRPWLuwhJLsOVtIdSbRVHC3cxNnYuvqYgTlcd5kDOZmZfdS8BJqXiuTi6loDMwYKNHC7cwvXDn8DL4PsNUXewYBsHCz/l7jFvYhT3btdOz5mr7ctdS0F9KvMGPoSn3syB3AO8tj6Sn4wPZepgNTtOvYfT6WJ6vzvQacSDq66epBZXM6uPrcDHGMnUvktZc1DPB/vKeWrxUUb2mvf171S5ubB0KfZDhzi0YSXjZi2+4Gdl5e+r1WrF6XRe8PO/cp6npydvvvkmK1aswGw2o3bvPunZh4io69nzK0YnCHQkgQuKOqWaUW7uKbQBMUQF+KGWJRrrSimraUCjbJUIC8fY3oeVsoua0xu56z+fcc+SZ5k1KOI8teaipng/K/54P4OWrebWMXHn/F7G1VzPyVPHKbM04WnwRa1y0GC3o1OD0+VCbwxhQJ9B+Hu2Zt92Oeo4lXmUBn0w/WP74NXujrbiFaKuI5fZ5dPW+aLOIdnYn7uWvMpspvW/jXCfONQqsd/s+8yYS3aSXZbMwcL1jOk9j94Bidgclg4XdZfSt/NFnbdnADXWUjZnvIfJGU5v02j0ao9LaVKc290JyDK1zhIyGzcTEzaAyXE34OKboi61cDuH8jYxo9+d9AochFYtKjt096m/WP9tjka+PLWKvs//iahjzm+IOm9TABWN+WzL+oB+wWMZGjkVnUYpMCSOriCgfLGvs1Ww4+T7aNR6ZvS/BYPWk4zS5K8i6nQGTlcdY2vW20yOu43+IaPRChHUFdNz5hoyFY2FbD/xbwK9ghnf+zr3HJ0r6qYPhsMlW8kqPcSEuKX08r+qC/snLiVJLvJrj7Pj5HskRs1gSNg4Pj6g5597y3hh6RFG9logRF0nLhMh6joRrmhaEOhhBFSv/vsPXwv6kFwuTL6DWTRlFv4GiYyUT1mXXcDwoQsZ3T+e5uo0duzbTZPVyLCptzAkyqddsWxKBdB9G3/Dz9Z/xNgBP6V/kBdSix2d71XMn7KYKG8NVYW7+O3TCxl81yHumdDnTJSLQlymuSadV/56Ixb/m9A1FzDk6puQMl/h16f8eDwxjE1HGvnFgy8yNMyEw1ZBStI7vPqflznhOYBHb/ojC0ePwtuob3d0V88VdU307huJ0cNw0W2DPWytu4dzvqhroZlaSxmbM/+OowVCzLFoVO21zz2R0PcfU4vkoLTxBFH+8UyMvx69zkhzs+PyEnUmf1ySxJGirW4JY1KFoVObvv+gxSu7IQEZi6sCs8nMtH7L8DOHIkvSORF1dyIhYWuxsCH9LRptdYSY44Wo64YzfWldVmFx1FHamMGSfxwl/HDjN0Sd2eSLy+kkpWADGSX7CDH3xagVov/SOH//s5UY5Tp7OTZnLTMGKA/W4lGS0WaWprhF3Rxl66vegKPFxt7Ta8itOkKY1wC3TL184vq///i7wyuVLZVVlgJklY3pA+4k2CsarUpP8jkRddMTWqix1bLr5AfUW2sJ8Yo/k/qkO4yw+/dReahaYTmFvymMaf1uQyP7UVarorqpmfDAJoLMwejP/RgsIuo6dNKFqOtQnKIxQaBHE1AlV+TIyuYN5UOMChcHd77K52l2nnzoJQx1qZTLvQgw2snO3EyqJZxrr55FpJcau82CyuCH2aDC1mxHydN0doujkrNJpcZg8ECn0aJSSZSe3MY/13/AVePu5ereYbQ017Lqo1+x3TKSlx58mr5+OqoKk/jD8wvwmPQaN46dQFRQCN5eZjSKqKvN4PW//RJ7wCQ0rjrGj5vFqaTfUh66nOFeZewr0bFs4VKqC3axdsebbCyAZQt/xxDHFv695R2Iv5UloxYxcsAgvA061Bf51NaTRV1c3yiMHkb39q4r7ZCcMin5G91P2EfHzMWJ3b2dscFWxcnKVKotxUiSJD7UX+LCUGy/Vq0lzCeO3oEJeOi93FtK7WdEXXzgUGKDlBx1zkts+YedrsxtdWMZKXkbGdt7Hj4mf5R9sy0uB0W1WRTUZtLstHX41vkf1mvx6s4m4OcZTFzgUPw9Q9xFZ5T8h6n5OyhvymPu4LvduRSVaMym5jpOVR6hsrEAl+QU7wudPTE/UvttTys99GZifROIWvEvdBu2Ip3Z+nqkcCdjY+fjZVIeTKpobrFTUJdFYU0GDmezWBddMG+tdbRUmA1+xAUlEuoVi6xSijqp3aIus3wfcwfdg06nd8+Rw2njZMVhShtycLpaxBx14Rz5eYYQHzQUP89QpTIUWowcyN3PX9dHcOOYMKZc1YIkq2hy1HK6Wnl/zUcRfB2dwqYLhtwNLyGjUakJ9IomPnAY/h7B/GuHnm2ZYDZAmQV+txBGxp8zNCHqOnSehajrUJyiMUGgRxNQ5cuyHHX2z2ML+zb/nv8ml/Hz+/+EVLCeLWl5GPzjGDd0OBpHHWrvvoRqq1j3xcv4Dv81YwIa2JWWREOznaqyXdSqIogJisfD4M3wxHnEBPhhqzrKJ2vfoSXyGq6fNBVfDy326iyeePMRWkJu4vnbbiPQIJ8VdZ6TXmN6lIni6hoi+l/NkKh+eDpO8Prff4UjcCo0ZONQuZCCEhgTGUJtfTH+EaPp4+Pis92fUtJkx6kPZEh0BDrJSmlRNvWSEZUuiBmTbmJE794YlDKNFzg6R9RpGHHjz9Dr9F8vDNGFS6zJ2kBwLzN6vf4KjKhTKtXC8dI9bqk0KGwyLprd9BWho0RuSme+sYmn75e2KNu+6LYJ8NbsbDKOlhaOFm8l0rc/Eb59LrGYxKX14dvOVua1zlpJRukeEiImYzb6nMlt2TrDbfP9w68kWuhOBNwPppR8gW0PK2TILEum1lrC+LglrVWj3UpXqY7XWiqk9X1CHD2RwLnzq3bJ+D7/MoYN26jYuppKTT0nypPd7x8mg/IAwp3RsrWK+Zk8lGJddP6qOHeO3ClAz9yVynt8blU6eTVHGd97KTqt7kw+UeUklVLPXty7nT897iuc/Rxw9v21NberBgNpxWn8z4aB+Hn0IthXUlK4ut+DNSoJtdz6fiuOriOgzEpFi5o7h6hIydew7ggomYOKrfB/N8PV/c/pixB1HToxQtR1KE7RmCDQowmocmVZ7nX2C4iDfRuf56OD5Tx6/5+J8jVgaSgj/cgH7DhZxqRpTzGmlwfHd/6G/znal9/ffTvhnjIN1gaUnAfb1zzNYfUY7p09Dy+9DpPJD6k+k9df/zm6xGdYNn0c/p7K006J3NS3ePjfHzFz4SvcO3EoOpXLLeqee2YBCXelcvuoMCpK01j1xV9w+cxjwYQBrP3gKYo1iejspzF66ClURzNr2CCsZV+SUhTGg8seJtpXjU6txyk5cCnVDJQvW2otOrWOFpcNldqIUW9wJ3W/0NHRom7Dy/fQKPkx/paHQa3kQOv6jyXup8xYaVIVn/3w2qNX97cOzv0JX3nIi+zOWXvuPIivWx2zHr5iqqw59wdyhfTZyr8dc5V2t6KETLkn/fxXiPluN8MeeeLX731leSpf6t0FP8T7Qo+c8fYMSiVJxLzwd8xb9nD8i7eQPT1a14P7M4P4e9Eehp1/znnz4Jbpbbs6xBx1Pv/2XOHr8yC5NJwuHoy1+fx0Oa3aWxxdS0CZnRZJZlgMbMtU8cUR8NBBuQ1evRHG9ROirrNmRIi6ziIr2hUEeh4BVZ4sy9HnRtRt+h0fpbSKul4B5tYRy05qSzOo1QTgKN7Mu3tzWLTwEUZHB5wlIktONn74IPs0U/jFomvxMbYm3nY0FZNR1EBs3AB8dMoWIydNNZn87R+Pk+81nl/e+hiRPkoy5jOi7tcLGHzHQe6e2K/1y71UR07OCUxmE5998DhF4dcyLT6a8hMbWJN2nP79h+Gq3k+RNIVnb76d7NQ3SCmrp7GhGtkzFH+DisbTUUj5AAAPt0lEQVT6SlwGE9ERY5k/4TYifS+eFLyjRd36Ffcge8cw9/6nUGtEDrSedyuJEQkCgoAgIAh0ewIOBzz7LKxbB0lJEPDV55xuPzYxAEFAEBAEziPwzg7YmYW7OGCdHZ6YC8N6d62oe/HFF/Hy8mp3HvHuPIkxMTEUFRVdtCpudx6j6LsgIAh0DAFVakWBHHymLSXS7XDSa6w7Vs8vH/ozsQFeILuwNFVTU1fBkeObyatuYOCwW5jQN94dBdfUWE1Tc7N7C9GOtc9yWDOG+2bOwaTXoDf64Gs2o1XKbcsSzfZ6SnIP8OGedyipD+emRY8yJi4SjTuyqVXU/e7ZBQz66Vei7uwwHdVs++gR1jlHk6hpBP9wdOlPkBq2ghGa/STb+vDEzQ9iaC6iIGsLr65ew9D5TzHKUMRHnzxPRegNPHb9HQyIiMSovXj57w4XdS/dg2SOZp4i6rSiFH3HLF/RiiAgCAgCgoAg0IEEmptbRd3nnwtR14FYRVOCgCBweRKot4K9pXXTgZLqwdcEZ2ItWjvcyVtf33jjDV599VXMZnOPFnVKqgTlCA8Pp7CwUIi6y/N2EL0SBC4rAqrn379fVuK72kLPLfX1aE0TuWfxMsxSOWmnj5F1/L8UtOiJjl7KhMEj6BUc5JZvUksDqcnvsTPnGC61jqa6KmwYCfBWqiiqiY+/kZnDR+OtV1NTlMLmL/9LRpmdqL7TmDhsCnGBfuhaLR3gpCJ/B088sJghP0/moWkD3VnD3IfspCZvD/f99UlmXPcO/SveYUtVANf1buDnG2v5zbyx/Pn/55NZfuuviTOUsGH9n1hV7MNdYweRX3ycelslBbkZBAx5gWdvWUqwhxB1l9UqFJ0RBAQBQUAQEAQuBwJC1F0OsyD6IAgIApcLgS4QdatWrcLT0/NyGXGn9kOr1ZKbm4vL5erRYrJTIYrGBYErhIBKblP83xiwi8rCZNYc2ElIzHxmDRmE4fvu2JQc5KSt4UCdN9NGTCfY9G0NSVjqctm9dw/Bg+YwrFfQ2R7JUguVecmkFFgZP2kqzSVHOVbpYnhsIMdTjxPdfwhFBfsweA/FXpNMenkRRo0Tpy6a2RNvJtykpjF3I5vzaxkz9DoilD24FzlERN3FCInfCwKCgCAgCAgCPYyAEHU9bELFcAQBQeAHEehkUffmm2/y/PPP4+3tjVrZgdWDD+Urd1xcHMXFxSKirgfPsxiaINBRBC4g6jrqEt2zHSHquue8iV4LAoKAICAICALfm4AQdd8bnXihICAI9EACXSDqVqxY4d762tNFnbI6RDGJHniPiCEJAp1EQIi67wArRF0nrTjRrCAgCAgCgoAgcLkSEKLucp0Z0S9BQBD4MQgIUdeh1IWo61CcojFBoEcTEKJOiLoevcDF4AQBQUAQEAQEgXYTEKKu3ajEiYKAIHAFEBCirkMnWYi6DsUpGhMEejQBIeqEqOvRC1wMThAQBAQBQUAQaDeBNlG3bh1s2gS+vu1+qThREBAEBIEeRUClgoICWLYM++HDHNqwknGzFqNSfXcuOSUPm9VqvWgONuU8pYCEkqNObH3tUatGDEYQEAQ6iIAQdULUddBSEs0IAoKAICAICALdnECbqPvb32DRItBdvPhUNx+x6L4gIAgIAt9NoKkJtm7FXlUlRF0HrBMRUdcBEEUTgsAVQkCIuu+Y6MPp+/nNa8uprC9Eoza4z5IkiZzGKtavSGL4oDHtXiKSy8n6l+5BMkcz7/6nUGv17X6tOFEQEAQEAUFAEBAEuoiAwwGvvw5r1oBG00UXFZcRBAQBQeAyJiBJ1O/aRbqIqPvBkyRE3Q9GKBoQBK4YAqpTZcfkK2a07RmojLvqUHp2Kq+/+xL1TRWo1Voh6trDTpwjCAgCgoAgIAh0ZwKyDG3/uvM4RN8FAUFAEOggAg6ngxU39GLWPW8wcva1YuvrD+AqRN0PgCdeKghcYQRUf9oyW4i68yZdrdFRWWxn39ZMHM3Os3+QRETdFXZ3iOEKAoKAICAICAKCgCAgCAgCVzCBFruFvywNYtL97wlR9wPXgRB1PxCgeLkgcAURUFU1lghRd96Eq1Qq0jJTeelvT1LdWIJG3bpVVYi6K+jOEEMVBAQBQUAQEAQEAUFAEBAErnACnS3qXnzxRby8vFC+f/X0IyYmhqKioosW2+jpHMT4BAFB4OIERI6672B0OH0fv3n1ASobRI66iy8jcYYgIAgIAoKAICAICAKCgCAgCPQ0Ap0t6l555RXMZnO7sCkyT6kY21lHZ7cfGRlJYWGhEHWdNYGiXUGgBxEQou47JvOQIupeW05VfZEoJtGDFrwYiiAgCAgCgoAgIAgIAoKAICAItI9AZ4q6N954gw8++ABPT892RdQpkq6zRV1nRfYp/TaZTOTm5uJyudo13vbNkDhLEBAEeiIBIeqEqOuJ61qMSRAQBAQBQUAQEAQEAUFAEBAEfiCBzhZ1H374oVtgXexQUhAFBwdjNBo7TdbV1dXR1NT0gyRam0j8NuGn9D0vL0+IuotNtvi9ICAI0C5RJzntNFkbURt8MBn0fCODgNRCg6UeNGbMHkbUl5hiQJZcWJpqsTudqNQqJAlMJh9kZzOS3gcvXdfPlIio63rm4oqCgCAgCAgCgoAgIAgIAoKAIHD5EOgKUXduRF2b6NJoNF8TWkoUmpLjTZF6nRVVV1FRQU1NzfcWdUq/9Ho9DofDPYHnyzoh6i6fdS16Ighc7gTaJepq8pL416q/MXjRy8yMC/umqGss4J+fPIc19A5unzYWL4P6ksbtsBWz+uMVpDXVY7NbCYrsw6zExZw4sJKT/jNY0D+AkIAonJZSKq1NeBj8UcnNNDls6DUqnC4JnT6IXhExmPWa1mvLzZQXZtGgCSIqOBzjJco+IeouaQrFyYKAICAICAKCgCAgCAgCgoAg0MMIdKWoU0SXIuT8/f3x8/MjJycHRdgph/JzpWpqZ4u62tra7y3qmpubmT9/PvX19Wzfvv0bkYJC1PWwm0MMRxDoRAIXFXWSs4H9m5Zzz0dbWTLncQYF+yI5LTSqB3PthAn4G7VQd4LnXp1PY8wrPHP9NfgY1FxK4R570yne/vszFGm8KClJIWH0g/TSlHIgP5sAf1+MpnCujhvP7i9eIF3WE6CLpnefeMpPf0pylZrBISZKavrw6H2/IyHURLOtlpNHV/Kvla+SZhzDI4vuZ+LgwXgp0YDt7JgQdZ246kTTgoAgIAgIAoKAICAICAKCgCBw2RPoKlGngFBEnVJYYuDAge4tqOnp6Wi12m4j6qxWK3fffTfTp0/n+eefJysrC51Od/b7pxB1l/1yFx0UBC4bAqoma4PcJq9aw4g16HUGtO6nFzI1+dv5v1XvEppwHYnhXjhs9Rzc9jxP5M4mc8WvifUxQP1J/vDGzZwwLuLu2UsYGBGJj9mMRtkCK7tobrbglL9jP6xKg8pVwrtv/ZpSn/70C9ORemA7TZ7xXD1kPH0igjHoY+nlY+Odt5+mJXgy6pY6Jk1aTMGuP3PE8xom+uezK8/AHTfeg6o2jW173mV1+nHGTX6MgY59bDu4h4DEO1kyfDLx0dF4apU3zAvPgRB1l80aFR0RBAQBQUAQEAQEAUFAEBAEBIEfgUBXijrlO2m/fv0ICwujpKSEjIyMbiXqbDYbd9xxh/vf0aNHefbZZ2loaDg7BiHqfoQFLC4pCHRTAqq/fvKsrJY9UOPCqbKiVscwYdQiBkQEIjXmsmbtSxSYx/OTa24g0EOHtTaLt/96K/81Pczq+28mwENzRtTdSrZhEQuH9iK3sIbxY+cxMDoCL2cFSUkvcbjJB/35ckx20mzoz6zhCRxY/Srl+gCKiw/Tb9htjIiJoq42h0YJQgKHc1WIhvffeZrmgBnQkIlKSSQaEMvIXjE0NObjHTySWI8G/r7mGSobAshFxzWDRuAhVZKR+QWSYRJN6kJuWfgaU/r1x6i9sKkToq6brmjRbUFAEBAEBAFBQBAQBAQBQUAQ6BACXSnqlA4rEXWKrFOi07pbRJ0i6pSIukmTJvGXv/zFLeuUrbttQTFC1HXIkhSNCAJXBAFVZVWB/OXnv2e3tTeP33wXOlmNh6cZXXMZWz55gG2qsTy05GGivD2RZRf5R/7KrX97jSVLP2b5lGG409EpEXWvL8US8zK/XDwBKpJ55YMb0cW+xh0zp2LWOHHIqm/mtkNGVmkx6Gp5/83H2FVlwddXi59PGBqcaNFRX1HLsKkPMa+/P2+//TSq4Fm4qvfT6HKRY3XSK8wLmp041cP46bW3EO6tQa3SIElOXJISIYi7QIVOq8fZ4kCjM+JhuHjBCyHqroj1LwYpCAgCgoAgIAgIAoKAICAICALfQaCrRF2bzFJy0fn4+Lhz1CkVUrtbjro5c+agFKVISUlxV6g99xCiTtxmgoAg0F4CKqfDIiet/hU7rfE8eeuDGLWthSCaKzNIOlnNkGGjCTLqQZawVGfx1tuPcIgp/P7uR4jx9Wi9zhlR1xD9Ik9dNxMfoxpncx3pacl4RY0gNtgP9QX2msotFras/hn/yGpm6aTr8DeChBq1rYhNa36G74zPuW9sHz75592ke01nYu84bKVfsrfYweQx03EUbeTL8lieXHYPTWV7yatroqa+BJshmmgT1NQWg0cQEYHxDO47hgDTmYITF6AkRF17l5A4TxAQBAQBQUAQEAQEAUFAEBAEeiKBrhZ1CkNJktz56toknfKz7lBMQumzElWnSEdFyomqrz3xjhBjEgS6hoDKbq+V96x9hl2WOH65bDl6lQqVSoNGpRSEcCeZQ3I5qCvLZMvmF1hbYuCn1z7HlH4xaNVnto9+i6i7lO4rom7Dygf467EqZg+diVnbgqw2orEXsW3bCvovWsfyyWNIXfULPpNGMdQggdmLxoMPkx/zP/R1bidNHsFTN90LTQXkn9jJa6veI2LWH7g5vIH3//skdeHLuH/hMvqHheOpv3hVWiHqLmUGxbmCgCAgCAgCgoAgIAgIAoKAINDTCPwYou7bGCryLjAwEIPB4JZ4nXEo+eQsFku7iw9+Wx/a+vZtBQxFRF1nzJpoUxDomQRUz73+kFxSnERpiy9Deo9AJUFw5BRumDaNAJMBmms5tPsf/GvXG/j0e4nbpk6gd0gwOvU5lV1/qKiTXNQoIvCLx/nl4Waeu/5JLOl/pCpwMdcOH01FXioO2YuklPcIH/MHEiwrSbGGMcOvhEeP+fLcmAg+2HOMZT95htGBsHv9Y7yT14vl4xPYsWcV+3M3kNcoc+u1n3Pv/DGY2jGXQtS1A5I4RRAQBAQBQUAQEAQEAUFAEBAEeiyBy0XUKQLs2+RXR4Lv7GsIUdeRsyXaEgR6NoH/B1V++OWqoId6AAAAAElFTkSuQmCC"/>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3657600" y="1714500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2055" name="AutoShape 7" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABOoAAAIPCAYAAADNWzHUAAAAAXNSR0IArs4c6QAAIABJREFUeF7snQdgVFX6vt8pmZn0Xmmh9yo9oCKgSBEUEBUsiKhr13V/7q7uquu6q2tdxLoWpIkKAkpTURCkSu81JBDSe8/U//89ycVJSJmBIKjfdWeTzL333HOec+6Q++T7ztG1iI93QTYhIASEgBAQAkJACAgBISAEhIAQEAJCQAgIASEgBC4qAZ2IuovKXy4uBISAEBACQkAICAEhIASEgBAQAkJACAgBISAEFAERdTIQhIAQEAJCQAgIASEgBISAEBACQkAICAEhIASEwCVAoF5R53JVZsXqdDro9fpaq8tjtBeP83bT85xzOM/b68jxvw0CTqdTNUTL1/Z+xP02OEgrhIAQEAJCQAgIASEgBISAEBACQkAICIHfHoGzRJ0m5yjmLGYzLL6+8DEaYTAaUZsUcTgcsNvtqKioQElpKTSRUlPauUs/k8kEP5br4wMjyxVR99sbWReoRdp4Ky8vR2lZmRpvDY2fM5MwulzqWPVzlYSuWc0zY1zG5AXqQSlWCAgBISAEhIAQEAJCQAgIASEgBISAEKiLQK2izqDXIygoCH5+fjAYDB7RozChOCkqKoLNZjtLnlDUUZL4+/sjMCBABJ1HVOWg2ghwLDldrsrxVlioRHFdsq7mSikNReBpQplRng0dK70jBISAEBACQkAICAEhIASEgBAQAkJACAiBxiRQa+prcHCwkmkNRSrVrAglR1l5OXJzc1U6rPvGnynpQkNC6kyjbcyGSVm/fQJqvJWVITcvr87IOm/Fm/u49Xb8//aJSwuFgBAQAkJACAgBISAEhIAQEAJCQAgIgQtJoJqoo6Tw9fVFWGiox5F0tcm6gsJCFBQUnBFyVHZMnw0PCwPTXms7h17P4XSptESDHlBz1wFgqiPTcClNRJxcyKHw6y07Pz8fhUVFtUZxslVejxvOu1h5okTV/XqHhdRcCAgBISAEhIAQEAJCQAgIASEgBITAr47AWRF1ISEhKprufLbyigpkZWYq2aHmBHO5EODvD5Zd26IUTGM0my3o0jwQIb467DxVgeycfPhaLGjdpiVOnUxRKbW1nUuRx/KZosuv/Lm2ee+0dFzu0zYey/e1KCotPZd1plDkV6ZV8rq1XZvHcz/n2mPqL19a+fzearWqsjUGmjRiXWsTlufD/Pd6LtkyBTYnJ6daVJ02D11dkk6bV5Fiuta+rQIq6a+/15El7RYCQkAICAEhIASEgBAQAkJACAiBXyMBNTVbaelZVbdYLModeR3M4wEEuiV6Bl5DK58+iOs50Bl5Oq2c8kYt4uPP5KiysMiICJjN5rOq4b4YhLZTk1A1DyaUjIwMWCm5qkRdaGioknW1AbHaHBjTvyWmtEpCkCsV35UNxkcbChET74vmXYJxeE0+kpJPwmisPl8eQURFRSnplZqaisDAQISHhyMtLU0JOG6ayGvZsqUCdPr06TPijfPwNW/e/Ixcc2/H8ePHUVJSgqZNm6oOzs7OVru1FXBZbkBAACIiIpCUlKTm9KOIPHLkiJrbj+nDLJudock+TdgxNfjUqVNnyvOgz383h6j555zOs+QrOda18rDNblf94z43Yn2rwvK4yMhIREVGIik5GVyYoi4Rq/X576YDpKFCQAgIASEgBISAEBACQkAICAEhIAR+pQToX+hwrhs9Gg6n84x34fs7du5U02c1tqija4qPj1fO6/CRI9Wu2aljR6Slp4OZgO6BY/XhrSbqKCtioqPPMn1apBoFCk2gFmnG9/lzzY37Keo4Xx3L5HEUI4yQq7kRVlxsLB6f2AU9c2fD4CrAdsdV+Dw/GiesO+BECUJO98Lhw0eriTpNHI4bN06JxXnz5qFLly5ISEjAokWL1Dx5vDYlHvdPnjxZCbxvvvlGiSBKuF69emHEiBFITk5GWFgYmjVrhsOHD6uOW716terc22+/Xck+vrS2shP27Nmj5Ny1116rpBvLjI6ORmZmppJGiYmJqvy4uDhVHjeef/LkSSXu5s+fL6KuxmBgn/LFPuT4OXDggLLRgwYNAsWpJllrjiGX04msnBwl3M6Y66qDaouIK8jPV/1+/Q034LXXXlN9Uts4rk1O/0o/q6TaQkAICAEhIASEgBAQAkJACAgBISAEftME6GXoBvr36aOe9Tdu3HjGSbVt2xYvv/IK9u3b57Ew8xQWJdw1V1+NCRMmYO7cudj600+osFoxfNgwjBs7Fq+8+qoKLvM0s7JBUafJissuu0w1ZsuWLSpyqXPnzoiJicG6devOEk6UJRRWTEnURB0j3yw1IvUov4IDAzD45qkIat0VvfLXA8e24ljFYKRHnsbiA2+jU3QnmFLisXvbQej1lfPUaUJnwIAB6Nu3r4qq+/TTT5V8u/zyy5Woy8rKUkaToo1ps61bt1b709PTVRTcm2++qb5SCjH9kRFbbBfF0Pbt27Fw4UIMHjwY/fv3x4YNG5QEZHmUdNu2bUNxcbEqk0wYOcfrsfwOHTooJps3b0arVq3Qu3dvJebat2+vOoWyiQJQRN3ZQ543FVlxcJPtggULlOzs1q2bErEnTpw4M1+h+9lMnaYcdRd1td1QWqpyYUGBEqzjrr9e3TDJSUlqDGhzIXp6M8pxQkAICAEhIASEgBAQAkJACAgBISAEhEB1AirYy24Hn9VrbnQ6tU1Xdr4MeU2ul/D3v/0NvS+7TDmbvPx8MLCnSZMm+Omnn7Bu/Xrs2rWr0UWddu2bJk1C3z598MbMmcoT0W3QT9Gj1Za5WlebPRJ1FCiMahozZgxWrVqlFoq48cYbsWnTJixevPgsyJ6IOjZE73Ki6+VXQTdkOpJcwYi158Jv6fcwlwcAXTcgz3oErQP74PTJDOzYvB86VC4qwU2dr9crGUY5xwg6ptcyxZXRbpRllG7Dhg3D2rVrFSDOY8b3hw4dqurNVNUrr7xSRfsx2o5ykTKOEXKURPfdd5+SawcPHlTXiY2NVTKPUXcsh6KQaa4UfoROWcTIPB6/fv163HDDDWjTpo26bl5enqoPBwUlFK9Pro0dcnm+g/tin095S+Zjx44F5TBvrvfff19F2NW1oIgnok4bL+xvbhSqlK9r1qxRC1Gkp6Wp8cz+lD652KNAri8EhIAQEAJCQAgIASEgBISAEBACv0YCWmBVRHi4mp6s5kankp6RATsXDq3yO43RTvoVTov1zNNPq+f7zz7/XD3fFxcV4f0PPsDWrVvx3erV2LV7d6OLOtZfW6fgyiuuUC7IPyAAb7/zDnZs366uV9dUXrW1vUFRp0kxwmZ0GWUdpRQjxpYuXaoWTKgZieSJqGMjggJ9kTBmONJjhyLfLw7+p04gdsshlDc7jizTZjiSY5CemAed0YmiohLAxYi6ymbwfEb0jRw5Ugk0Che+xwi2L7/8UqWzUq5R1DHazd/fX6WgMnKOYo1Wk+dTtlHUUQgx8o7ReUy5XLZsGW6++Wa1j/KIqZe8DqPhmOLKtjN0kpaU8+JR7vH9lJQUFVlHkdepUyd0795diTtKIZbFevHY77//XlayrWVEsg/Je9KkSRg4cKASnO+9956KRNTSrmue5qmoMxoMuOuuuxAaFqbmF2SaN606U7TZv0yLFlHXGB+RUoYQEAJCQAgIASEgBISAEBACQkAI/B4J0B1Rxt1y883o07cvak5HxSCcd959VwWAeTpnmyccVYbe/5+27G9PPYXE48fx5ltvqeCsjPR05Ys4Px2nOLsQEXWaN2MG5hVXXIFp06aB/uG1119XGZnaYqWetIPHeCTqtIsSNuUJZRZlWF2roXom6lwICvfFkGt7IzPFAeiaYkCFHkdD9uBw8BGYj7fE4Z0nYbNXqLa4Rzlp6bhDhgxBnz59lIgjeHYyI/+++OILFYHFdNPbbrtNyTOmsjKt8pZbblFhjzNmzFDyjG1hOxiNRxFHYbdy5UolIgmYL8q5/fv3qznsuJ/zzrH9FHtMoaTw44ISjJjjeTyGdaKku/7665Vk4jEUenz/0KFDSgTWbJennfZbPc499ZXslixZgh49eijh+tFHHzVK6mtqWhrsVituGD8et06ejOf/9S/s3rNH9T/TX923+hak+K32gbRLCAgBISAEhIAQEAJCQAgIASEgBITA+RCgs8nOyqp15VVKq4ioKPgYjedzibPO1UTdU08+qUTdzJkzVVRbXm6uCsbKLyjAX598EkcOH25UQaj5ssLCQtBRMf31xZdeQs/u3TF8+HC8yum2Tp2C2WTyOHvPY1GnXVyTZPy5rtA9tZhEZqaKYKtrjjqn04WAEAsGjeiGvOw86AvsCI/VwexjhO5YKFYc3IMSaykMen2dncfrsOEUdJRznK+uX79+SqIxlVWLqOM+prVyY2oswxA5Rxyj79geCjoKNqZaMhqOQo+yjnOjUfzRijLdlYKP+yndmBrL96ZPn67O4/W4MWqO8+VxPjVGhTGSjyGWjAajGOT3FHxcwEBSX6t3LXlw49yATGWm6ebquYx6JGsK19rSXz2JqNOupHLHCwpw9fDhuOmmm/Dqa6+paLpaVzquOqm2BSka9RNFChMCQkAICAEhIASEgBAQAkJACAgBIfAbIuDujmo260JMN0WfwHnrn33mGeUNlq1YgcCAAJUG+9xzz+GZZ55BYlKSmjuvsa9PT9S5Uye1RgKni1u7bp3ySGNGj0af3r1VdB8DumpbxLK2Lq8m6ljZqMjIeleicIddV+MIiKLOZrVCV7Xqa83FJFiO0WBEs9YxaNIuBA6XHX5perRMDcPmjOPY40ytXDzirEDJn5vBSDcaS4ozLRWWc8RxwQiKsGPHjqFnz54qpVFbgpfpuxR6FG3cR0HDiDemsNLscj67rl27qnMZIUcJR1nEtvJnSjwe99Zbb6nzKP2Y4sprsk1NmzZVHaNF0fFYzodGYceIOh7HunD1EX7PVFzZqhNg6iv7kwKWX/kip7rEsDeijlfiDcMxExUdjZPJyUq+1la2RNTJyBQCQkAICAEhIASEgBAQAkJACAgBIXDpE6CPoajr2KGD8jsOrglQVe3iqunJONVVY6bbalRKS0rQrn17GH18qkXs0T106NhRrVuQn5fn8bWriTpehKLL38/vvHrBarOpCDYtYozAalv1le/rdHr4mHwqhZy1UsrYdXZOR1evpGMFeT6NJCWONn8ZJQ9/ZjkUYuwEzqOnCUamN1K6cZ9mM7mfc5ZRwrFjeX5l3SpXI9EkkfYev1IS8hoUcexsbjyeZbBsfmVdKOgo+HiOJpy083lMY5vc8+q4S+Rkra/cFw7R+NZWxTpFHVeYqWNySvaNjQtXeDmp4yWCSKohBISAEBACQkAICAEhIASEgBAQAkJACLgRoEug36Frcd/odBikdaH8i+Z7tMAuXkctqgGoADa6p3NeTIINoVgKCQqC/hwjvViZouJi5OfnV1uhNToqqs7laKuFRHog6NyBa+fWFlapdYK78KkpgbSytPfd4dVXtnacgl9jyWH39EwtnbPm3VPXCqZyl3lPQOW/Z2erRSGqzWVYaXO9vhnrGiPe10zOEAJCQAgIASEgBISAEBACQkAICAEhIASEgOcEzoqoo+hgqmeAv/85CY7yigo1vxgjljSLSHsZGRFRb0qt51WWI4VAdQIUa7l5ebVOVKmkm66+BOqzy9LeuVC2XfpPCAgBISAEhIAQEAJCQAgIASEgBISAEBACtRE4S9SpueOMRgQFBamUTi7mUN8kgCxUE3JlpaUoLCpCBeemq0o5ZEQZ003Dw8JkPjYZgxeEgBbFyUUiam5n5pmrCjutT765j3ORdBekq6RQISAEhIAQEAJCQAgIASEgBISAEBACQqAeArWKOk28MQ3W12JRkXB1rU7BHFzmAPNFSeeeNqilhYYEB6soPdmEwIUiwEkas3Ny1DyAZ9u6Sl2n/l+bs849XZnvVf2sJpusY167C1V3KVcICAEhIASEgBAQAkJACAgBISAEhIAQEAJKSbSIj9eCjs4ioqQHF1QwGNTrLIHhcqmVNCjrtIUWai4AwAn7IiIiVGSebELgQhHg+CsoLERRYaEScnVFxJ0Z7LWIOomiu1C9I+UKASEgBISAEBACQkAICAEhIASEgBAQAp4QqFfUsYCG0l61i9SUHDyPUXiMpmPqq2xC4EIToDCmrCspLT2nRSQudP2kfCEgBISAEBACQkAICAEhIASEgBAQAkJACNRHoEFR5w0+9xVQLRYLgoOCLugSuN7UTY79fRBghCej6rjyMCNCZXXd30e/SyuFgBAQAkJACAgBISAEhIAQEAJCQAj8FggoUaelrWpfz7VhXN2VKbJmiwWBAQHQS7rruaKU886DAMdxeXk5SsvKYK2oUMLO6Z7qeh5ly6lCQAgIASEgBISAEBACQkAICAEhIASEgBBoLAI1ndyZiDouGMFVXinaKNi8nq9LpwMn4ue5FHayCYGLTUAJOk3Siai72N0h1xcCQkAICAEhIASEgBAQAkJACAgBISAEqghQ0NFZcBovFWhktao9StRxdVdGwBmNxso3ZdVLGThCQAgIASEgBISAEBACQkAICAEhIASEgBAQAkLgghHQ1oWw2e0oLi5GcUkJdG3btXOFh4WdkXQX7OpSsBAQAkJACAgBISAEhIAQEAJCQAgIASEgBISAEBACZxFgZF12Tg50PXr2dAX4+wuiRiagWVH3BTYa+RJSnBAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6ZQM0FGH/LGZaap6kN1qXSbkbV6fr16+fy8fE5506VE6sTYMfTgtpsNvWV+cb1DQbhJwSEgBAQAkJACAgBISAEhIAQEAJCQAgIgYtBQBN1XGuAboiv3+rCoA2JuvNdYLUx+s9qs0GXkJDgulTMYWM06mKVwQ6lnCsrK4PD4VCCjptIuovVI3JdISAEhIAQEAJCQAgIASEgBISAEBACQqAhApoT4leuXWA2m8EFR3+rwq4uHpeCqFN1GDRokKuhTpP9DROoqKhQE/9pgo5ncJDXJeq8kaNaGd6c03CN5QghIASEgBAQAkJACAgBISAEhIAQEAJC4NdA4JfyApqs8vX1BV81U2N/DaxYR3cX461L+aVY18VSRF0jjDJKupKSEhVJpwk6mmeaaL74PTua+xl1px3nyaXPZ3B5Ur4cIwSEgBAQAkJACAgBISAEhIAQEAJCQAhc2gR+STegyTo/Pz9YLJZGiaz7JevvLuqqSzoXwFA1nY4qT/sf+FPle9W3ixVhJ6LuPO5FLd21qKjoTCQd87oZIspQUX7vbp95PCPuKOso9/i1oe2XHswN1Uf2CwEhIASEgBAQAkJACAgBISAEhIAQEAK/LIHzdQPeRonxeAYd+fv7K7/hbVSaOx33KD26EAYvnWt5nrSjVlYuF/if0xSA0tJ8WB12BEQ2gcFRBGdZOQx2QK+vdDjaJqLulx3jjXI1Di5KOk24cRAHBAQoUad1LsUcX/yZ+7X3udBEaWmpEnZ1DVBPBmCjNEQKEQJCQAgIASEgBISAEBACQkAICAEhIAQueQK/lDzSfAQ9RnBwsMoW9Gbj+VarVTkPupP+/ftj8ODBOHDgAFavXq08Cheu8CZiT5OHDIqiU6lrO8ulUNLp9dDHtEOZfxiOblsKg8mA/qPvQlhQBQqzi1Fw+BgcmWkAHIBOf16yju0tLy9XgtNbbryw1xF1WlQYvxKOKqSWEEFvOrCmaeXP2uBrrLLdo9kIjbBYf0o0Djwt+s3TerM8bV46jQHztxkayn3afg68Jk2aqNTYjIyMM4OQ7aop+mqGZFbOd1cp97xGrKI4K+uhynW5qkI5vSurPmuvtVOrd93WupLqmfYpk/3ze/XN5VcZllp1bpUBV2+455yTj3rDCVfVPh5T2ezqUzC6M3avd211r/4e+4E8q4/NSgbsJ9agOtvGHsOejk05TggIASEgBISAEBACQkAICAEhIAR+mwS8Dejh8ZRaCQkJyMnJwZEjR6oFETVEiefTdTCyzlM/o9WxTZs2aNWqlTqvR48eaNq0KXJzc7F9+3Yl8fj97t27ldTyZOEKOpLAwECEhoYiNTW11si8s0Qmn+F1TlhatYN/28uxe9tinD64CiHR0eh65Uj0v2wIAgPb4NCxnUjZ+hPKDu+D3sVn+0pZV58TqclO805BQUGqvceOHUNaWprX8/x5Jeq0CrZs2RLNmzfH1q1bVVSYJ0Ab6nxtP+VVeHi4ikrLzs4+r5BIrUxNxrVv3x6dOnVSsoyrs548eVJ1cmFhIdavX6+i4TzdWE/KNw4ubqwvzycL7qNxHjp0KKKiolTUHffztWPHDuzcuVMdw2N5vpY6+/Ogd8FudSA8tgUCfAqRnpEPu5MhmJ7Wjs7KCaOvP2KjI5CXmQZLeBx0eZnIKi6DTu9NQS7o1Bx7zirXV3Wu0w6rTwhaRAehNC8VOTYzmjRphhCzDmVFGThxMhcuoxHBMU0RF+QLW2kBUk+mocLHguiYWIQE+qIsPx0pGXlwungDuOAfGgk/lCMtowgRsVHQOx3wMRmQnZUJe+X0f/APj4Sf3oHiQidimkfCbNSjPC8LKTnFCI2ORZi/GXA6UJyfiuSULDRp0wXBfmboDU4Up6YiNbMAQXFxMDuLcDq7FD56wGk0IzKmCSICfFCWm4XTGdkod1jQpGUThPr5oKQgC6fSciplnI8voqIjYC9IQ1ahHTAYENe8NUItQElBLlIycitZ6U0Ii4iArigHuWVWxdAL6p53tBwpBISAEBACQkAICAEhIASEgBAQAkLAjYDmbjRJRwfyj3/8A4cPH8asWbPUke7TdNUn4LQoNm+i6ug7KPbuu+8+JaoKCgpUkJSWbahNGdahQwd89tlnOHjwoIo+a2jj+SEhIYiIiEBSUpISkDV9VDVRVxVoYw9xoUuPMTiWnogfNv0PviYfhMYEIyQuDJf3G4t+5uHITjuIlPxsJQAzko/C4axMz/VW1DFSsE+fPpgyZQq++eYbFT2otbuh9mn7vRJ1vGB8fLwSUKz8mjVrVLhiY4o6NoADoFmzZsjPz0dKSorX9tG98VrU16BBg9C5c2ccOnRIWVtGvlHasT0//vgjFi1apDrck00b7O5z03EQcvBz4wAbPXq0qvcPP/ygfmb0HQVnv3798P333ytrzKg+lkVRSI4/3xwO5Jwqwk2PvIjuMd/j7Q++Q2G+HiUVVjh1Rvj7+cLHaIDLYUNJaSlsDh18/fxgggMlZWVw6AwwGY1o2qk77r3jJqz85D20vOFe+Hz+P7y9aQ8sgYHwNZugczlQUVaMUpsLRh8z/P0sSiZVlJWiwuaA0WSErdyGCZMnYfN33yIjrxRGgw4mkw8qCjMQe8WdeOD6nlj/6cv4Kb8Nrr6qD/RlVkRF6fDTFzOxxjAMd428DMbyYoRHRmHHwk9x0hWJEWMHIf1UIeKiXNjw/ULsPFoGA0wYPmEiLOlb8dYnibj17vEoc5ShTbQTn876HKV6C/TGcFwzaQLCnceQWdgELUKKkWU3w6f4NNYcSMawcbegeX4ykq2+iPbLxcrP3kK/299GtD0Jp8t90NLfgLXzFyBoyBhEl2zHS58dQFwAEN7pckwc0Ru2rNMw+QVjy8cfILXVMNw4ojOys0oRFVSKb1bMw66TsRgyfBCGX9kW6+a9goVbitFs4BW4b8RA5B1Pgl9EID59dz4yfXToc+UI9L+sHY4u+BDLjmXCZPYRUefJzSXHCAEhIASEgBAQAkJACAgBISAEhMB5EdAy+DTJRIczbNgwJcwWLlyI48ePKxfhPj1XQxdkYJLmPBo6lgKNUW+PPvoo5s2bpzwM/Yf7FGEsa/r06fj666+VH6FTaWjTfBFFHQOveJ2akrGaqHO6YLD4Iic+B5H+8Thx8gDSUnOBChvi2gXhph6jMTj0KnTW94N/pgkOHweOB6VhxtevICknEQa9oXLxiaqtoYhCLaIuLCzsTEQdnRa3hs51b7vHoo6iieF7EyZMUJJu8eLFqlO1FU0ZCnkuubesDBtD4+pufRlVR7GVnp6urudtaqpWLjuSMm78+PFYtWrVmWi2G2+8EQzDpMH96quvMH/+fDWQPNlYT0bCFRcXn0ktJRu2n8KtZ8+eGDBggDLV5Na3b18lHHkz8OZo27atup6WU82oRL7cRV3WiQLc9tf/omfM13j5+fnIjEzAFR3jYbbnYNX6fQg0OWHT+6Jj916IDbTh5PGjOFXui64d2yC4rAC7Du+FLboT/nb/VCyb/QZaTXoEYTvWY9epkziVdBj7TxYDLiuadk9AlxgLctISsf1ACgKcJYjoNADxMYHIPXEKrrCmeOiRqdi2agHWbNiJcqcP8jJTcVLfHk88div6NLVj6ex3sOWwE766Yhw4VoQJf3gYPfWLsNo1Hn2MR/HOB1sw8v6H0NFxGMklEWhh2o3n3liJsQ8/healu/HxF18DwQNwxw19sWfdOpRFNkdCnx5w6srQRJ+Db1ZvwMEDR+Fo1hN3TBqFE5s2Ij6hL75441VsO21Fq+bh0Ec1waTx41C0egHm7cnF1LtuQ8neuQju8yDytnyE2Usy8ejLz8Pn0HxkB/RCRNlPeG7eXjQJ9sMVE25DL+MePP7atxh+y58wyHwEOfEJCDuxEv9dlYg77p8KS/I6LNzsj5vGNUPb9q2xds6/MG+jHrfdPx1di77Co7OOY+L9j6H1pjex0ucyDL+iL4KjgpE293/4/GgGLCLqPLm15BghIASEgBAQAkJACAgBISAEhIAQOA8CdCD0KZwTjo6DUospp9999x2io6OVj6CfyMvLQ3JysnIk9c2dr1VFS3/1pGr0OwyOoqjjtZYuXaokobuoY3nTpk3Dhg0bsGXLFiUBG5JZXok6LubpsKNVl4Gwd3QhtfQHnEo9htyT/gg0Ay27uzAmZhimH/8HTKGxcFS4YNAB+ZY8vLT5BWzO2AaDrnJxCW/SjbXALk0Y0mV5G9zmkagj5JgM0qDkAAAgAElEQVSYGCW7CJMpr3xP23hhGlLOwXYuso4NiIyMVBMJao1hB3BQ8X3mUGdmZnodLqjZTEbTMXruvffeU1Vm3YcMGaJSVbW6c0JDT+0wy+VAZkQdN5bBKEB+ZUotJSDrv2LFCvW1devWKoqP+eA89+GHH1YWmwKSHcZ8bKbR/rw5kJ1UgNv+PAM9olfiv9/l4q4/PI6IxK0osrSCNXcrnnn5S4x65M+4IqIMRYWhKMvfiO25fhgS3xTFnS9Di4NL8c7iXbjzwWlYMfsNtL39GfQ1pmJPii8GdfHByy8+hYw2k/DUqHic2JON8GYt8P0n/8LygH54c8Jw5J1KRFFOAU5kWDHujjE4suEr7M8xo3sTH7w0YwF6Xz0R3YNKgchAHNm4FGu2MT3VCV1Me9x84ygUL5oF0+ip0J/6Cp8s2oR2ox7CDQPDkWK3wL5yIeZu2oJ2ox7DDbHF+OCV/yHq1oeQEJOGBT/mYsp116BTyyiUldjgLMnDgd0bsWrJBkRfOQHXdS/CB+9vQMcbp6C3XybWfLcVB4+dRGmzDrhz8njYN32FVYku3Hz95di//GU0u/5FlO7+HIu3mfHIY5ORuHwmKloNRWzZVjw3bzeahzbHxDvGQ3/4OcxcFYB+A/pg9LUJKA8IR8rnczB302kMv/sejLWfwAuvfYjizj3x2ENTcWDpi1iwuTke+eN4lCx7EO8caIUhQ27CiG6r8fRbKUBwIK696x5ErJyHz46IqPPkw1yOEQJCQAgIASEgBISAEBACQkAICIHzI0DnwKw+Og9m+p06dQrbtm1TmYTMIqTA43x13D755BMVzdZQaqY2T50304UxMIlTgdEj0SFRCGrCitejW7r11ltVNiUDwVjHhnySN6JOBYRZK9Bj5I3QdU1HUt5aOPLbITdrC4xBKTBHONCmPAQ3vjAFrYK6I6BrV8BsxOlDP2Ch7w78oDvOFQPUf56KOi0IjQ5oxIgRqt2c/oxbQxLSvdc9EnUEzAtRQLFwirPKhQ4qN8KkAU1MTPQor7jmsGNj2DlaTrKWrsrQR5pglnv69Gmv56tzF3WMnPvggw/UpTk4GMHGNvTu3VtFxjHazZOcaJ7fkKi76aabVF2XLVumrsHcZHbO3r17lcx74IEH8MUXX6g21S/q/ouu4T/iqKsDrm1yENOmfYyCbsPwr7/eidxZP6HlhDjMfOktHEjRIy7SiaDmnRDvb0Jxx0l4tEsSFny+AgkTp2HlnJloc/OfELxqBp6esx8zl3yI1P0/Iii+C3JWPoFnPq9AwtQ/4rHOhXh2N/BA3+bYv+ZbJKXuwcYdWfj3uzPw6Vv/wdEcI2ICfBDWug+GXxaExa9vxtBHRiN9+6dYvjYZsR17oNugyxGdswcff3QUN//tNiB5GeYv2owOYx7C6F4WpCEYzm8WY86mzegw6jGMjMzDm7M2Y/xjd6Jo6xwcKo7GlQkj0LqlGRXlNpTmnMa2Dcux5pgNYyfdDMeez/HlxjSYwqPQq//l6NumIwpTv8OCgzmYfOOdaFmYghMFFShM3onFC5bjrjfmIdZxCmn5pcg/vBer127DoCnTEFO8pUrUNcPEOybAcPg5vLEqUEVCDh/aFfbQpkhdNA9zN5/CNdPuxjDbMbw0Yw7sXXrh0Qdvx74lL+KTTc3w6B8noHTFg3j7YGtcNXQShrX4Fs99nAJnaBhGTrsLESso6tIlou78/q2Rs4WAEBACQkAICAEhIASEgBAQAkLAQwL0EQwiYnYf017Xrl2rpuVigNHIkSPB+fvnzJmjgofoQRqK+KIDYWAT5/j3ZNOEFWXc5MmTlQykE6kZUUdXQtfEiDuKRAZv1bd5K+pgcyFgsAXonYhA52UI0LVHavFslDkyYPZ1ISREh9iDLdB0XQv4OVui3OEL+CbigKEch7PKK5eM9CKiToum69KlC8aOHavatHHjxp8X+fQEnqervmr2kJ1JK8voM4ZNaqGJWv5zQxa2rjrVzI1mOTS1XB2EkWbaJIE83xsLqYk6SrpRo0YpW3zixAklFikfuSDGddddp0ItOXC8iajTUl+1hSqY+spBxUg7LjncrVu3MxF8HJi0x7SpNNc02LwpeONwYxv5vXvqa2VEHUXdWqQaOmNQ8E5cOWUuDF2uwkv/uA+W5XsRe00Q/vPvGTh6PBPOVn1x6+03o23eSaToeuOa3klYuGQFBo6sFHWtJj0Mn0/fxYtLVuPVzxcjN+kAYuJbYPf8aXj9SxN6TXgYTw33w2uPvYSSkeMxftAAtPI5gvnvvocJT76BOa+9gH2J2TCY/HH9PX/CoOZ2HD5Qhi59WyHj0FrM+/YIRo0agqSta/Ht+u3IyDdi2hOPIzT3B7z10S5ce++f0DMkGWm6SATvWo1/frkOY+/7O9rb9mHR3hjcPzEIi9+biX05Qbhi2pPobdqHogo/HFizCJtSyhHa7grcPjASSz+eh2T4Q19ehLzCCvi1uA7PPNwJC9ZvQr++10C/cRnm/rgPFpMR6ccT8fgbHyL3p8+wdM0RmHwAK/QYddOtCM9bh2ff2YbIqHDceNc9aJb/Kf7yzgkMHfcArmqbB0ebXihd/ilmbj2NaQ9MR3jaVrz2/ipEduiCBx+8DfuXvIj5GyNw3+NTELDjITy1KgY3TH8YvY58ird2ZMIeEoYRU++sEnUSUefh55EcJgSEgBAQAkJACAgBISAEhIAQEAKNQEALMOKCDgwSolehs+BCB1zg4aOPPlKZk546Fm9TX+lXbr/9duVeli9frjIw3SPquH/q1Klqrjmuf1DdidQOwBtRx7nlHE4n4loFIb5fFLZYNwKWQhgDbGpVV6PJBovFjvIiB6y5BlgP+wGHYtAqwYSMVBtKj4So9SS5qKc3EXU8ls6J0YsMCqMj8tZleRRRpyGinNKkF8MSKbjcVwpphLGkALDD2rVrpwQWl7M9n2uwI1kmbSbF3LfffqvSUDm5H+eL4/eff/55tQjBhtqhWVKmvtJUs37ui0kwF/u2225TK6qsXLlShXuyg/iVoZ0chJs3bz4T1snFJMi2+hx1hZj61Ez0jFyJZ3cb8fIdt+H0Vx/htDkBvVql49FXvsM9Tz2GmMQfcSgpFL5dXAgO6wDrmuU43Hci7m1yHHM/+xKDrrsbKz5+A21uegQ+n72Df3/xLV5f9CWSti3H4cCeeLhzAb746jjaDhiCjB0f40DM5UjQ5+B0QRP06VaMT2e8issfex/ZWxbihL4Dhrc34b9vzkK50winIw533jsKJzYvR1bzsZjSIhdfLN+CEj8LynNO4qSxB24f2QYnE0+iZc/eOLL4U6TYwzBiTB9sWHsEPXo3xe51K+HqNxEtT32D/y7YjvDwICTcdAsCT3wLl7k1DmzYgBMlpbj8lrvRtGA7Pl68Gb7dr8b4hDBkHE6D3n8A+nU5jg837sc1Q26Cfe0iLNh0FCazATmJJ/DYmx8ge+sCfLX2CPQGA1w6Ha656U509MvEqs0nYXIUwRbZGdcNiMfR7VsR2rkf9r/zX6T3moBJCXHYvicd3Tr6YdO3H+DrbU6EN2mJhx6eqkTd7HUliL/2ejw5pC22r96KuH7dsOB/s5FRXIjywBCMmDYdEcvnYMEhiahr6J6S/UJACAgBISAEhIAQEAJCQAgIASHQMAFPpRFdCDP6HnroIRUJR9FGaUaJtG/fPsyYMUPNX+epqDuXxSR47dmzZ6usTPe0Vs373HPPPWpl1D179jTaYhIaQRdcsDvtaOrfFP8Y+g+8n/8ylmMFjH4G+Po7oNfb4XKUoCLHjqIMoOygAYHhJjQPDYUtPRKuUi4WSlPnnajj9U0mE5o0aYKsrCzlgi6oqNNSUrlYQosWLdQys5RV7PzG2jhwaHUpvjjpYG2reHh7LW0ZYIZ8coEKWmRGwDGlluGf2dnZDYZ61rwmBR2Bc/EIbgwXZZ1piFlnXueaa65RKbacNJH7aVQ5QBn6qC0jzPMp6qpHI7pQUWpHu+4JiPBLxuYNuxB2+Y24Kj4KhooCLF68DCXlpdC364fRfToj2GDFiYM/INd1Gbp3DoeuvBzZBclIOnECMfE9kHxoN4Lb9YDh+AHsTE7FoGFXo/j0Hmw+XYGhQ0egXaAeeZnH8eWqTTBediXGtGsKs7MYx/Yswur9FnQZNAx944zISE2FTm/Ajh27UGF3wmoNQu/+bZF3OhEVQW3Ru11UZQa3XofSrCRsWLMVfv2HYWCzEBSmH8fW9ftgDQpHl149EB8djNOH1iMZ8Zg6NgE/zp2JNWlGBPnoYC0uhMPHX61KazQAuqhuuHV8Ao58/Tk2nsiFwTcK3Xp1R9MQC+Aow8Fd63AgLwC9uraGPeUYjmYUQq/XwVpWiu4Dr0BZxhGcOJ1f9QGkQ9O2ndE+Pg5Ggx7Oslys238MsS06o2OkL1L37Mauo0koKfDHZWMT0DLMhLTj67Fxbxn8LTroLUHo3r0jchN34GiaFbBb0fWq0WgZpMPJYwew71gK9Do97D4WxHfsAHPSYRzJK4XByOx22YSAEBACQkAICAEhIASEgBAQAkJACJw7AU9FneZW7rzzThVRRyHGgKWrr75aPRu/8soryl944nN4nDYvvyc157XpXBjNt3//fhUg5S4E2QbKLEb3LVmyRGVtepLh6B5Rx4UwtMAp9zpp6x7wPafLiVJnOSbFjsGpyONYG7QBeh8zjL46VJTkozAzHyUpVlRkupTLiGjvgxi/GPgkxkJnp4zwXNLxelpQF50Zg7S4ou33339/YVJfazaaHcmoMUa8nWu6a12dq4UJcn9jSDrtOlqKKgcmpRl/zs/PPxNe6alF1spjPRmaSRHHjQOXTDi4tHxsbeVa2msOIE7iyJdWFx5H0VnXCis2axnsDiPMFiOc5YUoKue8gEb4B/jBx6iH01qB0tIy2AH4+gcpaVVWXikO9QYL/P1NKlJPtddaDpfRDB+jQQksGEwwGXUoKygEAzENRhP8/X2hc1hRWFwGl84IXz9/mH10qCgrQZldB18zF/tA5XxrKk/bWdlHeiP0TiuKSq3QG/SASwcfsxlmHz3s1gqUWZ3qJjSbjBy6sJWXo8Jmhd4chPhuvdC7qQ/WrNqIUqMRerf8bzXQHTYEtuiGy9r4Ys/W3cgtcUAHJyrKK2DjgiY6g2Ju1AN2mx06HyOMev2Z4WWzVgB6HyXltJBVh60cpRU2dS2dwQcWkw+ctqp6st5aPSvKYbU74WP2hcnI1V4qbzxrhRUGkwlGvXoD1ooilNn1sJgsMPlUrgoDlxM21sdgVNeWTQgIASEgBISAEBACQkAICAEhIASEwPkS8FTU0UEwYo6ZfQxSor+ht+Cincxg5PRfdBENiTot+o0RdZ56Ey2ab+DAgWqlWfc1DrT2sy4MfmIgE4ObGqqHEm9OpxKA9DoM7GpI1CmnABd0OhdKY4tRHlMGH39/+BjNKM0rQlpiIiqy7HBUOGCw6NE0qAnCHTEwWE1K0qnzKUE8nIZNm36N0XScEo2MmWnp6fkaG69SX7WTtIp6ezFPB+SFKl8rtyZoTwdbzfpzUDAajl9ZJgcWBw1DOrXow5rnaGm8HGCUfNo8dbXVoVo9XRxeP2/uExrWyZUDy1U5vrRza06E6M66+pGVpbqfe2bQUES5DVgepVPDv/pWKbaq17n6eSzECYdLpyLgKM5qbqp+rkoTrtNXRqWdXSeduvHUtSjf3AqpbB/3//xm9Taf3UqtL+oah+p9t+vUflxVfTy8oT29N+Q4ISAEhIAQEAJCQAgIASEgBISAEPj9EvBUHGnHaYFCGjHNVWjzxTXkQ3gcg4/oORo61v0a/L42Qed+DMvztB6aS6B34YvZie7RczWvXTOCz2VwwhpihTWuAqWudBTllaE4sxTOQsDksiDG3ARhxggYwACj6v7A03ZrddSEHdt2LlO5nZOo+/3eEme3nBFrjIpzjyxkCiyj2LTOrCnVKPYo6eqKpKtVVonwkWEnBISAEBACQkAICAEhIASEgBAQAkLgd0nAU0HXWHB4PS1zkPPbXSqbJxxqDaZhDA8XmDDYUOpTiDKUwWnVweLwhR/8YNKbK1eOOA9J11iMRNQ1AkktBVazxRzMnAePL37Pl2ZUKeko95gyys0TM+vJQGyEZkgRQkAICAEhIASEgBAQAkJACAgBISAEhMAlSOCX9ALatTjNlDYX/yWIpN4q1clLJe1Vpf6ptSLqnk2+toi9X4KDiLpGoMzOKy8vV1FyNefsqyniGntOv0aovhQhBISAEBACQkAICAEhIASEgBAQAkJACAiBM+mklHSMpNPSN3+taLyVbb+kEK2LqYi6Rhpt7ExGyXGCRm0l2Dqh1zIXWyNVQ4oRAkJACAgBISAEhIAQEAJCQAgIASEgBISAVwQ0QaUtHuo+nZdXBV1iB9c193xd1RRRd4l1YGNUhxFzTG3li2mu/PnsxQsa40pShhAQAkJACAgBISAEhIAQEAJCQAgIASEgBM6dgLbYAQUdp++ioPNkBdZzv+LFPbM+P+PJ1GS/RO0lou4CUNZWURFJdwHgSpFCQAgIASEgBISAEBACQkAICAEhIASEQKMSoJw7lxVKG7USv0BhIup+AchyCSEgBISAEBACQkAICAEhIASEgBAQAkJACAgBIfBbIKBLSEioWu7it9AcaYMQEAJCQAgIASEgBISAEBACQkAICAEhIASEgBD4dRLQJQwcLKLu19l3UmshIASEgBAQAkJACAgBISAEfnECLljtVsAlj1G1ovdk4TyXS82FpTfoAeh+8R6UCwoBISAELmUCutF3DpR/YS7lHpK6CQEhIASEgBAQAkJACAgBIXBJEODcRk7Y0K/VSBj15kuiTpdSJRxOJ+By1l8lF2AwGnH48GEkJSdBrzeIq7uUOlHqIgSEwEUnoJv6XlsRdRe9G6QCQkAICAEhIASEgBAQAkJACFzqBBxwwO7MwFtTjsPXJ/RSr+4vXj+HwwG73a4mpK9vMxqN+N///oePPvwQfv7+0ElU3S/eV3JBISAELl0CutvfjRFRd+n2j9RMCAgBISAEhIAQEAJCQAgIgUuEgNPlgs3pwNt37EWIb8wlUqtLoxqMNiwtLW1Q1PE4Pz8/vP322/joo4/gT1HnJvbqW5FRa2lDIvBciWjXvlDln2u95DwhIARqJ+DpPcvj3I+91O9x3boDS0XUyagXAkJACAgBISAEhIAQEAJCQAg0QIAPTi44MKDtCJiMvsLLjcC5iLpZs2YpaVdT1PFnvV5/5sFau4wnEo/Hag/ldR3Psms+qPNYvs+XJ1GB0vlCQAhcXALaPct7mdG8tck37TOA93VISAgMBgPy8vJgs9nU8d4IO+1zxdvzzoWSzuXpp925lC7nCAEhIASEgBAQAkJACAgBISAEhMBvnkBdoo4Pte6PnO4Rde6iju+bTCa0bt1aPUg3adIEOTk5SuTxIZyLTzBir6SkBGlpaeqBu66NZYWGhiIwMLDWQ1h+UVGR2qc9qDudTlgsFvj6+iI/P7/BB/iaETruZZ1vZ3saJeTJdRorksi9D72RG7XV0b1O3E+JcrG3yva5oNOxLlr0VU2RU/l+5TGeb972Z00h5O35ntes4SOJxQWyIYtLazpJ7TODnxG5ublnfSZwPz87Kioq0KFDBwwYMABmsxk7d+7Epk2b1Pf8XPFkPFf2uw5BQUEoLi6uUwzWJFpbX2pl1XddndPprBZR50klG+5OOUIICAEhIASEgBAQAkJACAgBISAEfi8EahN1FDBZWVnqYZgPuNzqE3Wcuy42NhaFhYUIDw9XXynveA73Wa1W9dBN0VaX3GE0XPPmzXH99dcjODj4rKg8Pu+uXLkS27ZtU2W4izpKOu2hv67nYk2aUACUl5erMlhHij62szE2ls2tpoz09lmddSUPMuNGEVmf4Gyo7ixLizp0P9abernLE55HdudTp7rq7G2dnA4r7OW5MPlHqwWdnfZi6I1My/5ZyrlcDjgd5TAY/bxbrZjnOa3QG36Owq1vfGn3SFlZmRq/2vjSIj29aVtDfVrXfkoipvqXuVzg6KEW99Pp4FOVps5ZKDnm+dI2LQrWPdKt9ig3lg3YlRL9eeM1jPqfZWBDcpj7KduYPp+dnV1tHGmCjIKuWbNmStwXFBQonq1atcKRI0fUZ9P+/fsbRMRz2M6ePXti7NixmDNnDo4dO6auV19f8Dy1urVer/7IwON5b7O+/MrPs7o+x3Tz589TbAL9/NC1ew80adpUfQjKJgSEgBAQAkJACAgBISAEhIAQEAJCwBMCNUUdH2xTU1Px008/qZSzHj16qIflukQdj+cDLB+iDxw4oB5iubnLibZt26oH3JMnT9Ypd5jS1qdPHyXrvv/+e3U8y6b4i46OVg/WfGA/ceJEtagYHkNRxxdFYH0ihcdeccUVYH0yMzNx9OhRdO7cGV9//bVKqaNYoRzTHtT5gM6ftfd5DIUg32eEIB/m+QzOchnpN3LkSCUeGPmjpQZTCtaV3ldb/2iypFevXmjXrp3iuGfPHsWW0lTrL9aB9WJ7KYZYD8oP8udLuz6/HzhwoIpy3LVrl5KgLJPneBMRxzZ269ZN8WKbKDy4AjDrwI1Cg3XQpKCWZkhGWl+yftyv1Y/v8zxtvkN+r0UteTJ2HbZyNGvXGwlj7sbyD/8Oa0UBBox6AHvWf47CvExYfANRXlqApm37oFnbntix9jNUlBXROkNvMMDpcEBvMMJht8LiHwSn04HyEkpmP7hcNsS26oGoZp3w0zfvweIfAVtFaZ3V0kQmxxfHydatW9G0aVPFa9++fUhOTm5QEHnS5vqO0SRdR39fXBkahOYWM4ocTqzLK8CWwhJwdWf2S2RkpKob+5915X3Je4yRrCkpKUhPTz+rH7Sy4wN80D3cBBW/qNLOdcgoc2BjRnnlvVclxyiX2dccN7Wlq3MscIxyXLoLXx4fERGB4cOHqwg43n979+5VY653797qHN4Hy5cvV9F49Y1hTdSxD4YMGYIvv/xStbW2FHp3rqwDP4d43/APAxzrbdq0Qf/+/VVEHz836nJvuubRka783ByYff0w9c478cif/ozYuNjz7Vs5XwgIASEgBISAEBACQkAICAEhIAR+JwRqijo+/DJqhQ/IfMDmwzsFDR+mKcO4mETN1Fc+lLdo0UI90PLhnOfwwZ8PxDyPcojyT5MVtaHVRB3PW7Vq1ZmoHz5gU1hRhPH6S5YsUSmu2gO6Juo8iahjW4cOHarE46FDh5SsGzZsGH744QfEx8cjICBAyQEKQbaHZTJ6h/Vn206fPg0KNEqGxMRExMTEKJlJ8USxed111ykBtnv3brRs2VKVxe9ZnqfRVCyLYqFTp06qXpp8ZIQROVBuJSUlqbpRaHA7fvy4qgfrw76j1Ojatas69tSpUyrakWnH7FMKVdZx8+bNXsk6cr7yyiuVnNmwYYPqZ44LRj2x/ykTWSfWhXxZH44DSiGtvqwfufH65E3ZQelBCcJ2//jjj6qOngpEJera90bvYVOQcnQPkg7+iO6Db8SBLcsRGt0SweFxKMg+jYDQKMR36IdTR3cgLWmfEnNh0c2Rdfo4zH5BcNrKEd9pgIoS2/XD52jRoT/8gsJgt5bB4GNBfmYSjCY/HN62slbxpI1nTTJRbrONFLZsGxlR+HC8cfN0LHj7EWR3uRDlY8QDzWIQbDQiwuSDTKtNRcHNScvCruISGHU6Jb/ZL1FRUSpVnX3G+473GPtszZo16nv3epKN1enCDa0DcV/PUBQW25FVZkebCDOO51nxwJoMMEbPYjKpdFWWv3379lrT0bWIutpEHccs7x3e92vXrlXjf/To0erep5zj5wSFOMcgRXFD0bCa7Kecp+xmtG9D40uT5exH3ou879kejlX2aX0yWTf7ww9cr7/4byQeT8SVQ4filZlvwuLrh0MHDiigMbGxyEhPUxXv3a8/SktKsG/PbqSmpcLFv0yEhaNrjx6IjonF6VOncOzIEdgddnTo1Bn+AQE4dGAfiotKEBEZiQ4dO6ob8cD+fTh18qSCExYSiu69eiEmLs7b8SPHCwEhIASEgBAQAkJACAgBISAEhMAlQKCmqNOin7SqadFl/Flb9dVd1PFBmCKrX79+6sGaUVF8wJ00aZJ6yKZ44fMjJQwji+qKROExffv2VbKJEW6sBx+or776alXO+vXrcccdd2D16tXIyMg4L1FHCUdpyAdvzn9FiUjpRElJqcIIHkbMse2UGYzCYdQXBR3Fi5b+xmMoORjhw3ZS9FHGUFSxHHIiH7bZUzlDfhQRvAZFHc8jB0rALVu2KGHBSB/uJ0/WkfMDxsXFYe7cuUqKTZ06VYkzSlL2BTdGLrVv314JMYoayhjKOi0irqGhyHZQ6mhRTTyXEZDfffedkjwUIaw75Qz7kO+RA6/LCC3KG44B1ontY71ZHs9hFNfHH3+s+Hkjshz2CjRv3xcBIdEIjWqBspJ8BARFwGG3Ia5VN5SXFiIgOBKHtq9CUEgsMlIOIyAkCkYfM8JjWyAnPQnWsjJExLXCwZ9WIDyuDfwCQuDj44u05H2oKCtF98E3ID1pH47tWYv8rFNVc74xgfTsTUtZZrsol9h/lEMcwxQ9Cxcu9CpisKE+qbm/wuXEDRGhGB8dgU0FRUirsMKk0+Pq8GBsLyjG26mZMHDuSadTicTx48crccW+5bjl2OE4o1TUIs/OfA5UibqJbYPwUM9QHMksw748K0a3DsTpIhumr06Hw+VCcFAQLr/8cnVPMDKWfV9TjNUn6lgX3mdMVaXo5v01ffp0df/NmzdPSWiOpU8//VTdA/VtWkQd6zN58mTMmDFD3TOepL7yXN4ro0aNUi/+gYCfS5TS9c5Rt+izBa6nH38c6fmFePX1V3Hd9Tfgw3ffwfP/fgGGkhJ07NkdyalpeOjhR3HlVUPw5kv/xopvVyPCbEFifhGcZePUFI8AACAASURBVGV45LFH8ewLL2D+x7PwxOOPI7e4BEuXLFad9qf/ewIZmVmY+fpr6Nm7N96d+QaWzpkHHf9iUFaGnOJi3D/9Tvz9+ReUzJNNCAgBISAEhIAQEAJCQAgIASEgBH5dBGqKurpqX1fqqybywsLCVPQZH24phzjXHIXasmXLlATQUgNrn/uq8qGYso/RX4yocxd1LJeSZ9q0aUoMnY+ou+qqq5T4YzmUcJQVrB+/Z4QOxQXTAinvKLEonCgw+B6jxCgRGLXGc7p3766kBtPktPRgbf6sa665RskZygpG5DQUxaNxp4igWKDsWrFixZk0XEYCzp8/X0UbUXRRYmzcuFEJDC2akQKP4ovsKDJ4LKPgKAopQilPKCooJBlhR9Hoab3Yf1q027hx41Tb+PMXX3yh0n2nTJmiPMKOHTsUM74YNETpSXFFmcuIKMpCto+SlKwYucX9lC9Lly5V/D2d0osRdS069kdASAxOHtuGgddOh8nij7KifJh9A3F834/IzzoJs9kXTdr2wpFda9G577UqzbUkPwshkc1wdM9qtO42DKtnPYfIZu3RaeC1KC3MxcFtX8E/KBZjpv1LpczuWPsJ7LbKKNO6lmYgI/YHBSa5Ui5zbHTp0kVJUUorLSW4sT8lGPFW4XTh7tgIXBsZhoPFpXjudDruj47AgJBA7Cwoxgun0lXKqsNmUyL52muvVemglKyMGOW44HtMkWYkpvvY0CLqKOoe7BmiIupyyh1oFWbGiQIb7l6dBodOB3vV/G2UWyyH48wbUadF1PE+5T3Pe5Vji38k4PjnmKUEJVtGxXoaUUfBTmnK8dbQmNcEHyNYmcrM8c17R0t7ra8Pdb07tHUxh/r6G2/GA4/9Ud2Qf370IXy7/CtExcah34CB6NKjl4q2SzqeiKWLPkfzlq3Qtl17zPnwfWzdtBG333MvXnjpVcyd9QH+9sQTiIqOxPMvv4aVy5Zh1uzZuOuuaZh+7x+waP58zHxzJtq0aY3p9z2ANV+vxLLFS9GrVze8v2ARWrRs2djjTMoTAkJACPx+Cbj4V658FJSWwscSilB/f+hr/8Pd75eRtFwICAEhIASEgBBoFALuoq6h+Z7qSn3lQzQfhDnBOx+kmR6qpTNqkTUUW7UtPqA9FDPKa9CgQUqGUfZwoyxjlB3lGCVaQkKCEgsUPOea+kpJxOgzls1ILso2lk2BxOgvygptvjsKIwonRhdRJvGBnalwvD7FBs+h+OI+pgxSIPI9Lf2TkmbdunVeiTpGFJEZU/+4UWCyrnyPL23eL3Ijb9aVQo7ptZScFB2UG0yL5bkUdJQZrBvrw/f4PdtMh9CQtGAdeC32HfuUQpNla0JNE4CsI6ON2H/kpqXskgXlCEUjvzKSUZsfjbxZb5ZJ2cjFQsjYY1Fnt6o56hhRt+Pbt9F/9OOI7zwQB7euQFzLbigqyEZWylGkHNmIIRP/jKSDm9GiYz847TakHN+Flp0T8M3Hj2DAmP+D2TcARh8TDm9fjahmHXHq8GaY/IIQ32GAitTjWp77NiyC08U5185ePVYT0YzQZJ9QzLG/LrvsMjVWDh486PFKped6YzM19bJAP9zVJBqpFVYEGQ1Iq7ChrZ8FK3LysCK7APqqlXEpcNlfjPJj37DO7BtGllKC1ZzvkaLO5nRhfOtAjG8TgNNFdlTYnQj1NSCp0IbXd+Uxp1fN+8fISJbP+9hbUcfxz3HM8U9ZyPHK+48Cm2nbFL68fynaOeYaWkWa/cKxpUX8apK/vqg41oGinG1g3zGSlZ9pFK6MROXnRp1z1HVoGutyOe0Yc/0EPP/Ka9ixfRsev/9+HNy7B/f/6U+Ydve9iIyKUmGMmzduwNZNm5CRno78vFxs27wRzv8/geQTzz6HW6dOw3szZ+CZJ59UKbIjRo3ErA8/QoW1ArPmzlMfBE89+gj279mFsNAQ9Bw4GIf37sXeo8dw5+234bn/vIxwiag713tJzhMCQkAIVCfgcqK0IBkbdqzAwdxjsJi64fJ+Y9EuKkxknYwVISAEhIAQEAJCoNEJaKKOD8LavHS1XYQPtowae/fdd8+ao46RZ5RAlHF84Ge0DmUOU8UGDx6sfmaUHAVXzQdrLV2QEo7CgJtWD4obih/KNT6wUw4xUoxfz2XVV16LbaAU5EZRRIlFWcT3KBgoGimUtMUw2DayodTgcZRM/J5t4cbjKRL54M4oN0o7LQ2WP1MM1DenVW2sNVlHSciNkVgUcBQU3MefeU1NtLHelKVsC/uA12c9eV3+zPf5HuvNdpIly+BXT1JytTm72KeUT9qCI5rI5M+MGmT5lG5aX2kLXfDabAvPpQDifpbFNjEKj/VnW2pbxKC+Ac8UTrNfIAxGE4rzM+AbEIbAsBjkZyQhMKwJ/IMjUFqUi+yUA4iO74GK0sKqRSTsalEJi38I8rOS4BcQjtCYlmpOuvQTexEc0UwtQsEFJ3zMAer9gNAY5KQerbMvNeHMsc7xyXkUGWXK+4FjxZsFRc71Judqr2Q+ITIUQ8JCEGEyotDmxIaCQizMzEGR3QH+7Z9jmgKcddQWvWA0JscQo0UZBVmzvtpiEp1DTbAYdEgusav57tT96nAiv8KlnlV4HvuT6b4UXJRp3kTUaVKYYozCjhGKnNeQ9yA/SzhGWCZFKI+td3y4XOoYljVmzBiPV33leObnDj8rKC/ZJt5DFH4cvzUXwHCvg65/t86uoyeSMHDQYMyZ/wnmfTwL/3nmaQSFh+G92XNVRF1RUSE+mT0b/3z0MQS3aYNbb7kZx48dw4oli9CpSw+8PHMmunTvjhkv/gsv/eMZ9Bw4CD5GIw7s3IWH/vokpt93P95947+Y8eK/ERIRhRtvvRVBgUFK9vED9oqhw9Crd58LsizzuQ5OOU8ICIHfNgFXaQZ+3DEPe3PzoFP/1Hi2ueBCdNxEjOrVDZYzfwRzwVFegJOpKfCNbIuYQHO1whwOK2wOu9svMPyw18FoNMGo50Lkjb85bPlY/8Mc5AUOwLW9uiPjyGL8cKwcI4ffhHA/kxctbvy6XeolWvMTsWbvj7D7dUT/jj0Q5udzXrwcaT9i3q61aBI/Egltu8Ni9K7PXS4nHA4b7C7+UlTXWNXGlBlG/c9/ndV+8aj/l+cKbPvhWWwuikCvzhPRP76p+gWJ0fZ2uxVOXe1XVWXrjDD7yHi61Me01E8ICAEh8EsQ4L8LfAjmwy8fiOv6t4diiNE2nEus5mIS2j5KIS4SoKW6MoqID70dO3ZUD7d1iTq2kw/kjEpzXyWSD8Xc+NDMh31KHcoybu6ijoKBQoTRcPX928m21ny414737N/eyugybasrjbfag3uVzPBEiGnnadeoWaf66lizXnUd6/6+N3Vi3dz51cWtPinpvq82yeJ1WqhbX/zcK/yucvVRqOUhdCrSCy5n5Vf1O1nV++4dxf1Vx6rf2qp+dfv5EpXneDK+6mLjLW9v73/FwOVCmQtobjGhpcWMHK41UFIGH0ClvWob7yU6Hd672qrFjI7kPajNW1hzMQmWbeOvkQCMRFrFspJX5e+dLItSi+KeUo0Ctma72fe8Lu95RlC6y3ttXPAziRKcEYkjRoxQEphz/jEdnJ8HvN894cn6aJ8X2mdLQ+NMG+eaoNaYeXK+Lj4yzOVr1OPhv/wVYyfchP978AEsXvwFRo27Hq+9MROxcXHYsmkjpk+eiNSUTFw7ehTGT56CBXNmY83X32DKnXfiib8/jfCICPzn2acx8+WXEB4bi+KSEjAf+Knn/43IyCg889c/46OZbyJh2DD86aknsX/vfvy4dg369OuLKVOnIazqrxHeDiI5XggIASFwLgQcuYfw+ge98VZqLAY1CYNBV/9fUtS/V3YrdqYcx2Xd3sXLU29BqLHyyvzwzTi2GM8sfBNNuj6KB4aPQKi5aies2LH5Hczavga+BkPVv+kuFFX4Y3DCo5jUu2e1f+yq/TvvcsJuK4e96p8vb9rpqMjEdz9+iZiON6NPiygU527Hqg0/otfgaWgVGnBe4qn+erjgsJUgPeMUinVBaBIeApPRAh+D/ux/BLnsusupVpAy6PWwluYiu9iOyIhImAxnpwJ40/5zPdblLEfi7k/w8EePIbzLC/jnLVPRNOD8RJRt96u44v0XMXD4a/j7iIkIMvFXHE83F6zl2di04S2sPLIHrhq5yzqdDxwOO2xMJYEvOnW9FxP69kOw2QBbeS527l+DDFs0hlyWgACf2pg6UZ6xBnf/80bsMQWibfzNePWOp9E00IDMk+sx65sPke0oP3uMugCbw4nCyFvwnzHjEOarjXdP2yXHCQEhIASEwG+NAH8fYsQTU9QYPVJbKiSP4cM70z4p6dxFHXnwAZYv7VztAZpfeS4FAB/G60tTY9RKzcnhtfQyRrdx01aRrSYQXC71Pl9aFNxvrY9+7+3hHz/5Un7tUtsoqHS1/L58EevJe85aJdX4Z2azQV/nc8uFqKa6vtWqokzrSnf39J7lvc4oTZZD8cd73JN07erPZq4zn0+eyL3zYaIb0K2La/ykSbjp1tuRePw4HrrzdiQmncRfnn4aj/3lr+qDdM233+K2m29GcVEBOrRti3adO2HjN6tQajDj2X8+h1tuu0OZzH8++Ve8+dJL0DEHPz4e/3n1NVw1fLjKL3575gzM/M9L0PuY0L5dW6SmpSG2SSwefeIvuHzIVR6vEnM+jZVzhYAQEAIaAWfeUbwx5zr8EPhH/HfcOAQYGv4X2150CnOX3IPj/n/C81NuRLDmJvgX5OKTWPzVY3hzTxqmXf8ubundBWYD/x7kQOLRVfg2cSt89ZV/gCsvSsUnm5aj96CZ+Od1N8BUR7fYK9Kx5odPsC8vHzq93gu5xr9EleNk6hG07nwHRnZtj6wT63C0MBzXDB6FUF8fOKxFyC8rUJLMi4J/rqlLB4slDIEW3+qnu5woyNiOBcufx8YCF9rF9ESbpn3RvU1HxIbEItDX8nPqrdOOnNR92J9lRc9uvVGW9A1mb9yBYUPvR4+44IswWF2oKD6NZcuewEubv8D4kctwc98OMNUrcY3wt4TB31xXLwK2fW9h/Nx/os8VM/DI0HEINHkjtVyw24px7MiX2MY0Cbe6cEyUF2Tg6y0LUBx0OYY0NWNTcgVuHPMsRjYPxratH2D29nXo2uMhTB86DsGWsyP5nBWZ+OGr6Xj5eBs8PLg/vvpuBoK6PYFHhg+DqSwRa/esRIGrBDXPdNiKsWPzZ3jH71Ek/+E+RAd4Ix8vQtfKJYWAEBACQuCCEzgXUffRRx/VGdFSX0TVhWrMxbjmhWqLlHs2AYowg9GnKiLu0iPksFVUisRz+uX80mvPL1UjT+5bHqMJ/IZWa/2l6l3fdXSH9u9zNWnWHH7+/jhy6BB2/rRFpWT1GzgQrdu1U+fm5ebih+9WI+X0aTRpEofY2DikJCfBZTCgd5++aB7fUkVK7Ni6FYcPHIDD6UTT5s3Rd8AA+FctjZyVlYltm7cg+cQJtYxvTFwcevTqhaYtWoikuxRGgtRBCPzOCChRN3sMNoY/g//dOBF+xspw5ro3HZyFyfhgwRTstzyC56dM+lnUqag6J4rSN+OdTybg7YxmeHfalxjeLroqdNsBNddDVeGFGdvx+Mf3IKLz3/FcfaKuPAUrv3kPu1T6hRcRZjoXCrN2Y9fpFHTuOAGtQ4MQEZmAwd37IDaYC0rokLj9Lfxx8X9xuIwu0fPUX9UEeiYDcM/I13HXoBHwd7c4rkqxlJ17HEcTt2D70b1Izd6J9WlZ8I/ri3v734perXuieWQEjLAj9cgS3PrZZ3hswssY2syOj+f+EUlhE/H42MkIt3hZr/Mcw/wHPHnfB3hu4aP4KacEdlMruJzG2n9VYtV8XIBvNzw77p+Y2LN9nVc/P1EHOB02FOZlwWoKQLi/35nrOMozsXjJg1iU6MQfbnkFfaOMWLb8r/jgwE7Emx2wWq7ENQm34JpufRHqa4atLA+FFUaEBAfCqCb/KEfins/wh/kP4tbJOzCxUyQObJqJmxe8g5tHv4/7ErohK/0wijjZsbvH1gH2sgx8/+0/8KbPfdh9z72I8vdGPp5nR8npQkAICAEhcEkS8FbUUdJxAnqmrf0eNk9kwu+Bw0Vro8uB4Ob90HzALTCafS9aNeq6sMNagBM/zEJh2n7o9cYG50275BogFWpUAjonlx2p2i50+N751ryueQDOt1w5XwgIgd8fAYq6t+Zcj8Ul3XBD574wNeTBOGdXWSa27JsL/5Yv45+T3SLqNHyOCpzYPQcf7yjEDSMmo0vT6FpSBl3IT92CJz6+G+Y2f8S/J94O/0b3US4c3vAs/rhwGcbfPhu3de8EFdznth3b8gIeW/IG2na+D1e36wGjB6m/lae7kJP8NT74aTmGDpuB+64ag4D6plxz2lCYnYzDqYewa8dizNu/EMbgQXjwuhcxvEsX+NrS8MnscfjUPg0zb50C24k5+HCHHtPH3o4WYXVHqTX+iOU8gxn430cTsOCUBZOH3IXWIQF1ZkboHEVYv/UdLMuy4C83vosbusbXWaXzE3UulBeexOIl9+Db/O64a+SD6NkiCo6iJCxd8iAWnCjAneM/xLVdO8Ci16E0/wg++eIRvLBjN+4asxD3XdUXdGhF2Yfw1dev4bCuJ+65bhqaBJpRkLkdsxc9j+y4u/DXsSNVZKeuPBvff/00kkMm44q4Qtz5+h+xDxlntc2ldyJGX4yKlq9j090i6hp/PEqJQkAICIFfH4FzEXVceZWi7lJ/Dj3f3tDm0uK8eNpcV+dbppzvLQEXjAGxsET3gt7wS/6O6Vk9XU4bylK3wF6a7dkJctRvmoAu6cQJF6MrTGazmieOE/Zdihuj8PLy81FSVAS9QY/QsHCPJ/67FNsjdRICQuDiEqCoe3vuWHycFYDWsS3gaKg6OsBgL0J+6la0af9O7aIOLtitxSiy6hEc4F/rHA6V89ktwZNzpsPR+mm8PuVBhHi3tkBDNQVc5fhxxQN4Zt1R3Dd1Lsa1b3bWSq9K1H31Ma659m3cM/BKNZGrR5vTjuS9s3D3Zy/jyiEv4cEhDYi6/8feecA3Vb19/JedNOneu5SWDqZMy95DNjIVWSqCgKh/ZcgQUFQQGSqigGxkiLJl743sWVb3nmmTZo/3fU4aLKW0BVFB74F+OnLvGb9zbnLu9z6jRKU6dS6yc+7hbOwl+IZ3Q8MqPhDyLUi5vRsn4yVo06w5nIQGqDQmKBydIC5BF1lCBYvxsUOKWMGHkC9kVoTlFYtRiUuHPsX/dq1Hg2ZzMOGlXnCTPnoTZ9Em48dVr+OXLDkmvvoDWoR6VQjq6jebh3fa9IRLOfU+XAnF/NMiPel37Dw0B8ezJagfUR8FmUdwNkuGt3t/iqbhoZDd18oCdX4c9u4dj10JQN26r6CWixHHft+BDL47erX+H14MC4XIkI4t20bhSJoCTRr2RZCzjD25pZiBYoEHwkPrwFmoR15BHotNUlo9oyYFOzaPxsd4E7dHDIeHA2dRV6nrhzuIU4BTgFPgX6zA44I6ik9HVnWUwOG/UChTaUJCAouNxZV/SAGrERaDErbYL89W4fEE4EmcwOOLOWu6Z2tq/pHe8Fo0b2alJxgikRivDx2Cl7p2Yxk6nrVSoFRiyXffYueefahWLRzjxo9HaNWwf/3Tl2dtHrj+cAr8WxSwxajriuMuH2FR7z7lW4XRoMlTsCAeyzcNRazs/YdcXyurCwGna2e/wIz1k5DpPwWrR85A8FP2+LDq07F+dScszAzA/CFrUM/PxZacqkSxgbrlaNdhEYY3bQ3JY4C6hMvL8Namr9Cq1RyMLgnqLEao1YXgiRWQScRlwjFbBlMzeHwhBMWJESwWEyxmQCAUPtRPe5eV2eew+JfZOG8sFbaD4v6JbF6oBtr3lvJgFvD8MK7HZNTy83gIVtrrthhUiL24HJM2ToUwdCQm9/wANXwpwcijM6yqMk/hs+8HI861G2YOmo4wF8UjlwCzqFv1P2gVdVAj5CW8XL8nwn0D4KJwhFgoeOSYS1ZoNRtQmHYOX67ojiMqH9Sp8gI8ChNwRe7Dsm894JnKs0JnMKGGSI5cTTri8pSIjhqC19sNRJSPC/gwIuHyciw4chjVg2ogKe0OUnOOINvqiQDHYHgFDsDbnTpAYi2E3vwwpKN+GYqSse2XkZhp6IMDAwfCU+EIJwcniIQVmaZW9krhjuMU4BTgFOAUeN4UeFJQ91+wqKO5pHvspKSkMhNV0Oe4mQXtt33uing8to+q7PaM6mcP3IqTcdDv9oQZj1pHJb3VHmXRaN9fPE4/SrfH2imOu8baqeDhqX0sbPtd1rElMrQ+0FbJFKvP28VTPH+PPWbbCc/haP89XS6ZwbW8a40APX1RYgz6qsiKmPdK75etZ44fQ15OLpq0bIG5336H8IgIdqFriopYKlu6sZI5UJprBctOrNfpYTIZWeVSmc2/W6vRsBsFSj5BiSXo/CK1uvh8K+QKOeRyBcuyQTdpOq3WlnJXLGbJJgoLCyEUCeHi4so6ToWyBhGgIwu65MREjB87GudOnkGH9h2wYOVKeHp5VTjAf88S4EbCKcAp8DQVsIG6ntjB64UpLTrAoUKTMisomcS2IzOg8pqGT0smk3iMjlktZmz/uQfmn9kBLb8L5ry3Fk38nR6jhooPNWSfxRcLWuCi3xQsGPgeAp1KJXwA8PRBnQXKlONYsHY4LH5voUV0ffh5VEGwny9koj9vMqjKj8Xew9uQZqZNa/G2kQIC6zNx5PIcpItqomVEX3g50FPIYphHG1aeB9o26YlIb7cyQZ3VrEfKzZ2Y+8sHOGhojm/f+BwxIT4QlrfpseiRdGUlxv00Cb4N5mFa1wFlJmqwzxQDdasnwtGnFxq5u+PC7aW4wq+Bt5v8DzERdRHi5w/5IxJM0OcvJR+JvXkAP+2agiuiZhjU4k20jQ7C9ZM/45qONvKlSB3jlQ54oeZLCBIlY9uez7H69hl0evFr9GvaBmHe3jAVpiC1QA//gEBYTTrs29QZC5XtMf/lNxHk5gFjxiFMXPs2NqUoizMV22ITOksAsQXI0lMLaoitEuRbJGgW8Qq+GvQZwt2f7lqueLVzR3AKcApwCnAKPCsKcKCu/Jl4FKgj4y6d1QJ/qQThcgcYLRbcUGugNBohZZlAKwYxdF9N985+fn4ICAhgQODu3btQqVTs3rysOugchULBsmpSNt3Sx7D5pL1UqWHRNosey0l4/Ec+BLWfYrWaYdalQShxh9mYD/DdIBCVHx+O+kFWltpiXlCyedpHm3RZsOjVD4ktkCkgEHuzBGzPW6G5IItLGvPDGYetMGoyYdGrHhqWUOYFgfSfSMD2vCn81/SXuBbNG11D9FXWNWSPTRkeHs6yzlLG2Xv37jFeVl7WWd7BvXutH4weidi7cRg6bBgmT58BuaMCZ06exLGDB5GTkwWj0QxPL0/06tsf4ZER2Pbrr7hw8SLcXF3Rp39/5OXm4tdffoFCJkOnrl1RLSISRw8fwtlTJ5GZng6r2QrvAD907toNDWMaIzkpCT+tWsHgHL2Z6DRa3L51i4HA/oOGoOGLLyItNQV7f9uJEydPQe4gg1QswZ6d25CbkY1Jn83E4NffZAkwuMIpwCnAKfAkChCo+35NdyyIy4dQ5FQpC3grzwCJIQMt6q7CJ6/0KU4mYYEy4yJ+O7YTKWaAJ7CCx3dEq/qvoV6w50NdM2tvYcbc9lC69oY4Zy1cG/2C0a0bw0lU8SasUuO0mpFybSneWvgBwjpuxCed2sFJ8rBb4l8B6opy7+DA2bXYdelnnMjToKqiBqqHNkatKvXQILwmPJ09WXbUR+83rVDn3cbZqxfgFd4eUT5u963u6MOMNnsM0d2Xigd+0R3M+TYKB2QvY+4rSxHhrijxOj3B5YPPF5T9RNpsQNKdvfhmy8c4XBSIGQMXokOEf4Vp583abBzY/Ca+OBeLwa+swYC69cuNcWiLUTcTjVotwJimbaDMuIPbCcfw89mNSDd4oV7VGDSo3hp1Q6Ph6eT4gCWfJuM8Vu6YiW2JVxFTawL6N+mCEG8v5hZsJfcNKz2ZLmNlWOlJuhA8qwVFBcm4enUHlh2ZjyR+TQxr9zF61K0BXVEWiowmdvrx7X2xpLAtZnV7Dd6ODixfSE52PLI1ehYSg57q63PP45d903DH9X8Y16YZZEICsLbtutTBC6H+oXCUPJvhMyp17XAHcQpwCnAKcAr8KQWeFqhjn/kWMywWmxm9QCAGjz2VqvxeybZvsLBkXJUBXU86cLs1DZ1fOllE6XbLAnXMgo4vQF8/L9RwdoKSLG4AyAR8bMrIxqX8AkjpmHJgHcECart9+/aoUqUKUlNT2XDoPvvy5cs4e/YsO780FCAgFBQUBIqbp1arH2iDPt1lfD7quTrDSSyyPQQtLjQVGpMZ5/ILUGg0PsKDguZQD4lMgBodpkPq5MmSY8WfWY/MuycAvqjMRGk0DjLa8fX1RXZ2NnQ63f1+0WsiqRxhMYPgFlS7eD9pWxc0vqy4M4g7sw5GrYppSscTPGGeHGRgJJX+pWuB5LFDNtL6cdYd9ZNATmZmJjQazf25Iq8THs+Emh0nwsU3stgl1o5KrUi9uhvxv68HeHSN8NnrpJkdAtEejvpB6/RRmU7pNfvxdCz9bLf8epwxlLyGbNefbdFQHU9az5Nel3/XeQTHw8LCoFQq2XVU8horqYGPjw/69+/PjqN1uHbt2vsGbXaNSveZ90afPtaTp0/AJyQUX86dh2oREVi3cgW+++47SC0WNGrSEIePn0H87TsYNnI4xk+Zhk8mTcCKlWsQGRWBz7+cg62bfsai5SsxpH9/jBo7Fnt37cTKVavg6eKEkCpVcGzXLqjNVvQfPBgzPp+Fvbt2YezbIyAXidEg5kUo8/Nx6dx5OEjFzC1BmwAAIABJREFUmPntd2jXoSPmfjkLG9esgcTRCSEhIchIiEdOViYCgwIxe+EiNIppct/y7u+aCK4dTgFOgX+PAjaLum44KB+Frzp3gbxCizrArErCuh1jkeg4voTrqwXKzAvYuHsZrhiNyM48ifNpOZg+9BRerR/6oGBWLe4cnozhB6/hg14zIbg3G1/ddMJnQ2ehrr/7QwkfnkRtszYNO34ehrGXlJj/+k/oHBUKURkPFp8+qKPeWmAy6KAuUkJZkIobtzdie0IqrKoiCKxGuAY1Re8mr6OGr5ct6+gDxQqTPhe79kzH/OOH0LPzCgxrXBcOZXW+5HmqW5i1MBIHZL2x4NUfEenuVLEHgNUCfVEWrl1eiW8Pb0aepAaGdngHnavXKlOrB/tpQc69bfh02Wu4qOiCuYO+R11/53JvHUonk1CIBLCY9ShUZuDOnV+w89pFZBaoIHLwRkRUR3SMboFgDxcI+QKYtEk4cnYfnAOaIcrbCVdurcD5QoCi+TzK86Nkf2lf7yAJR5PqLSHTJeP321fgHdgadQIV2LJ9Bg4lZEMsALKztiPNHIxwj2iI+FI0jnkP7YL0+OHQUXRoPQwv+LrAkH4IC5b2xQn3uVg5bABcpULAakRWWiwK+b6o4u1Rxrw+ySrmzuEU4BTgFOAUeB4VeBqgzuYmaYWbTwjcvLxhMVuRnngDRYX5DLzxBSLwwIfZbLNe4fMJIhFosBTDGQusZiMkMkcoXH2Rl3GHUB94dF4lLNMqozv1USaToXr16syVNT09ndUdGhrKvMvu3LnzELSjekuDOnJ1pRv74VUC4SERY29GNjK1WuotQh0VeNHDDfuyc3AsKxdSAj9ldI76QgCGIJ2LiwsOHDjAjGGoPy+99BIaNGiAzZs348SJEw+529lBHcED8qIrqQ/zlOPzMbRKIDr7edtgXAlgeDAjG9/HJUJtNJUJ6ixmA6QKBWp2+gia3BSk3TwIBydXhDV9A3dOrkX6zYPFsO7BUZUL6ixmOHn5o+mQH+HoFgQre1jIQ0H6degLsyFx8sXZXyYgL+kaeAIJU4vmhMAIgbCUlJT72hAMpPFTezRnBPPodzvYouNJV/txdtBFf7MnA6FzmIegSMSOJQ2joqKYFWNWVharj/5Or9uvDXudpaGpHdSRtRVZ1dlfNxm1kMrl6PHxueK1bgV4fKjSr8OoyQdP4oIDC7vDbBICfAGzRCT4SudT36gfVLeHhweLj0hgyZ6TwB4rkSzC3N3dcePGDbauqY7AwEBm+UVjKTlG0tQO8mj8pA99py86l4odjhKcojWVlpbGrDpp7GS5SfWR5uVZk1XmOnwWjikP1NFYCZy3adOGjZ8AKgG6rl27wtPTk+mxb98+XLt27b52D+zhg12crB4+3hgyfATeGj0GN65exYdj38G5s6fRpWdPdO7aA19/+y1Onz6Nd0a8iYnTPsHMKZOwdtlyNGnZHB279cDCeXOhN+qxdNVP0Go1eH/kSGTl5WPmF5+jWmQkXuvVE3q9Dr1feQ0Tpk7F7JmfYPWPy9G8TWv8b8JEHNy7B4vnzUVk7dqYv3gJstLT8M6bb0CZm42PZ89FZHQ0Jk+YgNuXLmHA68MwfsrH8A8IeGpvts/CJHN94BTgFPh7FbCBuu7YLxuBL1/qAgeB7eOeyqOe15rVydiw832kOk94wPWVmeGbjbCYNLh0YALG7d2KkUNOo3/dKiUGZUFR+hnM+L4TsoK/wIyXB8NVeRRjFg1ESOMVGNOuHdxkfzIDlcWIzIT9+HDJMOiCJ2J2/7cQ7CIpczx/DagrhbTMJuj1hcjNTUJCymmcupOGps1Hon6QD0SlQJ3VYkDsxR/x0a9fwLXKe5jc+y2EOMsqdKmAKhazFkbhoKw35lcS1FnNOsRf24DZa8fAFP4/jGj3BmoF+kIsqNhVwqLLxt4dg/H+vt3o020XPmjfHo4VWEOWm/XVYoZWq0RK6gUcu7AVh2/uhsahOro3+RBd6zWCs1R4f7PPK7iKqd83wNbC+mjqHQBBBa4dPFiQl38FidpQTH7rB7QN9rfRPbbZNiIp5RLS1UUMEJ87PBa/qmMwpkV3eCkc4eNVA57WeMxYOhT6sE8xpUsnOOQfxtfL+mOzMQKzhuxAMz8+4q7vwHf7FsIt6kOMbPMSPOS2jTFXOAU4BTgFOAX+ewo8DVBnMZugcPFCTKc3kZeVhIyEq8hNvwu5iy+cPfyQlXQTZpMZ/mE1oVWrkJt+D1K5Cxwc3aHKS2WAztnTD7oiFXyr1EJO+l1o1QXITr5ZJjx7kllill0iEdq1awdnZ2fs37+fubQ1btyY3TNfuXKlTCuikqCOPou1FgvqujpjWJVAzLqbiA5uLnAVE4gE4jVa6EwmNHJ3xbxbcVARFCkDNBJsqVq1Klq0aIFffvkFubm5bEg1a9ZkoI5+JyCyfv16BgpKwpHyLOqoDpPVCi+ZFJOiwlDfzQUmi5Xtyy7lFWBW7F0ka3WsTw/tm8ld1lwE/+ptEVKvL44seg18iRQmbR7qdJ8OqaMXru5dAJO+6CE31YpAnbO3P5oNWw0HZ2+2Yy/KT8HtfZ9D4VUTPtU74OymD5ATfxF8oc3zrl+/frh+/TpefPFFNi/JyckMaJLrIVlCEUiiv5P1ob+//32YVa1aNWbRR3AvODiYzXN+fj6DsN7e3kxHglv0d/obwU46dvz48YiNjWUAl+YlJyeHvU6gpnbt2sxajvpAAKwkGH0kqDNo4ODkjJ4zLsNstFkGagszELtnNpx8IuAZ0RZ757eFySRiXhbUJoGhS5cusX67ubnh8OHDDKiRxRcBOLLaI8BEP1O/CcjRWiYdCKDRcZ06dcLWrVtZv2lt03gI+tnjHpL1H7lN5+XlMQBNMPTcuXOs3jp16rDrg861H0Mwm9ohXQkM3rp1i7VDsOp5Lo8CdQQjSatBgwYx8HrmzBkG42i8dB0STG/VqhXTaOXKlezY0g8SePWjI6zxySmIadIEq9dtwM9r12L2J9MY6XR1cYJEIoazB10IwMh33kOT5s0xY9JErPvxR7To2JFVemjffkz59FP0G/gavpn7JZZ8/S2qRoZjwfdLcfv/F+qwt4bDWyzB1NlfICIqGqOGDEZWegqGvjUS/Ye9gS+mT8feLZvRd/AgTP18NubOnoWv585D3VrVsfG33Th/9ndMHDsWeanJ+GLxEvR7dSBbDFzhFOAU4BR4UgXMubFY8GMNTIsF5CJAIbbCXWKBRsdHtpHHssA6iS3wEAO5Wj4KKNkBAJUB6N14NeYNGQDXUl5+FkMRzu4ei/H7tz8I6qxWmPU5OLxrCt7etQJz/ncPnar5Q8gz4tiWgZh3MQvDB6xAu4igchIYVDxSQ1EG9ux4FzPOnMO7r+xGn/pheBT6+ztAXekeG/RaCMSyhywH6Sl4WuxWfLl+ApIULTB5wBeoG+BW8YDpiCcAdWT5p6FNzp1E+ITXhp9T5bLNkettxt3tmLJ8NK6Ie2HJ8E9Q26/iuCDlgroSozQZCpGRchlbDszDLaMXRvf9AhEeLn8cobyKT5e2QW7QIoxv3wIO4vLBIs9qwoULszB7/y2MHfo92oQEsDVMheByRupNFPHdEeLrjcMbWuLL/G748ZWRkCuP4K4xBJHBYUg4/A5G7krGRyMWoYXjbSxc2R/L0szo2HA62rjmYenuWajaeCHebvsyQjycOIu6yq1a7ihOAU4BToF/pQJPBdRZzHBQuKFJl7egKSrAgXVT4OEXhVpN+0IkkcKg0yHh5hmE1XoRYqkTUu5eRLUX2kKnzkda/A34h9aC0ahGetIthNdqBZNBA4FIgtO7lyMn9RazyHsahSyIqHTu3JkBERo7wZGTJ08+0sXwAVBXnP+qR4AvPEVCfJ2YitUv1ECksyOzUNuZnolNCSnoEeSHI5k5OJ6bD1kZUINu+lu2bMnapLbt4KB37964cOECNm7ciNGjR+P3339ncIRAjL1UBOroAXaO2YyWbq6YXiMCnlIxEos0mHntNs4XqKB45ANOKywmFQLrdIZfZEcc+XYAZF7B0KnSUb3Nu3Dxj8bVPfNh0OaDMp2WLBWDugA0GbwE+oIMyFwDkXp5G9RZ91Cjy2TodWqc/mkMchMvgyeQMfDRtm1brFu3Dm+88QaDRmRZRgAuLi6OWdsRNCKdCNoRNDl06BD7mVxvSVOaUwJfBNhIrzlz5jD4Yrceo74TDP3tt98YiPrwww8ZhCMYSO0TyNuxYweztIuOjmZ/O3r0KJsru2Ub1VE+qHNF96lnUJAWC4ncDbePLoFRk4voTh8xT5Y9X7WBySxgoI4AWo0aNVib1P8RI0YwmEb9pz6TBjQmsv6j/pBl1/nz59GkSRMGFV1dXZm7NFmCEXijfpOFHY19w4YNrJ+NGjVCw4YN2bgJTtIYCRASpKZ6SS9yvyYISNCOQBVBTgKm9jhtpD8Bbqr3ebasKw/UERzt27cv04/WB0HjF154gUG7n376Ca+++irThSA6vZ+U1oFXOyzUmpmdg559++DjGZ8ya7k1y5ehZceO+N+4iUhMTEDstasICQ1Ft169Ifz/WDUE6jasXI6gquEoUBbgxaZN8OmsOdBoijDx3THYu2c/XhkyCG+MGIk1Py7BsqXLUb9+fXw2dy7OnjqBmePGwcXLC1M+/wIubm74cNRIGA0mTJg+HW06dMSYt4bj0P796PVyL8z++lvMnDwJG1augF9IEFb/sgU1a9d5Gu+vXB2cApwC/2UFDIW4l3IRGRoyLzcj5e5erD34C15sOw1NggMh5FmRdHMd1l5PRb+2IxHqomAWd2R3J3eqieoB/g+5SRKo+33PWIzb9yCoM+kLcOncMnyzdx1CXpyHD9s3uZ9lVp1zBfPXvY5ziMHM/tMQ5elWYYy0sqbNbCjE6WOz8eWBzQiIfgfT+7wF93KMm/4JUFe63wToyAX199+XYdn+xciWN8bIHp+gQ2Ro5YHPE4E6O6yiuDCVj3dTmHMDa7e+g8W3VBjz8jIMqFcdsofD/z00PZUFdcW9gladC7WezzZLD7gIK69gxuIWSPD+GCMaN2BtMzvQkilfqRIWto5cZEy4HrsCy05m4v3Xf0DbEqCOXG93bR6H65Z6GNFjAE7+3BJfKbth2avDcX21P/Z7rsL47j3gpLuO9b9tRnTTkYgWXcU3K/rjgLE+Ai2xyBfWQ592H6BDnbpwl3KWdP/lt1Nu7JwCnAKcAqTA0wB1VI/ZZICTmy+qvdAKUrkbRGIHePhWQWZKLOSO7rh1fhe8g2vB1SsAmcm34B0QgbP7ViAoqjFMeh3OH1wBN69g1GzSF9dOb0Wd5n2QcucC4q4fZfHunkahsZJrG4EHugEnKLFmzRpmKfOoWGClQR1Z1Q0MCYDOaMKK9EysqlMdUc5OzGptR1oW1sUnoW9IAC7lKbE9IxuKMkAdARhypaN2CQBQyCiChwRbDh48yOZk4MCBzKqLYB3BqMqCOjan9EzUbMEr/j4YFhaM7+4mYHNqJhwr8EKgfYbC3RcvdJmKxPNbkXn9NEQOAjQcuABpt0/g1qGFAJ+SXDz40LEyoC5m4CKkntuAwsxbEMk8UCVmIFyD6kKdm4jT6999ANQRoCMAQjH4CDyRVdvq1asxYcIEBonIOIkAFRkBEbAi0DR06FAkJiYywBIfH88sxghCkRsxWcMRxKLXCPKRWyfNN1kzksYE6ghcEZyaPn06gzG0nyP4N2/ePAa5aIw0V/YEmhWDOjd0m3QUtw8vgTLld1iMOlTv8imcfCJRmBOPvV+1g8nMvw/qyJpy9+7dDP7QWAiu2S28CNoRxCO4THyG1i8lHaExrFixgkE2gm4EdEkfcl8lsEn6bNmyhWnVp08fBuLod3KzjYmJYZZyVEg/gpA0vmbNmjHrQ1qL5JpNutgzn9J3gsh0/PNsVfcoUGd/fyBtmjZtij179rAYdaQTuboSnKO1QWB4165dDKA+ZFEX5KiwNmreHGM+/BDRNWrgvbdHYt3GTejYoR06dXoJ27dshkanw9j330eXbj2g1enw2dTJ+Gn5UghEYkRVr4kpn32OmCZNcf3qFbw3fDiOnjmLrl06IbRqVWz5dTPcXN3wwcSPUPuFFzDm7ZE4duQw6kTXwKxvvsH2Lb9i/vyvUatWLXz7/SK24Ie+OgA3rl5DzRrVUa9+fWzeth3ZuXno368flqxaBZHo6bzBPo03aa4OTgFOgX+BAoZ8nDgwGf/bfwxfjd2LmCAf8Cxm3DrzGaYeuYNJQxagto/rAwM1GjTQm6yQSWX3XRAfBHWnmOurSV+Ii7+vwveH1iOoxhiM7dwfLiXewqwWIxJvbcasTTOg9x2GD7sNQbina/lZR0v2hFwnVWn4/cxCfHlwNbyqjsK4nqMR4VF+9s1/HNSZ9chMvYYDJ7/HqvNn4VetG95o8xbqBflDUol4gfcl+BOg7nFWbpEyAbt2T8bS82cR02Qm3un0MlwlFbvKUhuPB+rK6VXBDcxdPRB7sw2QWIpg4bvCW+EBcnEtWcgJxaC7g1StFQqxC6TSBnjr1RloFuh336KOYsec2P0e9mR5YUzfCbi8tTXmKHtgWe+OWDi/AYI7ncLgmDqQCqwoKshGdm4uzIY4/PLLUFzwmY8hAZex4Uoa+nSeilYR1eBQCWD5OHpzx3IKcApwCnAKPH8KPA1Qx4LaC4SQyZ0gFMsQUa8j3L2DYDabcPvyUeiKlKhWpyVo/6QpUrN4dK4eATi+/RtE1O8MqYMTYs/vhkgsg1/oC7h5dgcath+M9ITruHf18FMBddRHuqkmiySykCFXR7LUIldIgmMEb8oKoF8a1BkAdPHzRoyrMz6/E4/J1ULh72AL+3E6V4mzOXnoEeCH9YkpuFSoYnHqSheyqGvevDlzY6R2CQQRkDpy5Mh9K53hw4czcEPuiyXhUEUWdfa2dBYLIuQOmFIjAh9fv414dRGLX1deYYH0TWq4BUShWvNRzMXVoKNMrTyWEOLuibXISTwHfilwWhGoc/EOQLPXV7FEYXEnl8Et+EV4hjUGjy9CUX4yTq8b+wCo69mzJ7PcsluUkfXhDz/8gGnTpjGLMHKBJcBGbq/kHkuAjeDS7du3mRusXC5nlnfbtm1j7sQEnMgijXQkAEdx3ciSjsAV6Ttx4kRmuUbaErwjUEOQjADNzp07GQQjizsCf5UHdS7o+ckFFKbHI+XCGvhEd4NLQC2mpSo3EXvmkEXdH6CO2jx16hSzliOLNgJltD7oO61XWqekB42fLAcJMhPApTVClnIE5chlluAmASQCS+S6SnoQoOzRowcDbMePH2ewj9yGCeBRG6Qfgb+bN28yaExjp9+7dOly3w2W6iHNaL3ar6Xn793O1uOKLOqGDBnC5puuR5p7Ara03kjTjh07Mni5fPnyMi0LeZ9Pm2Zt37kToqvXBF/Ax5ZNm7BuzRpkp6dAKBQgIDgUnXv0RKfOXeHs4oz8vDzMnDoZG1avAF8ix8QpkzFw6OtM+NycHGzasJ7BPVV+HlvYwVXD0bNPHzRp3gKJ8XGY+fFU5Oblo1Wr1ujasxeWL/ked+7eRZ26dfH2mHcgFIow57NPcWj/PoRUqYrI6Ci2qCjG3bDhb6F3vwHP6zxy/eYU4BR4JhWwQp15EYuXtscS8TDsePNThBJJs5hx4+R0fHzsHiYOWYB6vh4lem/Gnas7cCZRhXatesNbbnPFL+362j2UhxNHl+Lb4xtQu+HHeLNNDwS4Kh5UoTiOx80LyzBu+Uy41nwP43q+iRo+7hXGZyPYkpF0FnuOLMQXZzejVd0ZGPXSYET7eN3Plvooyf8xUMeykKYi9uY+bDg0H2cLhHipySQMbNEOXo6Olbeksw/srwZ1VjMKc2Oxfcf7+OHcFdRqOBUfdh2IIFfHSueee2qgzlSE5IzbyClMx6H9E3FI1xjvdhsBH4nhPqpj9oFmC24eGoov7wbh/Z4TUMvPGz5eoXCV/hGv0Gox4cbJmfjmSj4+6DsT8fs62lxfO7fA6v1L0br9p6jnKUFy6hWcObUKO+7FoXWjgcg/NwHHfBZhWfco7Nj6Jhbec8G4vrPRpVY0pM93mJFn8t2J6xSnAKcAp8DzpMDTAHUWsxkOTm6oFdMDchd36HVaJMaeQWj1xhCJpchKuQOjQYcqNepBp9YjI/E6HJ09cOnoz5C7euOFFv3AsxqRfO8azCYTEmNPIbpBJ+Sk3UPqvYsMAv7ZQvCBXBspjhe58BF0IQskivNFcIMSN5TMBmtvr3SMOoPFgqpyB4yLDMeJnFzsysyGhT17s4InEuL1QD/wrVbMvpPAsrgLyohRR1ZTBJZee+01BkzIpW7v3r3MSonuxcnaj8DRzz//zCwAS1rtPA6oq+mowJQa1TDp+h3cK1RVCOrYKNgeV8fiBkqd/WDQKKFT3kFk20lw94/C5R2ToFaqHnBHLh/UWaDw8EHjgd/B1TeSuX1Sdlc2pzwe8pOv4Oymj6BMv83AHbmWErikGG1kVUfwiWAbWZSRqye9RhqQWyJZPRF4I2swAk4EVSiWG0EmgrA0p6QzWSuSvmSlRm61VMilkyzICHi98sor7Du1RccTyCEARolHIiMjGZghwEVflXF9NRtJPwk6TzgOidwVJkMRBCJK2mDLpJp57wyOLH4FFquQWdSRBdzLL7/M+kdfBG0JyhGwo0JjJAs5Wp80TvpOsJJApT2RBlleEpwkIElxF2n90DqncdMxpCHpRWudLDkphh3NG8E8stirV68e+05WifSd3GMJgtLxpAGtTQKc1Dd7ltw/e03+U+dXZFFHa4TWGYFNcj2n65NgL8F1WgvHjh1j648A6EMWdXq93mqfFBogXcCaoiLk5+dBIBDC1c2NTQ6dePH8Oezcvh27Nv+K6/fi0a1dc8xauAR+/rbEDvYMIEVqFQoLVff9oCWUCpnPZ2+WtGAomLVAKGRfRoOBnScQ8JmlHF1ErH1lPuQOcsgcHNjTACr0BliSPP9TE8K1yynAKfDvUIBcL42aNBzcPw3v7tmGkQN2Y2TTuhBTrH2LGddPTse0Y/fw0ZCvUdfXvcSgDTh5YDp+vpiJt9+Yj3AXBXtfsxhVOLfnPXy4eweGDz2Bdp4JmLdyFDwbzsOg5h3h4fDop49WcyHOH5uNxaePot/Lq9AyLPjBDRk9maR/FjMMBi20ynvYf3Ebdp/eiCPqfLzefC4GteoFP2dxpQCSDdStQLsO32F405aodMQWqxlJl5fjrU1foVWrORjdqut9N94HVgXrr22TRlDIYNRBrUnB5SuHcPrqTqy/fhHRUV3wZtt30TQiEjLRoykPq+Mh/05bazz1bcy+n0xiKSLcHMvMBmILdUybmorXLrUHcsvVFSAp/gg27p+OpbfS0afZlxjZ/mWEuMkrhKglW3lqoM5eqUmF68e/Qtttp7B2xGq0DPd6oD+G3LOY8e3LyAubjWk9+8CrDHM3ireXfH0p/ncsFh/1nILcwy9jVm5HLO4/HJ5SPiymQpw8/gMWHvgJhU4ueKXpdLQNkmHThgE46fMdVg/uAWveZaxa0wffZUkxvseP6PFCfbj82YQoFU8PdwSnAKcApwCnwDOqwJOBumXsns9+k2rL4wkIxHLw+EKYjRoWZ44sr8RSBcxmI4x6FcQyZ5gNemZRZ/9wt4LiPIkhkipg1BfBajY9qFRZiQ+eQEvak1B/CbwVFhTa9md0P0tZN+VyqNW2RAGl0yw4OjkhKTGBwQl7nymhRDN3F/QJCkBikRYX8gogFfAQ4+EGo8WKpfGJyNYbIHrkBobHrA0jI6OYCyy5apLFDkGAunXrsntvclEkiy+6j34SUEf9CJRJ0D84ACuS0pCt0T6UFKw8GS0WM9tX0ZjZP74ZkS3ehoNrAM6uex1CqT/LZEqlXFBH1pZCEbyqNICjZ5Xi+HbFIUB4gDLjFrLjz7O98v31RHs6WlPFrML+M/EFgiPEFwg2EdSktgmo0HeaWyr0u/0cglp2CzD6TpZnxEnIqpGAjb0Nu5spzQFZU1FbZKlG1msE8MjdkeappMvno2LU0b0KLEb4RreFo0eITWYbzWUlO+E88lKusHVPFw61TdZx1DeybiNIR/NObdHfiPuQJR39TmOk8dnjo5HhFfWDzqPXaZ2SPvR3Gh99UbFrR+0QfLMDRzqPdLHrSq+xPXVxsWeGJc3oWOJOz3spL+urPbstzT15jZI1I1lmtm7dmsFLSqZBgNfuLl9aC561pHrlKEXwbMWyH7Fh489wkUpRr1ED9B84COERkZW68XneJ4HrP6cAp8C/RwH6ADeatCjIjcOBk/Ow/MIFNGrwCca07wxPBxswsoO6qYeu4p1X5uHFQM/iDxserCYV9u74EDvTJJgwdD5CneUw6ZS4c3Mzfj6+DPc0IkRW7YZ+LQdCbgHcvTxRQWLQ4g9eAwoLNZA7OTF3Wnp7Npv10Bu00BUVIleZhczcq7hwaz8uJp9FsjYIdaLboUe9XmgcUe2xElHcOf053tnyHerWfx+do+tCUOKDtLyZpn1iVtx2zD26Ce3afYMxrbs9AOosFgP0ei0MOg0KCnOQo8pETvZlXIo7h9vZccjXyeDl1xi9Y3qhZnB1eDrJKgCLZNF2D3fTk2HgCR48lscD35COjVsG4KKkBUa0Ho9AR1mpmG20fRbByysSwe7u5VoaWs1mGExaFKmykZJxDUfPrMahhGswOdbFKy3fQYdadeEiffwn8X8G1LGn0RYjDCbazPyx2THknceUL9pA2mIj3mvbDi4SG4GkBBJXjk3C/47lYvKrn6FZFW/wSswtu4ERitimT6XKRHqeCjKhAAd/64fleTUwrHZ1KHOSEBTWFwptAozOAagRVAeerg4wpB/GgmWDcM5/EdYO6QUnsQBFebew8bfPcSBHgZHdJ6FJFb9/zxsFNxJOgf+4AiazGTq9CfTdbLHAYrY8HBM3Uop9AAAgAElEQVTzP64RN/wHFaBPXKPBiKzsLCSnpIJfVhxYK9iNfbVq4djw8y/YtHU7ZBLpww/Z2GdXMbazQyoGe4ofeto/20oDLPt5pWKf/RVzRdcECwBf/BDQ9qCPulj2U0GFXI609HSYCSQVd8iWsMGEaIUjGrm7w1MogJUHJOoMOJSVBb3RCEk5bqZWk5EByQJlHvw9HVG3fiM4u7ixfpFrISVKIFhUViJGAidkDUWwhsBJaYseu2Zs92EF20NZ6OFpsevvk2pqMRuZkY6jVzgKMm4xIGsX0WbAI2BAi0AGgaOS/SJwZdIVwqzT3V8e9n4IZSIIJK4Pxb0rq5/sIfAjIB4bbonXHmzfBmmpEIhhey8CkMV/K4lW7D/TXFBMOAJYZG1H82I/z943glZk1UbJBUqPmYwBjNo8mPWlwBYPEMkcIZDYMtzai71fpdsoOSb7GEuPjf5O/S09jtKu3CXHXlqrkq+V1Qf7+nnUenvSdfVPnEfzRpasdA0RmCydEIKuMVrHBG0pCzO5HVP2XLLqJEBHvz8qRh8vPz+f3gsYaaUnAI8SjIhqRloaiorUkMkc4OTiDEdHpwqD/1HnqOMWkwkisZhZyD3PmT3+iQXAtckpwCnwdBQgKyKNmmIi3MHV27/j7O2fcFsnR7sXJ+HlRi3hpSBTcluhjUD8tWWY/vMciH06oJ5PgG1jAiv0mmScubkDkrAx+LzvKLiYs3Ds1HJsvnwKEbVHo3t1Xxw9PBexOm/Uqdoa1YKD4eHsBLGQAvxXFNPDDItFACdHT8hEPNy9sQO7Lu5HuvIa0gtzoYcAvq7NUb1qHdQIboJqAYFwonTfFcQKKa1g3IW5mLBtEjQ8NziKHSplhWcThp6k5SNXB3RvvwrDmr4EeQljOGXGKew4+jPi828gTZmJXIMeDqJABPo2Qp2qtRDqWxuBnt5wdXSsJFjU4vb5FViwYw6yxPyHLf+sBhRpk2DgKeAo8YKwDB308Ef7ZrMwJKYhJIKHN89WswGFqgykJN7ElYQLuJVyAlezr8BR3gpN6nZBs6gYhHj5QSqsXEy60loTqOu95lPUb/E13m3TA47iysM+skaMv7sf+69dhpl9WrMtDwTmApw/9zmuituje3RTOElsNpE8swrnYjfgtiYEneq0gqtYQPu74jUNeHjXQesGzSHM+x3rD25Cti4BuapUpCpjoePXQTXPmqjqWxWN6vRHlI87xEIr4i6uwOFkFdQFF7H/8mZUabYTX3ZvDQcR6WGFWpmK9HwVPH2qchZ1T+etiquFU+AfVUBrMCI+NQ9xKVm4m56P7EIt8jV6ZKp1MLPPQa5wCjxaAfZwyGQCAaTSFmW2bQStIR54Uin0SiUKVEUsy+l/oRC4JPBdVjFbwXRw4FHkWSu0xdCv/JxXPJh1hYDZCItBB70qGyZlBviadJgM9KDXAr5A8Mj7ddrX2qFMRfDN5t1gw2lPA7DQPpv2OLYsvA/Pf0kLuOd9bZB2dldUgtRkiVZaw8eZi+ddj39T/ys7b3ZLUWJu9oQaFV1HvHFj37EKhAI4OTmjU9duqF6zZpnupWUZ3lVUOU1C/P+nPl7141KoVSrUbVAf3Xv1ZkCQK5wCnAKcAn+3AhajEnu2foCvT62CQSpFzdDJGNZ+KKL83FlstNJPlYzaHJw/swG7Lv+KWO018HmUZtMCsaABaof0QpcW3RHmqUD8hRWY+st8NGr7A95o1hgOIh60hSk4fnQO1l5aijydABYTWRpJYLWWH8jLbFZD6BCEsUN+RLvQYCRc34D1h/ZC5tMEDaMaoVqQL6QiOWQSsW1j+4RuHBTjQqXXPPDE7HHmgzbZYokjZGLpA26XBZnnsXTHIhQiCHVCG6N2RCTcnBwhFskhFROorLwLqq0/FhgNRSjSaUulTPijtyWfSpc9Bj4kEic4iEVlbC6t0KuSsX3bB5h5YgvcXV0Q7jcQLzd5E40igiCTyGxA8Ql1pv4YL32FZktno3HbuZj2Ul84iSvtaMyCZV88PxfzD34BvaVkdjQhhHwZkTmYzTpY76sjgIBvmxOzWcM2+/ZCdYWHTsaIrm9CoTyFpet+gLRKJ9QJikZYeCikQjpXwiwbbOCXB55ZgyuHRmL+ufVQWQMQ7DsaI7q8gaoef2SnKrk/qMy+4HHWGXcspwCnwN+nAL1bXLqThrW7fsf1tHwodRY4ObpA4uAEgVgCoUT2WJmy/76ecy09awpUHruVhfKetdH8vf2xw7DKtWqFQVMEs0kPo64IusI8mA0amDUFKLy5D/qcBFuyBl7Ze89n+fO7tPVX5fR4vo/6L475+Z4xW+8rM29PwtJ4DSOqWm8mpTLf6m4vdcKXX3+DKqFVme+xTqeFXqdnjRP9JcBGFJC9ptXCYrUwFxp6Q9FqNCC/e6Ly9LPeoAefx2dZXUe+PZrdAMyYMR1vjn4HQoGAZY/V63S2usUiODjY6ibCSHVTIQs8imtnNJmYbzQdS6+xOHcUs04iYX7hz3NK33/D4uTGwCnwvChgtZqQmXwBcUogNLgWfJxtSSD+bNGrc5FTUAR3n6CHA+obtUhLuYWE3DQU6Augp1gq5RR6XikW+6N+jRh4K7iHGn92bipzvtViQHbyZdzMNiAyrA68XORP1WLEnHMZ+27fgIdvPdQKCoNY8GSWeZUZC3cMpwCnAKfA4ypgMluQnl2ApXsv4bdLSXBxdIGTiwekChcWY9rG+/+A/o9bP3c8pwCnwF+tAD1QpGfJVuiLlNCp8qFX5UGdch3quHMwFaT+aXfVv3oEXP2cApwCDyrA2/rLJuu0CR/iblwi+g7oj+mffwE3dw9cu3IZv585jZTERAbmPL280bRFS9Rt0ACZGRnYvX07ijRq+PoHsECAt69fxZujx6KwsACH9+9HUnwcfAMCcPP6Nfy6fgMiqlXDnEU/oHbdFxB74ybOnj6FpLg4BuE8vb3QtkNH1KhVG/fu3sG+Xb+xlMtBISFIS01h7rKt27ZnWWPPnj6N7MwMWCxW+AcGocNLL6FqeDgH67iVzSnAKcApwCnAKcApwCnAKcAp8BgK6Awm/H4jESv3X0FCAeDs7g2JgyPbh3OFU4BT4PlUgJI3GDQqaPIzoU6/C9W9U9Cl3eRg3fM5nVyv/6MK8KZOGG/dsGo5nFzcMPvrb9DgxRgc2r8fMz75BJr0JNRs8CJib9xARmY2mjeLwZcLf8CVS5cwYsQISPRaOEglyDdZ0bJZYwwf/Q6WLfwahw8egZe3JyQyGfJyc5GbmY4+g4dh3KTJuHLpIuZ9/hnycvNR78WGuHf7DmJjY9Gnd3eMm/YZftu+DZM+mgQXIQ8ysQxpOj3eGzMaHp6eWPL993BUOKBaZBTOHT+BhJxcTPt4Coa88SYUCltmFq5wCnAKcApwCnAKcApwCnAKcApwCpSvAD30Pn4lDgu2noVO6AYndx/wBQ9mheQ05BTgFHg+FaAQd5S0oYg8OtLuQHl5J/RZceAJKh8n958euT3hQ+lEBmX1qzLuh09rPI/Tr6fVJlfPf08BnrtIaA2PrMYg22vDXkfc3bsYM3o0jh44gLHvv4t+A17F+AkTcPH4EbxQry4WLP4Rq5YuwarF38PR2Rnd+w5Ao8aNERkdjdVLfsDShQsRGBqKL7/9DhcvXMD38+bApNPg829/QI1atfDqwIHIjL2B5u3bY/BbI7Bx7Vrs2PQLevbphdEfjMeCOXOwc9MmVKtZHd1790Gt2nUglkrx2aczceH4EbTr0hX9Xh3IMgpR5pmwyChEV6/OUgdzhVOAU4BTgFOAU4BTgFOAU4BTgFOgfAXoRjMuNRfTVh1CHs8Frl6BLAYrVzgFOAX+bQpYocpKgTL1NvLO/gxTYYYtc+4zmsCD3pvIm4889gjQUaZUjUbDJoVCcdmTUpaOK02v0Zf92LJi5toBG9VPr1NdlYGAJVeEPXkAhd6ikF0VJeH4t60mbjx/nwK82uGhVmV+Pjp07oJ5Cxdh6+ZfMX3CBFgtZny/cjXkCjlGjRqFOxcvYcy4D9Czd19MGDMSV69cQf36dTF3yUpUDQtDclIi+nRoj+t37+GNt97C1E8+xaxPpmP5D4tRu24dzPn2O1y/dg0fjRsHodWE8IgoBAQHIy0pEVn5BRg8eDCqRUZiwjvvIDs7G2+9OxbDR42Gl5c30lJSMHvmpzjw204UqVXwDQhEWFQ0+g8ciNbt2peZbvrvk5BriVOAU4BTgFOAU4BTgFOAU4BT4PlRQKMz4POfjuBMYhHcfatAIKx8kpvnZ5RcTzkFOAVIAbPJgIL0eCgTrkB5aSss+qKHMq0+C8mgCHxRRtTw8HDUrFkTzs7ODKYRWMvLy8PNmzdx69YtBsjskI3GZ7FY4OrqCkdHRyQnJ7NJLyurKh1H8e07duzIgN6+ffvYuY8T75764uXlhXr16uHQoUMsdv6zoB230v99CvBeiAizJqakolOXrpi74Gt89dmnWPL9IjRp1RpfL1yEwwf3Y9rUqRBarVi8ajXy83Ix5cMPkJaajvFTpuD9CRMhlcmwddPPGNyvHxzkMnz5zULUb9gIo18fguOnz2Lse+9i7P8+wNdzvsTqH75HSEQE3hs/EQX5+YiLuwdHhSM6dumKwwcPYPbkKRC7uuLbH75Hu46dWOa5lORk3I69ibh7d3Hh9BmcOnEMd5NTMWLkSAYEXVxc/n0zw42IU4BTgFOAU4BTgFOAU4BTgFPgL1Dg4Pk7mLb+NLwCq0Ei+yOL81/QFFclpwCnwD+uACWZUCEv+Sbyr+6FOu4MLFb+fUD1uFZlFQ2HrMwIgJV0Ry0J1so6n8XE9/REu3btIJfLkZSUhPz8fBQVFbGkkm5ubqhSpQoyMjIYIFMqlfet66gt4gFOTk6PBHUlIV3Tpk0Z7Dtw4AAOHz7Mfq5sITAXHBzM+rl27Vpm+We38qtsHdxxnAKVUYDnKxZYq0SE46NPZ6FBo4YY/fow7N65C21f6oReffpgzZrVuHrxIka9MwZD3xyBL774DGuWLIaCZ8K6vUcQ08S20BfOm4eJkz5CgKc7OnXtjrzcbBzeuwt6jQE//LQeTVs0x4ejRmHnr7+iZedO6P/qa/hx2TIcP3kKUydOwEvdumPa+2Nw4MARNGwSg4XLVyG0alWkp6bgjUGv4frlqxgxehSqRUVi7pdfIj01FdM++4zVQ9lfucIpwCnAKcApwCnAKcApwCnAKcApUL4CKo0eNcevQQ1ffzh5BHA3mdyC4RT4DyhA0EydnQJl4mU4Zf2OqsF+uHLlKurXr4+9e/ciJyeHgTVyNSXwpFarmSpk4UYhpiprNUZ1kIUaWbjZXUPJJbWwsJBBrUcVAnUE4kJCQnD58mX4+vqyn6lotVrExcUxa7pOnTrh+vXryMrKeixQR32pVq0amjRpwsZD7en1epw4cQLx8fGVsqqza0DQkPqxfv16BiTpiyucAk9bAd6br71q7d67L5q3agWBgI8fFy3CiuXLkZGXDxGPBxc3V7zavx9eGTwUsFoxaeJEHDxyBG2aNsbs+V/D09ubLU5KAvH26DHs5zpR1Vg/r9y6i+jwqlj4w2L4+vlj1fIfsfC775GnVMIJgMLDDd179sQrg4YgMy2NxcJLSErC8CGDMXbcODg6OqGgQImpEz/Cr9u3w2I2I0DBh5ObP3q/9hp69+sPdw+Pp60JVx+nAKcApwCnAKcApwCnAKcAp8C/UoHDF+/hozXHEVglGiKp/C8foxWAVCxg9wh6owX8vzE2FgXUZ4XH/j+VIhbzwePzYTHReMx/63ieygCesUpojqywwmwF+Mxlkd1ygk9z9jeulWdMlr+kO0aDDvnxlxGCFFT1EGPPnj3Mik2n08Hf35+5hV64cIFZsrVu3ZqBO7Jgu3TpUqX7Q9c5gbDXXnsNQUFBDIDdvn0bO3fuZO6r5c0ptUfwjNxKe/TogdTUVGY55+HhwSzsduzYwWAf9bOkFWBlLOrY2wCPxwDdgAED2Bi3bdvGwKQ9Zl15g6Q26Nj27dtDKBQyCz+VSsUA4unTpx9wxa20WNyBnALlKMBLTU62EuyyW6VRltbkpCSoCgvBF/CZGal/QCCcXVygKSpCfFwc9Do9nF2cERIayhYqFTo+9uZNGI0GlqHVarFCrVJB6uCA8GrhEApFUObnITEhgRF6et3F1QUBgUFwcXVFXl4uUhKTGHn38fODn78/W/B0waalpiItNQVajQZCkRju7u7sdYWjI/cGzi1vTgFOAU4BTgFOAU4BTgFOAU6BSihgMJqxeOspbLuUAc/gqL98H22xWlHNxwGv1PPEjiu5OJOkhogIzN9VikGdGdZiCPTn2hYJeGhWRYGqXg5wdBBh9ZlMZBQYWII7rjy5Aj7OYgR5yKDSmpBZoIefqxQ30otgIXrHlaeqQG7iDXgZEhDmqMOpkydhdwOVSqUMjFEhKzr6nazsyKpt8eLFLFFDZQu5h7Zo0QIDBw5koG7OnDnMGq4i91d7sgcfHx8GEMkKj2AYubRWr16dATqy/qP4ciXhWmVAnd0Vl84bMmQIA3UbNmxgbrb2xBIVgTp6vXbt2ujatSu8vb1x48YNbN26lbnbEhPhwHJlVwh3XGUU4FntzuPFR9t/LelTbnuYwbvvZ26vuHS2FfZ3egRSxtMPOrasulnNJV4rr+4H+8R9IFZmgrljOAU4BTgFOAU4BTgFOAU4BTgFSIFspRqz1h3F3UIJFO6+jyWK2WqFwWyFgMeDWPDgPpxeM1oAMZ8sof54TW204I0XvZBnsGD/jXyYTdanmmySbjsMFiuzlivZJ7pnUEgEaBflgiA3KVILjTh4Iw95Gsr2aBt2yXMJHpa+fbFYAb3FCjEP90Ec1esmF6JHLXcEukmx4lQG4nP1TwTqqH3SjVmOgQcTxfWy2jQsfcNPwJP0JdmFzxkUNFrIWs4KMZ9XpvWhg5iP7jXdcDxdi4beMlRxlyA+T49fL+U8cSJis8Vqmzs+j83Nn7lrNNKaL17X+mJwSPWWXi80TvqSCHjsGnk2Cw+q3DRIsq+ipquWxX1v3rw5A2Lk/klgrlmzZswoZuPGjQzc9erVC5s3b75vnFOZcdnjwXXr1o1ZyK1atYrBtsrEcrPHt6N2Bg0axKz9CgoKEBYWxr4TWCOXU+qzvb7KgDoyPiLoR4CuX79+7PwtW7Ywqz+CkFR3eaCNwCXBONIpOjqagchff/2VWfxRHVQ3GRxxsK4yK4Q7pjIKPATqKnMSdwynAKcApwCnAKcApwCnAKcApwCnwPOlQEpmPj5ZewS5fG9IFc6V7jyBIm+5CG3CnRCXb8CxeNV9oEQ31t6OIrQIdcTWG0rojWQFZQNLNb2laBAox40sHS6kFsFqfRhwVLoTpQ6kduViAVpWdYTWZMW+2wUPQCzqMwFCbwch5vSuis0XsnH0TsF9SEdgr3W4EywWKw7dU4GAjJ2v0LmechFeinLGkXsqBo4YgORZ8WKgAtU8pdgSW4DsQgMDM497c06QTijgIdpbihSlAXkaExoGyuEuF2FnbAEDcvZC45SJ+WgZ6oSkfD2uZmifCAw+qc5/5jyjxcL08nMW4dBdFVR6AqWlIK/FimyDBd0inVHDQ4IdtwpxJ08PJ+Hj60p9JShYzV2CZqFOOBxnm7snwWYMGIGHRoEOSFUakFxoRKdIZwbhaE1ojH+MhVZ8A38ZavnJ2fylFRqeWVinVeVBmHUNtV3UOHX8CFq2bMlg0927dxnEIrdTgmEEwSgOnJ+fHxYtWsTcWR+n2K3j7AY5lYF0JesnF1eKKUdWdOSWSxZ25IZLcezWrVvHPPQqA+oI4pEVXf/+/dnxV69evQ8d6bVGjRohMzOTQTeyJCzrWiYAR3CuVatWLAGFPcYdWQsSvKM6Nm3ahNzc3ErByMfRkTv2v6sAB+r+u3PPjZxTgFOAU4BTgFOAU4BTgFPgP6RAXEo2Pl59GHqnUIglskqPnOBHlLcDRrXyh1DIx7TtCUhX6hkYs7m3yvFOK3+M3xoPjcbEYo5VcZdiZEt/5BUZQVZTmy/l4kKSmrmg0utU7NZ3BK4szD21bJDH0J/VdhZBF/qin70UIoxqHQC1wYKZOxNArqn0mr1endmKt5v5QCISYMflHCTlG+7HQFOI+Xi3fRDMFgsW7E9hEMkeF43gXYi7FK828sL2K7m4nFLE+ls3UIGeL3gyKz5HCR/fHEpDar7uIe+gP/pZ9njIco4sxwbF+GDdmUzEZuvweow3gj1l+GhbPMjJ0D5OatdRJkTvup64k6HB4bsFD7gP27Wh4+y62H+m7yXC9N2HEHa97cextkoANPvr9j5QqPxHzQ1rgzVCYMtWbLHmeNCYLHiriS8ifB2w4EAK0gsM9y0I71s2AqjlL0ff+l5IzNPDx1GElaczkJRr07VkKbkGbDjYrtMfOtNa9XAQ4o1mfshWG7H2TCaDsPZYeKXXXem1aG/PZLGt4Q86BGHp0VScTVJjWtcqEPGBhQdTkF1kuj8WKw+o4iZmbV5N02DDuSyQeeTjAtxKX5B/4kCDRg113Dk4ZZ9EckI8A19ktUbWdPSdkjgQwCJgR9lWCZgtWbLksVxfbWuCNC++zvm0Ih6v0LkE2AiGkfttTEwMHB0dcezYMdy7dw/kXmvXl/pLySvodXJDZeu6eO1QPQTaKGkGQcmyPPl2797NAB5Z1pU1Z9QPLy8vdO/enbVRstDxBDkp3l/JPj3eaLmjOQUeVoADddyq4BTgFOAU4BTgFOAU4BTgFOAU+A8ocCcxE5NXHgLfu3qlshzaJSH4EVkM6gidXE1VY82ZLGgNFP0NDNSNbuGHCdsToC0GdaGeMjQKUiAhS8PiuaWqjAxiiHiAq0zAIF9mkYnRFrGQBz+FEDkaE9SGB91jbYAFcHcQwFHMZ+63dB6BFG+FCG+38meQ7esDqawOcj8k6ychuegKeQh3FbO2lTobRrInK5CL+RjbLhAmswXLjqXDQWhzP01TmRjUkQp5CHURIbmQ+mRh9dYNVqCKs5jBuWBPB5xNVjOgRGPxUQjZcWRx5SThMys/Gg8lhCzLrbZxqCODftsvZuFKmhbdarsjxFOGT35LRKCjiAFQe1/+n43C31GEAr0Z+TpKyPHgYqX2yEIwS2NGkJOIaZOuNjFwR/0i182sIjP0Jhs4oWO95ba/k545GnrNwiz1yG2UtPGSC6EzWVCot8DLQYgsjQlaY9muy9RXR4kAblIBqz9Ha9OMXEXfbGwDdQS7zCbbHFBd1Bc7UI32k6OqqxixGRqEeTvgfJoGmcUAtORIadyeDkIo9WY4SwRsjqh/Sp2ZHUb9IHDiJRcgzF0KT0cxTsSrkKk2MrjpIRfAbAEbL2lDlotexWvGBt5swtL8k0b1ghV4vZkf1p5Mx/G4QrzfPojN76oTaex8ai9DTWsRbO00DpJD4SDC8XuFMJoszySoM2rVSL9xEtnHFsFSIgmrHVARmIuKimKgjizQKJEExWJ7XIu4p/V2aneFJSs/sl6jhBSlgRqBOoKKlOzBnr22rBBdBNkI/JUsBOHIbdX23lC27aUdOFL9ZVkWFhUV3Yd0zyKcfVpzwdXz9yrAgbq/V2+uNU4BTgFOAU4BTgFOAU4BTgFOgX9EgTuJGZi08hCEPjUf68bbDupGt/LH+t+z0KuuB7ZdzMGxuwXMiqokqNNojMyts2O0K1pFujOYotabcTg2D3tjlZAK+RjQwAvujmLM2p3EYEeUjwPGtPbHpnNZ2H+r4H68OZu1GNAwSI4udTyZayjBo6Ox+fjtej5cZAKMau3P3GyLtEaEe8uhM1uw4VQGjieoUcvfAW+38MeyE+k4n/xHIguqk4G6tgGQiPjIUxkQ5i1ngGvrhWzsjlUi2keGsa0DsOp0Bk7Hq2Dl8zCqqQ+i/OSsf/laE7ZdzMa5pCK4SAV4t10QCrRGOEoF8FSIoTaYseViDk7cK3ggThrLaMoHvuobBjcHIbQG23go0l6EvwNSc7SoHeQEvdmCg9fzsPlqLjwVIrzR1BdXk9XYeT3/gXh8BJs613RHiIcU2QV6xIS7Qmc0Y9ulbChEArSt4c4sDU/dLcC689kMTnWt6YY20W4MTFAm3ivJKvx6IYcBME+5EL3qeqJOkCPUOhNupGvQIMQRPx5Px/kk9UMx8gjs+buImUVcmJcDA1iXk1XYeD4b6SojhjfxRZ1gBZJytAj1dGBWVkdi87H7Zj4bu5ODEF1quKF+iBMkQh5yikzYdjkH5xJVD7mPKv4f0r3bKgA5KgNCvWSQCfnILDRg7ekM3M3RMRfhVuHOaF/TncWnI62TKN7d+SzE5esxqJE3FCIe5h5JZ1aLIW4SjGgVgAuJKqw5m8nqo0LroF6Qglk8ejqJUaAxYfWpDLSMcIXz/685cnkmqEplx6UcHLilhNpkxeT2AQyQkhWfPYPtP3Khl9OoHdTlnlgMs8EOr+2A0gZyaY7IHZbAmN0N9p8EUBVZ59Hrdku58mAbAb3SxZ49tqLx2ftQKrw/q84OMSuq41lbC1x/nm0FeAaTnkun82zPEdc7TgFOAU4BTgFOAU4BTgFOAU6BP61AXFI2pq4+CsGfAHWzdieiaVVnhPk4YOHhNObaGlHCok5dZETD/4+nNizGB2fjCpCQqUGYrxwNqrpg+dFUXEorwhtNfBkAmbotgYG6mn5yfNQ5GCuOp2HXDSWL+0aFAKGfkxgTXgqGWmfGsdhcBntiqrnis+3xzFKKXF9DPWQMYsWmqdG6hhuzmvpsVyL8nCUY3zEY3xxIxtlE1X2XUTuoG9MmABE+DriRWoQrSYVoHukKoVDAziXLrYmdQ/DD0VQculOA0c180aCKEw7dyENGvg4xEW6gbKULD6UgT23CxM5V4CYX4OjNPJa5tEMtTxar7LvDqdCUis1G7Xev6YoWUW44fTsf5xLViAl3QcsoN+ZSfCI2D9UDFQj1csuZSqIAACAASURBVMDnuxKZ1di7rf1x8f/YOw/wNqvrjb/a2/KQ5T3ikZDt7L1DJtCwoVDKKLRsaEsLZbR0/EuZZc9CoUALZYVAtrP3nnac4W3Zlrdl7fXnHFlBcZxgJw5Jyv14/NiW7nfvue/3SUE/v+ec0lZ8tqfxqD6kEUk1L8+E6f3jUNnkwuaiRozMieE0WmuLB5sONyErQYuBqQa8lF8BVxC4c1IKthxpRrnVgdQ4DYZlGbFwTz3v87I8E2YMiMPKggZ2hZHWJr0CL+ZXYlPptxqGgQ7Z++6dlIw0kwarChq4IcZFQ+Lx8Y46fLW3Eb8Yl4Tp/WNQbHViQxHtKwrpcWq8udaCfdUO/GxMAoZnG1k3a5MLQ7NjkBqrwgsrq/icyI66+m9cgH+6qBc7JZfsqmMgPKlfLHaW2fDSmmpMzTXi+tEJWH+4BRarAzqNHDMHx6O83oFnV1Zj5oBYTMqKwpNLKlBn92Jcph6/mJqGpxeXYW+14yiEpD2Q63NiThTmDTNj8a46LCtqwc8mpaB/so7vs52lLRiTEwPNN07CF1ZU4YDVib9dkokquw9vrbGAfFvnYk8JBnX7N6B+/esIcD1JcQgFhALnogKSd9c/Kl6h5+KVETEJBYQCQgGhgFBAKCAUEAoIBXpQgaZGPZZvjEVUxmhIulE3KtJR9/SScti9AdwxKRmHrE68s8mKgSk63N2e+urz+nH35BR4PH68u6WWXU1GtQzXDjdDp1XguaUVDFPMXQB1VAtuet8YXDksHq+tqMSWSjuS9QoGXAeq7ahrdePOKakwahV44JPDnG75o4FxuGxYPJ5bVg6JRIqHZp8Y1N0zLRUxOgWeXlKGkiYPZvWJxpUjE/DiqlCa5sNzM/Hq6irU2Tx4YEY6VhU2YklhE7sIKR30p+OSsN9ix5pvHFW/np0Ja4sbL62qQp3Dh+uGxWNUdhT+nl/Fj0e6bQgEZZvVuGVcEqfdHqhz4ubRCRjWKwoPfFYMm8vP8PKOyclYsN2KjRV2/Hp66klB3YQ+MfjjlyWotHlx8YBYXDPCjNdWWbD6SAsGJmvx0KwMfLy1FlZ3AD8bZcaHW63YW2WH3x+gHhlcx82oleMXE5M5nfcfm2oZNF01JB7zhsbjheUVx4E6ctNRY407p6Vh0f5GfL23gVOEL7wghlNq1x1pwS2jEzEsU49XVlmw12JHH7OGaxd+vaue1//tnAxsLWnlLq90jtmg4FqIDS1u/H21BRrKz20/CNQ9PjcTO4qb8cYmK2LUMtw8NglJMSrc/d8j3HAjK16N5QeaoFfJEatX4Oph8exu+9uScq5pePe0NHy2pYYbolwz3Iz+qTr839dlsHuOTSn2fOPM7Juow29npfO9tL3Sjt/PzeQ5XlxRwQ1SqIHKdWOS8Ob6anZdPnkegDqPsw21BRtg2/auAHU9+N4qphIK9LQCkqtfThSgrqdVFfMJBYQCQgGhgFBAKCAUEAoIBc4pBQLwutLRUn0jEnInnTKoe2ZJOYob3ZiUa8TVIxLw8qpKOPzAr6akcI26YCCAx2ZnQCWXwu7yHXUVERDjRhTzS3DZkHiYjd/tqKMaZ9ePScTQFC3+8FUZ18Sjwx0A5BIgyaDA7d80saDaaX/6uozdZWOzo3Dr+CRuXkCZfb87Cai7d3oaN7Z4YXkl1zkblq7DrRNT8NraajhcPjwyNxMvr65C0B/A7ZNTOeUxQHY9SXsziygV9lTaOA2YGlMUVjs4RbLNG8DMvjGYMzAOz+VXwtKh3hrBy9wEDW4am4h/rq/GAasLN44ys/ONGnKoJGCXIIHEVfvrseSwDb85Cai7dIgJ/VP0+ONXpVz7beoF0QxDH/miFJZmN/okaPDg7Ax8trUWO6sd+MWEJHYD0n4szR6uOUiNPsjl+PMJyfhyuxXrv2meQMfgFD0emJ2OlzoBdQTlpmQZcO24ZG6wQCCO6rzR43T4qEbduCT0TdbihRWVvFZqtAp3TU3BioJGFNc68as5GazB1vI2SKjwfxC4cXwyekXJ8ejCilB34QhQ98isDKzY34Cv9jdxQw9Ko+6XasCN/ypCr2gl5g6IxYAkLTcQoRRWgnV1rV48vbSc4yFNW5w+fLrdilsnJuNItR3/2l7PNQ0jHXB0bt8kLQNagpTbKtrw2EWZnHb8yopKrk03IEmDX0xOwTubarH2cCueOk9AXf2BjZCVLIPE5zmn3qFEMEIBocC3Ckh++nquAHXijhAKCAWEAkIBoYBQQCggFBAK/E8rEIDbmYD6qutgzpl42qCOqMY9U1OQFKXEor0NuHJ4PB5aUMYE688XZ+BIjQMVVnu7kyzUW9PrBzZV2PHjkQnHgLoByTo83EnqK4E6cq0NStDgsa/K4PGFXE/EgahWVNh9ZXMH8NfF5ZxuSKCO6rl1CdRdmMaOspdWVDGoG56ux88mJh8H6qgRwW3jk7BkTz2cTu+3HSURREWzB5ZWH34zJwP7LHZ8sKmWHYdUo2/2gG6AutFmblDx6IJSKKhrbjuoW7m/Hku7AOqoZtvfFlcwjJpyQTR+MjoRj84v5XTYC8Kgblst5u9rQrpRibwkDQZnGdEnSceAc8m+BqwvtuH2SclYtLMO+UdaGZD1T9biwTmZJwR103OicNXoRE6N3V/j4Lpy7ZyO6wWGm0m8SHCrxYPUmBCoy9/fiFKrE7+anYG3qP5dRagjsNMfxE/GJqG/SYnffVUOpSQS1CnwyKx0LN/XgEWFTaDOvdeONKNfigE3vl+Eu8ckYMIFsVi624o2pw9FjR5cOszMTUfICUpOx6vz4jCqdyy+2FaLi/NMXN9uj+XbtNfwW0DnoK4XqIzdqysrYbUTqNPi55OSzztQR6mvDWtfgS+imcT/9FvfaW6uY6dYUYvuNAUVp3dJAcmNr/cWoK5LUolBQgGhgFBAKCAUEAoIBYQCQoHzVQE/3E4z6qquP21QV9LoZnoSrZLh9z/qhVaHj91YD3xRgoAvgF9NT0VpgwtvbaxBMABuZpBiVHJn0NoWD7u90uLUePjzYu6YOSbLgHump+HdDjXqKBVy7uA4XNQ/lsEb1QHTKqTIjFXD4fFz04S7pqTC5g3gr4vODKh7ZXUVbE4f7p+exk0ClhxoOtqpNiNWDa83wI67B+dmchrs+90Ede+sq0aB1YlbxiScFqjLjtfgiSXfDeo2lLVxw4hCqv/GXWEV3DQhxaTB80vL8dOxSdhb3oqPdjXwjT6rbwzD0s5SXwlmDSJYNSUVn+2o45RTgnvUXIIaMxyoc+GWMYnc9bUjqFuxvwm7Ktrw4NwMrChswqKCRoaMMTo5bpuYArfLi6dXWKBur1dIseh1JwF1Hx7E32amMej787JKqKWARinDI3MyoJFL8OzSCtTYvOhr1uAXU1I4vVenlOCvyypBucwd+31Ggrrnw466ub2gkJ3/oM5auBG+gvkIet3n65vZ9x63z+eD2+0GdcXtrCnF9x5QFxYMN9mgoZE/d+FUMeQcUECAunPgIogQhAJCAaGAUEAoIBQQCggFhAJnVoGeBXVU5J9SHMf1isKN4xI51fDOjw/D4fDhwn4xuHhQHNduO1jrQEKUErMGxuGI1Yk311VjzoBYXDTYhI+21MLp9WNMlpG7jP5zfYdmEoEgskxq3H9hGkrrnFh1sBkExy4eYsLnO+ux7lAzd2Y9k6COmklsKbVx3T2CYYv21qOyyY0cs4a7gC7c14jdZa34zZzugbocsxq3TUzG2qIm7KywY0qfaGSaT91R1xVQ9+nWWtS6Arh5jBmrDzTjQI0dOrUcs/vHgtyLzy+vxGVDTBjeKwofb7FCIgliWt9Y5CRoOwV15Jyjrrn3Tk6GWiXDkv0NoLp1lw6JR2mDG6+uq8ZNIxM6BXUrC5oYet4+IQnpcRosLWhAk93H9wHVPPxoqxUbS2zHdLg9Kaj74CAempzEDTiogys58aiBxvBMA9cUfG5JOQgwByUS/H5WGjLMWqwpasS7m6zHdbKl1yGBut5mDdcp/HKnFfkHW3DH5BQee7476gjU+Q98CXhF6mt33nMJdhGwczgcDOxOdNA4v9/PcCzyICcedYgNd4ntztqnMpaAolKpRHR0NKxWej1Teve3SPpkccpksmPGnsr64pzTU0CAutPTT5wtFBAKCAWEAkIBoYBQQCggFDgPFDg9UNcvQctF/p9dWo4jDW7uxkkf9JQKKX4+PgnDexlx+38Ogbq+RmnlmDcoFuNyY8jKwUCvoKoNn2yvQ22bD6lGJadm5iZq0er0ciH+Swab8K8N1Vx7LNz1leandSbnGjF7kAl6lYybHuwqa+WuoiqZFFRnzubx489fl3Hq5PhcI24em4gXV1TBEwzid+1dXyM7ltLnZ0qb/OXMdAZLzy+rQJPLj5EZBvx8cjJeXm2Bw+XHoxdl4PU1FqwqakaSUYmbRicgO1HLzRcIbK0vamYnGLm+HrkkC/uq2vDehlCNujn9YzFnYCyeWV6JqkZXhw/IQJxezt1vKWWVOta2uv3INmvx0PwSTn0l8Hb31FSsLmjA4kOteHBGGnaUtuKTXQ3HdX2lZhsEqP6ysIxdadP6xeCG9hp15Y0u9E3UcPfbL7ZbsfRgC67Mi+MOt8FAkNNUyxpc+GSbFYfqXXxtrh1lxgWJOnYSWlo8GJSux0vLK7GxY9dXhNKQ+5jVuGq4mbu1SiHBYasT/9lai6I6F26fmITeBPpWVKK62YO0GBVfsxUFoTpz6TFKXDLIhAGpek7BpaYOC/c2YPXBZu7eG1k3zqBX4PdzMrBsb32oRp1SiutHJ6J/qh7X/fMAJmbocTWlVRsU8PuDOFTjgM3tBzXaeG5JGXZbHFy38CfDTZjWP46h8bbSVq6r1/GgbsRapQx/vCQT0Vo5g8tROdGg3hbUPZfu48FJWvxiaire2lCDNYdb8Ny8XtzM4/XV527XV2omwaCu8EtA1Kg7pfdtgnRtbW0M4zoe9J6lUqmQmpoKrVZ79GkCZB6PB+Xl5Qz6wsCMxofdbqeSUksw7kTgj+KjGBITE1FcXMzjIteln/v06QOFQnHMNlwuF4+PdA6G46Q5ImOOjD0STJ5sL5FzhRf+Lh1OtD7FSM+FAej/knNQgLpTenmKk4QCQgGhgFBAKCAUEAoIBYQC55MCpw7qyBdCEMWgkKKFSEfEQc8ppIBOIUWzO8AphFxDDkCUUgKq70bupFZPyF1CNeYIjlE6rFEpZeBl9wURp5KyM476RURyEzrLHwR0cgm0MgloGoqBoBzNpVdI2DFlpyckoSYTFCfNRXFEq6Ro9QS4SUFHHKOXSzhOWj9yjwTaaM5opRQ2TwDeQGg/dFDMVKfM5Q/C5g0ejcOglHANPno8rIlW9m0cHfdEc6lkgFYe0oDAkFwaWo/Gkt56hRTOb7rP0vqJOjnc/gDqHX6Gl5EHzUNOrzZvSHiljPSSotkT4FhoOO2F9uVuZwsUL10bgmGkFWnM17H9mmikIV1GZRlxy/gk/HFBKY7UOY9bm+IIn0u6UwB0rX304RkSqOWAUhpamzSlEbQvql9H+6J9SyCBUSXlPTt9dD+Erm/HD/u0a71SApcvyMCNftfIKW4Jmt2hK0SQl+4J2hftn+aMUUvR4g7wfUj7n9M/BhP6RDPMbbB5TugcovuH4ictKX5qJEFrks6sKwDS0eENxWNQfHs/HY/+zo33ihCo2wB/4QIB6k7xkhAMItjmdDo7nSEzMxMmkwk2m+0YMEbQjM45fPjwUUce3ePkXiP4912griOEIkhFUDDs7ut4/slAHZ0zePBg6PV6tLa2HrMPnU6H5uZmFBYWsiMvDMIi45TL5QwqNRoNa0Gx0Pr0OLkO6YiMN1znj//4IpMxWKNxkWNOdC7/uyGV8tyUfkw/0xx0PsVPMba0tPDv9HN43s5iOMVLflZOE6DurMguFhUKCAWEAkIBoYBQQCggFBAKfJ8KnDqoC33gCcGqDoyIHwtneBGcCAOpyMfp/MjnIucLP0fjO46JVCfcoCByrsg1wnGFH2NQQt1ZCdBFNCTobM6Tnhu5p3YNwnNEzkvxHbP/9rEn21NY08iYwuO/3UcQGpUMPxlp5np4r2+sharDReh4bY77vf0adZz76D5CH6thNii5mYTb68fbm61c2+3qYWbE6uR45MtS+HyhD+MdD0ZkEdp0qkP7NQjH1tmYznSNXOtk5x69hh3iCN8DFKBOJUO0ToFbxyZyjb6Pt1r5BjkZIIm87zrG1zGe8NiOr5Hv81X+XWt5HDY0HNwMafFSuGwt3zVcPN+JAgSXCHQRiOuY3krDc3NzGVzV1dUdA+oIgJnNZgZgBJwIdGVkZGDQoEFYunQpwydytxH4UqvVPIaOSCgWrpNHz5ND78orr8SmTZtQVlZ2XB26k4E6mmfixImorq5GY2Mjrx16Xw5yqmxsbCw2bNjAjjza6+jRozn2BQsWgEDkpEmTsH79eiQnJ2Pnzp18Hu0lOzsby5Yt4/noi8BkOA047HobNWoUDAYDNm7cyDrR81FRUZg+fTo/VlpaygAunGZMz9O8M2fOxKuvvsrPXXTRRdi9ezemTJnCc5DDceHChZg6dSpWrlyJhoYG1o00p+ft9nBjo/Pnlhag7vy5ViJSoYBQQCggFBAKCAWEAkIBocApKnB6oO4UFxWnnaYCITcLEK9XIhAIwtrmOw6WnuYSRz+gk8txYo4Rc/NMbIsk/5jD68d/tlqxs9LOzrXz9SAX57gcIy7Ni2MH4GurLSiud3Van+583WNX4iZQ5yrbgSRnIQr2hgDLdzm5ujLvD20MQSRycZ0M1DU1NR0D6giukdPuwIEDDOFojqysLAwZMoRTTYcNG8aP7du3D+np6di1axe7x3r37s0wjQAgAaj9+/cztKL5BwwYwA695cuXcx26yDTYk4E6gnzjx49HbW0t7yMS1BFEI1hH0IxAHcVKYI6A4o4dO5CQkIBevXoxGKNxBPJGjBjBwI3mpcfHjRvHMO7QoUPYvHkzzz906FBccMEFDOUIYtJzlHpLII0cfBQPQT/6GjlyJGu3aNEifo7O+9GPfoSnnnqK5yVASfqQnqQH/b5kyRIMHz4cixcv5n2NGTMGffv2RUlJCUPF8+0+F6Duh/auIvYrFBAKCAWEAkIBoYBQQCjwA1RAgLrz9aJzfaajjsMzA8vCqb3E4mI0ckQppZw63Oz2o8UZypftxEx33khKGpKjLl4r49TcRofvO910583muhEogTrrgU3wFc4/2kzifAMY3djuGRv6XaCO7jeCa5E14ToDdQS88vLyGIaRU6yoqIihFEE3glDkFCMQNmvWLFRWVnK9uY8++ojP+eCDD3DVVVdh1apV/FzHWnNdAXW0DoGwSFBHIM1oNB4D6iZMmMDwraKigkEZjfn666/Rv39/jpPirqqqYsBGjkCCjjQ3jb3nnnsY7N1www14//332clHTjcCbQTW+vXrhzVr1jAApO8UD4FIevzNN99ktyD9fPHFF+OZZ57hOa+44gps27YNF154Iafu1tfXM4wjnQju1dTU4KGHHmKw+NVXX7G231cTj5666QSo6yklxTxCAaGAUEAoIBQQCggFhAJCgXNWgVMHdaEUv/a6XNQ5MGKPYYgUrtl1sg/9fi6cHkqfpVm+T/BDcRJ44rU7dj48SzGdq7dKuMYgw7l2QHdm8OD3q0B4X7SX89gceFqieZ1tqC3cCG/BfEj9J+5celqL/I+fTO8lBNYonfJkjrrOQF18fPwxjrowqCMYR0CKYBfBJ4JO11xzDTvPKAX1uuuuY9ccQSlyoKWlpeHtt9/GL3/5S071pBRWAnWR721dAXXkPIsEdTQ3QbqYmJijqa/kkiO4RkCO4CC54GbPns3PE6gj1x255ggqjh07liEcgTx6jDQgB2EYrn344Yeg1FdKnyVwSUCN0mfJUUjarFixgtNXaR+UfvvJJ58whKTmHAQlX3vtNa6LRz+T449AH42ldfLz8zFv3jxOzyXnIbkSyelH4//9738zjDyfoLQAdf/jbyRie0IBoYBQQCggFBAKCAWEAkIB4NRBHakXb1AgRqfAwRrHUXcXPU74jjp5qhUyHLQ6ucB+Zwc1TOgdr4ZRp0BpvQvNDm+n3TZ7+kpRA4E2f5A7hPZP1MLS5IbV7oWKuhcC0KpkyDWrYWn2oN5GBd17OgIxn1Dg3FEg3PXVVzAfEgHqTunCEJwjKBWuIddxEkpnJVjVMfWVHiNYdPDgQXbJhWvUEeyi38mBRsCNUkDJBXb11VczRCPnGrnRCJhR/TaCUlQPjpx11157LQMvgmYE9bqa+krrkestnHYaCbAIqtHj5HijucM16sjNR2mlBAkpRqqNRzCMACHFQ/slbfbu3Ytp06Zxh1tKO6VactTkgVxy5Gyj+Um/cNo1zbtu3TokJSVx6i81yCAoSACQwB7BRIrn8ssvZ4BIde9Ie1qHgB/FSam55OSjeCiVl7Sk+amuHmlOgJFq1glQd0q3vDhJKCAUEAoIBYQCQgGhgFBAKCAUODMKnDqoI3g1vU80RmYb8cTCMvio42Y70KJOnj8ZEY+kGDWeWFoBeSfBU2fP3HgNdw9tdfrR4vLh/c21nFJ5Jp1NXn8QIzIMGN83hhsjZMaoYLV5sWhfI7aVtnKH0WuGmdAvWYd3NtSgqsl9Xn2QOzP3iZj1f1mBMKjzF34pur6e4oUmSBQGTR2nIDhEMIpgFjm5IlNfCXhR6ijBt/BBkIvAFB3hGm8E9Mg5R0CL5iMAFhcXx18ul4vdYuFOp1Qjjhxw9BgBrK466gh8EQjLycnhuSIPWoMcbgS+CPxRDDSWQBc10KCYKUZyFNLPFDelrdKcBMloDLnj6Bz6mdJS6aDf6XEaT+MoVoqfACRpQnoRGKTnCNTR4wQfad5wvATewmnFpCdpR2uQ5mG96Xu4Ey7FTPPR/CL19RRveHGaUEAoIBQQCggFhAJCAaGAUEAocKYUOD1QN7NfDMZkR+OPC0oY1HkCQbgDQWjlEtwyJhEpsWo8+lUpPL4gu+rocZlUwqmuOqUUl+fFQaGQ4p1tdbh3XCJ2l9uw9FArZBLA4QtCKQUX+XcHAIWEzpcehYH0uMMbYAecWiaBNwgGgir5ie1vNNbuDWBchh5XDTNBLpPCHK1Gk92LL3fVY+GBZnbZ/WJsAtaU2LCu2Max0Lp0OH0Bbp5Aq7r8AC1Fz4XBIqVR2n0BTqfVyAFfQML7Vsk6T+n1BoIMBgls0lwaWUgfOmj/tDbF7PKTFhLeZ2QnU9LbFQilDtNz1Pn1aIdd0s0fhJsaAwDQSCXcJIGep/F0nWheOkjn0NzCOnimXmnn8rzfgroFgC/UVVQcXVOAABHBIwJUBI5OdNBzBPM6jiFQRGDpVIBRxxTbjun7nTnFTpb6SrHTnATlIuOkx8iB1t04I+OjWDr+Hl4vrFlnYzpLI+64r87mDc/Z2fmR63XtKp87o0Tq67lzLUQkQgGhgFBAKCAUEAoIBYQCQoEzpEDPgTq/BJiSbUS/RA3e2VKHK/JMSDOpseZAE8Zk6uHyBfF1YTOKah0heCWXYnCqDhN6GaCUS3GozoWVR1phbfHArJdj3qA4HGl0I9mgRK84JXc2XVzYjLJGN6SSIPomajGrbzSDsy0VdvQxqXGkwYWlB5oZdnVETgSnNCopJmUbMSRFiyaHD4ca3ZgzyIRPt9ZiY4UdNw8zoaDGgUWHWhGlkGBarhGDUnR4Z2MtOz3mDYpFnd3HkDEnXo0Wlx8L9jehrN7FsC03Xo2L+8dCq5Qy6MuNU6G21YvlRc3HOA4pFqrNNzzTgAtzo6CUSdHq9iO/qAUHah3w+IO4ZXQC6uxeUNfV/gkaVLR4sKSwmecjfKdSyjC1txGDEjWQySQoqHEi/2ALbE4f3ytGrRyTcowYkKSFy+vHljI7NpXa4PPTuVJM72PE4CQtj61s8WL5wWZUNLp/cB1Pz9AL67yalkBdbeEGuPd8iqDXc17FfjaDJehFLi0CdefLEeoYLWXHHAG58ynt83zR+EzGKUDdmVRXzC0UEAoIBYQCQgGhgFBAKCAUOCcU6BlQ9+j8EozPNmDWgDjkH2jGioPNuGlUAkZkRaHZ7sWeKjt6J2rZ8fVUfgVsTj/m9I/F9L4xOFTr4NTTASk6blPwwsoqdpfdPTUVMTo517+rtXkxPteIigYnnltRhaQoJe6cnAK3L4CiGgdyzRqkxqqxoqgZ722sCTnHOuhLZrFLB8dhXG401hxqgVEjQ98kHeL0Cry/oQY7qx148MI0bC1pwb+310OvlOLKYfGYkBuNxz4/AolUijumpCAhSsFr1rR6MC4nGtZWN55aVgmtUoaHZqaBUmv3VrWhT6IWSdEqbC5uxfubavnxsGGNnHTD0vW4YXQCCqudqG31IC1WxXX93t1Yg70WB564LBvRGhnKGpwobXBhVK8ohpz/2mxFm9uP60aaMSRNj53lbfD6AxiabsARqxPvbamFTCLBlUNNGJYZhc1HWhGlkbH+b6+rxv4aB0PQMdlGbCuzscuFdAj4A3g6vwo+37dxnhO3qAjijCtAzSSqCzagccNbCHhP7Ao744GcZwuczK11rm8lXAvuXI9TxHesAgLUiTtCKCAUEAoIBYQCQgGhgFBAKPA/rwCBugTUVV0Hc85EhlFdPQg6UerryCwj/rOpBjeOT8a6Q81YvL+R01AJ1A3rZcAvF5TB3ebBoDQDfjY2ER9vrsHuWid+e2EaCqva8MH2ekgQxAUJWtw1NRVbSlvx5Z4G/Hp6Krvu7vu8GEF/EDePScTorCg8uagMQ3pFYUJWFJ5dXskNHyZmG3Db5FSuM/evTceDOkpFTYtW4vbJKVh9sAmLCpogl0kws38sLs+Lx/sbQ6COYtpa3IL/7AiBuiuGxmN872j8oR3U3T4lGXF6JW776DBkvgCuHBqPGf1j8fTScvRN1mFu/1g8yDdxhAAAIABJREFUsbgCpQ1OjEjX454L07DqQBM+2Gw9BtRRyundE5PQL0WPp5dVoNDqhFYhhVolR8Dnh8sbwBOXZnGO6qtrLChvdGN8thFXj4jH3/KrEKeQ4MZxSXhuUy32lNg45XdQmg4/G5WAT7bWosrmw/3TUrHpSDO+2NOIaLUcVw0xobrVjS/2N+HRGWkg390zK6oY+unVMtba6/ZzWqzIgO3qq+B/Y1wY1DWsfwMBevGKQyggFDgnFZDc8FqOeIWek5dGBCUUEAoIBYQCQgGhgFBAKCAU6CkF/PA441FnuQEJOZO6Depm9I3BrIFxnD7V2ObBSyurUNdGXVIluGl0AjLjNXh4QSlkwSCy4zW4a0oq8vfWYUONC7+fkYq31lVjb6Wda6MFJMDDM9MRlErw5rpq3Dc1BTXNbjy5vBIKKXDJIBMuGxqP11ZUYHTvGEj8ATyZX8UNIRL1CjwwKx27Ku3sSOvoqKMur6PS9bhmdCLeWGvBwRonqJlFVrwG905LxRc76roE6shR5/YH8Lv5JdDIpJiQY8TN45Pw1poqDM8yQi+X4tGFZfw9SiXFb2dn4Eid8zhHHaW2XtjHiOvHJqHB5kFVvRO7qx3IP2KDLBCELxjEX+dl4YjVgf9stbJzUKOW45FZafh4VwPSdTLMzotHqdUBX7sDSqmQoleCFot212NPjQt3TknGW2stKKh2cqpsuOadWi7Fj4fHY0r/WJTW2lHX4sG60jZOnQ0GAqJOXU+9tM6jeQSoO48ulgj1B62A5L4PRwtQ141bgKz1/gCVlRVW4W7IJoYKBYQCQgGhgFBAKCAUEAqcVQX8cNhNKD8yD/HZ3XfUEai7JC8eG4tbMDBFh0V7G7DqYAv/HzGBuuQYNf64qAxSAnXmEKhbvqcOm2rdeGx6Cp7Nr0J5A9VJouYJATw8Iw16nQKvrrbgvikpKK5z4qXVFlAvhzCoe2NlJcb0iYHf48NTKy3QyiQw6eR4YFYG9lZ1Duoo1XR8pgFXjEzAq6urcMRKNeWCyIhV477pafhyZ9dA3Z1TU9Ds9OHPi8o5jXdSrpGdbf9Ya8GobCM3ZXh8YTl0cinXsXtgZjrKGl3HgTpyrZF5cVyOkdNX02LUMGplsDS68enOOuyotOOvl2ahqNqO/26vg8cXgE4jxwPTU7lOXaZBjskDTCistrP7jg768EbpbDtLW9HiCeC28Ul4cWUVShvcnAYcarsBrg9IKcWUtpsTr0Evk5obcFCK8dsba9Fo93LqrDh+OAoIUPfDudZip+e3ApK/fHGtAHXduIbBoB8JsRnQqaPa/5nsxsliqFBAKCAUEAoIBYQCQgGhgFDgLClQ36jE0rWxiMoY021HHaW+js+NxiPzS3DdsHh2dJGrrsHuw81jErjr6+MLjwd166uceHRmKj7ZVoc1R1q4IQTVePvdrHQ0u/x4e2MNfj0ttVNQ9+LyCgzPNiJJJ8cfl1SAWqxmRivxmzmZ2FzSekJHXV6yFjeMT8YHm2qwo7yNYWK/JB3umpKCT7dZscNi59TXHaWteH9bHXd/vXaEGaNzvk19JVDX4vThTx1A3asrK5GXYUCOSYMH55dwTCatHA9fnIl9lXZ8sPnYGnV0qdONCkilEpQ0e5AQpYJaJ8ctw+NR2ejCG+tr8cdLMmFpdOHdTTWwuwNIi1Ozy/DVDbXoG63A1AFxeH5lFUqsTsglEm46kRmjRL3diyidEndOScGHm2qwrbyNm2sk6uWcznuowY2cWBUaXH44PAGYjCpkmdW4YrAJqwsa8fHuBu4wK44fjgI9CerCddu62qQgcnxXOnz+cK6K2KlQ4HgFJOOuSxagrot3Br2hHGxtwtf/twSDLhiKYPtfq7p4uhgmFBAKCAWEAkIBoYBQQCggFDhrCpRWNOIP/1oPWdIg7gbY1SNco25MdjQeX1CCBKMSd09OwZaSFry/rR53TkjqFNTl76nH0sOtXINOGgzg1bXVqGrz4YqBsbhiuBkfbbVic6kNv74wrVNQRzXqkk0aXD/CjLfXWrCiuBU3DDPhkiFmLN7XiPdOUKMuRivDfVNTYff48auvyhGnluH2sQkYkxON99ZXY0OpDfdPS4H0mxptjy+pQLZJjfumJEOlkOHxL4oZYp4I1D23rALROjlum5CMd9ZXY0FhM64bEoerRiQgv7ARH0bUqKMPWQQJ756YiCyzDi+uqsLmSjui1TL8eU466m1evLquBn+6JJNdefT8jioH7p2QiP6pevxlcTmnEj82NxOHrQ68ur4WFpsX1wyOwyV5JvxnYzUK6lysb0ObF39eVoUkgwL3T06Cyw/8ZUk5/jArjbvQPr3KwueOStPh/qkp2FjUjA921EMlE6Cuq6+D/4VxJwJ1bW1t3B2Uvrpy0OdiOkcmk0Gj0XxnR9FAIAC73Q6dTsdjqQspnWuz2dDQ0ACDwQCz2Qy3280xyOVUjVEcQoEfrgKS0VcLUNfVyx8MBlDUUo/8p9dh6IBRXT1NjBMKCAWEAkIBoYBQQCggFBAKnHUFDpXV4JF3V0KWOLD7oK5vDEbnGPGnBaVkIsPFg+MwrW8M7v28BDfkmZAcq+I0UUl7jTrq1Jq/tx7zC5oxLsuAy4aaYVBJ4Q8Eee391Xa8udaCeJ2CHWHF9U68vLr6aOrrpUPj8dySMlS1enHX1BRkxKjg8vgZQBk1cqw93HLCrq/0x3RqyDBvSDzkEvpNAoc3gFidAh9trsHiA824dEg85uXFwe0Juc1sbj8SjSoGdZBKuNNsi9t/NPV1Yg6lvibipRWV3Kn1wdkZyIwNxeT2B6FWyrCzzHaco472m2xU4p7pqRy31+PnDg6tbj/+u41SX9s49VWvknE3Vq65J5Vgyb4GLC1o4npzc/vH4KLB8ZAggICfcmkl2EFrba3jJhTTL4jB7EFxkARCXVxJo7fXWbDP4sC47ChcOdzMqboBel4mRWWzG2+urkKT0y/q1J31V+X3GwCBOkvBBjSse52bSRBwo6+ZM2eisrISe/fuZUhGr1GCa/RcGOqHXXD0u8/nQ15eHo/ZvXv3UbBGv9NBMI6+wvNrtVpMmjQJq1evZsA3fPhw1NTUYOLEiYiPj0djYyPee+89TJ06FQUFBaitreV1CeaF5+iqc+/7VVSsJhQ4MwpIxl6bIhx1XdQ2EAyguLUeC/+2BsMGjO7iWWKYUEAoIBQQCggFhAJCAaGAUODsK0Cg7uF3V0LeTVBHkafFqpEYrcS24lZQwwaCXgPS9KhrdiEokUCvkWNbqY1BnVErx4BUPSz1ThxpcDMMSo1RIjdJxxCqodWDQoud67HplTL0T9PD5vRx3Tnyd2WZ1Mgwa7Cv3MZQMFmvQFSMmiGWy+HFjeOSsbywEZ/sqDuumQTFykBBIuFaeZnxWri8fk4tTYxRoaLOibJGNzemGJhuQLROgepmN1xuP5Jj1dhe3EKYAf3TdNy9dVuJDWQ6S45WoU+yDvsr2uDzB5Cok8MQo4ZWIYO1yYVbJyZjS3Er/rvdCn/g2G6qpJfZoMAFKXqolVJ4vUEcrG6DpcUD4m4E6oqtTuytsSNKq4C1yY2iGjt89GQ79MgyazglllJorS1uFFU74CWrHMBdbbPNWqTEqfmxklonKptdXMyO4EaGSY1Ms4avA+m8v9KONpeP02TF8cNSwOOwofHQFkTVroccAVgsFmRmZjIgI3CWn5+PuLg4hmf0nN/v598JtBHEU6lU6Nu3L6qrq+HxeBioRUdHIysrC16vF9u2bUN2djZiY2P53J07dzKYi4qKwo9//GN88MEHaG5uxpw5cxgMjhkzBlu3buUYaBy56tavX4/Dhw8jIyOD1yIn3v79++FwOL7TuffDuppit//LCghQ142rS38hKLYJUNcNycRQoYBQQCggFBAKCAWEAkKBc0SBUwV1xL24lVoQXCONXFvUSdUXBEMsep6QklwSAkPh5+h3gkOh54No74XA59BX2HFD81Aibhgc+YNBhl30+7UjzegTr8EzKypxuMmDqwbE4JaJyXh1RSU2lNgY1HV2cMztMVK8MmoI1x5jKKZQ/LSnUCxgaKbg5gqh5+in8Pw8V4AaQ0jw4xHxyEvV44llFdhtdePyvtHs+qO02hUHW/i8jj0awrEwQ+R56bsEXur6emk2iqrb8OE2K9ze4DH6hMEjxUkx0RHWjxbhaEmvYCh+3ivp3g74wteunemRGS+0X/pPcLpz5JX5/YXhdtgQrN6L3goLjDoVwzWr1Yo+ffowfCOIRqCN4FhSUhKnqJaUlDCgo+cI4FF66qpVq9hRR6mr5I4jsGY0GjmNNTc3l8fQuQTjFi1ahJSUFFxzzTX497//jaamJsyaNYufI5cdfVcoFCgtLeU4CNQVFRXh+uuvZ+C3cOFCPofAoHDVfX/3iljp7CogQF039BegrhtiiaFCAaGAUEAoIBQQCggFhALnlAKnCurO1iaogyulbt48Pgk+bwBurx9RWiVK6hz4+4oqbrzwfcMmimlomh53T0uF1+uH0x2AUa+ApcmNvy+vQIPD1+V0UuJuNN8T87LYQfdxe9dXASNO/44jQEkHeQ7D1Ri/73vl9HfR8zOQo85Ruh0ay3pIAl6GZ4899hiuuuoqlJWVsaON3G30M6WdqtVqfPrpp0hNTeUvcsklJycfhXcE52j8O++8w7XlKJWV6s199tln/Di54t566y2Gd1dccQWntxLEmzdvHg4ePMjAjmrcHTp0CK+88gruv/9+rFmzBgcOHMDQoUMxY8YMhnYE75xOZ7dS9ntePTGjUOD7U0CAum5oLUBdN8QSQ4UCQgGhgFBAKCAUEAoIBc4pBc43UBeGLXlpOgxIM3CKJ6WwrjnUAofbf1ZSN8NwbUiqDoPTDVAppAzp1hxsRpurezFxs4kA8KMhJtS2uLlDLaW7CqB0+i8bTpk2KtA/UYuiWgfKmjxn5X6hndB97KNacO1uSOlZdDMSqKsr2gR58WKMHDqUU1KpJhw53qjuHLng6LFNmzYxUBs9ejRDsoSEBAZ0lP46bNgwpKWloaKiAvX19eyoo8fpPIJpBOi++OIL9OrVi8/75z//yfPPnTuXQR+dN2TIEJ53xIgR2LJlC7v4aG1y8dHz5O6juWjNsWPHYv78+QwHRZOJ039tiBnODwUEqOvGdRKgrhtiiaFCAaGAUEAoIBQQCggFhALnlALnG6iLhByeQAh0KCSAQirpsmvtTFwAioOaRLjbY6J0YGrWQCm13T1oLk87nKO021OYortL/iDGK2QS/HiUmZuV/GNDDerbvJCdBXEJ0hHMHZOp59qOR+pdqG71csry2TgI1LUc2Yokxz54HTaGYgTTWltb0a9fP05hpd+pLh3BspaWFh5DrjeqRUepqPQ8Oe6oZhzVsSMIRymrBNoIvg0cOBD79u1DTEwM9Ho9N5ug1Fk6n2rhEawrLi7mOchpR2sSgKN6dAQHCc5RSi6BOjqfauft2rWLzxNu07Nx14g1z4YCAtR1Q3UB6rohlhgqFBAKCAWEAkIBoYBQQChwTilwOqCOYFKjNwCtVAKDkjxB3x7U9bSFuqoqpSesGdddIQhwEJxr9gYQJZdAQ0XdIg563uUPwOEPIlop47pr33VQnE3eAOKUUoZ9NAfFTbXfYhSSs+a4orgpFoc/gCZvEAZZO7ALBhGlpOp6PX9Qyi3tPUouhbKDeE5fAK2+IF9P0qmzg+Jt8wVg8wWhl0mgV0i5/l1PH+SMa/MGuJZglPL4NQh+NXoCMETcIwQ/6fGBZjWKW71wRjgdqUGIMxCEXn768VJtQJs3yLUPjYrO4THppJRLMDFDh15mLTRqBd7dVIMWl5+78NL9rZFKoFUce3/3tI7h+TzONtQUrEfd6pcQ8MuPWYY+63bs9hru3hq6R4Pc5ZWOcCfY8AQE0eixMEjrDKiFzw93kqXx9HO4VmXHNcKP07jIuc+UNmJeocC5pIAAdd24GgLUdUMsMVQoIBQQCggFhAJCAaGAUOCcUuBUQR01d7ggQYu7pqSgstmNJ5ZUcHdXcpBRk4TeSTrcPSkZD35ZCofD1yOuMPoA3zdZh1vHJ2FFYRO+2NNwtJEFiUpMaHIfI6ZeEIsXl1egus13UlhHgGZirhE3jU/Gs4tLsa/Gyam0t09IgsmgxKtrLKhrPTvF6kPgQoJ5Q0yYMyAOBVVtsLn8IFfYU/lVDMF68iCINShZy1q8tb4aBVX2o5DS7Q/gssEmzBoUhxeWV+JAjeM4gEnxKmRSXD3SjDFZUThgseO9TbVocfr4yvSUcY3daHIJfjo2EaZvOv8+u6wCLu+3qcF076VGq/CrmWlYsq8RC/Y2MFiUy6S4ZUwChmRGYVtpK/65sfZoB91RGXqMzY3G22staHEHTgsuOn1B3DslGVEaOddM9IU7dnS4WLQPcl/+ZLgJvZP0eGONBbWtHsTqFbh9UjKKqu34cFs91NR95QwfXmcbqgs2oGH9Gwh42wv5neE1xfRCAaFA9xUQoK4bmglQ1w2xxFChgFBAKCAUEAoIBYQCQoFzSoHTBXV3TklBjE6Bt9ZUYfWhUHdT+qjfO1GHuyaHQJ3TQbAm5GjyBKmDqYQBGjmi2MVGHVUD9PO3HWHJ3UU+nfA4SiPlOYLApN7RyEvS4PUNtfB4Q80j3H6AjGaJUUokRCtx0OKA29d5bTeKgyAJdZGd0ceImyck45nFZdhT7eAuqXE6Oa4fYcb28jasK25lGEgOs3Bqq1Iq4fpiNJZ+Dne9PbrHQAhY0n6oqy19P1GKZbhWGTkFSTuaj8aSJgSirh0Wj6IGF3rFqBhA/XNrHYosdu4QS3OTPhQHxUNpsrRW2LlEMNXlD3LjBNKZxpOO4U66kTciu82StLhpQjL+sa4aBRZ7SNcA1cwL4sq8EKij5hh7LA5+TkV7b7fM0T7yUrUYn23EgqJmXDEgFrsq2rCiqIXvB7qe4YO62tJptNdwbTYCbJ4A7SUIJe8/dHR09oVB3Q1jQqDuqaUVaPX4WTOKh+4+rVKGnGQt6po8qGp281wTMg0M4zaV2zAiXY/dpa1YdtjG+7h5dAJyE3V4/MsSuHyB73RRUox0vxJD81D3Yoq5/bqRo/OeySkM6p7Jr4TDE0rNVEWkQfM1p/sPwPDsKDS0eLjOIu9XLkWvBA0cTj/KGlzfGUtPvJkIUNcTKoo5hAJnXgEB6rqhsQB13RBLDBUKCAWEAkIBoYBQQCggFDinFDhdUEeOukNWB+L1IQcagRHCJQzqyFG3IOSoI7gxItOAwak6VDV7UNnoRq5ZjdVFLdCopBiebsDWUhtqbF6GOKN7GRBvUKK4zokkoxJrDrfA7gkg1qDAJf1ikBatZAdc/sEWaGUSTO8fi+0lrQw/eidqsK6oBTbP8e4oSpkcmqLD6Owo1LR44PUGcO2YRDy5sBR+qRRDUnShJhDeAKfzjsqKQqPDh/wDzeht0mB8byM2l7SymzDeoMDeSju2V7YxdSTQ1DdBw+fYXD5sLLFhTKYBW8raUNPiPq5eHQEeIkV5qToMStPD5QmwBkfqnazB+F5RyI5X441NVk7xzIhVYWCqAUWWNhxqcGNaHyOKrC5kx6mRYKTOt05sKLEh4KdYgsiIUWF6vxjY3X4UVNtxQaIWhRYHCmocx6UjdwR1e6vaoFDJcU1eHO9jQJIWswbG4d+ba2EyKGDUyLHuUDOK6lwMqQhipsaoMLdfDAg5yfwBLD/YgvJGN4PEqblGvjZ+fxB9krRocfiwobgVdTYvwzWNUoZJuUbeR2GVHfL2NNSVB1ugikjDjQR1sTo5PtvVgJEZerQ6fVhc0AS3N4BorRwT+kTjcHVor8QIc0xqzOkfw2CNXG6f7mlEU5sXwzL0uGa4GTF6BVYVNmFxQSPHdqK6ZzRXkkGBYZkG7Kxsw/AMA/QqGbaU2Ph1QKnUBOr0ajmWFzRgYJqeG4osO9AMO7kL6cUhkYAajwxM1TMwpvXWHKRmKD6GjHRv1ts82FlhP2GacU++iZxtUEcpsvRa4NdDNw66RtSFtuO1CqfThlNyuzolzRNOp+04J81FXyeLMXx+xxTgyPTe7u4xHPuJ5u5KXCfa/4n0O505T7ZWpL6R487Eet91zXty753NFb6fv+ue+a44Oz4vGXNtSvdeJd1d4TwcfyLTsQB15+HFFCELBYQCQgGhgFBAKCAUEAqwAj0B6p5cUo7rRyXA2urBe5trQSmlkaDObvdibE40bhmfyO4u+qDh8gbYvfT3JeWI0ilw3ehEfLChGnurHZx+euu4ROSYtVhZ2MSw46VVFpj1ctw7PZUhEYEhch/tq7Jj5f4G3DQpBf/damUIMnNALJ5fUg5Lh9RXcnVN6xONm8YnsUtMAglqbR5Ea+T42+IypMVrceUQE15aXoF9NQ6kGJX49cx0FDe68cTiCszoHYU7pqXB5fEznCLoQnv5aIsVX+9vxOBEDe6blcHPkUOszU111IJ4dU01CqvajnNHSSVBzO4fix8NNYfShqUStHkCeHZJOYob3LhpdAIy49V4eEEp5EEgy6zBPVNTsWp/A5aX2PCH2RmI1slBVcW4qYZciq93WPGvHfXoa1bj9smpDNV8viAc3gD0ahn+vbkGX+9rOgZ+0X0QCepeX2vhrrV/uiSTmxy8sLIK03tH44oRZthdfmja6w42O3x4bXUV9tc4GAreMy2V4SqBMAJtJXUuvLSqEhXNHjwwPRVDMw2seTAQgEIuw6HqNjydX8XX8taxiRiZEw2v14+gRMJgd09FG55eXnlMmm8Y1P1kdCL6JmkRrVNwMT/aO6Vg3/PxEfQxqfDbWRlYtLeeQV5GjBJ/uSyb4STFplTIUNnkwjNLKzAyKwpXDYsPnV/vwgurqlBNsPkEubqcIpyoxQ0TkqGWS6FXUQ02wOkN4k+LylFsdeC+KSl8z6o5PTkIpUzKqcBPLa/kWC8fYsKMgSYE/AHmdqRVdbMHd318BGlRCtw9LYXH/2tLHTTfY+pr45qnEfAqz8g7Y1BKVk+qrfhtynYYZhgMBuh0um7VnKNzqclEc3Mzd6YlYEdHGITRfNR0Ivx4VzZFzSpsNhs3rIiEbQQS1Wo1jEYjFApFp1OF46EGHDRP5PnECyiW7sYTXig8NzXxoL2G56Z5KS7ST6ns3nWjOWmfFC/Nc9SF6/dzkxDq1nuivXZFy45jSEPSlpqN0BFej9am2Gk9+v59NAYJ7530DNdgpJgoRq1Wy7F0tZMwnU8NUzrORY+HdezqXF3RVTL96lQB6tqVopvFhyDINB0M/Xt8zCFAXVduKTGmJxTwB3xwetvg83uOpgP0xLxijlNXgN8Pulk6RAopVAotVHLtqS8szhQKCAWEAkIBoUAPKdAjoG5xOeL0clwzMgEfbbWyg6x/cshR99sFpdQOFfdPTYXN7cNLq6uhUcvwwJQUhizPLCpDlF6B60Yl4IMNNQzICNTdMi4Rvc1aPLyoHHNzorDiUAtun5gEnVqOF1ZbcKDOhdm5UfjxyEQsKWxEokaG3RYHjDo5ZvaPxd+XVaDa9m2NOgJmlCpJDkCHJ8DQRPJNOuujM9ORaFTiqcVlSCVQl2fCy/kV2FfrRLJBgV/NSEdJkxt/W1KBGblRuGNqKnaU2fDcGgt3m33m8myu5/b2xho8OCsdapkEL662cD25X05JRlKsGi+utBwH6ujDllEjw33TUrkO3rOrLIjTKXD7uETsr7Jj/v5G/GxMAjLitXh0QSkUCKKXScMwbOX+euSXtOEPs9PhcPnx1PIKOIMS/HZqMuRyGZ78Jo33sjwThmQY8PLKKhxodOOOMQmY1CcG72+qwcL9JwZ1N45PxvxddexwjDUo8ff8CnZAXpFnwlUjzFh5oAlvbrbiglgV7p2ehmUFDVi8vwl3T05GnEHJ9e02VNgxKV2Hm8cn44ClDc+ursajM9MYrP1jbTXmH27F3SPN7Hp7Ob+SGyvcNikFq4qa8OqWOlzVLxrXj07EXosdz5wA1NHzE3ob8cm2OnyypwEX5kbhxnFJeG9jLdfQ+93sdCzc14Blhc24Z2oKu96eXVmF/XUuTOllwH2TU7D2YDM+2lmPG0eZuabiY/NLGFieqFnGUaCZqMXt01JRWufE0yst7Hakeox2jx+PLS7H76amIi9dj39vqcX8whZcNSgWswfE4o1VFlS3eXD7xGSO8dXNVuhUMlw7KA6XDY3H/y0sg9Xmwb1TU3Gg2o73t35foM6GqsItKC7aAY/H00PvLJHTBCHzOaGzV0HptTGUpvufAAZ1iyXQFAmLuhJAuOEEfVavqqpiCEQHgbnExESGYuExXZkvPIbOIfhXW1t7FBqZTCbQV9ihd6KmGOFGF3QuzREeRx1waY9hMNldGBW5j8i9UkzUiTcSfHV1r2GgSXuiTr5tbW0cb3ivpxprx/XD64SbhdB1In0IitFB8JPugVPZQ1f32llMtFfaO3UvJmBJv1Mc1JX4VPZOc1VWVh4FkXQPUkfjnj4kv7+8jwB1YVUlgAMBlEo9qJb52LId+blcgLqevv3EfJ0pQHCurHEfdlvy0ea28l9nxXH2FZBJ1ZBJ6O/YXad1cqkS8foM5KVORYw28exvQkQgFBAKCAWEAj9oBXoC1D2zpBxVNi9uHJ2A9Fg1HlpQij5mDe6dnILffFkKs1aGuyan4PX1NThcHWpSMHdgHCb1iQ456joDdWMTMTQjCkv2N6Cq0YWyBjcevzQLC3fX46t9jexMCkoluGVsIvol6bC/0obPdzUwnJrRL6ZTUJdr1uLuKSl4cZUFhdVtXO+OgNalQ+Lx14WlXQJ1t09Lw3sbqjnN0uMP4PdzMiAJAh9tt+LRi3vh6511+GxPA3dsnZhlwBUjE/DGuprjQV0QSIlV4f7pqfhwUy22lNnYiWc2KPj/8ygFmPQ8Gah7bGY6dpa24p2tVkSrZLh6eDzyMqLwf1+V4saxiahucuOgvrfwAAAgAElEQVTtLVYGigxOp6Tgi511JwV1P5+cilYXpWBK8Y81Fq7bR+7DSwebcFGeCS+trMSuCjvUCgkenZOJgzV2LCtowu/nZWFNURM+2VHH48krRvBpSIoWd31Wgkemp4JSVZ/Or4TLHeAUaIJt766tQlqcGqOyjHh5lQV1bR7o1DLcMZHAV+DEjroxicg2a/DXr0vR5Ay58J6Yl4nSBjcW72/EAzPS8PW+BuysaMMD09NQ3uDCthoHdygm88X0XCM7Hl9dXYV5g03ITdLhia9K0dpJunTkGwQ7DxO1uHFCMj7aWsupyvS/gVMviMHcAbG497Ni3DU2iesk/mVJOXzeAN+ft4xPwqeba7Cpwo6ByRokGVVQKWVINaqQaVIj0ajCk0vKUNboxn1nAdRVFm3HrgoLHL4QQOnxI+CDzt0MU2MBNK4GBnVJSUnsCCNQRK6k7qQJElgJO7EIVlksFoZNBMVUKhXDILvdfhSudWU/BA4JqFFcVqsVDQ0NDMLMZjPDQHKDkaOts/TVcDxh8FRaWsrrp6enc5wUHwGhMKDqSjxHcUSHvRIQoljT0tKOQkpy8XXn4LqJKhWDKdpfUVER7z0+Pv479/rd64QrlX47kgAquRxpLdKFrg/B1OTkZNaZHGm0h+6nBoca1XTnPNo73XexsbEMCouLi1kH+p20pfjoOnflIHcjXV+CcjRXWVkZfyfg2d25urKe5OnL+wkKcIxSIUfdHpkT5TKfAHVduYvEmB5TIBAMoLyxACsPvYu0mH7IMg1qh0M9toSY6BQUoDf5PaXr8eWuJ6CSEXD7blhHb6wqhQpxMfEYkDIe0/rcBJ3SeAqri1OEAkIBoYBQQCjQMwr0FKg70uBmZxqliu6tsGFjWRvu/cZl9MCXJciKVuGmsYl4ekUV6pqogpmEu7POGhCHF5dVhEDdyAR8sPFYR12/ZD27yZwuH+I1cvz1qhy8u86CFYdauYkC+XIuzjNhVLoef1pcAY/Hj6l9YnDhCUBdXpoeP5+QjF9+VsxzUkOASTlR3EDh/77uGqi7Y2oaXl1difWHW7m+2MOz0rmBw1d7GvDrWRl4f4MFSw+0cI05qldHjSqowyh1bY1s4kC1znqZNew6/Ht+JSoaQ7X9Ql6jUGrYDaPMJwV1j8xIx4bDTfhsdyP0SimncA7PMuKvX5XglvHJ2FfRxm4zyp4kgPqrGWlYuKceX5/EUXfP9DQ4vQFoVVIs2FmHL/Y0cmrq0a6v+aGur9R59XdzMnCk1sm13f58RTbe31CNZUUtnNxIqatj+8Tg0v4x+MUnxfjd1BSuQ/fy6io4PSFQ95MxifjnGgv6peg4zfmV1VXcJValkPL9Qh/An15+bIfbjs0kqOsrNQ1p8wXw+Jx0uHxBLNzbwM5DAnWFNU5Ou6U01MgP89Tso6TehdfWWHDJoLjugbokLa4dnYgPN9eikBuQBDEiKwo/HhaP339dhuuGxSNKq8DzKyvh8QbZSUig7vMtNdhqceKWsQnISzNwCvBBqxOtLj+DyufzK1HW6Dp7oK68Co52p1PPvLt0mCUYRLStAub6nVApFAyxCGCF0yFPZU0CXzQPHfX19ejduzeDl7BDrLtz0j1CwIYgWGFhIX9vamriubuSRkvnEywkkNbY2IiMjAyOh+BPx9p13Y0tcq+UnllXV8dA8XTnpRhpbxQ7ATOa83TSNYPBACChNjHHHjQ/xU1wrqCgAFlZWezgrKmp6RZo6zArAgFw2YDuHgSGKQaKi6Al3YuUCnwqetK1obkI8BGoI0hHrspTmetk+xCgrhN16NKXST3YIXPCH5ECKxx13X1JiPHdVcDn92JDyWdotFdiTv87oJRrujuFGH+GFFhf+CVeWP5TaOUp3aqpoNcZ0CdzIC7qfy8yYvudoejEtEIBoYBQQCggFPhuBXoK1JU0urmz5+QcI24Yn4wth5vY3fXA/BKkGhTsqHt+lQWlVgfXKZveNwYX9o/FC0tDjrobCHxsrMbOKgdUSiluG5/EqZ53f3wYKglg1snxlytz8cmWGiw50AxpMAiJVIKfjklEokGBxxeVQy2VYEqf6BOCut4JIUfdXxZXwNLkZEfd7H4xuHpkIp4gR51JiyuGmPAKpb7WOJAcReAxDcWNnojU1w6gbnY6O9Y+3VGH383NZLj16e4GRm5DU/T4ydhEvLWhtlNHXbpJjfumpeDtdTXYU9nGzSYC9Dmj3ZDy05FmZMZr8fCCElBlrF7xGtwbkfrKoO5QEz7bEwZ1ZgzPisJfFpTgZxOSUF7vwtubQ4667HgN7rswDV/tqjspqLtlYjL+sbEWQ5K1GJ0djT8tKEZZUyj1dfagOIZJHUFdfkEj/nh5DhbtqcP83Q3tjjpg1iATJvYy4I5Pi/HItNROQd27ay3sjKPmDC+urOLmEmqlDLeOT+I01BPVqKOur8nRSjy1pIJTTv2Q4P8uyUBVixeL9jXiVxeGQN3+agd+Mz0Nz6+pxvIjLXyPEOzzSMA161JVUq4FSF1fyZ3XWQOSyFdR2FF3/bgkTm3dW9nG7sHJfaLxo4Gx+PUXJbh1TCJ3fe0I6j7bUoMaux+/nJHGUPrj/c3QyajzcDR+PjEZz+dXnF1HHYG6dicR1USUBQE3l5QL3ZCUsqokKEI1Jkk/UNdeaogCeCHhLs3KYJDvYYUv1PnYL6U5yMUYAiladwtSLGsRpVUzsCkpKWEnFV0Uu60FNruTUbUxLh4ahZxfCydLFSXIEnZDEUzLycnB1q1bQ/XuQB2LfbDbbGhzuKCMioVO4oWt1QaJLpodnvY2G2x2H6JNcdAoQnXu6PP9pEmTsGPHDgZ1BNoIKIVTW/0+L7x+6vrrQXNLG7w+JUyJMfw645RemQy5ubkMaii2ffv28WME4f32Rq7lqdTqEG0wMLw/USotpwNLpUeb0NBeyblFrjf6vnnz5ggQFITL6YZSreY/EnQ1vZbWIEg1aNAgTh+mvYZdg8GgH/U1ddCazNDKJQj4XWhs8CLGbOBO13Rx+M5oz/QK+Jxw+jQwmYyA2w6H13dMAx0aR0Cwb9++rG1eXh5DOnLUUbx+rwstNhd0BgNUcim8Ljtcfil0Oi3Pc0zZSE6fJrU1MBqVcDQ1oL65FRJtNAxqGf8bEzme1g7Xo4usj0fOt9TUVHZ0Ejw8ep0cNriUemglPv7jgU6jgjQYgMfrQ9DnQEubFyptNGKN6qNvD3RdyIFJem7fvh0KhZzfaxB0weGUQq2Ww2WzQaYzQB70ccMfGhvufP3d/1oDAtR1ohK9IVklPmyU2/mNPcxsewLU+ZyNqLPZERObAjVcqLaWo8nlhkymhik+G1p/PSwNdXD7/ZCrYmAyaGFvrUOrxwOZjCyrVChW/7207+7KDSTG9KwCXr8HKw7+EzKpDFNyfwqZlFItOz/oLxgOWwvcVMRXpYNBp+6Cz6tn4/0hzba28HO8suIWaOWp3foHUS6To19OHub2vwe55iE/JMnEXoUCQgGhgFDgHFOgJ0EdgyYEcceEJAxMM3CB/ns+OQJ5MIhfTU9FQbUD/9pi5Q9S1DwgJ0GDZxaVQ6uR47aJSViyuwEf72/CkEQtbpuQBLlMinv+ewRqKbio/oOzM7ib6hvrq1Ft8+ICs4brfW0pacUnO+qhlJ0c1CVGKXHn5BR2LRGMcgWC+M20VHY8Pb2oDNEGJW4Zl4QPN1Qj/0grJmWF6p7tqLTjyaXhGnXHgzqlRIKX11jw0JwMNNk8eGVdNRxuP24ZZcaQXtF4aVVVpzXqYnRy3D8tlWvcvbvVCoNKhisHx0GnlOK51TW4bpgJ43tH43dflvK+qfHEVcPM+HpnLdeoOxGoe+zzI7hsSDzSYtV4elkFmtx+XDooDlcMi+eurSerUUfuwtfWWmBz+PDQrHROyX13cy3mDYjDnE5AXbHViU931uG+aWnsvHt7Qw1Km93IiVNzncHGb7r4/nFZJX4/I61TUPevdRaGOAQ0/7utDksOtWB4iha3T0hGcYPrhKCO0mapuy7BrQ3lbZiQYWAX3YdbrNhracMjszO4Rt3qQy2sMX2Wo9qGVS0eJH/TTfiG4SY0u/z4YncDOxH7JOvw+Jcl3MyDAN6J/DlhUPfzKalYf7gZr2+uRbJWgVvHJ3Jtu99+VcZpvp2Cus01sLoCXDPvzbXVWFNqY4h99bB4Bn1vrbVge4Udv5z2/deoqzywHbuKy+FwuYCgFqNHj8YgUyne+PwQoFEDEh/SBk7A3BEp0Dua8OGqfRg9Zjg0cg9UDjuWfr4GLWnJuGxsf1TX+TBqSAICdjeaGmrx+crdqHZ62WWl9diQUrkKRr2GU0wZ1Hnc8GtiMeXK6zEuVg6nXInGw1vw6VfLYWm08/9jS+UKqFVyOOxObkihVOqgpjcGBNnBRJCEHGYEyDZt2sSOML/bj+i+Y3Dp7LEwKX2oKy+DzWNCVm4UmioPYuHag5h+6Y9gltlRsjsfC1YfgE8ih9/nw7Rp0xi2EMQ5fPhwe8pqEA6nFzMvvRKpUUEctvgxdkQuPLZ6bJ7/NbbV1JO1i++dfv36Maij2Pbs2cPvTY1yEy6/9S5MjXWhrPwIPvj4E1TXh2rDyZUq+LweBpZ0qLRRMMdFwe5wwO50Q6WQ83PkSCPdCNRt2LCBwZff60Zc1kBcOmM0li/4L/YequnQYVoFnVYCu4PczKHDYIhiFxo5wahpxNChQ9lNduTIEX7M53LAlDMYd99zF0qXP4l3PjuMQRfejKtnJWDBK29hdVElvHRdJCooFH447BpMu+52DEnehf2NZqi2rsdn+45wIxWFSgWNSsXr0l779+/PoO7/2XsP+CrL8///fWb2XiQhCTNAmAHC3kOGgKLFvVqtttZW7fi13+5ph93DVq1FrRNFUIbI3nuFlZAQssneydnj/7/uw4EIQRMElPo8rxcv4Jznucfnvs96P5/rujIzM5WLTZyHOreFoJG38435Azn82nMsOVjI1Hu+wdTUel57+TVyylAA0hyow2HzKi2Ew0QPncvdk7txYm8Bg6bMwFP4HP96uwSn10hQoBmn3aEAclBoOFER4dgtjVicOjUuuV7AmjgKJSxZ1kl0bvGEMuX2LzK2bSOv7bew4O55FC7/GQf6fo3bYoLwBoYQFamn7NRhlr6/HafLq6CgQD/ZhwLf9u7dS0CACWuLnSETH2BKZgNvLDnB7DtuJ+jMGl7ZGM/9C228+N811LdJxJUZndeN45KOVgGWIRqo6+j703lQZ8GhkypRvuOTgDpLbQ5Ldr9OQ3UpRbXNdEsZxfDYVLLzXqOFFMrrm7nr/n+SUr6Y1w6doE9yEoePNjJ94ig2ZWeTmd6DwoJthGQ8wSMTMgnyuqFkHxgSoXua4PzORON9xr4uasO5UAEfqFuMUW9iSt/7LgB1Xmxt1eQXnSG5dwZRZj3leQfIL6vBFtSdiaOGESq3d67g4XG7cHslAawB5E5LST5VjXYCo2JJTUrELI/7D68Ht1S00hsuy5LcuWF71Qeb2+vLVeG7s+NWFc7kA8hfZr1zbXXtrAtBne+OUkeZA87fLZNQZgXqemugrmtqa2drCmgKaApoClwNBT4JqBuQEMzXpibzx7W+KqXiDhFYI04nSYifGBnAV988RZvFpVxuEmJ4vMqqwiZ7RgWoH1B/WlOCxeXhyxOTiA83k11lJSHQQEp0AA6Xl6+fBXXyEZuZEsJdoxKosbioaXPRPzZAhQ0+v71CFWSQH4HT+oujLpo/rS35UDEJ9Rmtgwl9IpULL6fKgt0DSaFGYsPM/HFNEfVWN0/OSFHFLMQhGBVoID7cRE6V7Zyj7mvTU/jn5jK2nw19/eGcVJVbTqqFDkkM5u6x3ZQDTfK0JYWbVEXPf12i6qvoJZpM6hdJrtJFT4+oAN4+UK2KZwxLDuHLExOpbnVSb3MTE2BQee3WZteqqq8/mp3KzrxG5eALk9DXkfFk9Yrg/y3JVy61+8d1o67NpUBdWoRZ5UV7bc+li0kMSQpWobqiZ3ZZK2N7R3B3VrwKD+0XF+Rz1K0vI6fSQqBRxw9u7MHpKguv7qumf7dgVfm3xenhTLOT3tEBai+8uKuSI2fa+L+ZKcop94/N50Nf7xvXjVe3nyGn1s7DE8QhF8iRGhvpUWZVPfZY+aWrvoqjbnByKPVWlwKDGXFB2Jxufra6hIQQo4K6UvV1WXYdWWlhap+Kk+lUg4PkMBOJ4SZe3lnJ/pJWFmXGMGtwHDsLGllxtJ7qJoeCAh0dflD34OQkxVQOy34NMhAXYuQ/u6o4UNrCd6Z2JyzYyJ83+kJfMyT0dWIS4qiTYhYCreXak/V2kkKMBJv0Kk/fB0frWHmiQYXqSjGJa1X11WFpoer0QSo9ejJSkgm0uAhPTCezbwvbd5+horqAPQeb+cK3v0x8/X4q9WnExoUR72liV34lmT0T2fTcW9T36cMds8dQWGJnxMA2dmwup3/WEJa+/A6H61oVxOoQ1NltOEOTuOfbTxL/5gu83BTOk0/cxNrlK2klnF7dQmkqzyX7dBM9Bw2he4SRgiMbOV7Uhhd9h6DOoPPgCkvnq1//ChGlW3ht1Saq44bzvcfupm3nEp5/ZxMxA5/gu1+KZeXLz7I2u1IBOnmTEEfZpUBdY7ONh7/9/+ifFEVpSyg9HDt5/rUVlNZ5QEI+zx4XgTq9h1JDT374zB8YsPNVXtl+iDJbICNGDibUa6P01Enc0WkkRgaC20q5J5x7b55P+cEP+O/id6j1eNRvGgF1/kIFflDnsLaSNnIGj9+/gPVr1uHWGQkJNGOzWjEFBWGvKWBPvoXhIwcRFWTE1nCGnfsP0WJxIyaPjkCdvamRtDEz+etvf0PDwf/yi+c2MP2hH7CobxvP/PZZThFL39QwaksKKLeGkNG3P1nT5xNnf53V+90UHSsgOi2dWJODspNHOVxQoXJDyhxEm4tAnaOWwHk/5tmHp1O14Rm+/vfjfP+Pv2Rg4H6e/vVK4ocMI9xr4fTxOuKGJBMqrtjmCo4Sy7TUSDyGdGZPTmTrm3/nmDOF+CA3J0+VERrfg8RIPcaIeKaOyyJ327u88eY6GgWoer0fAnVHjx7FbJKQZQtz7/sB90+18s57Ndz25YXkLP0dxT1uJSPJTKTZzNH3XuSdTUdo8Iir1PdmcTGoM2NvrCZp1oM8vnA4m3edYP78mzGXb2bpLhNj+nvYlX2akFAzZadO0qKPpX/vWJrLz+AODCciPAid14nw1SCDjYP7d2ug7lqBOmdLOe8v/za/KRnAj0e08c6+cr4w8XayD/8Td8ggqpoSePKrX6d578/5566d9EruxeHjcMvM8WzYs5m+fVIoLNhC8sin+dr4vgQv+yc4TWCOgZRMGDVC3KDacZ0r4HfUGfXGi0Gd18uZvPd5Y2sOkyfPJjLQiNdtx+01ERyaQHxkKC2N5TTbnBfhI73RTFREN2U973xYv5OiQxvIbYxk0uRh1Jce441dhYyO1dMSkMSozOGqYpnV0ozLEESYq5EDRw4Q038GPaO7VjZcgFdLYyVt3mBiI8LV3c0OD4+NwoNvsr7AxMRJE+genUigrp7t7++AuGTS0weRFBvy8bvA46Kl4QxVbTb1xi0fWglxySqn3KWOD4O6s4xOJ3Wi2yXilbtNXqnV5itHr4G6j18K7QxNAU0BTQFNgWunwOWCOil4kBYZwBcyY3hlXzWVrVJh1RdWKCFJE3uHM75nOH/ZXkmr1YXFAwsHRTG5V5iCYK1OGJ4Wyl/WllDW5CQ1KoCFQ6OJDDKwvbCVmCCDCmn9y/YqFVImX2RUn3GBfGFwNBHBRkrq7bx7tIHaVof6qSSgbnj3EEamhbJkfw31Ns+HvuMIrHN4YELPMGb0i6Sm1cmxM21M6hvB6/uqKah30Dc2gEWZseq6lTlNjOoeRIPNw2sHaxmeGMwXhsey9HAdxyosuLxe7hkRp3LUSS63olYXM3uFc+PASBosLo5W2lgwLJbnd1Rw8oyviEb7Q8YjrkPJkze+VzgWh5v1J5s4WNaqClQ4vTAqNZQFg6JptLrYnN/M2J5hHCltIbvKxj0jYskua2N7YYvKwTatb7hyBz6zpYJqu4dhSUE8kBWvrj1da+eGwbEs2VfJxpNNyuHT/pA8awIJ5w+KZuXxBgrrbCqE8ZGxCQpcCRAb3TOMJQdrKWlwYDLouG9UPGca7azPa1Jhz92jArh5cDQJYSbKGuy8d6yRimY7TreX2zNjFIhcdrRewatesQEq7PiD4/UcqbYpB9q9w2NJizaTXWahT2Io9W0O/r75jAJZ/kP2l/Q9Z0CkciCearAzp38kJQ12XtpXi8PpVv3fkxXHztMt7CxsUW6XHjEythhiQoxUNTtZfqyOsgbfvokLNXHHiFiCTHreOFjre/yjQN3ZHHWbTjYwJiVEAeXVOY0cq2hTcPLWITGqmuvbh+vU3NOiA5g3KIrNuQ1qrhkJwcweEEl0sJFDZW1sPd2i9KlotLMmr4nbh8VQVGdjfV7zRet0Nd4ZBNSdKcpn8Pgs+gZV8t/lefQbOo7ZwxysP+JicFIrz+1p5slbBrH06Wc5FT+WX3/rBiqWvczvciL49henElBRjiUsjHijk+0nbcyYnEBDnZPiE3v5z6pDNEitg0s56gTUhSRy97ceJ/x3P+J7uYX8/LlXFLiN8tZzYGs+g6cOpa65jV7RAWx7/x22Hcyhqk6yyOs6BHU6t53IzFl8+75ZLPnHn9idW47JGMjU2x/l1vE9Kd7/Hq+tKuXGx77K4OBa1i17k9V7CzGajB8J6poaW3jw298nI9rD2j0lzJs/GXvpAV57fTm5FZZzv1c6BnVp/N+f/8J8XSHbsw/TmDCckebT7C8JZUgfHY6EIQSV7qPY2J2wglMkjBvFoY1v8+orK7EZJQxY9xGgbjqP3XMzBSUWJo0IYeOmRiZOTKSopJy4xEg2ZTsYFVtHtTOOEf2D+fEPfkB+hQ2Dzveb50JHnYC6HmNv5KlvfoHa1mYOHq+j9+CBJLTVkLNnJwlZ42iw6xiUEkx5tZum08dwpU9nkPE9yj2DeP+VtwhM7sOQrCkkN2/nV396k2avHsOlQJ29hsD5P+CXs7MIaiph9/FTDJs8Ab1tP8/9ZjspM7LIHDGKkP0uet6bxsn1qwjp1oMtrlBuDG5h35YGMgeZyG0xkd4jhhaHjgCrm5DYSCqyV7K7XMeChXPZs/w/LH13F84ACUvtANSZzTiaqkmevIgnvnIPbQU1mEwBhGDHbbazZ/cGjGkTmZwezp41r7FkzQFsOtMlHHUBeJ3NVEZP5DeP30v3wDb0liaIjcZlbWVHdg7VNVbGTZxFuLmRSnsEQ71H+O+SUuY+sojm3FxSp0/Ddmw9rvAkdixbrIG6awLqvF6cjhYKj73Mz5Y18ciMQNYfa+OBG+exYvn3yG2NpkfGvTx+8yzyNv+U5/ftoU9KXw4ddXHzzHGs3budQX1TKTy1kfjMX/O1qSMIXvsq3PMk9B4PTz0NMwf4PKLacV0r8FGgzmWrZsOqP5Nd7yBMrLhesFnKaSOD+27+BvHuMpav+iPFujDCA/xON9+33YqCNQyf9gZzh/Uh4NLRtB/WztvKgXVLyXVkcNu8IVQW7GXFoRAevmkADrfP0Wbwuji0by11wQOY2iOA7dvWEz/yDjISzsbwe73Ymoo5cnI3FTbBV25lsdYbTCrPhSkwhoz0cXSPDKXo5Dp25p0mICKdrMFZJEWEqjAY/66Wu0AOeyttVhstjSfZf2gz+tjRjB42HmfpAepcQQQn9KdPlJv83E2cbrKoD/T2X/bE/9Y3/QbS40IpPb6cFXnZ6otEfGR35o69g7CQqE6BOo/XRVrMIMal30xowPkCEfJjpaAym+35b+H2uM/mrtAcddf1i1IbvKaApoCmwP+QApcL6kQCcRdZ3F5CjHpV3OH856sAMa9yrAUbfJVMBSotPdHI3tI2Qk16HpvQTcG5p9eVYXN61I8maUtc+0F6lNtO/i3nnmtXHjvbpzxn1kGgQXcOgMlnugAjgSNBRsnt1PFCyfPSl4xZ3HASAhtyth1pv02S1yFtS3u+r9PSnsy3ze1Vc5IwRzmsLg9SGCI80MB3pyezp6iFN441KEfdV0fFMbJ3JH/bWEZ5o/2CcDTf2OS7mxSlsLl9t/RkPtK2HxQ5/GM9+5ycGyARAzrUNSKPhHGpdtweBfdiAg3cOjSaNruH5w7Uqn4WZETxwNhu/GJlMWUNtg5T5giss7q8agxyg9S/JtKXZH2SvmXuAhxFIXFCCpyV8cjXK5mz6CryCVwNarc2NtHp7BxUPqqzc5ZCFxN6hJHVI5QX99dS0OBQbrzvz+zOhrxG1h5vuAhWqe+7/3/FXRmDrKHVjdIhWL4j6s7vERmXH0j69825sRl1auxyyF5S6yg51M7O/VIvceWoSwzmrjHd+O/uSrWfZd0kNFvdVPZ6sbul6q1vLSUcXK6RtQrQS148vZq71ePTSaI3ZYwWl1fl/ZKv61ZZV9mbhvN7/2q+5QioKzldxJTJWRhKPuC558qZ8qUvMLr7YX6/28vXZo6kxKYntXofv1hVwc133ED/pGjC7fVsy6lgWN/u7Fq8nKo+vbhz2ggKim0MG9jE7lw9A2Pg5dfXk9Ps7ISj7nEiFv+Nf+nS+enD03DrvITZy/jBb9/k4e//H6kxBjxnCvjuj/6KCzOBwXoF8DsKfdXjhKRRfOfxB7Hte4sXlq6jps2J1xzNxIUP8Mi8QWx4+ie82xjGA488xpCgY3z/58/R5ArB67nYUaeqgHrdWJ1mvv6jX5Di2s0f/voKMUPu4slHb+H4u7/n2XcO4zWY1R7sGNT14of//AN93v8Hz2zNZdY3v0/aqf/w4gEzX3lgNu6QVHI2v81B8wjuaijAeMMkdrz3Im8u30RwWLjaAjLXDh11WTP4xr0LyS9qYUj39XzthQK0dw4AACAASURBVDB+cecA3sguZO7sOSTUuMg9vJR8dxJ3zxrC0z//Caeq7L7fXpcAdT3HL+C335zDir2tTBuezK6iXBKiemA8tJWkCdPJO5KLIQiiElN598UXSZn7DeYmb6TYNpCdJ5q4sbeJRkMSMc59/PxXL1Pn8uXb6zD01V5N0E0/5cdpwdQHdyNrRAjZu0oJSS7nzQMh3DUkAWdoDGGHvYTN1bPmb0+SMuN75AbFMJ0ytq6uYHhfDwVB6UzIjCf/RA5VOeU0B0YxaGgvrM15RKcMYfMrf2DJ9hIig02XBHVeZwstoSP4yW9+SmZACS+vyOaG226jW91Onnr6H+w5E8D8rzzBHT0t/O2nT3PE6sSk1xNzUeirmD1cNFYaeOSp37IwK4LXf/8KPe/8EiNjKlm37QQJPXqhN0QR7q5k9Y7TTJg4mnBbI7oIJ+tf/hvpX/47FbuepbnnHIYeXK2Buo7eCK946KvXQ23RBlYfXMehgnpS4oOotkQypXd/9h37D/qQUTS74vjaA4/StPeXvHq8gAmjbiUqtA8946Kor82nztrE7l0v4+3zPb4xMYPg9W/A8dMQmgyDJsCYYSBvYNpxXStwKVDncbZxcu9/WF9uYv7Me0mUbLR4qSnYwcZTzcyduYAQayn7sw+RNnQmCSGShvj8V92D79zFmbRfc2NWP8w6l/rS0GHQpk6vQjXVdxlnHRs+WEJ51CzuHZ9GXUk2q9cUs/DhhYSdbVocfft3raYmeCA39Alh586NxA9fRP/486DO0VbBycJdVNrB1VLKgZxC+mSMIS7UiDkghvQeo4kPDVbuwPraPA4VFtBkjWBc1hgSw4J9yWFVDL+TklPb2F5YTWpCLGmJg3DbGwiN7U9ckJfm5gZqHWZ6RBooLtpGUbPPIn8O9KmvUdCrx0xSYyLA7cTl8eB1O7AWv0do92mYQpMuuX/aO+pUMtvQGG7JeoKRvWZhNPj0rmkuY8nu33KoaDN6nTjrvFro63X9itQGrymgKaAp8L+lwCcBdZ1RQqX7Nht4bEqSyk23Or+J8EAj03uGsSm3gZXH6xWguJ5vLQs4Enfd92alkhwVwMZTTbjcXmb1i+RwSQtv7K9WMLKzCd47o+tHnSMg7ZZhMYzvG8ma3AYFTCf3CKOuzckfNpRhuiDR+ift75NcL98/M7oF89CkJAprreyrtDIyIUjpKMUlKhovHYb6Sfq93GsFukmI811ju/HqnipOnLFc0n13uX1c6+sE1NUUH8GU0p3M1Fjqi6pp9YQSYTzKO3k67pw1leQwJ6/863Wqowdw6+hklm2TaJ5RBOscmFubWfnSGprSe7BoSiZV1Q76dK/jgw2FDJ4wDeepPSw/WCFWSIIdzSSXbbkoR50rKIaZdz/AuBAPreYAqnM2szffyqQZM4k262g9k8eeghbGTRlNgKWSHVvfYd/xJvW9XvK1Sa4xKSYhOeqkyILBoMPhNjFg4izmjR+MztJAbU01Tn0ksQkRGFqr2LqxjqGz+hITEkjNsc28vnoXTn0AHo+bqVOnqhx1UkxCctQJqDOYzIydczuTB8ax8/3ltCSOILNnMrHBLra8+ybbcyvQ6Y0q9U7//v1VjjoZmy9HHdQZxDX4KNFrFrN4Sw59py3i9rlD8VitlORkE9hrKJV5u8g3pTOp5hRlQ8Yy2FTJOy+9TbHVoYrnCKhLSEhQ7e7atUvlqHM5bCSkZ3LLrEmUVVjpHb+PxetDuGV8KluKahg3YggcKCJqVD+6xafSPaSBn/7sVxTWOBWoE6OF5Itrn6POYWkjceB4vnL7GN5ddoBJUwex4kgBU0cNo3L7VsKHTiLO00RJSR4tIelk9Y7CExyDoX4tla4+5BXrmT0mlqZaG86Wo7z82nqaXQL5LxH66moiePz93B3ZyAFrMnPGBLJrayGpgwLYVtGNu4Yl0txqw3XCSehYA/uWP0N85h0UmiMYqavlyP56+neHLac9zJiVia6hhG15Z4iMSSWzVwIF+dmE9cgkviWfN15aTuXZAintc9Sp0FezWQHZlgYDtzz+GCMi6nhhzR4mLHiAXnUbWLW3iCEjZxAdG4v3zEFee+sDGl1yM0enQl/lT2Bg4Nkcdb6oLGdLJb1ufoJ7RkTwh6ffY/RNdzImuYIdOXWMGZ2JtcWBw1ZHdnELo4f2R19VidVk4fC2NSTPeJi6nFVYkrLom7NLA3XXBtRJbrEitm56hwJHC16vDmNgKmPikti06y8kZXyVwwd+Q9btq+ld+ntWlej40i0/JD6kXfigs4W3lvyQ3KhFfGv6aILtLdBYBAGxEBoLgUG+20zacV0r0BGo8zitFBx5iw3H6hk9/X6GJkepO6tet43DO1+n2J3O3IljcTeXsD/7MD2Hz6F7ePsQTi873riZqh6/Y+7InlTlrWLd8V04jL4cb/7D49ETlzCdG0ZNINJswNNUxOpVf4RRv2Fen2DsNSdYs+olMhb9lr5no0s9Lhu7ty2lMTyTG/pGXAzq2q+G10tr7TFWbj3MqEm30isuuMO18nodNLVYCAoOUznwXJYqThzLI3FgFuE6C2eK93OstBSHIZkRmePpGR2G21bP3m3vUBI+gdtH9+/SHnA7rdQe/gMRfe4gMKpPp0Cd7+6wgx7xA/jipF+RGjsAq6OVVYf+xfvZ/wGvAZ1Or4W+dmkltJM1BTQFNAU0Ba62Alcb1Mn4JWQ1NTqQ+YOjSIkIUO6lbadb2H6qCafr2gGsq6mluNEk/YdU/uwTF6hcdtnlFtbmNtBsdfuqV17NAbRrW24eSmiwhPeOSAlVN2NPVltVtdf6NmeHzr5rNLSLuhGQKz9yR6WFMiU9QkWASEjyupONqmJrh3eRP63BnnV09o4JZO6gaFafqKew1n7dgzqnpYXyPPkufQa9R6ecqlav5C/z0uqG7gkp9OqmY1v2afR6M8E6L61OF2aTiQAV7u6hze3Bo9cTIt+HxaUFtHk8mPQGzDovzW65Oa4jzFpNYuVuVUUzObk7JSUl2O12taIupxN5HeFxq+IKkvJN73Xg8hrArUOvHJN23LoAlStbr/PidrlVcYWgoCBVTCI9PZ3jx4+rSrLi+3TJuOQmvBQfQEIv3cquazAa8OhMeFwOvB4dJpO4vQRbeQkODmbw4MEKsAmok4IHUhFV8qt53B7lFpYCMjIsj8uFU2dS7lF5jasCB9HRChwKqBOolpub6ytGIelwJNe30YTeI+Py4nY48RplXkaMOg96KYKh3LUeFXrudovOAb7xezyqvdDQUAXsTp48SVtbm6/yq4zd7ZI0gKoCss5rUFFLXoMOe5OX1AGjmDR9OP17p+Et28Vfn19Ko9csAyY+Pl659GQd2s9VQSbl2hW3qVSkNmByu3HrdTgcUtFVkpYHYPQ4cMnjXi9GUxAmvVeN12F3qrx0RpNZ5f2UQyBWr169yM7OPuc6lHWTQ67ReX37yOOSdPvq3UE97rTb8eil6IZR7QWpreH2Sp45D+hkrn69QOe143YbMZmNGDw27CKkPgCj147DYyYwwJeiQeCrFJIICwtTffiBrOjp9YghRIfT5VZronfbcOkDMetkrlIB143HFKDcz2KLkrWRwiMyP1kfqSAre1C15RWnuFcWE69oaPBgd4DJrMdhc6jPR4MpgAC9C4fLhd4YoH4z6mX6OjdeKSQpFYDlhtbvb83oyFjzKb4lfvpdX3FHndjFG/fy48d/wtAvfZ8R4ZU8tXItNw2aQWnhG3hixpJ/5hT3PPBHIk/+lpVnQV1CaHtQ18Sbb/yQvJjb+daMcQSbNffcp79TrvwIOgJ1rZVH2HnkED1HLaJPpM9hJt9kbE35rFj7Pr1H30tmSjS2xiIF6noNn0PyJUFdH+xNJVQ2SZLXC75CeuT9N5rkbokE6r3UlR7k7VV7uPGLj9I9UGqxV/HBqtcwDvgi0/pF+pxuTgv7ty3F3m0s47oHseOcoy4Ar91Ci8VKYGSs+hIg75ItNUdZseUgoycvonf8x+SSkw8pVwNHtv6NNY2jefjGmURLXIo05bbT0NiAITiacLOOsqNv8kGehZkz7yUtqmvJGl2OVoq2/5Nug28lNK5Xp0GdvBG7PK3MHPQl7hj7HXLOHGDxlu/Q0FaPQe977Wo56q78a0RrUVNAU0BTQFPg8hW4FqBORic/VCS8T9xd8skdbNSpsNNL5QK7/Bl9elfKDyiBkBKKKV9zZI4B8gP+UxiSLzzUF4oqR5DBF4p6rVx9XZmy+tF8NuRY0vnLd0TRTpyBn4Z2Hzd2GauEp/pDhD+LY/y4ObR/3mltoezkAQ6XlmNxtcuzfPb3hQAG1MJIocLLn63B4yauPofIplPo9HoFbARmVVZWqiqt0nb71lX9l/Yh9QqdnD8EfskfCaWUyqF1dXUK1EmbApzEbSZXdHbIfqDXp08fBV6KiooUfJHQUIFt8revTV/OTIFQ59PxeH2pfPR6BflkTg0NDcpZJ06/srIydb3/9ecrbtNuvgrKnGv6Ah18kE7aHzRokAKSAib9QMhfOO/8a9sXJSWty7+k3mR4bF+GDkkBSy0nDmVTa5efYR7lIBsyZIiaq7Qn65CTk6MqlyoA6J+sautybzYIuPOBMdFTQKhAMYGOAhzl3zI/NQ+Z+blF/qgeO37uwj3T0etAgTO3W81V1kpgsYBVAWsyFv86nV+r8/tQwcR2G8rflvQjayP7Tiq/ylzz8/NVH+r8s2t94fUf/Tq9YI7StwbqLpbsqoC6poP87vtfhnEPMCisjncOlXDb8DmcOP4nCsP7MXXkY9w8fCh5m37CynI9D33hh3QL9bmivE4L5XWnWbPq91QlP8yT08d8KNFqV96ctXM/2wp06KiTEE25w6HsufLm7aC5Po8dO1fQGjSYG6fMJ8wM1voiDhw5TI/M2SSFSdil75D3v91LbqWyx2+YO7I/gR+bo86Ly1rHvq2vcSRgIg9NyVRfslXo6d43OdDYjWlTphJhNmBpOs2GLVvpmTWPjFA723dsIn7ErfQMrOfgruVUm4YxY9JYAuUujADrmmOs3JbNqIm30jMu8NwHi7prcPaNUH1wehw01edz+NBGTjZ3Y96Mm0mJOu8SVHeaJGS1rYzjR3eQU1zC4HEPMiytG3qdL3/MpQ75UPD3Jx9azdXH2Lz9IGMn30x8bOQlr7uw6quc6PG4CAuMY+bQO8ivOMzR0m3oJLOLfy5a1dfP9gtOG52mgKaApsDnTIFrBeo+Z7Jq09UUuG4U8IO6Y0XF2NxS9eEKH8KkXFbCW8uIbCnG4Pa5iKSCqbjhBGiJY025zjp5yPdqgUkCe/xOMAEt/jYljFOAnbTZGTgtvyMEWgmwkb+Li4txOBzKIZWamqrAiwA3eUxBtg4OAVB+SCPwR64Rt5bAKf94lNOvs+TwbB9yvoxD5mq1WhUMkjEI6JQ+BFDabLaPaFech3Zamtvw6M2EhYVgMugJCQlR45VrZb4C/2Suoqe0KXO9UocAzqioKAUDZfytra0KeiYnJ6u/RVu/s/JK9XmpdgQIylqJnrJHKioq1Nx79uypxiVzl3XqzCFtybX+tgTQyv6RtiwWiwLIomNX1/ySv1k1UHexNFcD1Nktp1nx5gvo0qeRFtjEvqIqRqQNo7pyC4nD7mdYciJ6r5Q3XsahBiPTRt9IZKAv75WnqYRlu9+nvqmG/sMfYEyv5HNJbTuzqbRzrh8FLl1MQt50HTTWnSYnP5uSqlK80aOYM3oS0cFnExzXF/DB5jdwxg0gNsh4DoKJ5ztv14+Iznqb+SPTPxbUif23+ORGtuRVMnXKLaRGnHe+eW0lbFi3loiMOQxLDmL35n9QaZjKDRPHEOGoYsu2dZCQSvWZE7SRyJSxUzC2HCW/rhGvTo+j+TR7ThSQPmAyiRFm5TgLjUwns/cApGKTw9FKadlRCqpKaGxsJihyAGOHTaJbuM+h5vU4sTttNNUXc7TgKI0N5ZTZIrlx0iJ6xUeo6O/Gsu0crazBeRYvfmj1vV6CQ3qS0TuDUKOb+jPH2X14B66EsdyQOfwjAXhHoE6NScE4A25ltfdVofMfmqPu+nntaSPVFNAU0BT4PCiggbrPwyprc9QUuLQCTmsrZ07spGLva7jFOXcVDr3Hhclp8fmy/NWhvV4FOSTsUkDUeQdX5wYgMKWpqUk5zPxOJbm5LwBKcoXJ310BJHKtADU/NFKhrhK+azKp8FCBbuccdR0MUcYj4EdAj1yn0uK43eeAmMChrs7R97vCq4CctO2fqzwubi3/uJQjsQuHCk11OM6N19+PtCPQ6ePm2oWu1Kmihx+CCWz0H6KHwEJx1nV1Dl0dg/98/9wFoskfWScZnx/8yr75qHVu36+/LYHNsu7+tmQ/y7wETHa2rc7MR3PUdaDS1QB1Xq8bh92hYpKlNLLDJclSjcqRozeaMep9xQHEJeRSsfOmczklpBqNRci5xP3L9WIVvXwncmf2hXbOp6SAD9Qtxqg3MaXvfRgkTl294zmoOrmWV/dsp3vaLDL7DiClWzyBxvMh0C57C4WF2dTaPBflI/F4rSR1H0P36HA+rqiU017Lng07iMjIIiM18YJKYR6KTmwkr0ZHz7AaVpVGcue0qcSHmtG1VbLs7R+xvSGOudPuZHi/AUQYnFSWn6C0yeLz9nndOCUXhUGlNlZ7PiAsmUFpaeQefosPsrOJThjNgJQEYuPTSYmNxOwvboEXa20u67Y+R15DJAMGz6R3t1S6J8QTEnA+315T+QHya1txqywCFx5eAoIS6JXWA/uZLby7PZd+w6YyNH0AYebzTriOlv9SoE7m4L/ZduEXBAXq9AYy+gzjxoHfoG/88E9pZ2ndagpoCmgKaApoCoAG6rRdoCnw+VZAQF3F8R3U7XgWj5QNvirH2R+qF4QNfpKu5Du23932oZBS+YXR7rnO9tFRe3LtpRx0F7b7Sa/vyjjbj+ty5trR2Lsy186O9VLnXbhen7S9T3L9Jx3LpfbhlViXi9ZJc9RdvNRXA9R9kg2lXfv5UUBA3ZZTr+F0W5me/kXMxrPVU/HitLVgcekJDgqVQkpX7RAw7HC4VaitVDK68PC4XTjPli33GIIIMp0FYlLG3NqqSqgHBwZ9LBC8sF2bpRmL00NQcChBkjW0g8PjstPW1orHGEio3AG5bBUkUWkbNreeELnj1Yl2tuUs55kNXyLYlNzprA3KWm8yk9F7GPMGfoNecUM70ZN2iqaApoCmgKaApsDVUUADdVdHV61VTYHrRQEF6k7spG7Hc1cR1F0vanx4nJeCdF1x6l2fM+/cqDV9OqfTlTpLc9R1oKQG6q7U9tLa6aoCUiL8ZPU+9pW8x5CkGXSP7K+qEmnHp6/AgdMbeH33jwg0xnQuua4XDHqDKqk+MGU8s/t/mcjghE9/ItoINAU0BTQFNAU+twpooO5zu/TaxDUFlAIaqLt4I/gBlL/ARPszBNL5Czh8nreQaOSvRqvpc212ggbqNFB3bXaa1kunFJA3QKuzhaNnNpNTtR2Xp00Cojvt4OpUJ9pJXVZAfIUWh4UmS60qFvHxdZAkJwcEGIPpHpnBmJ43kRY9EL3u8j2AXR60doGmgKaApoCmgKbABQpooE7bEpoCn28FOgJ1F4aUXg8K+cGRPw+cQDY5LjcvnBQFkGIXkkev/SH54srLy1Vhh/Zhk/7+zxeo81UIvZT77sLxXkrja7EWXe1DzvcXg5Dce+0PydUnBRra2trOae8Hen49LtSkvTOvq27FC3W/VnvVn4ewq+P9JOPTQJ0G6j7J/tGuvQoKqDc3r4sGSxU2l6XTuRKuwlC0Jtsp4Csh3rXkkAadkfDAaILN4V1KcKsJrymgKaApoCmgKXA1FNBA3dVQVWtTU+D6UaAjUCeVQAVwCay6Xg4BJ1I9VgohCDyRKqLytxQJ6OohRSCkcqcUVhDg1B4kCZiSx/Lz81WRB39f/kIP0p9Un5XxCOS7FMgRoCU6S8GBj4J5UvRB1kLy1V+NQ+bmX+/OaiX69OnTRxUCkYIe7fWRQgrS3rFjx84VUpDzBW5KwYjo6Gi1Ju3nrIwpVqt6vKvFF6Rt6U+uvVYFKdrvtcsBwZe7jhqo00Dd5e4d7TpNAU0BTQFNAU0BTQFNAU2B60iBwvJafvrfzVhDe2AO/LAz4jqahjZUTQFNgctUwGFtoerETmp3/Bu7xa4qsGZlZSEgaceOHecqsvoBioARASICKwRUCcwT0CKP+0NC5XH5vzwnj8n/5Xy5Tv4vz8kfgU8CbPzAS/qQx6VvP8jxwyN5zA9i/Of4gY+AmpiYGObNm8eyZcsUuLnhhhtUBdddu3adA2YC76QN6Ufa87uiLpROxpORkaHmVVVVdW4scr6AQAF4OTk5Ci7JWLp3785tt92m/i3X7N27V1WeXbly5TlHnjwn0M0Psvr378/IkSN55513LtLSD+dEv2HDhmGxWNi/f/85kCXjlzGKlvLHDyX9MO/CsFT/GqjilHr9OX1FC2l79uzZygV3/Pjxc3D2o/SRuQwePFjpWFhYeA6uSb+ij1Q8PXjw4LmxpaamsmDBAjX3jRs3cuLECbUO0o6sswDWO+64g02bNqlKtP595N8vort/v8haydylLzlPKsbOnDlTXSuVV+U5GZe0K3OQf8sfOVd09e9Xga3+Srz+9v170z82lVvcbFbrI3tKzpdxyNrOmjVLrZ3sAf++lb7luFouOw3UaaDuMt/mtcs0BTQFNAU0BTQFNAU0BTQFricFyqsb+cWrW6ghlqCwqOtp6NpYNQU0Ba6AAraWehylhzCUbMXjdDB+/HgFJAS0bNiwQTm+xo4dS+/evTl16pSCEgKqGhoaqK+vp2/fvpw5c0Y9LgBDrj19+jS7d+/mxhtvJCoqSsEucVgJmJL2BArl5uYyevRoBVz27dunHGzJyclUVlaydetWBVwGDBigQJXAEAFC0pfAObk+Ly+PMWPGKPgj/xdwNnfuXLKzs5XTS+CVtCUgKjMzU4EaOUecYHKsX7+e5ubmDkNj/X0LcBHY5wcvAmxCQkLUPGX8flCXkpKiwI30J3OQuQqsEg1mzJihYI+cL7BNgJVoJX2LjvK4uMzEcZaenq702LlzpxqnzFdceXv27FGPSZsTJkxQjj2BaklJScTHx3Po0CGll8xTrpc5iyayLvK4aCvti5bSnjwu0E6ulf6lTQFXZWVlar0ElsnYW1tbO4ROAqsGDRqkYFtpaemHQJ2sr8zHD+pEM1kzmc/AgQPVusn6SM7ugoICRDt5XkDryy+/fA7Uyf9FO1k3aePw4cOkpaWp84qKihSE69evn1pn2Sd+h+O6deuUjvL85s2bGTFihNpnMn+ZY69evZQ+8py07w/dlT0nYzl58qSCkNKH6CzAViCd6C37V2CgtCNwU0C2jF3mLGsrY9BA3RV4U+pKE1oxia6opZ2rKaApoCmgKaApoCmgKaApcD0oUN3Qym9e30JBcwBhsVLF3Hs9DFsbo6aApsAVUqC1roJ4VzkjE9zocbNixQoFVASuCfQQoLJo0SIFLgSaCNQRB5RAJgFTAijWrFnD448/rsCLhEJOnz5duaYEYsjzd999N0eOHFFg6K233lLuKYF8Al5+//vfM3nyZCZNmqRmJJDn2Wefpbq6mjvvvFMBOgFV4pCT9pYvX66uF8Ai4xBXkwBBAU7irJJxS58CaASoCBQSOOUP0xTA+Pzzzyt3ld95daGUXQV14qi79dZbkfBXaVe0EugjcykpKVG6COyU8cocRGMBRvPnz1dwTMY+ZcqUc24/eUwg0fbt2xXgEhi2bds25dyTa+RxAafifBQwJ8BMIKQAUoGCQ4YMUWBKHhOoJusph8A1AVsClgRACqwS2HTPPfcoQCVrK1DqhRdeUJpdSp+ugDo5V1x2U6dOVe43cRtOmzZNzVmAoOi0ZcsWbr/9dgXqBOQJGJW5ybq++OKL6jmZi8xN9omANllH2WvimBT4KaBNnpPzJLeggD0BptKvaC3/l/0kfQrsE03lWLt2rYJuoqkAPtlrEydOVNBNrpWxyF6X/Sjw85VXXlGAVMZ29OhRxo0bx/vvv69gs8zzqoK63y5I1T6hL3i1GtBRY4BdZidOlZbKl5dK6O7pllpW/3YrIwaNuUJvl1ozmgKaApoCmgKaApoCmgKaApoCV18Bj8fLv9/bzVt7S4nvOfCqhexc/ZloPWgKaAp0XQEddYXHcBTvItxSzLSpU/jhD3+oQkgF/kg4oTisxKkm7jqBXwKIDhw4oCCdQJ2FCxcq15b8EReWOMUEiIgbS6CMQIynnnpKgSEBWa+++ipPPvmkAiwCNubMmaOuEXeawDw5T9oW95gAQnG+iUtOYJKc9/bbb/PQQw8pgCXnv/TSS+o8AX8C8IqLi3nmmWcU3JExSR9yvUA7AS0CsQSuvPHGG+rcjvKaXQjq/LoKFBNAKGNr76iT0E6BYdLmL37xC+W6Em0ErEn4q/QjYEcAkkDEJUuWKBj0zW9+U7nhBFTJHAT8CKgSx560J0BRAJ+MR/QSt57AKAGjAvZkbrIWwiT8j4uTTNZLoKA8J2BQXGH+MGQBqKKDwCdxAQqQEm0ELspzjzzyiDpXQohF047COC8Edf48baKPQEABYeKo8xePEDgooEuAmKybjFscgqK9PCcQ8hvf+IYal7gCZQ5yvYC9119/Xe0ngWiypwR8itNQgJu43AQwylrLeMU5J3tUIKWshUBTcYj6q/fKGsh+FJg7atQoNT45T9qX9RSHnugs2oouslcE9sn5si+lLRm/jEmAqQDN4cOHq9eLzEdg4VUFdVtefUYDdRe8y+l1Ogpqinn1wDu0OJrPVWrUQF3XPw60Ky5PAZXo09WG2+PUiklcnoSfgat06HV6AoxBGA3XT3Lez4Bw2hA0BTQFPmUF7C4LTrdd+/z5lNfhk3SvO/v5YzJcnFh9x9FCHvvP77FnmAAAIABJREFUZvr2HIg5OPSTdKNdqymgKXAdKeC0W2gqOUZ3RwGlJ/YwZYrPQSThnf7QV3HUCWARCCcAR1xGAnAElIizSeCGPO7PYSfgRUCLgAsJLZR/y/MCpKQtgVRf+cpXlKNJoI4/bNHveBNYI+4ngT8CQMSVJk4xgTrivhJgIuGuAv0EGsrfAqMECoozT/4vME36FOAnh4A1+beAPnH1icNKHFQyx46KNAgYEzAk7cg8/cUS/DnY/KGsAoL8OeoEAkkfAsAEFMm5Apb84ZkybpmHuP4EiglIE0ehjMmfR03mJWGpoo2AN9FO1kLgkTi9BPSJ602AkPQjEE/WQmCSwCt5THTzr5/MQeYnffjBk4xRQKLMQUI8xb0nEE30l7akDQFk4voTLTsqliBzlhx74vrza+zf9tK3rId/DeV6cfJJ+K206w8/FmApGgjwkn4EQi5duvRc/jnZG/Kc6CH7RsYpayfXCDyWscqcZB0F3EobAu5kb4lLUOCn7EUJj5a5CrS877771PXSpszZH64s6/Dee++dg3eyX1avXq1gqew7maPATHHSyR9x/klOQllnWSPRUdZA+ryqoC6/fJ8G6i54g9Xp9eSeyuEfLz1NQ0sler1RnaGBuuvok+g6HqrH46a6tZiDZWupbSvxJT69jufzeR56kCmMnjGZDEycoCq/aoemgKaApsBnWQEvXqpbisku30R1y2l1s0g7Pn0FTMZAzMagLg1EAF1CSC8GJU0iNCDyQ9e2WOzc/OulBAREEpmQqm4qaYemgKbA/7YCXo+HpupiWkuOEVazn9rKMgWXxAUmgENcRAKpBFSIQ0rCDOVxcY8JcBEHnAAtATMCMgTmyfmSx04giIApcR8JzBEXlFwrIEralT78AE3aEXAiEEbaFZAiUEYgmPxfzpXfPtKHQDt/fwJqBNyJO0sgjfxfnGgCpQRoSbvSlrQjQE/gkoBFuV7GIjCsfdGK9qvtB3L+/Gntn5OxyHwk9NJ/CJgS2CN/CwQTrSR0VP4tfQsokv5kjALuRAfRSvqXcQoYkucEAgkoFZDnL8ogzjyBlwL9pB2BVNK3XCvwS4CWzF/mJvMWvSUXnTgPRQ9pT8bjDzWWvkUXWVdpT9x+AvNkjeVcGbecK3pfqtiGv6iG7IULK8XKnpD19Of2kzZlXNK+zFXgln+dZW49evRQbcj4/ftEdJXHBUqKy1DGK+0JzPNr7F9PmZusk6yraCPw8t1331VQVPqWvgQW+iGkP3+haOwfl7jiBIbKnOV5Gaf8W7SSPmW/+EOGZSyyx2Vvy/N+yCqP+avnXq13Dt13l07SQN0F6uqNBhqrLRzbWorLqYW+Xq3Np7V7sQLyQVHZXMj7uX8nzNyNHtEZ6HQGLYfMdbpZWm1NHKlYT3r8KKb1va/LP7Su02lrw9YU0BS4DhWQz5/a1jKWH3+KEGMyvWKHYDx7o/I6nM7/zJDFGVdYdYx9hR/g9Xo6PS+DwUhoSDAj025kQq9FhAREnLtW1nr38WKe+PdGUnoMIDD0/HOd7kA7UVNAU+C6UsBuaaauOIf6Qyuwlh1Bd/b93e8e84ct+v9/qcnJ83KuuLcEhgiI87vr5Br/810RR9r7uH47atvfV/s5fFS/l6rO6b/eX73Wf56/0qhALr8+/nG077t9uxfO/3L0kD46o4kANAFtAgclJNRfhbT99V2pSNoZfaTP9odc016frq6jf54CIAW8+XMjtl8D/3z8/coYxHUnjkqBfeLW81cUvrD/9vr78/uJXgJV2+/drujUvs2uXNeV14Sac0ldrgbqLlBNBD+Rd4Q///uXNLRUoNeb1BmfeUed14Pb48Lr0SOwUUJ4teP6UsDlcbKveBUlDSeYnfEwEYGxagLy5dzpcOL2eBHHp7wZGfRn11eeczpwecBoNGGUEtV4fddIuXS5RnfBNX5ZvF5cLic6w/n2vB4XDocLr06P2Wxqt4+8OO12XF7QG4yYLthj0p+6E6M/v/c8HhdOhwuPFzVulS/h3LBlTg7cXh3mQDOGc/vVqx53ub2qH7PJV3Lb9xo8OzZ0Ptu9vzGfSnhcHjVuvUF3zoXo9fjKvks/JnMAxnPGAS8upxOn24PeYMJs1F/xXD3yesyt3MOOojeZm/EY3SPTr68NqY1WU+CSCnhRry2XC71RXlfa5831vllcbgf7SlZTWHeM2QMeJDok8Xqf0v/M+Hfmrubfm7+rvuN19keBfO5HhkXTL20Yswc8TGp0xoecc3aHi78u3c7aE3XEJPXGaNJSNPzPbBhtIpoC7RSQH/puh42mitM0FR2h4fAKvI42+WL+iXQSx5E4lzoKJf1EDWsXd0kB+e0lLkJxnnX286FLHVyjk8UxJ3Pp7H4SKClOQwlXFnddZw+BbKKXwMX2gLmz11/L83TezmDPazmiz0hfh47v4cd/+So1zaUY9L78Hp8M1AnkaKGxtQG7y9WuxpZQ6GDCQqMJMZtwuQRQ6AkMMNDaXEG91YbJaCYiPJkQc7s3VAEsjlYabQ5CgqMwY6OhpoCiM4W0NAWQNGwC/WI6t2kdtmZaHRAWGoZJr1M/vmw2Cx6vAbM5AJNJHF3acS0UcLodbMp/CcFM09IfwHD2bpe1/jTrtxygwQZecygDhoxgeO84jDoPLdVF7NpzgCqLgcSefRk+eABRQUaaK0+ze+9Bamw69HodGVkTGZASR4Dh/A9qR3MFG1ftpdeM6fSNC0XncVJZcJDth05j04cyIDOLwT27YdZ5aKuvZO/WbZTZ9QREJjE6K5O0mOBzstgaSzmeX0+vwQOJCpRwcQ9n8g+x61A+No8ejzGQrAnT6JsQikHnpbroOLv3nqDJbqDPmLEM65lIkNFLS0MFe7ft40yLg5DoJLLGZNI9KgSvy0bpySPsPFyMJyCY/oNGMLhvPGbD2deFx8rJvcdwJaQzoGcEvkc9VJ4+wb5DJ2lwBdBn4HAy+3cjyKjD2VrLnj17OVVtJTyxF+OHDyQ+POCKhxm32Op5bf/PmZZ+H33jh6tRCdR0WFtotjWDPoyI0HAFCrVDU+CqKOD1YLM2UNPc0EF9RyNh4YlEBV+cx+ojx+J1U19xkBWbjjBu3r30jdB+5F+VtbuGjTpcNjbkvax6nJPx8DXsWevq4xTYkbuCF7f9CEmNIQCuM4d8vZc/Q/plMWvAw/RLyDqXc9l/fX5pDX9auovCFgPRCWnqhpp2aApoCvxvKeBxu2iuKaG15DgtJ9bjbKr4RJCus+61z7qK8ru+o3xsn/Vxtx+ffy1kHtcr0vkk++lC192nuXaX65y8aMziWJWbcrjRQN0lVvTAsV385K+PUttcdmVAnddJSfZL/N9LL5IxYhoxQWa8XnDZG8guPMOMud9n0bD+HNryHLvro7nrxpupOLKUjTmH2XRiH3fft4xbBkafhwheD2VH/svPtmRz94KfMMixncXLXiVswC30CHShS53MrP6duxteW7yXFbs2k9BnAmMHjSZc18r+navIr/MQ1n0IM0YMIsT08V/ePG4r5cUHaNB3Iz05FbPxvHvqnMwyabHMNheCxQjxqWBUpXU/zdfWZ6ZvAXUb8xZj1JuY0ve+c6CuoXAfh6u9dIuOwVZbxOpVhcx59HYygttY+8F2gnr3JyVUx6mjx3B1G8pNE/pRU3iK0so2QuPCsDXks/lwBZPnfIGh3cOU3G57E/tXvsXv3yzjq099jal9YmgozOb1dw8xdPpEIh2VbFx/iCG3fZlREbW898p6wiZMoE+Yl9qiHNaXRPLtBycT5GjjdP5Jdr3/CgcDJvCtL86ne6i4UC0cP3wSiyeIiHAjlorj7Dyl46aFs0nwlPCvFzYxcPpEkoMsfLB8Cek3f4vJiVb+/doG0oaOJj3ORPWpvWxpiuXhm2bgKtvDukNnGDJ0GEZLLYePnmLI1HkMSYmgraGSI3u38/IftzLn1z9k/ogEBeqsNcd467099Bg2hoRgBwdWvU/y/C8zvmcAh1a+zdHgwYztHUFFzn4OtvbmkUVZhHVir3dlw7Q5mvjv3p8wre+9pCeMUB+k5Xlrefv9f7Ps5Gk8IZHcPf3/ccv4icSFBWsvha6Iq53bOQU8DsoLd/HB4b245ZXhf7tVP+RDyBh+MxN6JeK2N1JQuAtb6Cj6dwvHaBBHbcdduO0N7Fz5GHe+lcv3v/xt+oUHYzQEYgjpw8g+vQjUiY3WCnuqoF8yCMiTNx7trb5za/YpnCWgbv3JF9HrjMzOeOhjRyA3HNxucUxLGEz7hRUXt9Hn7u7iZ7vHZaOhvgJzeCJhgYEfO4bPywkXgjrJJdgBdVdytNfc7XEzJD1LOfT7JYy6CNS53R725pbyt+V7qbLqiUvqidGs6f552VfaPP/3FXA5bDRXlajfDuaqg+haqz4RpBPF/E4kyc/V1ff4z4riMm7JNyZ50q7XOcjvCYkukkMcYtfrPMTV5q8G+1nZH10dh2gvayHr8MmAqRev3ogzPAlPYJgG6i61EArU/e1RapuuFKhzcHrfP/neSyuYOOMLJIf73AuOtjNs27uDMfN/xd1Zg8nZ+Rd+snovD97/Z+akd6Ot6gT/eO4eEuev5e7MuLMuIZTrrfjAv/j91iPcfdvvyLCt4+/v/JOxty1mSg9JDNy5LeZx2bE6nLTVFbDnwCpONyUx84a5JBgt1DVZcegC6ZmSRqDeQWtbE5JW+lzTOh2S4Dg4UBxSerzORk4dWc/yPbsJShjA+MwZDEhNJtBoAI8br/jEHBZ0h3dCdS60BEH/yTCgN4T4CnZ83g8fqHtR5QVqD+ra6+Ky1fLBi29gnXQrk8yVfJBdw6x504g366jM28/KIxYWLZxChADQs4ezrYb3VnxAzMDpTBrUDZ3HQf7eTew80YyxtYmEOTcxo3cYxzYsZ23bQL6+cAhmTwu7V71NtiuTm4e5+cd/jvPQ9+4kJdhAS9EhfvtSPg//+A66O1rIyz3B0SNbOdLQh688OO8sqPN17n/Dstfk8sb7+5gw5xZCClfztyMpfP+hsYTqoGbbv3ipMos7B8IfVx3hrvvuZ3i8jub87fxqVQkP372Q5iPvc1rfj4VTBqJzW9m/YS3V4QOYMzadttpycg7v4b0l+8h65AkWjOymXislG59lWf0g7ps3nqgANwW73mFrXW8WjgvjrcU7GHPfnQyKN9NSlccrizcz9sEHyIzrorPoYzbth0HdcByVe/j+n2/FmvwN5o0Ygrcpj9fXv0na2B/wo5tmE6A5WD/vbwNXfv4C5D6mVeEpjtY6Th37gJc2raN7v5lMHjGJft2TMMudWrdbgTYJbRdCUF+6nR++vJihQ2fTNzoIW1sN29f+nL94H+XUz58gqfIUWCrh2ZMwZjCM6Q+9Y7SbMld+da9Yi8pRd/JFBdnagzp5D3c7xAFsxYOewMBwFQFgay1n956V5DTUfyh1gbjxk7tPY+qITMLMRhy2VpxeE0GBvrCcj/p60lx9mKVrl5I++n4GJISpG5oGYzChQSEYP8dur/agzvctzIvH48CruzBXkAmDzqh0E60F1A1Nz2LWJUCdf/OcKKzk729v50i1nYSkHgSGSvEJnXbj6Iq9urSGNAWunQLqe7fXi93SREtVCW01xTQdW4OluhB0n+z3lrjQpEiAJOyXCpydDVO8drP/+J5EHwkTleIFUpH0sx7+eKkZyVpIxVY5pPiEwK7r7ZA5SAEM2U+FhYXX2/DPjVdeB1IYRIpqSLqlyz30bhuNPSZQ23MCGAI1UHcpIa8OqPsX3138JmOmfoHEsAD1w8lpOcPug/sZv+DX3DVqGPbWCrbt309wYhYT+sVTXbCZX/7rUVJmvcu3ZvbHH4QqoO7Exl/wn+wy7r/3T/Sy7eCp1/9Az8l/5Uuj+qPXSe4xO64LEj6en68OvSEAV0M+q7ctw5Q4jJF9BmGpPMHxphCmZI0l0F7BqZJG0vr1x9BazI5dqzkj+bzUHXIdXmsjlS0O5s55nIHdYtHjUW655uZayksPcSB3F8MmPk5GfDhlx1azvjKEhZMnErVvNXz3KQhPhrseg9unQoAWXitr8/GgzktbbQGv/nc7QxfdTFLjCbYW2Jk3dxIRJh0NZ07wzsoCpt07n55B512QbdWnWLZuJ/0nLGBEaji1JcdZd6iUEUMzKFy5Ct2sRcxMC2b3iiUci5vKQ5N7osfNqS3L+CAniFvvHkvue6s53OZkwMAB6OrLaAzP4ObJGfju5XipzlvJcyvt3P/lBaSEnQ2D83qxNteSX1BIeVUN9pAUZoxJp2Tjcyx33cB3buyPSQfW0vU8+66T2+/I5MCmNRytDGbk4GRcdTVYonsxY1wfjqxeQWvCSGaN7a1A48ndG9jfFseiGSMJkKm2lfPanxdjmPEgi0YnosfLwdd/x7HwmSycNZwwo4eanO2sOOTkhvGRvLOihHn3zqNXhAlnQzlvv76YkKmPs2BA2OW+v3Z43YdAXVxfti6+n2caRvGTex6lX0IEuC0c2PRn/ronn69/8W+MSg69ov1rjWkK4LZRW7aXE3VNoIrT+A5BJjp55w7px4S+aT6A4nXTUF9J0em95FZVMm7iPaSGBZC9+z0qTUlMGzEOLOWsee835BtG8+CtdxFl1NNSe5R//mkRm1J+xRsP3UJEfQ785dewvgiGTobvfgt6R2uOus/wduwI1Hm9blrrT7Jn7y7K7Y14PDq8YZnMGTeBOLOTxsZ6LE53uxt4vtpH5sBwoiMiMBk8lORs42hpDZGJvenfK4PI4MB2YK+dIF47hzb9jVcP7CWl9ygiTUbcTistjnjmTr2NvglX9r35M7wUFw2tPagTB2NcWHeGpk0lyBxy7maYfDWraT7DwaL1ON025Z7rLKiTDivrmnlt0xHWHy3D6Q0kODyaAAGkRrMKib1e3RrX0zprY9UUuFwFVKi7x4PH7cBps2BrrsdSV4ql8hSW4kO4mv3hrp10clxiIJJHTCqxSoVSSfp/vcIhcT9J1da8vDwV/no9vr/Jmgvkkr+lCuz1CBwF1EkBCQF1Uo32elwHeanI60CgqVSOldx5lzsPvb2B6uH3UWuIhoZqDdRdM1DnEUfdM3zn5XUsXPRl0iJ8oQW2ptOs2bySobN/yd1ZQ8jZ/yKrj28nY+xPmdsnnoNb/8VL65fhTH6Unz10GwmBvh9ZEmb6wZvfY3N1AI899HPi3WU8/dLvIPVOvjt/Mjq3hdxj6zlRWYW7g9ATt85M9x6TGdujG5XFOzlcfJSiej1ZQxcwrHcyBkcdm1d+k8OeO3nwljlE6KzU1lZhP/cLz4CndD1/XvsSd9z7FqPTEmmX+kz92HM4negNZhwNOfz32bs4mPojnrppFjH718Bb70BwIoy/GWaOAT/YudxPqP+R6z4a1HlxWpvY9f4H5OpSuH1OFo0nd7Oj2M28ORMJN+lprMxh2bsnmXTvTfQO9oE6t62eDUuXURk+gHnTszC3nuaDddkkjJjIqDQj655fgmnObcxIDWTHu0vIS5zBFyemKfB6eusy3j9uYuHd4ynYuI0KYyABLnHQnabnpFtYMLYvZvWZ76HyxAqeX+PkgQtAnaWxmtyT+ZQ3N2N1RzN9wmAqtj7LSsMCvjO7j4LP1orNvPBWCwvvHEn2tn20eMwE6+o5eryWQVNnMyMrmf2rVmJJGskNY3ygLn/PJna3RHP7zCwfqGsp45U/LcY86yG+cBbU7fvvrzkZO5ebbxhGqMFD7cmdrNhvZdrYSJavOcNN986lR5gJV+MZ3nrjBQInPs7CgeFXdDedB3X3kR4RwT9+uYDWkf/ka/MmEiquR6+HmrIdfO+FfzP7pt+wKLNzIetXdJBaY//bCrisVJfu4mh1A7RzJbms9ezf/iq58U+w+MEFKguB/5BcWFJoxmA0Y6k6yN9f+Q6mgU/wyJgh7N7wLLme7syacR99o8Pxeuzk7/k7j774Frc+sJiHx/TBWHQCtq2E94uh12C4/xZIT9IcdZ/hndYRqPM4G9m78VUKgsYxP6sfAR4bRdUNRMenEKFvpa6pAeeFdk2pAGcKJTosWjmEJZy1ujKXvPIiWttCGDFqMglhF+QD9TqpLlrPkvVHGDXzAQYlhitXdGtdHhv35zJy/I30ivn83sRoD+rEHxsRHM0dY75HZs/p5wpEtNoaWXHgeTbnvgZeccPpuwTq5MeeFJg4UljF5iNFFJfXUdXipMVtwCaA1lemSrn1rvYh3wuCjXof0NWBKTCE4Kj4Tufnu9rjuxbtS14xp91CU2MtFofrWnR5Rfrw3cpHFfsyfkTou+wlp8dLkNHwuSpG5He7feiHfBdTBFy4UFK91eNyIFFSTlsbztZGbNX52CpycTRVSyWJs5+9/sJsTtpa2nDrzYSHBCrXs9WhIzQ0BNPH5Ev+rIE6j8uJy+VWBpXmNivmoBCCAyX10qWBpMChzwqo8xc2kMIcEoorkEccWVIc4eMg6GcD1PkKi1nbWml1GogOD8RhbcPuMREWFvyxr+1PG9TJ2O0OJ3qjGYPHTqvFhjEwlECDl7bWVnTmYEKCAz62QOeVA3X1VI34InWE09Ok00DdtQN1dgr2/oWvPb+W